--- a/euro-cordex-esgf.xlsx
+++ b/euro-cordex-esgf.xlsx
@@ -21013,7 +21013,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>['ua850', 'rsut', 'snw', 'va500', 'wsgsmax', 'rlds', 'rlus', 'prc', 'ta850', 'huss', 'vas', 'rsus', 'rlut', 'ta500', 'mrro', 'va850', 'clt', 'rsdt', 'mrso', 'rsds', 'psl', 'uas', 'prsn', 'hfss', 'hfls', 'zg500', 'sfcWindmax', 'hus850', 'ta200', 'ua500', 'evspsbl', 'ps', 'ts', 'sfcWind', 'pr', 'tasmax', 'tasmin', 'tas']</t>
+          <t>['ua850', 'rsut', 'snw', 'va500', 'wsgsmax', 'rlds', 'rlus', 'prc', 'ta850', 'huss', 'vas', 'rsus', 'rlut', 'ta500', 'mrro', 'va850', 'clt', 'rsdt', 'mrso', 'rsds', 'psl', 'uas', 'prsn', 'hfss', 'hfls', 'zg500', 'sfcWindmax', 'hus850', 'ta200', 'ua500', 'evspsbl', 'ps', 'ts', 'tasmax', 'tasmin', 'tas', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>['ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'tasmin', 'sfcWind', 'pr', 'tasmax', 'tas']</t>
+          <t>['ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'pr', 'tasmax', 'tas', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>['mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'tasmax', 'tasmin', 'tas', 'sfcWind', 'pr']</t>
+          <t>['mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22441,7 +22441,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>['rlut', 'mrro', 'va500', 'hfss', 'snw', 'ts', 'rlus', 'va850', 'ua850', 'prsn', 'hfls', 'rsut', 'huss', 'vas', 'rsdt', 'ps', 'ta500', 'clt', 'prc', 'ta850', 'rsds', 'ua500', 'hus850', 'sfcWindmax', 'ta200', 'psl', 'mrso', 'evspsbl', 'rsus', 'wsgsmax', 'zg500', 'rlds', 'uas', 'sfcWind', 'pr', 'tas', 'tasmin', 'tasmax']</t>
+          <t>['rlut', 'mrro', 'va500', 'hfss', 'snw', 'ts', 'rlus', 'va850', 'ua850', 'prsn', 'hfls', 'rsut', 'huss', 'vas', 'rsdt', 'ps', 'ta500', 'clt', 'prc', 'ta850', 'rsds', 'ua500', 'hus850', 'sfcWindmax', 'ta200', 'psl', 'mrso', 'evspsbl', 'rsus', 'wsgsmax', 'zg500', 'rlds', 'uas', 'tas', 'sfcWind', 'pr', 'tasmin', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -29221,7 +29221,7 @@
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>['pr', 'sfcWind', 'psl', 'mrso', 'rsds', 'rsus', 'rlus', 'sund', 'prhmax', 'rlds', 'hfls', 'tasmax', 'evspsbl', 'wsgsmax', 'hurs', 'rlut', 'snc', 'ps', 'ts', 'vas', 'tasmin', 'uas', 'clt', 'prc', 'mrro', 'rsut', 'sfcWindmax', 'rsdt', 'tas', 'snd', 'hfss', 'huss', 'prsn', 'snw']</t>
+          <t>['sfcWind', 'psl', 'mrso', 'rsds', 'rsus', 'rlus', 'sund', 'prhmax', 'rlds', 'hfls', 'tasmax', 'evspsbl', 'wsgsmax', 'hurs', 'rlut', 'snc', 'ps', 'ts', 'vas', 'pr', 'tasmin', 'uas', 'clt', 'prc', 'mrro', 'rsut', 'sfcWindmax', 'rsdt', 'tas', 'snd', 'hfss', 'huss', 'prsn', 'snw']</t>
         </is>
       </c>
     </row>

--- a/euro-cordex-esgf.xlsx
+++ b/euro-cordex-esgf.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>['clwvi', 'clivi', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'zmla', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'va850', 'tasmin', 'psl', 'huss', 'ps', 'sfcWind', 'tas', 'pr', 'clt', 'rlds', 'rsus', 'rsds', 'zg500', 'ua850', 'tasmax']</t>
+          <t>['clwvi', 'clivi', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'zmla', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'va850', 'tasmin', 'psl', 'huss', 'ps', 'sfcWind', 'tas', 'pr', 'clt', 'rlds', 'rsus', 'rsds', 'zg500', 'ua850', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>['uas', 'va200', 'ua200', 'ua500', 'ta850', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua850', 'psl', 'clt', 'sfcWind', 'huss', 'rsus', 'rsds', 'tasmax', 'zg500', 'tas', 'va850', 'tasmin', 'rlds', 'pr']</t>
+          <t>['uas', 'va200', 'ua200', 'ua500', 'ta850', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua850', 'psl', 'clt', 'sfcWind', 'huss', 'rsus', 'rsds', 'tasmax', 'zg500', 'tas', 'va850', 'tasmin', 'rlds', 'pr']</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'zg500', 'psl', 'tas', 'tasmin', 'rsds', 'rsus', 'tasmax', 'rlds', 'huss']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'zg500', 'psl', 'tas', 'tasmin', 'rsds', 'rsus', 'tasmax', 'rlds', 'huss']</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'rlds', 'tas', 'clt', 'huss', 'tasmax', 'psl', 'va850']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'rlds', 'tas', 'clt', 'huss', 'tasmax', 'psl', 'va850']</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'pr', 'rsds', 'tasmin', 'rlds', 'rsus', 'va850', 'tasmax']</t>
+          <t>['rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'pr', 'rsds', 'tasmin', 'rlds', 'rsus', 'va850', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'sfcWindmax', 'sfcWind']</t>
+          <t>['sfcWindmax', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'uas', 'va200', 'va500', 'ua500', 'ts', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'pr', 'tasmin', 'ua850', 'ps', 'clt', 'zg500', 'rsus', 'tasmax', 'rlds', 'tas', 'huss', 'va850', 'psl', 'rsds', 'sfcWind']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'uas', 'va200', 'va500', 'ua500', 'ts', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'pr', 'tasmin', 'ua850', 'ps', 'clt', 'zg500', 'rsus', 'tasmax', 'rlds', 'tas', 'huss', 'va850', 'psl', 'rsds', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>['hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'psl', 'sfcWind', 'zg500', 'clt', 'tas', 'huss', 'rsds', 'rsus', 'rlds']</t>
+          <t>['hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'psl', 'sfcWind', 'zg500', 'clt', 'tas', 'huss', 'rsds', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>['rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'snw', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'huss', 'tas', 'sfcWind', 'rsus', 'tasmin', 'rsds', 'ua850', 'zg500', 'va850', 'clt', 'pr', 'tasmax', 'psl', 'rlds']</t>
+          <t>['rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'snw', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'huss', 'tas', 'sfcWind', 'rsus', 'tasmin', 'rsds', 'ua850', 'zg500', 'va850', 'clt', 'pr', 'tasmax', 'psl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'ua200', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'ps', 'ua850', 'clt', 'huss', 'rlds', 'pr', 'zg500', 'rsus', 'sfcWind']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'ua200', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'ps', 'ua850', 'clt', 'huss', 'rlds', 'pr', 'zg500', 'rsus', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'va850', 'psl', 'rsus', 'tasmin', 'sfcWind', 'rsds', 'huss', 'tasmax', 'ua850', 'clt', 'pr', 'zg500', 'tas', 'rlds']</t>
+          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'va850', 'psl', 'rsus', 'tasmin', 'sfcWind', 'rsds', 'huss', 'tasmax', 'ua850', 'clt', 'pr', 'zg500', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'zg500', 'tasmax', 'ua850', 'va850', 'clt', 'huss', 'rlds', 'rsds', 'rsus', 'tasmin', 'pr', 'sfcWind', 'psl', 'tas']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'zg500', 'tasmax', 'ua850', 'va850', 'clt', 'huss', 'rlds', 'rsds', 'rsus', 'tasmin', 'pr', 'sfcWind', 'psl', 'tas']</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>['hfss', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'prhmax', 'rlus', 'rsdt', 'rlut', 'prw', 'ua500', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'clt', 'zg500', 'tas', 'va850', 'psl', 'tasmax', 'tasmin', 'ua850', 'huss', 'rsds', 'ps', 'sfcWind', 'rlds', 'pr', 'rsus']</t>
+          <t>['hfss', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'prhmax', 'rlus', 'rsdt', 'rlut', 'prw', 'ua500', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'clwvi', 'hfls', 'clivi', 'clt', 'zg500', 'tas', 'va850', 'psl', 'tasmax', 'tasmin', 'ua850', 'huss', 'rsds', 'ps', 'sfcWind', 'rlds', 'pr', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'va850', 'rsds', 'tas', 'sfcWind', 'psl', 'zg500', 'huss', 'pr', 'rlds', 'rsus', 'tasmin', 'tasmax', 'clt']</t>
+          <t>['sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'va850', 'rsds', 'tas', 'sfcWind', 'psl', 'zg500', 'huss', 'pr', 'rlds', 'rsus', 'tasmin', 'tasmax', 'clt']</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'psl', 'zg500', 'sfcWind', 'rsus', 'rsds', 'tasmin']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'psl', 'zg500', 'sfcWind', 'rsus', 'rsds', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>['clwvi', 'clivi', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'rsus', 'rlds', 'va850', 'ps', 'tasmax', 'sfcWind', 'clt', 'pr', 'psl', 'ua850', 'zg500', 'tas', 'huss', 'tasmin', 'rsds']</t>
+          <t>['clwvi', 'clivi', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'rsus', 'rlds', 'va850', 'ps', 'tasmax', 'sfcWind', 'clt', 'pr', 'psl', 'ua850', 'zg500', 'tas', 'huss', 'tasmin', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'zg500', 'rsds', 'rsus', 'ua850', 'tasmin', 'rlds', 'va850']</t>
+          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'zg500', 'rsds', 'rsus', 'ua850', 'tasmin', 'rlds', 'va850']</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>['vas', 'zg200', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ta500', 'ta850', 'ua200', 'ua500', 'va850', 'psl', 'rlds', 'rsds', 'rsus', 'pr', 'ua850', 'tasmin', 'tasmax', 'huss', 'clt', 'tas', 'sfcWind', 'zg500']</t>
+          <t>['vas', 'zg200', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ta500', 'ta850', 'ua200', 'ua500', 'va850', 'psl', 'rlds', 'rsds', 'rsus', 'pr', 'ua850', 'tasmin', 'tasmax', 'huss', 'clt', 'tas', 'sfcWind', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>['clivi', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'ua850', 'tas', 'psl', 'va850', 'tasmax', 'pr', 'zg500', 'ps', 'tasmin']</t>
+          <t>['clivi', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'ua850', 'tas', 'psl', 'va850', 'tasmax', 'pr', 'zg500', 'ps', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'tasmax', 'sfcWind']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'tasmax', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'rsus', 'psl', 'tasmax', 'huss']</t>
+          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'rsus', 'psl', 'tasmax', 'huss']</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'va200', 'ua500', 'ua200', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'tasmax', 'rlds', 'ps', 'zg500', 'rsds', 'evspsbl', 'huss', 'pr', 'va850', 'tasmin', 'sfcWind']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'va200', 'ua500', 'ua200', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'tasmax', 'rlds', 'ps', 'zg500', 'rsds', 'evspsbl', 'huss', 'pr', 'va850', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'va850', 'clt', 'zg500', 'rlds', 'rsds', 'pr', 'ua850', 'huss', 'rsus', 'evspsbl', 'psl']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'va850', 'clt', 'zg500', 'rlds', 'rsds', 'pr', 'ua850', 'huss', 'rsus', 'evspsbl', 'psl']</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>['hfss', 'clwvi', 'hfls', 'clivi', 'prhmax', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'prw', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ta500', 'ta850', 'ua200', 'ua500', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'prhmax', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'prw', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ta500', 'ta850', 'ua200', 'ua500', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'rsus', 'tas', 'va850', 'tasmin', 'huss', 'evspsbl', 'clt', 'psl', 'rlds', 'ua850', 'zg500', 'pr', 'tasmax', 'sfcWind', 'ps']</t>
+          <t>['hfss', 'clwvi', 'hfls', 'clivi', 'prhmax', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'prw', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ta500', 'ta850', 'ua200', 'ua500', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'rsus', 'tas', 'va850', 'tasmin', 'huss', 'evspsbl', 'clt', 'psl', 'rlds', 'ua850', 'zg500', 'pr', 'tasmax', 'sfcWind', 'ps']</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'va850', 'clt', 'evspsbl', 'rlds', 'rsus', 'tasmin', 'ua850', 'pr']</t>
+          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'va850', 'clt', 'evspsbl', 'rlds', 'rsus', 'tasmin', 'ua850', 'pr']</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ts', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rsus', 'rsds', 'evspsbl', 'ps', 'huss', 'ua850', 'pr', 'tas', 'tasmin', 'zg500']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ts', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'zmla', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rsus', 'rsds', 'evspsbl', 'ps', 'huss', 'ua850', 'pr', 'tas', 'tasmin', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'sfcWind', 'ua850', 'zg500', 'pr', 'tasmin', 'va850', 'clt', 'rlds', 'psl', 'evspsbl', 'huss', 'tasmax', 'rsus', 'tas']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'sfcWind', 'ua850', 'zg500', 'pr', 'tasmin', 'va850', 'clt', 'rlds', 'psl', 'evspsbl', 'huss', 'tasmax', 'rsus', 'tas']</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>['prhmax', 'rlus', 'mrso', 'prc', 'prw', 'wsgsmax', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'tas', 'pr', 'clt', 'ps', 'huss', 'rsds', 'rsus', 'zg500']</t>
+          <t>['prhmax', 'rlus', 'mrso', 'prc', 'prw', 'wsgsmax', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'tas', 'pr', 'clt', 'ps', 'huss', 'rsds', 'rsus', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'clt', 'tasmax', 'rlds', 'huss', 'tasmin', 'zg500', 'ua850', 'rsus']</t>
+          <t>['hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'clt', 'tasmax', 'rlds', 'huss', 'tasmin', 'zg500', 'ua850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'ua850', 'tasmin', 'rsus', 'sfcWind', 'rlds', 'pr', 'tas']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'ua850', 'tasmin', 'rsus', 'sfcWind', 'rlds', 'pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'zg500', 'sfcWind', 'rlds', 'pr', 'tasmax', 'va850', 'psl', 'tas', 'rsds', 'clt', 'ua850', 'tasmin', 'rsus', 'huss']</t>
+          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'zg500', 'sfcWind', 'rlds', 'pr', 'tasmax', 'va850', 'psl', 'tas', 'rsds', 'clt', 'ua850', 'tasmin', 'rsus', 'huss']</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'psl', 'rsds', 'tasmax', 'sfcWind', 'zg500', 'rlds', 'pr', 'huss', 'tas', 'tasmin', 'clt', 'ua850', 'va850', 'rsus']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'psl', 'rsds', 'tasmax', 'sfcWind', 'zg500', 'rlds', 'pr', 'huss', 'tas', 'tasmin', 'clt', 'ua850', 'va850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'tas', 'rlds', 'tasmin', 'tasmax', 'clt', 'va850', 'rsds', 'rsus', 'psl', 'ps', 'ua850', 'huss', 'sfcWind', 'pr', 'zg500']</t>
+          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'tas', 'rlds', 'tasmin', 'tasmax', 'clt', 'va850', 'rsds', 'rsus', 'psl', 'ps', 'ua850', 'huss', 'sfcWind', 'pr', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>['ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va850', 'va925', 'mrfso', 'mrros', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'zg700', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'hus300']</t>
+          <t>['ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va850', 'va925', 'mrfso', 'mrros', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'zg700', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'hus300', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va850', 'va925', 'mrfso', 'mrros', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'zg700', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'hus300']</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'clh', 'cll', 'clm', 'clivi', 'clt', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
+          <t>['snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'clh', 'cll', 'clm', 'clivi', 'clt', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'clh', 'cll', 'clm', 'clivi', 'clt', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>['tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'huss', 'hus200', 'hus300', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hus400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd']</t>
+          <t>['tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'huss', 'hus200', 'hus300', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hus400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'huss', 'hus200', 'hus300', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hus400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd']</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>['mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg850', 'zg925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl']</t>
+          <t>['mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg850', 'zg925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg850', 'zg925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl']</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -16257,7 +16257,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>['hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus']</t>
+          <t>['hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>['clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200']</t>
+          <t>['clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200']</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf']</t>
+          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>['snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund']</t>
+          <t>['snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund']</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>['rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr']</t>
+          <t>['rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr']</t>
         </is>
       </c>
     </row>
@@ -18525,7 +18525,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>['rsus', 'psl', 'pr', 'rlus', 'huss', 'rsds', 'hfss', 'sfcWind', 'hurs', 'tas', 'rlds', 'ps', 'hfls']</t>
+          <t>['rsus', 'psl', 'pr', 'rlus', 'huss', 'rsds', 'hfss', 'sfcWind', 'hurs', 'tas', 'rlds', 'ps', 'hfls', 'rsus', 'psl', 'pr', 'rlus', 'huss', 'rsds', 'hfss', 'sfcWind', 'hurs', 'tas', 'rlds', 'ps', 'hfls']</t>
         </is>
       </c>
     </row>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>['evspsbl', 'sfcWindmax', 'clt', 'rlus', 'hfss', 'ta850', 'rlds', 'snw', 'ts', 'hfls', 'zg500', 'snm', 'psl', 'ua850', 'huss', 'uas', 'ta200', 'mrso', 'sic', 'rsds', 'prsn', 'clh', 'vas', 'tas', 'clwvi', 'snd', 'rsus', 'rlut', 'va200', 'tauv', 'ua500', 'rsut', 'prw', 'hurs', 'tauu', 'clivi', 'cll', 'tasmin', 'prc', 'ua200', 'clm', 'mrro', 'zg200', 'mrros', 'va850', 'hus850', 'tasmax', 'prhmax', 'ps', 'ta500', 'sund', 'rsdt', 'snc', 'pr', 'sfcWind', 'va500']</t>
+          <t>['evspsbl', 'sfcWindmax', 'clt', 'rlus', 'hfss', 'ta850', 'rlds', 'snw', 'ts', 'hfls', 'zg500', 'snm', 'psl', 'ua850', 'huss', 'uas', 'ta200', 'mrso', 'sic', 'rsds', 'prsn', 'clh', 'vas', 'tas', 'clwvi', 'snd', 'rsus', 'rlut', 'va200', 'tauv', 'ua500', 'rsut', 'prw', 'hurs', 'tauu', 'clivi', 'cll', 'tasmin', 'prc', 'ua200', 'clm', 'mrro', 'zg200', 'mrros', 'va850', 'hus850', 'tasmax', 'prhmax', 'ps', 'ta500', 'sund', 'rsdt', 'snc', 'pr', 'sfcWind', 'va500', 'evspsbl', 'sfcWindmax', 'clt', 'rlus', 'hfss', 'ta850', 'rlds', 'snw', 'ts', 'hfls', 'zg500', 'snm', 'psl', 'ua850', 'huss', 'uas', 'ta200', 'mrso', 'sic', 'rsds', 'prsn', 'clh', 'vas', 'tas', 'clwvi', 'snd', 'rsus', 'rlut', 'va200', 'tauv', 'ua500', 'rsut', 'prw', 'hurs', 'tauu', 'clivi', 'cll', 'tasmin', 'prc', 'ua200', 'clm', 'mrro', 'zg200', 'mrros', 'va850', 'hus850', 'tasmax', 'prhmax', 'ps', 'ta500', 'sund', 'rsdt', 'snc', 'pr', 'sfcWind', 'va500']</t>
         </is>
       </c>
     </row>
@@ -18621,7 +18621,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog']</t>
+          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -18653,7 +18653,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>['rlds', 'mrso', 'zg200', 'va200', 'va850', 'mrro', 'psl', 'hfss', 'sund', 'ua500', 'rlut', 'rlus', 'tasmin', 'sfcWind', 'huss', 'rsut', 'tasmax', 'mrros', 'ua200', 'hus850', 'hfls', 'rsdt', 'pr', 'clt', 'tas', 'hurs', 'snd', 'ua850', 'sfcWindmax', 'vas', 'uas', 'ta200', 'snw', 'ta500', 'snc', 'rsds', 'sic', 'snm', 'zg500', 'va500', 'ta850', 'rsus', 'evspsbl']</t>
+          <t>['rlds', 'mrso', 'zg200', 'va200', 'va850', 'mrro', 'psl', 'hfss', 'sund', 'ua500', 'rlut', 'rlus', 'tasmin', 'sfcWind', 'huss', 'rsut', 'tasmax', 'mrros', 'ua200', 'hus850', 'hfls', 'rsdt', 'pr', 'clt', 'tas', 'hurs', 'snd', 'ua850', 'sfcWindmax', 'vas', 'uas', 'ta200', 'snw', 'ta500', 'snc', 'rsds', 'sic', 'snm', 'zg500', 'va500', 'ta850', 'rsus', 'evspsbl', 'rlds', 'mrso', 'zg200', 'va200', 'va850', 'mrro', 'psl', 'hfss', 'sund', 'ua500', 'rlut', 'rlus', 'tasmin', 'sfcWind', 'huss', 'rsut', 'tasmax', 'mrros', 'ua200', 'hus850', 'hfls', 'rsdt', 'pr', 'clt', 'tas', 'hurs', 'snd', 'ua850', 'sfcWindmax', 'vas', 'uas', 'ta200', 'snw', 'ta500', 'snc', 'rsds', 'sic', 'snm', 'zg500', 'va500', 'ta850', 'rsus', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>['hfls', 'rsdt', 'mrros', 'snm', 'snc', 'mrro', 'va500', 'rsut', 'sund', 'hurs', 'ta500', 'rsds', 'vas', 'tas', 'sfcWindmax', 'va200', 'rsus', 'rlus', 'pr', 'snd', 'hfss', 'hus850', 'zg200', 'clt', 'tasmin', 'ua850', 'ua500', 'zg500', 'huss', 'snw', 'ta200', 'rlds', 'uas', 'ta850', 'rlut', 'psl', 'va850', 'tasmax', 'ua200', 'mrso', 'sic', 'sfcWind', 'evspsbl']</t>
+          <t>['hfls', 'rsdt', 'mrros', 'snm', 'snc', 'mrro', 'va500', 'rsut', 'sund', 'hurs', 'ta500', 'rsds', 'vas', 'tas', 'sfcWindmax', 'va200', 'rsus', 'rlus', 'pr', 'snd', 'hfss', 'hus850', 'zg200', 'clt', 'tasmin', 'ua850', 'ua500', 'zg500', 'huss', 'snw', 'ta200', 'rlds', 'uas', 'ta850', 'rlut', 'psl', 'va850', 'tasmax', 'ua200', 'mrso', 'sic', 'sfcWind', 'evspsbl', 'hfls', 'rsdt', 'mrros', 'snm', 'snc', 'mrro', 'va500', 'rsut', 'sund', 'hurs', 'ta500', 'rsds', 'vas', 'tas', 'sfcWindmax', 'va200', 'rsus', 'rlus', 'pr', 'snd', 'hfss', 'hus850', 'zg200', 'clt', 'tasmin', 'ua850', 'ua500', 'zg500', 'huss', 'snw', 'ta200', 'rlds', 'uas', 'ta850', 'rlut', 'psl', 'va850', 'tasmax', 'ua200', 'mrso', 'sic', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>['snw', 'snc', 'sund', 'snd', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'pr', 'ps', 'clt', 'rlds', 'psl', 'evspsbl', 'rsds']</t>
+          <t>['snw', 'snc', 'sund', 'snd', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'pr', 'ps', 'clt', 'rlds', 'psl', 'evspsbl', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>['ta850', 'ta200', 'ta500', 'hus850', 'ua500', 'va500', 'hus850', 'ua500', 'va500', 'ua850', 'va850', 'zg500']</t>
+          <t>['ta850', 'ta200', 'ta500', 'hus850', 'ua500', 'va500', 'va500', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>['uas', 'sfcWindmax', 'vas', 'uas', 'sfcWindmax', 'vas', 'huss', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'hurs']</t>
+          <t>['uas', 'sfcWindmax', 'vas', 'sfcWindmax', 'vas', 'huss', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'zg500', 'va850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'ta200', 'ta500', 'ta850', 'ua850', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26609,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'huss', 'tasmax', 'hurs', 'clt', 'rsus', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'vas', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'huss', 'tasmax', 'hurs', 'clt', 'rsus', 'psl']</t>
         </is>
       </c>
     </row>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'zg500', 'va850']</t>
+          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26669,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>['rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'tasmax', 'huss', 'tasmin', 'tas', 'psl', 'sfcWind', 'evspsbl', 'rlds', 'hurs', 'rsds', 'rsus', 'pr', 'clt']</t>
+          <t>['rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'tasmax', 'huss', 'tasmin', 'tas', 'psl', 'sfcWind', 'evspsbl', 'rlds', 'hurs', 'rsds', 'rsus', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'snw', 'sund', 'vas', 'uas', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'psl', 'clt', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rlds', 'huss', 'hurs', 'evspsbl', 'rsds', 'tasmin']</t>
+          <t>['hfss', 'hfls', 'snw', 'sund', 'vas', 'uas', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'psl', 'clt', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rlds', 'huss', 'hurs', 'evspsbl', 'rsds', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -27901,7 +27901,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>['uas', 'ts', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'huss', 'tasmax', 'psl', 'hurs', 'clt', 'pr', 'sfcWind', 'rsds', 'rsus', 'ps', 'evspsbl', 'tasmin', 'tas', 'rlds']</t>
+          <t>['uas', 'ts', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'huss', 'tasmax', 'psl', 'hurs', 'clt', 'pr', 'sfcWind', 'rsds', 'rsus', 'ps', 'evspsbl', 'tasmin', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -27929,7 +27929,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>['va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'ta200', 'ta500', 'ta850', 'hus850', 'ua850', 'va850', 'zg500']</t>
+          <t>['va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'hus850', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'clt', 'tasmin', 'rsus', 'pr', 'huss', 'tasmax', 'tas', 'psl', 'rlds', 'hurs', 'rsds', 'sfcWind', 'evspsbl']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'clt', 'tasmin', 'rsus', 'pr', 'huss', 'tasmax', 'tas', 'psl', 'rlds', 'hurs', 'rsds', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'va850', 'ua850', 'zg500']</t>
+          <t>['ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'hus850', 'va500', 'ua500', 'va850', 'ua850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -28053,7 +28053,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rsds', 'clt', 'evspsbl', 'tasmin']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rsds', 'clt', 'evspsbl', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>['mrso', 'prc', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'ts', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'clt', 'sfcWind', 'zg500', 'evspsbl', 'tas', 'pr', 'rsus', 'rlds']</t>
+          <t>['mrso', 'prc', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'ts', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'clt', 'sfcWind', 'zg500', 'evspsbl', 'tas', 'pr', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28885,7 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'tasmax', 'sfcWind', 'rsds', 'ua850', 'va850', 'hurs', 'zg500', 'psl', 'rsus']</t>
+          <t>['sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'tasmax', 'sfcWind', 'rsds', 'ua850', 'va850', 'hurs', 'zg500', 'psl', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rlut', 'prsn', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'tasmax', 'pr', 'rsds', 'huss', 'tasmin', 'rsus', 'tas', 'va850', 'evspsbl', 'ua850', 'hurs', 'ps', 'rlds', 'sfcWind', 'clt', 'zg500', 'psl']</t>
+          <t>['rlus', 'rsdt', 'rlut', 'prsn', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'tasmax', 'pr', 'rsds', 'huss', 'tasmin', 'rsus', 'tas', 'va850', 'evspsbl', 'ua850', 'hurs', 'ps', 'rlds', 'sfcWind', 'clt', 'zg500', 'psl']</t>
         </is>
       </c>
     </row>
@@ -29189,7 +29189,7 @@
       </c>
       <c r="J885" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'tasmin', 'evspsbl', 'tas', 'huss', 'ua850', 'tasmax', 'va850', 'psl', 'ps', 'pr', 'hurs', 'zg500']</t>
+          <t>['hfss', 'hfls', 'hus850', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'tasmin', 'evspsbl', 'tas', 'huss', 'ua850', 'tasmax', 'va850', 'psl', 'ps', 'pr', 'hurs', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="J888" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'zg500', 'rlds', 'huss', 'rsus', 'ua850', 'psl']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'zg500', 'rlds', 'huss', 'rsus', 'ua850', 'psl']</t>
         </is>
       </c>
     </row>
@@ -29417,7 +29417,7 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ps', 'ua850', 'rsus', 'clt', 'pr', 'evspsbl', 'hurs', 'tasmin', 'zg500', 'tas', 'va850', 'huss', 'rlds', 'psl', 'sfcWind', 'tasmax', 'rsds']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ps', 'ua850', 'rsus', 'clt', 'pr', 'evspsbl', 'hurs', 'tasmin', 'zg500', 'tas', 'va850', 'huss', 'rlds', 'psl', 'sfcWind', 'tasmax', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -29449,7 +29449,7 @@
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>

--- a/euro-cordex-esgf.xlsx
+++ b/euro-cordex-esgf.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'sund', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'sfcWind', 'rsus', 'rsds', 'zg500', 'tasmax', 'rlds', 'tasmin', 'va850', 'pr', 'psl', 'huss', 'clt', 'tas']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'sund', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'sfcWind', 'rsus', 'rsds', 'zg500', 'tasmax', 'rlds', 'tasmin', 'va850', 'pr', 'psl', 'huss', 'clt', 'tas']</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>['uas', 'va200', 'ua200', 'ua500', 'ta850', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua850', 'psl', 'clt', 'sfcWind', 'huss', 'rsus', 'rsds', 'tasmax', 'zg500', 'tas', 'va850', 'tasmin', 'rlds', 'pr']</t>
+          <t>['uas', 'va200', 'ua200', 'ua500', 'ta850', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua850', 'psl', 'clt', 'sfcWind', 'huss', 'rsus', 'rsds', 'tasmax', 'zg500', 'tas', 'va850', 'tasmin', 'rlds', 'pr']</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'zg500', 'psl', 'tas', 'tasmin', 'rsds', 'rsus', 'tasmax', 'rlds', 'huss']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'zg500', 'psl', 'tas', 'tasmin', 'rsds', 'rsus', 'tasmax', 'rlds', 'huss']</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'rlds', 'tas', 'clt', 'huss', 'tasmax', 'psl', 'va850']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'rlds', 'tas', 'clt', 'huss', 'tasmax', 'psl', 'va850']</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'pr', 'rsds', 'tasmin', 'rlds', 'rsus', 'va850', 'tasmax']</t>
+          <t>['rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'pr', 'rsds', 'tasmin', 'rlds', 'rsus', 'va850', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'uas', 'va200', 'va500', 'ua500', 'ts', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'pr', 'tasmin', 'ua850', 'ps', 'clt', 'zg500', 'rsus', 'tasmax', 'rlds', 'tas', 'huss', 'va850', 'psl', 'rsds', 'sfcWind']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'uas', 'va200', 'va500', 'ua500', 'ts', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'ua200', 'pr', 'tasmin', 'ua850', 'ps', 'clt', 'zg500', 'rsus', 'tasmax', 'rlds', 'tas', 'huss', 'va850', 'psl', 'rsds', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>['hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'psl', 'sfcWind', 'zg500', 'clt', 'tas', 'huss', 'rsds', 'rsus', 'rlds']</t>
+          <t>['hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'psl', 'sfcWind', 'zg500', 'clt', 'tas', 'huss', 'rsds', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'ua200', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'ps', 'ua850', 'clt', 'huss', 'rlds', 'pr', 'zg500', 'rsus', 'sfcWind']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'ua200', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'ps', 'ua850', 'clt', 'huss', 'rlds', 'pr', 'zg500', 'rsus', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'va850', 'psl', 'rsus', 'tasmin', 'sfcWind', 'rsds', 'huss', 'tasmax', 'ua850', 'clt', 'pr', 'zg500', 'tas', 'rlds']</t>
+          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'va850', 'psl', 'rsus', 'tasmin', 'sfcWind', 'rsds', 'huss', 'tasmax', 'ua850', 'clt', 'pr', 'zg500', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'zg500', 'tasmax', 'ua850', 'va850', 'clt', 'huss', 'rlds', 'rsds', 'rsus', 'tasmin', 'pr', 'sfcWind', 'psl', 'tas']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'zg500', 'tasmax', 'ua850', 'va850', 'clt', 'huss', 'rlds', 'rsds', 'rsus', 'tasmin', 'pr', 'sfcWind', 'psl', 'tas']</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>['hfss', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'prhmax', 'rlus', 'rsdt', 'rlut', 'prw', 'ua500', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'clwvi', 'hfls', 'clivi', 'clt', 'zg500', 'tas', 'va850', 'psl', 'tasmax', 'tasmin', 'ua850', 'huss', 'rsds', 'ps', 'sfcWind', 'rlds', 'pr', 'rsus']</t>
+          <t>['hfss', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'prhmax', 'rlus', 'rsdt', 'rlut', 'prw', 'ua500', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'clt', 'zg500', 'tas', 'va850', 'psl', 'tasmax', 'tasmin', 'ua850', 'huss', 'rsds', 'ps', 'sfcWind', 'rlds', 'pr', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'va850', 'rsds', 'tas', 'sfcWind', 'psl', 'zg500', 'huss', 'pr', 'rlds', 'rsus', 'tasmin', 'tasmax', 'clt']</t>
+          <t>['sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'va850', 'rsds', 'tas', 'sfcWind', 'psl', 'zg500', 'huss', 'pr', 'rlds', 'rsus', 'tasmin', 'tasmax', 'clt']</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'psl', 'zg500', 'sfcWind', 'rsus', 'rsds', 'tasmin']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'psl', 'zg500', 'sfcWind', 'rsus', 'rsds', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>['rsdt', 'mrso', 'sfcWindmax', 'uas', 'va500', 'ta500', 'ta200', 'clwvi', 'prw', 'mrro', 'rlus', 'snm', 'snw', 'zg200', 'wsgsmax', 'vas', 'clivi', 'prc', 'hus850', 'ta850', 'prhmax', 'zmla', 'sund', 'rsut', 'rlut', 'mrros', 'snc', 'prsn', 'va200', 'ua200', 'ts', 'hfss', 'hfls', 'mrfso', 'ua500', 'snd', 'rsdt', 'mrso', 'sfcWindmax', 'uas', 'va500', 'ta500', 'ta200', 'clwvi', 'prw', 'mrro', 'rlus', 'snm', 'snw', 'zg200', 'wsgsmax', 'vas', 'clivi', 'prc', 'hus850', 'ta850', 'prhmax', 'zmla', 'sund', 'rsut', 'rlut', 'mrros', 'snc', 'prsn', 'va200', 'ua200', 'ts', 'hfss', 'hfls', 'mrfso', 'ua500', 'snd', 'tas', 'huss', 'rsus', 'evspsbl', 'sfcWind', 'pr', 'rsds', 'ua850', 'clt', 'tasmax', 'psl', 'tasmin', 'ps', 'rlds', 'hurs', 'va850', 'zg500']</t>
+          <t>['rsdt', 'mrso', 'sfcWindmax', 'uas', 'va500', 'ta500', 'ta200', 'clwvi', 'prw', 'mrro', 'rlus', 'snm', 'snw', 'zg200', 'wsgsmax', 'vas', 'clivi', 'prc', 'hus850', 'ta850', 'prhmax', 'zmla', 'sund', 'rsut', 'rlut', 'mrros', 'snc', 'prsn', 'va200', 'ua200', 'ts', 'hfss', 'hfls', 'mrfso', 'ua500', 'snd', 'tas', 'huss', 'rsus', 'evspsbl', 'sfcWind', 'pr', 'rsds', 'ua850', 'clt', 'tasmax', 'psl', 'tasmin', 'ps', 'rlds', 'hurs', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>['zg200', 'ta850', 'rsdt', 'sund', 'mrso', 'va200', 'ta500', 'hfss', 'rlut', 'snw', 'hus850', 'snc', 'ua200', 'rlus', 'snm', 'mrro', 'ua500', 'hfls', 'rsut', 'vas', 'va500', 'ta200', 'uas', 'snd', 'mrros', 'sfcWindmax', 'mrfso', 'zg200', 'ta850', 'rsdt', 'sund', 'mrso', 'va200', 'ta500', 'hfss', 'rlut', 'snw', 'hus850', 'snc', 'ua200', 'rlus', 'snm', 'mrro', 'ua500', 'hfls', 'rsut', 'vas', 'va500', 'ta200', 'uas', 'snd', 'mrros', 'sfcWindmax', 'mrfso', 'hurs', 'huss', 'zg500', 'evspsbl', 'tasmin', 'rlds', 'rsus', 'ua850', 'clt', 'psl', 'rsds', 'pr', 'tasmax', 'tas', 'sfcWind', 'va850']</t>
+          <t>['zg200', 'ta850', 'rsdt', 'sund', 'mrso', 'va200', 'ta500', 'hfss', 'rlut', 'snw', 'hus850', 'snc', 'ua200', 'rlus', 'snm', 'mrro', 'ua500', 'hfls', 'rsut', 'vas', 'va500', 'ta200', 'uas', 'snd', 'mrros', 'sfcWindmax', 'mrfso', 'hurs', 'huss', 'zg500', 'evspsbl', 'tasmin', 'rlds', 'rsus', 'ua850', 'clt', 'psl', 'rsds', 'pr', 'tasmax', 'tas', 'sfcWind', 'va850']</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>['rlut', 'va200', 'ta200', 'ta500', 'sund', 'snc', 'va500', 'rlus', 'rsdt', 'mrro', 'hfss', 'uas', 'ta850', 'hus850', 'snd', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'zg200', 'vas', 'mrros', 'mrfso', 'ua200', 'snm', 'snw', 'ua500', 'rlut', 'va200', 'ta200', 'ta500', 'sund', 'snc', 'va500', 'rlus', 'rsdt', 'mrro', 'hfss', 'uas', 'ta850', 'hus850', 'snd', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'zg200', 'vas', 'mrros', 'mrfso', 'ua200', 'snm', 'snw', 'ua500', 'va850', 'pr', 'sfcWind', 'hurs', 'clt', 'zg500', 'evspsbl', 'huss', 'rsds', 'psl', 'rlds', 'tasmin', 'tasmax', 'tas', 'rsus', 'ua850']</t>
+          <t>['rlut', 'va200', 'ta200', 'ta500', 'sund', 'snc', 'va500', 'rlus', 'rsdt', 'mrro', 'hfss', 'uas', 'ta850', 'hus850', 'snd', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'zg200', 'vas', 'mrros', 'mrfso', 'ua200', 'snm', 'snw', 'ua500', 'va850', 'pr', 'sfcWind', 'hurs', 'clt', 'zg500', 'evspsbl', 'huss', 'rsds', 'psl', 'rlds', 'tasmin', 'tasmax', 'tas', 'rsus', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>['clwvi', 'clivi', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'rsus', 'rlds', 'va850', 'ps', 'tasmax', 'sfcWind', 'clt', 'pr', 'psl', 'ua850', 'zg500', 'tas', 'huss', 'tasmin', 'rsds']</t>
+          <t>['clwvi', 'clivi', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'rsus', 'rlds', 'va850', 'ps', 'tasmax', 'sfcWind', 'clt', 'pr', 'psl', 'ua850', 'zg500', 'tas', 'huss', 'tasmin', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'zg500', 'rsds', 'rsus', 'ua850', 'tasmin', 'rlds', 'va850']</t>
+          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'zg500', 'rsds', 'rsus', 'ua850', 'tasmin', 'rlds', 'va850']</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>['clivi', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'ua850', 'tas', 'psl', 'va850', 'tasmax', 'pr', 'zg500', 'ps', 'tasmin']</t>
+          <t>['clivi', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'ua850', 'tas', 'psl', 'va850', 'tasmax', 'pr', 'zg500', 'ps', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'tasmax', 'sfcWind']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'tasmax', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'rsus', 'psl', 'tasmax', 'huss']</t>
+          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'rsus', 'psl', 'tasmax', 'huss']</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>['rsds', 'rsus', 'pr', 'prc', 'rlds', 'ps', 'rlus', 'sfcWind', 'tas', 'hfls', 'hurs', 'hfss', 'psl', 'sund', 'huss', 'rsds', 'rsus', 'pr', 'prc', 'rlds', 'ps', 'rlus', 'sfcWind', 'tas', 'hfls', 'hurs', 'hfss', 'psl', 'sund', 'huss']</t>
+          <t>['rsds', 'rsus', 'pr', 'prc', 'rlds', 'ps', 'rlus', 'sfcWind', 'tas', 'hfls', 'hurs', 'hfss', 'psl', 'sund', 'huss']</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>['rlut', 'prw', 'vas', 'ts', 'rsut', 'uas', 'ta200', 'zg200', 'mrro', 'rsdt', 'snd', 'mrfso', 'zmla', 'va850', 'clivi', 'hus850', 'ua500', 'ta850', 'ta500', 'clwvi', 'snm', 'va500', 'snw', 'va200', 'mrros', 'ua200', 'ua850', 'evspsbl', 'mrso', 'zg500', 'rlut', 'prw', 'vas', 'ts', 'rsut', 'uas', 'ta200', 'zg200', 'mrro', 'rsdt', 'snd', 'mrfso', 'zmla', 'va850', 'clivi', 'hus850', 'ua500', 'ta850', 'ta500', 'clwvi', 'snm', 'va500', 'snw', 'va200', 'mrros', 'ua200', 'ua850', 'evspsbl', 'mrso', 'zg500']</t>
+          <t>['rlut', 'prw', 'vas', 'ts', 'rsut', 'uas', 'ta200', 'zg200', 'mrro', 'rsdt', 'snd', 'mrfso', 'zmla', 'va850', 'clivi', 'hus850', 'ua500', 'ta850', 'ta500', 'clwvi', 'snm', 'va500', 'snw', 'va200', 'mrros', 'ua200', 'ua850', 'evspsbl', 'mrso', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rsdt', 'snw', 'snm', 'tas', 'ta850', 'rlut', 'mrros', 'vas', 'sund', 'huss', 'ua500', 'mrfso', 'clwvi', 'zmla', 'prw', 'prhmax', 'evspsbl', 'mrro', 'ts', 'rsus', 'va200', 'ta200', 'snd', 'zg500', 'psl', 'hfls', 'prsn', 'mrso', 'hurs', 'rsds', 'tasmax', 'sfcWind', 'va850', 'hus850', 'ua850', 'tasmin', 'va500', 'wsgsmax', 'zg200', 'ua200', 'rsut', 'prc', 'uas', 'ta500', 'clivi', 'ps', 'pr', 'hfss', 'rlds', 'rlus', 'rsdt', 'snw', 'snm', 'tas', 'ta850', 'rlut', 'mrros', 'vas', 'sund', 'huss', 'ua500', 'mrfso', 'clwvi', 'zmla', 'prw', 'prhmax', 'evspsbl', 'mrro', 'ts', 'rsus', 'va200', 'ta200', 'snd', 'zg500', 'psl', 'hfls', 'prsn', 'mrso', 'hurs', 'rsds', 'tasmax', 'sfcWind', 'va850', 'hus850', 'ua850', 'tasmin', 'va500', 'wsgsmax', 'zg200', 'ua200', 'rsut', 'prc', 'uas', 'ta500', 'clivi', 'ps', 'pr', 'hfss']</t>
+          <t>['rlds', 'rlus', 'rsdt', 'snw', 'snm', 'tas', 'ta850', 'rlut', 'mrros', 'vas', 'sund', 'huss', 'ua500', 'mrfso', 'clwvi', 'zmla', 'prw', 'prhmax', 'evspsbl', 'mrro', 'ts', 'rsus', 'va200', 'ta200', 'snd', 'zg500', 'psl', 'hfls', 'prsn', 'mrso', 'hurs', 'rsds', 'tasmax', 'sfcWind', 'va850', 'hus850', 'ua850', 'tasmin', 'va500', 'wsgsmax', 'zg200', 'ua200', 'rsut', 'prc', 'uas', 'ta500', 'clivi', 'ps', 'pr', 'hfss']</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>['rlds', 'hus850', 'rsus', 'rsut', 'sfcWind', 'rsds', 'snw', 'va500', 'zg500', 'sund', 'ta200', 'huss', 'va850', 'ua200', 'mrros', 'mrso', 'uas', 'zg200', 'snm', 'mrro', 'ta850', 'tasmax', 'va200', 'rlut', 'vas', 'hfls', 'mrfso', 'rlus', 'evspsbl', 'psl', 'hfss', 'tasmin', 'hurs', 'ua500', 'ta500', 'rsdt', 'tas', 'pr', 'ua850', 'snd', 'rlds', 'hus850', 'rsus', 'rsut', 'sfcWind', 'rsds', 'snw', 'va500', 'zg500', 'sund', 'ta200', 'huss', 'va850', 'ua200', 'mrros', 'mrso', 'uas', 'zg200', 'snm', 'mrro', 'ta850', 'tasmax', 'va200', 'rlut', 'vas', 'hfls', 'mrfso', 'rlus', 'evspsbl', 'psl', 'hfss', 'tasmin', 'hurs', 'ua500', 'ta500', 'rsdt', 'tas', 'pr', 'ua850', 'snd']</t>
+          <t>['rlds', 'hus850', 'rsus', 'rsut', 'sfcWind', 'rsds', 'snw', 'va500', 'zg500', 'sund', 'ta200', 'huss', 'va850', 'ua200', 'mrros', 'mrso', 'uas', 'zg200', 'snm', 'mrro', 'ta850', 'tasmax', 'va200', 'rlut', 'vas', 'hfls', 'mrfso', 'rlus', 'evspsbl', 'psl', 'hfss', 'tasmin', 'hurs', 'ua500', 'ta500', 'rsdt', 'tas', 'pr', 'ua850', 'snd']</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>['uas', 'psl', 'mrso', 'zg500', 'sfcWind', 'huss', 'pr', 'tasmin', 'va850', 'sund', 'vas', 'snw', 'rlds', 'mrros', 'rsut', 'mrro', 'ta500', 'rsus', 'zg200', 'ua500', 'rlut', 'hurs', 'ta850', 'tas', 'ua850', 'tasmax', 'rsdt', 'snm', 'rsds', 'rlus', 'evspsbl', 'va200', 'ua200', 'va500', 'snd', 'mrfso', 'hus850', 'ta200', 'hfss', 'hfls', 'uas', 'psl', 'mrso', 'zg500', 'sfcWind', 'huss', 'pr', 'tasmin', 'va850', 'sund', 'vas', 'snw', 'rlds', 'mrros', 'rsut', 'mrro', 'ta500', 'rsus', 'zg200', 'ua500', 'rlut', 'hurs', 'ta850', 'tas', 'ua850', 'tasmax', 'rsdt', 'snm', 'rsds', 'rlus', 'evspsbl', 'va200', 'ua200', 'va500', 'snd', 'mrfso', 'hus850', 'ta200', 'hfss', 'hfls']</t>
+          <t>['uas', 'psl', 'mrso', 'zg500', 'sfcWind', 'huss', 'pr', 'tasmin', 'va850', 'sund', 'vas', 'snw', 'rlds', 'mrros', 'rsut', 'mrro', 'ta500', 'rsus', 'zg200', 'ua500', 'rlut', 'hurs', 'ta850', 'tas', 'ua850', 'tasmax', 'rsdt', 'snm', 'rsds', 'rlus', 'evspsbl', 'va200', 'ua200', 'va500', 'snd', 'mrfso', 'hus850', 'ta200', 'hfss', 'hfls']</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'va200', 'ua500', 'ua200', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'tasmax', 'rlds', 'ps', 'zg500', 'rsds', 'evspsbl', 'huss', 'pr', 'va850', 'tasmin', 'sfcWind']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'va200', 'ua500', 'ua200', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'tasmax', 'rlds', 'ps', 'zg500', 'rsds', 'evspsbl', 'huss', 'pr', 'va850', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'va850', 'clt', 'evspsbl', 'rlds', 'rsus', 'tasmin', 'ua850', 'pr']</t>
+          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'va850', 'clt', 'evspsbl', 'rlds', 'rsus', 'tasmin', 'ua850', 'pr']</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ts', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'zmla', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rsus', 'rsds', 'evspsbl', 'ps', 'huss', 'ua850', 'pr', 'tas', 'tasmin', 'zg500']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ts', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rsus', 'rsds', 'evspsbl', 'ps', 'huss', 'ua850', 'pr', 'tas', 'tasmin', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'sfcWind', 'ua850', 'zg500', 'pr', 'tasmin', 'va850', 'clt', 'rlds', 'psl', 'evspsbl', 'huss', 'tasmax', 'rsus', 'tas']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'sfcWind', 'ua850', 'zg500', 'pr', 'tasmin', 'va850', 'clt', 'rlds', 'psl', 'evspsbl', 'huss', 'tasmax', 'rsus', 'tas']</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'zg500', 'psl', 'tasmin', 'huss', 'ua850', 'va850', 'clt', 'tas', 'pr', 'evspsbl', 'rsus', 'tasmax', 'sfcWind', 'rsds', 'rlds']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'zg500', 'psl', 'tasmin', 'huss', 'ua850', 'va850', 'clt', 'tas', 'pr', 'evspsbl', 'rsus', 'tasmax', 'sfcWind', 'rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>['prhmax', 'rlus', 'mrso', 'prc', 'prw', 'wsgsmax', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'tas', 'pr', 'clt', 'ps', 'huss', 'rsds', 'rsus', 'zg500']</t>
+          <t>['prhmax', 'rlus', 'mrso', 'prc', 'prw', 'wsgsmax', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'tas', 'pr', 'clt', 'ps', 'huss', 'rsds', 'rsus', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'clt', 'tasmax', 'rlds', 'huss', 'tasmin', 'zg500', 'ua850', 'rsus']</t>
+          <t>['hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'clt', 'tasmax', 'rlds', 'huss', 'tasmin', 'zg500', 'ua850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'ua850', 'tasmin', 'rsus', 'sfcWind', 'rlds', 'pr', 'tas']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'ua850', 'tasmin', 'rsus', 'sfcWind', 'rlds', 'pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'tasmax', 'rsds', 'psl', 'sfcWind', 'huss', 'zg500', 'ua850', 'pr', 'tasmin', 'tas', 'rlds', 'clt', 'ps', 'va850', 'rsus']</t>
+          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'tasmax', 'rsds', 'psl', 'sfcWind', 'huss', 'zg500', 'ua850', 'pr', 'tasmin', 'tas', 'rlds', 'clt', 'ps', 'va850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'tas', 'rlds', 'tasmin', 'tasmax', 'clt', 'va850', 'rsds', 'rsus', 'psl', 'ps', 'ua850', 'huss', 'sfcWind', 'pr', 'zg500']</t>
+          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'tas', 'rlds', 'tasmin', 'tasmax', 'clt', 'va850', 'rsds', 'rsus', 'psl', 'ps', 'ua850', 'huss', 'sfcWind', 'pr', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
+          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr', 'prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>['rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'cape', 'evspsbl', 'clt', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts']</t>
+          <t>['rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'cape', 'evspsbl', 'clt', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts', 'rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'cape', 'evspsbl', 'clt', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts']</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>['clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'uas', 'ua200', 'ua925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clh', 'clivi', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'ua100', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg925']</t>
+          <t>['clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'uas', 'ua200', 'ua925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clh', 'clivi', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'ua100', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg925', 'clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'uas', 'ua200', 'ua925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clh', 'clivi', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'ua100', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'psl', 'rlds', 'rlus', 'rlut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'tas', 'tasmax', 'tasmin', 'ts', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'prhmax', 'prsn', 'prw', 'ps', 'hfls', 'hfss', 'hurs', 'hus100', 'mrros', 'mrso', 'pr', 'prc', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'huss', 'mrfso', 'mrro', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'uas', 'va100', 'va200', 'ua700', 'ua850', 'ua925']</t>
+          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'psl', 'rlds', 'rlus', 'rlut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'tas', 'tasmax', 'tasmin', 'ts', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'prhmax', 'prsn', 'prw', 'ps', 'hfls', 'hfss', 'hurs', 'hus100', 'mrros', 'mrso', 'pr', 'prc', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'huss', 'mrfso', 'mrro', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'uas', 'va100', 'va200', 'ua700', 'ua850', 'ua925', 'rsds', 'rsdt', 'rsus', 'rsut', 'psl', 'rlds', 'rlus', 'rlut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'tas', 'tasmax', 'tasmin', 'ts', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'prhmax', 'prsn', 'prw', 'ps', 'hfls', 'hfss', 'hurs', 'hus100', 'mrros', 'mrso', 'pr', 'prc', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'huss', 'mrfso', 'mrro', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'uas', 'va100', 'va200', 'ua700', 'ua850', 'ua925']</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clt', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'uas', 'va100', 'va200', 'va300', 'va400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clt', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'uas', 'va100', 'va200', 'va300', 'va400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'va500', 'va600', 'va700', 'va850', 'va925', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clt', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'uas', 'va100', 'va200', 'va300', 'va400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>['rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ua925', 'uas', 'va100', 'va200', 'va300', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ua925', 'uas', 'va100', 'va200', 'va300', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ua925', 'uas', 'va100', 'va200', 'va300', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>['tas', 'tds', 'pr', 'prc']</t>
+          <t>['tas', 'tds', 'pr', 'prc', 'tas', 'tds', 'pr', 'prc']</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m']</t>
+          <t>['ua100m', 'va100m', 'ua100m', 'va100m']</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'psl', 'rlds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'ts', 'sund', 'tas']</t>
+          <t>['cape', 'clt', 'psl', 'rlds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'ts', 'sund', 'tas', 'cape', 'clt', 'psl', 'rlds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'ts', 'sund', 'tas']</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>['prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus600', 'hus700', 'ta100', 'ta200', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'va700', 'va850', 'va100', 'va200', 'va500', 'va600', 'va300', 'va400', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'hus400', 'hus500', 'ta925', 'ts', 'ua925', 'uas', 'ta700', 'ta850', 'ta300', 'ta400', 'ua700', 'ua850', 'ta500', 'ta600', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg925', 'zmla']</t>
+          <t>['prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus600', 'hus700', 'ta100', 'ta200', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'va700', 'va850', 'va100', 'va200', 'va500', 'va600', 'va300', 'va400', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'hus400', 'hus500', 'ta925', 'ts', 'ua925', 'uas', 'ta700', 'ta850', 'ta300', 'ta400', 'ua700', 'ua850', 'ta500', 'ta600', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg925', 'zmla', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus600', 'hus700', 'ta100', 'ta200', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'va700', 'va850', 'va100', 'va200', 'va500', 'va600', 'va300', 'va400', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'hus400', 'hus500', 'ta925', 'ts', 'ua925', 'uas', 'ta700', 'ta850', 'ta300', 'ta400', 'ua700', 'ua850', 'ta500', 'ta600', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg925', 'zmla']</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clh']</t>
+          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clh', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clh']</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>['clt', 'zg600', 'zg700', 'zg850', 'zg925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
+          <t>['clt', 'zg600', 'zg700', 'zg850', 'zg925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'clt', 'zg600', 'zg700', 'zg850', 'zg925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg600', 'zg700', 'zg850', 'zg925', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>['tas', 'tds', 'pr', 'prc']</t>
+          <t>['tas', 'tds', 'pr', 'prc', 'tas', 'tds', 'pr', 'prc']</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>['va100m', 'ua100m']</t>
+          <t>['va100m', 'ua100m', 'va100m', 'ua100m']</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'cape', 'clt', 'rlus', 'rsds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'ts', 'sund', 'tas']</t>
+          <t>['psl', 'rlds', 'cape', 'clt', 'rlus', 'rsds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'ts', 'sund', 'tas', 'psl', 'rlds', 'cape', 'clt', 'rlus', 'rsds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'ts', 'sund', 'tas']</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>['zmla', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus600', 'hus700', 'hus200', 'hus300', 'hus400', 'hus500', 'vas', 'zg100', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'rsdt', 'rsut', 'prw', 'rlut', 'snd', 'snm', 'snc', 'mrros', 'mrso', 'mrfso', 'mrro', 'snw', 'ta100', 'hus850', 'hus925', 'ta200', 'ta300', 'uas', 'va100', 'ts', 'ua100', 'ta850', 'ta925', 'ua850', 'ua925', 'ta400', 'ta500', 'ta600', 'ta700', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
+          <t>['zmla', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus600', 'hus700', 'hus200', 'hus300', 'hus400', 'hus500', 'vas', 'zg100', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'rsdt', 'rsut', 'prw', 'rlut', 'snd', 'snm', 'snc', 'mrros', 'mrso', 'mrfso', 'mrro', 'snw', 'ta100', 'hus850', 'hus925', 'ta200', 'ta300', 'uas', 'va100', 'ts', 'ua100', 'ta850', 'ta925', 'ua850', 'ua925', 'ta400', 'ta500', 'ta600', 'ta700', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'zmla', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus600', 'hus700', 'hus200', 'hus300', 'hus400', 'hus500', 'vas', 'zg100', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'rsdt', 'rsut', 'prw', 'rlut', 'snd', 'snm', 'snc', 'mrros', 'mrso', 'mrfso', 'mrro', 'snw', 'ta100', 'hus850', 'hus925', 'ta200', 'ta300', 'uas', 'va100', 'ts', 'ua100', 'ta850', 'ta925', 'ua850', 'ua925', 'ta400', 'ta500', 'ta600', 'ta700', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>['hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'clh', 'clivi', 'cll', 'clm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snc', 'snd', 'snm', 'snw', 'sund', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'zg850', 'zg925', 'zmla', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100']</t>
+          <t>['hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'clh', 'clivi', 'cll', 'clm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snc', 'snd', 'snm', 'snw', 'sund', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'zg850', 'zg925', 'zmla', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'clh', 'clivi', 'cll', 'clm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snc', 'snd', 'snm', 'snw', 'sund', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'zg850', 'zg925', 'zmla', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100']</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>['pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clt', 'evspsbl', 'hfls', 'hfss']</t>
+          <t>['pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clt', 'evspsbl', 'hfls', 'hfss', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clt', 'evspsbl', 'hfls', 'hfss']</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>['rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl']</t>
+          <t>['rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>['pr', 'prc', 'tas', 'tds']</t>
+          <t>['pr', 'prc', 'tas', 'tds', 'pr', 'prc', 'tas', 'tds']</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m']</t>
+          <t>['ua100m', 'va100m', 'ua100m', 'va100m']</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'evspsbl', 'hfls', 'tas', 'ts']</t>
+          <t>['cape', 'clt', 'evspsbl', 'hfls', 'tas', 'ts', 'cape', 'clt', 'evspsbl', 'hfls', 'tas', 'ts']</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'clh', 'clivi', 'hus925', 'mrfso', 'mrro', 'mrros', 'mrso', 'prw', 'rlut', 'rsdt', 'rsut', 'snc', 'snd', 'snm', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'ua100', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300']</t>
+          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'clh', 'clivi', 'hus925', 'mrfso', 'mrro', 'mrros', 'mrso', 'prw', 'rlut', 'rsdt', 'rsut', 'snc', 'snd', 'snm', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'ua100', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'clh', 'clivi', 'hus925', 'mrfso', 'mrro', 'mrros', 'mrso', 'prw', 'rlut', 'rsdt', 'rsut', 'snc', 'snd', 'snm', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'ua100', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300']</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>['hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700']</t>
+          <t>['hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700']</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>['zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clt', 'evspsbl']</t>
+          <t>['zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clt', 'evspsbl', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>['snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700']</t>
+          <t>['snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700']</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>['cape', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ps', 'ts']</t>
+          <t>['cape', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ps', 'ts', 'cape', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ps', 'ts']</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>['clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'mrfso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'snw', 'ta300', 'ta100', 'ta200', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'zmla', 'zg600', 'zg850', 'zg700', 'zg925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snm', 'snc', 'snd', 'ta925', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua200', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925']</t>
+          <t>['clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'mrfso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'snw', 'ta300', 'ta100', 'ta200', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'zmla', 'zg600', 'zg850', 'zg700', 'zg925', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'mrfso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'snw', 'ta300', 'ta100', 'ta200', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'zmla', 'zg600', 'zg850', 'zg700', 'zg925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snm', 'snc', 'snd', 'ta925', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua200', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>['clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'ta700', 'ta850', 'ta925', 'tas', 'ta300', 'ta400', 'ta500', 'ta600']</t>
+          <t>['clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'ta700', 'ta850', 'ta925', 'tas', 'ta300', 'ta400', 'ta500', 'ta600']</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>['clt', 'evspsbl', 'hfls', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
+          <t>['clt', 'evspsbl', 'hfls', 'zg500', 'zg600', 'zg700', 'zg850', 'clt', 'evspsbl', 'hfls', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>['mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
+          <t>['mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>['ps', 'pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'ts', 'ps', 'pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'ts']</t>
+          <t>['ps', 'pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'ts']</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'pr']</t>
+          <t>['sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>['pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas', 'pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas']</t>
+          <t>['pr', 'sfcWindmax', 'tasmax', 'tasmin', 'sfcWind', 'vas', 'uas', 'tas']</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>['sic', 'ua500', 'ua200', 'sfcWindmax', 'uas', 'rsds', 'evspsbl', 'ta500', 'hurs', 'clivi', 'clt', 'prw', 'sfcWind', 'ua850', 'tasmax', 'clh', 'vas', 'va850', 'hfss', 'pr', 'clwvi', 'prsn', 'tasmin', 'rsus', 'ta200', 'tauu', 'cll', 'snc', 'prhmax', 'rlus', 'huss', 'snm', 'va500', 'ts', 'mrso', 'ta850', 'hfls', 'rsdt', 'hus850', 'rsut', 'rlut', 'rlds', 'va200', 'tauv', 'tas', 'prc', 'ps', 'clm', 'psl', 'sic', 'ua500', 'ua200', 'sfcWindmax', 'uas', 'rsds', 'evspsbl', 'ta500', 'hurs', 'clivi', 'clt', 'prw', 'sfcWind', 'ua850', 'tasmax', 'clh', 'vas', 'va850', 'hfss', 'pr', 'clwvi', 'prsn', 'tasmin', 'rsus', 'ta200', 'tauu', 'cll', 'snc', 'prhmax', 'rlus', 'huss', 'snm', 'va500', 'ts', 'mrso', 'ta850', 'hfls', 'rsdt', 'hus850', 'rsut', 'rlut', 'rlds', 'va200', 'tauv', 'tas', 'prc', 'ps', 'clm', 'psl', 'mrros', 'mrro']</t>
+          <t>['sic', 'ua500', 'ua200', 'sfcWindmax', 'uas', 'rsds', 'evspsbl', 'ta500', 'hurs', 'clivi', 'clt', 'prw', 'sfcWind', 'ua850', 'tasmax', 'clh', 'vas', 'va850', 'hfss', 'pr', 'clwvi', 'prsn', 'tasmin', 'rsus', 'ta200', 'tauu', 'cll', 'snc', 'prhmax', 'rlus', 'huss', 'snm', 'va500', 'ts', 'mrso', 'ta850', 'hfls', 'rsdt', 'hus850', 'rsut', 'rlut', 'rlds', 'va200', 'tauv', 'tas', 'prc', 'ps', 'clm', 'psl', 'mrros', 'mrro', 'sic', 'ua500', 'ua200', 'sfcWindmax', 'uas', 'rsds', 'evspsbl', 'ta500', 'hurs', 'clivi', 'clt', 'prw', 'sfcWind', 'ua850', 'tasmax', 'clh', 'vas', 'va850', 'hfss', 'pr', 'clwvi', 'prsn', 'tasmin', 'rsus', 'ta200', 'tauu', 'cll', 'snc', 'prhmax', 'rlus', 'huss', 'snm', 'va500', 'ts', 'mrso', 'ta850', 'hfls', 'rsdt', 'hus850', 'rsut', 'rlut', 'rlds', 'va200', 'tauv', 'tas', 'prc', 'ps', 'clm', 'psl', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'clh', 'clivi', 'va850', 'vas', 'zg200', 'zg500', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
+          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'clh', 'clivi', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'clh', 'clivi', 'va850', 'vas', 'zg200', 'zg500', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>['tasmax', 'tauu', 'mrso', 'snm', 'ua200', 'va500', 'rsds', 'ua850', 'snd', 'clwvi', 'rsut', 'sund', 'hfss', 'tas', 'tasmin', 'rlut', 'prsn', 'vas', 'clh', 'cll', 'ua500', 'prhmax', 'mrros', 'ta850', 'ps', 'uas', 'pr', 'sfcWind', 'hus850', 'ts', 'snc', 'sic', 'prc', 'hurs', 'snw', 'ta200', 'evspsbl', 'rsus', 'clt', 'clm', 'va850', 'zg200', 'va200', 'hfls', 'rsdt', 'ta500', 'sfcWindmax', 'rlds', 'prw', 'rlus', 'tauv', 'huss', 'zg500', 'mrro', 'psl', 'clivi']</t>
+          <t>['tasmax', 'tauu', 'mrso', 'snm', 'ua200', 'va500', 'rsds', 'ua850', 'snd', 'clwvi', 'rsut', 'sund', 'hfss', 'tas', 'tasmin', 'rlut', 'prsn', 'vas', 'clh', 'cll', 'ua500', 'prhmax', 'mrros', 'ta850', 'ps', 'uas', 'pr', 'sfcWind', 'hus850', 'ts', 'snc', 'sic', 'prc', 'hurs', 'snw', 'ta200', 'evspsbl', 'rsus', 'clt', 'clm', 'va850', 'zg200', 'va200', 'hfls', 'rsdt', 'ta500', 'sfcWindmax', 'rlds', 'prw', 'rlus', 'tauv', 'huss', 'zg500', 'mrro', 'psl', 'clivi', 'tasmax', 'tauu', 'mrso', 'snm', 'ua200', 'va500', 'rsds', 'ua850', 'snd', 'clwvi', 'rsut', 'sund', 'hfss', 'tas', 'tasmin', 'rlut', 'prsn', 'vas', 'clh', 'cll', 'ua500', 'prhmax', 'mrros', 'ta850', 'ps', 'uas', 'pr', 'sfcWind', 'hus850', 'ts', 'snc', 'sic', 'prc', 'hurs', 'snw', 'ta200', 'evspsbl', 'rsus', 'clt', 'clm', 'va850', 'zg200', 'va200', 'hfls', 'rsdt', 'ta500', 'sfcWindmax', 'rlds', 'prw', 'rlus', 'tauv', 'huss', 'zg500', 'mrro', 'psl', 'clivi']</t>
         </is>
       </c>
     </row>
@@ -17681,7 +17681,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog']</t>
+          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>['snc', 'mrso', 'zg500', 'hurs', 'hfss', 'ua850', 'mrro', 'snm', 'rlut', 'sfcWind', 'ua200', 'rsut', 'sund', 'tas', 'ta500', 'pr', 'rlus', 'huss', 'ua500', 'va850', 'va500', 'sfcWindmax', 'evspsbl', 'hus850', 'ta200', 'rsus', 'psl', 'sic', 'rsds', 'tasmin', 'mrros', 'uas', 'tasmax', 'clt', 'hfls', 'rsdt', 'snw', 'rlds', 'ta850', 'snd', 'vas', 'zg200', 'va200']</t>
+          <t>['snc', 'mrso', 'zg500', 'hurs', 'hfss', 'ua850', 'mrro', 'snm', 'rlut', 'sfcWind', 'ua200', 'rsut', 'sund', 'tas', 'ta500', 'pr', 'rlus', 'huss', 'ua500', 'va850', 'va500', 'sfcWindmax', 'evspsbl', 'hus850', 'ta200', 'rsus', 'psl', 'sic', 'rsds', 'tasmin', 'mrros', 'uas', 'tasmax', 'clt', 'hfls', 'rsdt', 'snw', 'rlds', 'ta850', 'snd', 'vas', 'zg200', 'va200', 'snc', 'mrso', 'zg500', 'hurs', 'hfss', 'ua850', 'mrro', 'snm', 'rlut', 'sfcWind', 'ua200', 'rsut', 'sund', 'tas', 'ta500', 'pr', 'rlus', 'huss', 'ua500', 'va850', 'va500', 'sfcWindmax', 'evspsbl', 'hus850', 'ta200', 'rsus', 'psl', 'sic', 'rsds', 'tasmin', 'mrros', 'uas', 'tasmax', 'clt', 'hfls', 'rsdt', 'snw', 'rlds', 'ta850', 'snd', 'vas', 'zg200', 'va200']</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>['clt', 'sfcWindmax', 'rlus', 'snc', 'tasmin', 'zg200', 'va200', 'rsds', 'psl', 'hfls', 'rsdt', 'tas', 'hfss', 'snw', 'snd', 'evspsbl', 'tasmax', 'mrso', 'zg500', 'va500', 'vas', 'va850', 'ta200', 'sfcWind', 'huss', 'rsut', 'ta850', 'rsus', 'ua850', 'ua200', 'pr', 'mrros', 'sund', 'sic', 'ua500', 'rlut', 'snm', 'rlds', 'uas', 'hurs', 'ta500', 'hus850', 'mrro']</t>
+          <t>['clt', 'sfcWindmax', 'rlus', 'snc', 'tasmin', 'zg200', 'va200', 'rsds', 'psl', 'hfls', 'rsdt', 'tas', 'hfss', 'snw', 'snd', 'evspsbl', 'tasmax', 'mrso', 'zg500', 'va500', 'vas', 'va850', 'ta200', 'sfcWind', 'huss', 'rsut', 'ta850', 'rsus', 'ua850', 'ua200', 'pr', 'mrros', 'sund', 'sic', 'ua500', 'rlut', 'snm', 'rlds', 'uas', 'hurs', 'ta500', 'hus850', 'mrro', 'clt', 'sfcWindmax', 'rlus', 'snc', 'tasmin', 'zg200', 'va200', 'rsds', 'psl', 'hfls', 'rsdt', 'tas', 'hfss', 'snw', 'snd', 'evspsbl', 'tasmax', 'mrso', 'zg500', 'va500', 'vas', 'va850', 'ta200', 'sfcWind', 'huss', 'rsut', 'ta850', 'rsus', 'ua850', 'ua200', 'pr', 'mrros', 'sund', 'sic', 'ua500', 'rlut', 'snm', 'rlds', 'uas', 'hurs', 'ta500', 'hus850', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>['rlut', 'ua200', 'hus850', 'sfcWind', 'psl', 'ta200', 'tasmin', 'rlus', 'tauv', 'huss', 'prhmax', 'clivi', 'uas', 'rsds', 'evspsbl', 'tasmax', 'tas', 'ua500', 'hurs', 'hfss', 'snm', 'rsus', 'prw', 'ta500', 'rsut', 'vas', 'clt', 'va200', 'hfls', 'rsdt', 'prc', 'ta850', 'clh', 'tauu', 'rlds', 'sic', 'clwvi', 'clm', 'ps', 'va500', 'mrso', 'sfcWindmax', 'va850', 'prsn', 'ua850', 'ts', 'cll', 'snc', 'pr', 'rlut', 'ua200', 'hus850', 'sfcWind', 'psl', 'ta200', 'tasmin', 'rlus', 'tauv', 'huss', 'prhmax', 'clivi', 'uas', 'rsds', 'evspsbl', 'tasmax', 'tas', 'ua500', 'hurs', 'hfss', 'snm', 'rsus', 'prw', 'ta500', 'rsut', 'vas', 'clt', 'va200', 'hfls', 'rsdt', 'prc', 'ta850', 'clh', 'tauu', 'rlds', 'sic', 'clwvi', 'clm', 'ps', 'va500', 'mrso', 'sfcWindmax', 'va850', 'prsn', 'ua850', 'ts', 'cll', 'snc', 'pr', 'mrro', 'mrros']</t>
+          <t>['rlut', 'ua200', 'hus850', 'sfcWind', 'psl', 'ta200', 'tasmin', 'rlus', 'tauv', 'huss', 'prhmax', 'clivi', 'uas', 'rsds', 'evspsbl', 'tasmax', 'tas', 'ua500', 'hurs', 'hfss', 'snm', 'rsus', 'prw', 'ta500', 'rsut', 'vas', 'clt', 'va200', 'hfls', 'rsdt', 'prc', 'ta850', 'clh', 'tauu', 'rlds', 'sic', 'clwvi', 'clm', 'ps', 'va500', 'mrso', 'sfcWindmax', 'va850', 'prsn', 'ua850', 'ts', 'cll', 'snc', 'pr', 'mrro', 'mrros', 'rlut', 'ua200', 'hus850', 'sfcWind', 'psl', 'ta200', 'tasmin', 'rlus', 'tauv', 'huss', 'prhmax', 'clivi', 'uas', 'rsds', 'evspsbl', 'tasmax', 'tas', 'ua500', 'hurs', 'hfss', 'snm', 'rsus', 'prw', 'ta500', 'rsut', 'vas', 'clt', 'va200', 'hfls', 'rsdt', 'prc', 'ta850', 'clh', 'tauu', 'rlds', 'sic', 'clwvi', 'clm', 'ps', 'va500', 'mrso', 'sfcWindmax', 'va850', 'prsn', 'ua850', 'ts', 'cll', 'snc', 'pr', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>['hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus']</t>
+          <t>['hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus', 'hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>['clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200']</t>
+          <t>['clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200', 'clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200']</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>['snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund']</t>
+          <t>['snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund', 'snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund']</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>['rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr']</t>
+          <t>['rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr', 'rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr']</t>
         </is>
       </c>
     </row>
@@ -18793,7 +18793,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>['ts', 'va200', 'ta500', 'tas', 'ua500', 'hfss', 'sfcWind', 'hus850', 'rsus', 'clivi', 'va850', 'rsds', 'hfls', 'rsdt', 'cll', 'psl', 'clwvi', 'rlut', 'tasmin', 'snm', 'ta200', 'ps', 'va500', 'tauu', 'prw', 'rlds', 'tasmax', 'ta850', 'sfcWindmax', 'vas', 'clt', 'rlus', 'clm', 'evspsbl', 'mrso', 'ua850', 'prc', 'clh', 'rsut', 'snc', 'pr', 'tauv', 'huss', 'prhmax', 'hurs', 'sic', 'prsn', 'uas', 'ua200', 'ts', 'va200', 'ta500', 'tas', 'ua500', 'hfss', 'sfcWind', 'hus850', 'rsus', 'clivi', 'va850', 'rsds', 'hfls', 'rsdt', 'cll', 'psl', 'clwvi', 'rlut', 'tasmin', 'snm', 'ta200', 'ps', 'va500', 'tauu', 'prw', 'rlds', 'tasmax', 'ta850', 'sfcWindmax', 'vas', 'clt', 'rlus', 'clm', 'evspsbl', 'mrso', 'ua850', 'prc', 'clh', 'rsut', 'snc', 'pr', 'tauv', 'huss', 'prhmax', 'hurs', 'sic', 'prsn', 'uas', 'ua200', 'mrros', 'mrro']</t>
+          <t>['ts', 'va200', 'ta500', 'tas', 'ua500', 'hfss', 'sfcWind', 'hus850', 'rsus', 'clivi', 'va850', 'rsds', 'hfls', 'rsdt', 'cll', 'psl', 'clwvi', 'rlut', 'tasmin', 'snm', 'ta200', 'ps', 'va500', 'tauu', 'prw', 'rlds', 'tasmax', 'ta850', 'sfcWindmax', 'vas', 'clt', 'rlus', 'clm', 'evspsbl', 'mrso', 'ua850', 'prc', 'clh', 'rsut', 'snc', 'pr', 'tauv', 'huss', 'prhmax', 'hurs', 'sic', 'prsn', 'uas', 'ua200', 'mrros', 'mrro', 'ts', 'va200', 'ta500', 'tas', 'ua500', 'hfss', 'sfcWind', 'hus850', 'rsus', 'clivi', 'va850', 'rsds', 'hfls', 'rsdt', 'cll', 'psl', 'clwvi', 'rlut', 'tasmin', 'snm', 'ta200', 'ps', 'va500', 'tauu', 'prw', 'rlds', 'tasmax', 'ta850', 'sfcWindmax', 'vas', 'clt', 'rlus', 'clm', 'evspsbl', 'mrso', 'ua850', 'prc', 'clh', 'rsut', 'snc', 'pr', 'tauv', 'huss', 'prhmax', 'hurs', 'sic', 'prsn', 'uas', 'ua200', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -19053,7 +19053,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19197,7 +19197,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>['va850', 'rsds', 'tauu', 'uas', 'clh', 'ua850', 'ua200', 'tas', 'rsut', 'vas', 'snc', 'clm', 'psl', 'hfss', 'sfcWind', 'va500', 'hus850', 'rsus', 'ta500', 'ts', 'clivi', 'hurs', 'rlds', 'prhmax', 'mrso', 'tasmin', 'tauv', 'va200', 'prc', 'rlut', 'evspsbl', 'ta850', 'huss', 'sic', 'clwvi', 'pr', 'hfls', 'rsdt', 'ps', 'tasmax', 'prw', 'rlus', 'clt', 'cll', 'ta200', 'prsn', 'sfcWindmax', 'snm', 'ua500', 'va850', 'rsds', 'tauu', 'uas', 'clh', 'ua850', 'ua200', 'tas', 'rsut', 'vas', 'snc', 'clm', 'psl', 'hfss', 'sfcWind', 'va500', 'hus850', 'rsus', 'ta500', 'ts', 'clivi', 'hurs', 'rlds', 'prhmax', 'mrso', 'tasmin', 'tauv', 'va200', 'prc', 'rlut', 'evspsbl', 'ta850', 'huss', 'sic', 'clwvi', 'pr', 'hfls', 'rsdt', 'ps', 'tasmax', 'prw', 'rlus', 'clt', 'cll', 'ta200', 'prsn', 'sfcWindmax', 'snm', 'ua500', 'mrro', 'mrros']</t>
+          <t>['va850', 'rsds', 'tauu', 'uas', 'clh', 'ua850', 'ua200', 'tas', 'rsut', 'vas', 'snc', 'clm', 'psl', 'hfss', 'sfcWind', 'va500', 'hus850', 'rsus', 'ta500', 'ts', 'clivi', 'hurs', 'rlds', 'prhmax', 'mrso', 'tasmin', 'tauv', 'va200', 'prc', 'rlut', 'evspsbl', 'ta850', 'huss', 'sic', 'clwvi', 'pr', 'hfls', 'rsdt', 'ps', 'tasmax', 'prw', 'rlus', 'clt', 'cll', 'ta200', 'prsn', 'sfcWindmax', 'snm', 'ua500', 'mrro', 'mrros', 'va850', 'rsds', 'tauu', 'uas', 'clh', 'ua850', 'ua200', 'tas', 'rsut', 'vas', 'snc', 'clm', 'psl', 'hfss', 'sfcWind', 'va500', 'hus850', 'rsus', 'ta500', 'ts', 'clivi', 'hurs', 'rlds', 'prhmax', 'mrso', 'tasmin', 'tauv', 'va200', 'prc', 'rlut', 'evspsbl', 'ta850', 'huss', 'sic', 'clwvi', 'pr', 'hfls', 'rsdt', 'ps', 'tasmax', 'prw', 'rlus', 'clt', 'cll', 'ta200', 'prsn', 'sfcWindmax', 'snm', 'ua500', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19705,7 +19705,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros']</t>
+          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>['prsn', 'rsds', 'tasmin', 'evspsbl', 'sic', 'tauv', 'ps', 'tasmax', 'ta850', 'hurs', 'pr', 'ua500', 'prhmax', 'psl', 'ta500', 'va850', 'hfls', 'rsdt', 'hfss', 'rsus', 'clt', 'cll', 'clwvi', 'rsut', 'clh', 'vas', 'mrso', 'ta200', 'rlut', 'sfcWindmax', 'snc', 'uas', 'va200', 'clm', 'hus850', 'prc', 'ua850', 'snm', 'ts', 'va500', 'rlus', 'huss', 'tas', 'tauu', 'sfcWind', 'clivi', 'rlds', 'prw', 'ua200', 'prsn', 'rsds', 'tasmin', 'evspsbl', 'sic', 'tauv', 'ps', 'tasmax', 'ta850', 'hurs', 'pr', 'ua500', 'prhmax', 'psl', 'ta500', 'va850', 'hfls', 'rsdt', 'hfss', 'rsus', 'clt', 'cll', 'clwvi', 'rsut', 'clh', 'vas', 'mrso', 'ta200', 'rlut', 'sfcWindmax', 'snc', 'uas', 'va200', 'clm', 'hus850', 'prc', 'ua850', 'snm', 'ts', 'va500', 'rlus', 'huss', 'tas', 'tauu', 'sfcWind', 'clivi', 'rlds', 'prw', 'ua200', 'mrros', 'mrro']</t>
+          <t>['prsn', 'rsds', 'tasmin', 'evspsbl', 'sic', 'tauv', 'ps', 'tasmax', 'ta850', 'hurs', 'pr', 'ua500', 'prhmax', 'psl', 'ta500', 'va850', 'hfls', 'rsdt', 'hfss', 'rsus', 'clt', 'cll', 'clwvi', 'rsut', 'clh', 'vas', 'mrso', 'ta200', 'rlut', 'sfcWindmax', 'snc', 'uas', 'va200', 'clm', 'hus850', 'prc', 'ua850', 'snm', 'ts', 'va500', 'rlus', 'huss', 'tas', 'tauu', 'sfcWind', 'clivi', 'rlds', 'prw', 'ua200', 'mrros', 'mrro', 'prsn', 'rsds', 'tasmin', 'evspsbl', 'sic', 'tauv', 'ps', 'tasmax', 'ta850', 'hurs', 'pr', 'ua500', 'prhmax', 'psl', 'ta500', 'va850', 'hfls', 'rsdt', 'hfss', 'rsus', 'clt', 'cll', 'clwvi', 'rsut', 'clh', 'vas', 'mrso', 'ta200', 'rlut', 'sfcWindmax', 'snc', 'uas', 'va200', 'clm', 'hus850', 'prc', 'ua850', 'snm', 'ts', 'va500', 'rlus', 'huss', 'tas', 'tauu', 'sfcWind', 'clivi', 'rlds', 'prw', 'ua200', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro']</t>
+          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20501,7 +20501,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt']</t>
+          <t>['rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt']</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
+          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas', 'hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>['prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'hus850', 'huss', 'mrro', 'rsds', 'rsdt', 'rsus', 'rsut', 'tasmin', 'tauu', 'tauv', 'ts', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'zg200', 'zg500', 'va850', 'vas', 'wsgsmax', 'ta850', 'tas', 'tasmax', 'snw', 'ta200', 'ta500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850']</t>
+          <t>['prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'hus850', 'huss', 'mrro', 'rsds', 'rsdt', 'rsus', 'rsut', 'tasmin', 'tauu', 'tauv', 'ts', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'zg200', 'zg500', 'va850', 'vas', 'wsgsmax', 'ta850', 'tas', 'tasmax', 'snw', 'ta200', 'ta500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'hus850', 'huss', 'mrro', 'rsds', 'rsdt', 'rsus', 'rsut', 'tasmin', 'tauu', 'tauv', 'ts', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'zg200', 'zg500', 'va850', 'vas', 'wsgsmax', 'ta850', 'tas', 'tasmax', 'snw', 'ta200', 'ta500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -20665,7 +20665,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>['clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'vas', 'zg200', 'zg500', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850']</t>
+          <t>['clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'vas', 'zg200', 'zg500', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'vas', 'zg200', 'zg500', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'clt', 'evspsbl']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>['hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr']</t>
+          <t>['hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
+          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas', 'hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20837,7 +20837,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>['rsut', 'sfcWind', 'sfcWindmax', 'sic', 'tasmin', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zg500', 'snm', 'snw', 'ta200', 'ta500', 'va200', 'va500', 'va850', 'vas', 'ua200', 'ua500', 'ua850', 'uas', 'rsds', 'rsdt', 'rsus', 'ta850', 'tas', 'tasmax', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'hus850', 'huss', 'mrro']</t>
+          <t>['rsut', 'sfcWind', 'sfcWindmax', 'sic', 'tasmin', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zg500', 'snm', 'snw', 'ta200', 'ta500', 'va200', 'va500', 'va850', 'vas', 'ua200', 'ua500', 'ua850', 'uas', 'rsds', 'rsdt', 'rsus', 'ta850', 'tas', 'tasmax', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'hus850', 'huss', 'mrro', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'tasmin', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zg500', 'snm', 'snw', 'ta200', 'ta500', 'va200', 'va500', 'va850', 'vas', 'ua200', 'ua500', 'ua850', 'uas', 'rsds', 'rsdt', 'rsus', 'ta850', 'tas', 'tasmax', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'hus850', 'huss', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>['evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'va850', 'vas', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
+          <t>['evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'va850', 'vas', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'va850', 'vas', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>['va850', 'vas', 'zg200', 'zg500', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt']</t>
+          <t>['va850', 'vas', 'zg200', 'zg500', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt', 'va850', 'vas', 'zg200', 'zg500', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>['ua850', 'rsut', 'snw', 'va500', 'wsgsmax', 'rlds', 'rlus', 'prc', 'ta850', 'huss', 'vas', 'rsus', 'rlut', 'ta500', 'mrro', 'va850', 'clt', 'rsdt', 'mrso', 'rsds', 'psl', 'uas', 'prsn', 'hfss', 'hfls', 'zg500', 'sfcWindmax', 'hus850', 'ta200', 'ua500', 'evspsbl', 'ps', 'ts', 'ua850', 'rsut', 'snw', 'va500', 'wsgsmax', 'rlds', 'rlus', 'prc', 'ta850', 'huss', 'vas', 'rsus', 'rlut', 'ta500', 'mrro', 'va850', 'clt', 'rsdt', 'mrso', 'rsds', 'psl', 'uas', 'prsn', 'hfss', 'hfls', 'zg500', 'sfcWindmax', 'hus850', 'ta200', 'ua500', 'evspsbl', 'ps', 'ts', 'tasmax', 'tasmin', 'tas', 'sfcWind', 'pr']</t>
+          <t>['ua850', 'rsut', 'snw', 'va500', 'wsgsmax', 'rlds', 'rlus', 'prc', 'ta850', 'huss', 'vas', 'rsus', 'rlut', 'ta500', 'mrro', 'va850', 'clt', 'rsdt', 'mrso', 'rsds', 'psl', 'uas', 'prsn', 'hfss', 'hfls', 'zg500', 'sfcWindmax', 'hus850', 'ta200', 'ua500', 'evspsbl', 'ps', 'ts', 'tasmax', 'tasmin', 'tas', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>['rsut', 'clt', 'vas', 'pr', 'ta500', 'mrso', 'sfcWind', 'rsus', 'rlut', 'hfls', 'mrro', 'ua850', 'rsds', 'zg500', 'huss', 'psl', 'ta200', 'snw', 'uas', 'rlds', 'tasmin', 'tasmax', 'tas', 'rlus', 'evspsbl', 'va850', 'hfss', 'rsdt', 'hus850', 'va500', 'ta850', 'ua500', 'sfcWindmax', 'rsut', 'clt', 'vas', 'pr', 'ta500', 'mrso', 'sfcWind', 'rsus', 'rlut', 'hfls', 'mrro', 'ua850', 'rsds', 'zg500', 'huss', 'psl', 'ta200', 'snw', 'uas', 'rlds', 'tasmin', 'tasmax', 'tas', 'rlus', 'evspsbl', 'va850', 'hfss', 'rsdt', 'hus850', 'va500', 'ta850', 'ua500', 'sfcWindmax']</t>
+          <t>['rsut', 'clt', 'vas', 'pr', 'ta500', 'mrso', 'sfcWind', 'rsus', 'rlut', 'hfls', 'mrro', 'ua850', 'rsds', 'zg500', 'huss', 'psl', 'ta200', 'snw', 'uas', 'rlds', 'tasmin', 'tasmax', 'tas', 'rlus', 'evspsbl', 'va850', 'hfss', 'rsdt', 'hus850', 'va500', 'ta850', 'ua500', 'sfcWindmax']</t>
         </is>
       </c>
     </row>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>['rlus', 'huss', 'ua850', 'rsus', 'sfcWind', 'tas', 'zg500', 'mrro', 'pr', 'rsdt', 'rsut', 'psl', 'uas', 'tasmax', 'tasmin', 'evspsbl', 'snw', 'vas', 'ta850', 'ta500', 'ua500', 'hfss', 'hfls', 'rsds', 'va500', 'clt', 'rlds', 'rlut', 'va850', 'ta200', 'sfcWindmax', 'mrso', 'hus850', 'rlus', 'huss', 'ua850', 'rsus', 'sfcWind', 'tas', 'zg500', 'mrro', 'pr', 'rsdt', 'rsut', 'psl', 'uas', 'tasmax', 'tasmin', 'evspsbl', 'snw', 'vas', 'ta850', 'ta500', 'ua500', 'hfss', 'hfls', 'rsds', 'va500', 'clt', 'rlds', 'rlut', 'va850', 'ta200', 'sfcWindmax', 'mrso', 'hus850']</t>
+          <t>['rlus', 'huss', 'ua850', 'rsus', 'sfcWind', 'tas', 'zg500', 'mrro', 'pr', 'rsdt', 'rsut', 'psl', 'uas', 'tasmax', 'tasmin', 'evspsbl', 'snw', 'vas', 'ta850', 'ta500', 'ua500', 'hfss', 'hfls', 'rsds', 'va500', 'clt', 'rlds', 'rlut', 'va850', 'ta200', 'sfcWindmax', 'mrso', 'hus850']</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>['ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'pr', 'tasmax', 'tas', 'tasmin', 'sfcWind']</t>
+          <t>['ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'pr', 'tasmax', 'tas', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>['ua850', 'ua500', 'rsdt', 'rlut', 'tasmax', 'hfls', 'zg500', 'mrso', 'psl', 'rlus', 'evspsbl', 'snw', 'sfcWindmax', 'hus850', 'uas', 'rlds', 'va850', 'vas', 'rsus', 'ta500', 'huss', 'clt', 'tas', 'sfcWind', 'ta200', 'hfss', 'va500', 'rsds', 'rsut', 'tasmin', 'ta850', 'mrro', 'pr', 'ua850', 'ua500', 'rsdt', 'rlut', 'tasmax', 'hfls', 'zg500', 'mrso', 'psl', 'rlus', 'evspsbl', 'snw', 'sfcWindmax', 'hus850', 'uas', 'rlds', 'va850', 'vas', 'rsus', 'ta500', 'huss', 'clt', 'tas', 'sfcWind', 'ta200', 'hfss', 'va500', 'rsds', 'rsut', 'tasmin', 'ta850', 'mrro', 'pr']</t>
+          <t>['ua850', 'ua500', 'rsdt', 'rlut', 'tasmax', 'hfls', 'zg500', 'mrso', 'psl', 'rlus', 'evspsbl', 'snw', 'sfcWindmax', 'hus850', 'uas', 'rlds', 'va850', 'vas', 'rsus', 'ta500', 'huss', 'clt', 'tas', 'sfcWind', 'ta200', 'hfss', 'va500', 'rsds', 'rsut', 'tasmin', 'ta850', 'mrro', 'pr', 'ta850', 'mrro', 'pr']</t>
         </is>
       </c>
     </row>
@@ -21221,7 +21221,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>['ua850', 'rsdt', 'hfss', 'rlds', 'hus850', 'pr', 'va850', 'clt', 'ta200', 'hfls', 'sfcWindmax', 'vas', 'ta850', 'psl', 'evspsbl', 'rsut', 'rsus', 'rlus', 'uas', 'sfcWind', 'tasmax', 'mrso', 'tasmin', 'ua500', 'zg500', 'huss', 'snw', 'rlut', 'rsds', 'va500', 'mrro', 'tas', 'ta500', 'ua850', 'rsdt', 'hfss', 'rlds', 'hus850', 'pr', 'va850', 'clt', 'ta200', 'hfls', 'sfcWindmax', 'vas', 'ta850', 'psl', 'evspsbl', 'rsut', 'rsus', 'rlus', 'uas', 'sfcWind', 'tasmax', 'mrso', 'tasmin', 'ua500', 'zg500', 'huss', 'snw', 'rlut', 'rsds', 'va500', 'mrro', 'tas', 'ta500']</t>
+          <t>['ua850', 'rsdt', 'hfss', 'rlds', 'hus850', 'pr', 'va850', 'clt', 'ta200', 'hfls', 'sfcWindmax', 'vas', 'ta850', 'psl', 'evspsbl', 'rsut', 'rsus', 'rlus', 'uas', 'sfcWind', 'tasmax', 'mrso', 'tasmin', 'ua500', 'zg500', 'huss', 'snw', 'rlut', 'rsds', 'va500', 'mrro', 'tas', 'ta500', 'rsds', 'va500', 'mrro', 'tas', 'ta500']</t>
         </is>
       </c>
     </row>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21537,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>['tasmax', 'ua850', 'ts', 'va850', 'ta850', 'psl', 'ta500', 'rlus', 'snw', 'wsgsmax', 'sfcWindmax', 'tasmin', 'tas', 'hfls', 'rlut', 'ps', 'prsn', 'rlds', 'prc', 'vas', 'rsus', 'uas', 'rsut', 'rsds', 'ta200', 'ua500', 'hfss', 'huss', 'mrro', 'va500', 'sfcWind', 'mrso', 'hus850', 'clt', 'pr', 'zg500', 'evspsbl', 'rsdt', 'tasmax', 'ua850', 'ts', 'va850', 'ta850', 'psl', 'ta500', 'rlus', 'snw', 'wsgsmax', 'sfcWindmax', 'tasmin', 'tas', 'hfls', 'rlut', 'ps', 'prsn', 'rlds', 'prc', 'vas', 'rsus', 'uas', 'rsut', 'rsds', 'ta200', 'ua500', 'hfss', 'huss', 'mrro', 'va500', 'sfcWind', 'mrso', 'hus850', 'clt', 'pr', 'zg500', 'evspsbl', 'rsdt']</t>
+          <t>['tasmax', 'ua850', 'ts', 'va850', 'ta850', 'psl', 'ta500', 'rlus', 'snw', 'wsgsmax', 'sfcWindmax', 'tasmin', 'tas', 'hfls', 'rlut', 'ps', 'prsn', 'rlds', 'prc', 'vas', 'rsus', 'uas', 'rsut', 'rsds', 'ta200', 'ua500', 'hfss', 'huss', 'mrro', 'va500', 'sfcWind', 'mrso', 'hus850', 'clt', 'pr', 'zg500', 'evspsbl', 'rsdt', 'clt', 'pr', 'zg500', 'evspsbl', 'rsdt']</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>['hfls', 'sfcWind', 'mrso', 'rsus', 'vas', 'pr', 'rlus', 'rsds', 'sfcWindmax', 'va500', 'rlds', 'ua850', 'ta850', 'clt', 'psl', 'ta200', 'ua500', 'snw', 'hus850', 'rsdt', 'tas', 'uas', 'tasmin', 'tasmax', 'evspsbl', 'ta500', 'zg500', 'va850', 'huss', 'rsut', 'mrro', 'rlut', 'hfss', 'hfls', 'sfcWind', 'mrso', 'rsus', 'vas', 'pr', 'rlus', 'rsds', 'sfcWindmax', 'va500', 'rlds', 'ua850', 'ta850', 'clt', 'psl', 'ta200', 'ua500', 'snw', 'hus850', 'rsdt', 'tas', 'uas', 'tasmin', 'tasmax', 'evspsbl', 'ta500', 'zg500', 'va850', 'huss', 'rsut', 'mrro', 'rlut', 'hfss']</t>
+          <t>['hfls', 'sfcWind', 'mrso', 'rsus', 'vas', 'pr', 'rlus', 'rsds', 'sfcWindmax', 'va500', 'rlds', 'ua850', 'ta850', 'clt', 'psl', 'ta200', 'ua500', 'snw', 'hus850', 'rsdt', 'tas', 'uas', 'tasmin', 'tasmax', 'evspsbl', 'ta500', 'zg500', 'va850', 'huss', 'rsut', 'mrro', 'rlut', 'hfss', 'huss', 'rsut', 'mrro', 'rlut', 'hfss']</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21601,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>['snw', 'rsus', 'mrro', 'hus850', 'ta500', 'va500', 'hfls', 'sfcWindmax', 'rlut', 'ta850', 'rsds', 'rlus', 'uas', 'hfss', 'tas', 'rsdt', 'mrso', 'huss', 'sfcWind', 'evspsbl', 'psl', 'zg500', 'ua500', 'ta200', 'clt', 'tasmax', 'tasmin', 'pr', 'rlds', 'vas', 'va850', 'rsut', 'ua850', 'snw', 'rsus', 'mrro', 'hus850', 'ta500', 'va500', 'hfls', 'sfcWindmax', 'rlut', 'ta850', 'rsds', 'rlus', 'uas', 'hfss', 'tas', 'rsdt', 'mrso', 'huss', 'sfcWind', 'evspsbl', 'psl', 'zg500', 'ua500', 'ta200', 'clt', 'tasmax', 'tasmin', 'pr', 'rlds', 'vas', 'va850', 'rsut', 'ua850']</t>
+          <t>['snw', 'rsus', 'mrro', 'hus850', 'ta500', 'va500', 'hfls', 'sfcWindmax', 'rlut', 'ta850', 'rsds', 'rlus', 'uas', 'hfss', 'tas', 'rsdt', 'mrso', 'huss', 'sfcWind', 'evspsbl', 'psl', 'zg500', 'ua500', 'ta200', 'clt', 'tasmax', 'tasmin', 'pr', 'rlds', 'vas', 'va850', 'rsut', 'ua850', 'tasmin', 'pr', 'rlds', 'vas', 'va850', 'rsut', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -21641,7 +21641,7 @@
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -21677,7 +21677,7 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>['mrro', 'hus850', 'mrso', 'hfls', 'evspsbl', 'va850', 'tas', 'ta200', 'sfcWindmax', 'sfcWind', 'vas', 'clt', 'rsds', 'prc', 'huss', 'ta500', 'psl', 'rsus', 'rsdt', 'rsut', 'ts', 'rlus', 'tasmin', 'wsgsmax', 'rlds', 'uas', 'ua500', 'ta850', 'rlut', 'snw', 'va500', 'pr', 'tasmax', 'ps', 'hfss', 'zg500', 'prsn', 'ua850', 'mrro', 'hus850', 'mrso', 'hfls', 'evspsbl', 'va850', 'tas', 'ta200', 'sfcWindmax', 'sfcWind', 'vas', 'clt', 'rsds', 'prc', 'huss', 'ta500', 'psl', 'rsus', 'rsdt', 'rsut', 'ts', 'rlus', 'tasmin', 'wsgsmax', 'rlds', 'uas', 'ua500', 'ta850', 'rlut', 'snw', 'va500', 'pr', 'tasmax', 'ps', 'hfss', 'zg500', 'prsn', 'ua850']</t>
+          <t>['mrro', 'hus850', 'mrso', 'hfls', 'evspsbl', 'va850', 'tas', 'ta200', 'sfcWindmax', 'sfcWind', 'vas', 'clt', 'rsds', 'prc', 'huss', 'ta500', 'psl', 'rsus', 'rsdt', 'rsut', 'ts', 'rlus', 'tasmin', 'wsgsmax', 'rlds', 'uas', 'ua500', 'ta850', 'rlut', 'snw', 'va500', 'pr', 'tasmax', 'ps', 'hfss', 'zg500', 'prsn', 'ua850', 'ps', 'hfss', 'zg500', 'prsn', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -21709,7 +21709,7 @@
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>['tas', 'rlds', 'evspsbl', 'huss', 'hfss', 'pr', 'hus850', 'rlus', 'rsus', 'uas', 'va850', 'ta500', 'ta850', 'sfcWind', 'mrro', 'ua500', 'rsdt', 'ua850', 'psl', 'sfcWindmax', 'rlut', 'tasmax', 'mrso', 'ta200', 'snw', 'va500', 'rsds', 'tasmin', 'zg500', 'rsut', 'vas', 'hfls', 'clt', 'tas', 'rlds', 'evspsbl', 'huss', 'hfss', 'pr', 'hus850', 'rlus', 'rsus', 'uas', 'va850', 'ta500', 'ta850', 'sfcWind', 'mrro', 'ua500', 'rsdt', 'ua850', 'psl', 'sfcWindmax', 'rlut', 'tasmax', 'mrso', 'ta200', 'snw', 'va500', 'rsds', 'tasmin', 'zg500', 'rsut', 'vas', 'hfls', 'clt']</t>
+          <t>['tas', 'rlds', 'evspsbl', 'huss', 'hfss', 'pr', 'hus850', 'rlus', 'rsus', 'uas', 'va850', 'ta500', 'ta850', 'sfcWind', 'mrro', 'ua500', 'rsdt', 'ua850', 'psl', 'sfcWindmax', 'rlut', 'tasmax', 'mrso', 'ta200', 'snw', 'va500', 'rsds', 'tasmin', 'zg500', 'rsut', 'vas', 'hfls', 'clt', 'zg500', 'rsut', 'vas', 'hfls', 'clt']</t>
         </is>
       </c>
     </row>
@@ -21741,7 +21741,7 @@
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>['hus850', 'tasmax', 'rlds', 'va850', 'tasmin', 'uas', 'zg500', 'rsds', 'evspsbl', 'tas', 'rsdt', 'rlut', 'pr', 'rsus', 'rsut', 'huss', 'vas', 'snw', 'sfcWindmax', 'sfcWind', 'ta850', 'mrso', 'hfls', 'psl', 'ta200', 'va500', 'rlus', 'ta500', 'clt', 'ua850', 'hfss', 'mrro', 'ua500', 'hus850', 'tasmax', 'rlds', 'va850', 'tasmin', 'uas', 'zg500', 'rsds', 'evspsbl', 'tas', 'rsdt', 'rlut', 'pr', 'rsus', 'rsut', 'huss', 'vas', 'snw', 'sfcWindmax', 'sfcWind', 'ta850', 'mrso', 'hfls', 'psl', 'ta200', 'va500', 'rlus', 'ta500', 'clt', 'ua850', 'hfss', 'mrro', 'ua500']</t>
+          <t>['hus850', 'tasmax', 'rlds', 'va850', 'tasmin', 'uas', 'zg500', 'rsds', 'evspsbl', 'tas', 'rsdt', 'rlut', 'pr', 'rsus', 'rsut', 'huss', 'vas', 'snw', 'sfcWindmax', 'sfcWind', 'ta850', 'mrso', 'hfls', 'psl', 'ta200', 'va500', 'rlus', 'ta500', 'clt', 'ua850', 'hfss', 'mrro', 'ua500', 'hfss', 'mrro', 'ua500']</t>
         </is>
       </c>
     </row>
@@ -22021,7 +22021,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'tas', 'ps', 'pr']</t>
+          <t>['huss', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'tas', 'ps', 'pr', 'huss', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'tas', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'uas', 'tas', 'psl', 'ps', 'pr', 'huss', 'hurs', 'clt', 'vas']</t>
+          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'uas', 'tas', 'psl', 'ps', 'pr', 'huss', 'hurs', 'clt', 'vas', 'rsds', 'rlds', 'rsus', 'sfcWind', 'uas', 'tas', 'psl', 'ps', 'pr', 'huss', 'hurs', 'clt', 'vas']</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -22153,7 +22153,7 @@
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>['zg500', 'tasmax', 'tasmin', 'tauu', 'vas', 'wsgsmax', 'zg200', 'sfcWind', 'sfcWindmax', 'sic', 'tauv', 'ts', 'ua200', 'snm', 'snw', 'ta200', 'ua500', 'ua850', 'uas', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'hfls', 'hfss', 'hurs', 'hus850', 'mrso', 'pr', 'prc', 'prsn', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'clt', 'evspsbl', 'ps', 'psl', 'rlds', 'huss', 'mrro', 'mrros']</t>
+          <t>['zg500', 'tasmax', 'tasmin', 'tauu', 'vas', 'wsgsmax', 'zg200', 'sfcWind', 'sfcWindmax', 'sic', 'tauv', 'ts', 'ua200', 'snm', 'snw', 'ta200', 'ua500', 'ua850', 'uas', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'hfls', 'hfss', 'hurs', 'hus850', 'mrso', 'pr', 'prc', 'prsn', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'clt', 'evspsbl', 'ps', 'psl', 'rlds', 'huss', 'mrro', 'mrros', 'zg500', 'tasmax', 'tasmin', 'tauu', 'vas', 'wsgsmax', 'zg200', 'sfcWind', 'sfcWindmax', 'sic', 'tauv', 'ts', 'ua200', 'snm', 'snw', 'ta200', 'ua500', 'ua850', 'uas', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'hfls', 'hfss', 'hurs', 'hus850', 'mrso', 'pr', 'prc', 'prsn', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'clt', 'evspsbl', 'ps', 'psl', 'rlds', 'huss', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200']</t>
+          <t>['ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>['mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros']</t>
+          <t>['mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>['mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
+          <t>['mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'hus850', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22329,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>['snw', 'rlut', 'rlds', 'rsds', 'mrro', 'pr', 'sfcWind', 'ua500', 'tasmax', 'rlus', 'tasmin', 'ta500', 'ua850', 'huss', 'tas', 'va500', 'ta200', 'rsdt', 'hus850', 'psl', 'hfls', 'ta850', 'hfss', 'va850', 'sfcWindmax', 'evspsbl', 'mrso', 'zg500', 'uas', 'vas', 'clt', 'rsus', 'rsut', 'snw', 'rlut', 'rlds', 'rsds', 'mrro', 'pr', 'sfcWind', 'ua500', 'tasmax', 'rlus', 'tasmin', 'ta500', 'ua850', 'huss', 'tas', 'va500', 'ta200', 'rsdt', 'hus850', 'psl', 'hfls', 'ta850', 'hfss', 'va850', 'sfcWindmax', 'evspsbl', 'mrso', 'zg500', 'uas', 'vas', 'clt', 'rsus', 'rsut']</t>
+          <t>['snw', 'rlut', 'rlds', 'rsds', 'mrro', 'pr', 'sfcWind', 'ua500', 'tasmax', 'rlus', 'tasmin', 'ta500', 'ua850', 'huss', 'tas', 'va500', 'ta200', 'rsdt', 'hus850', 'psl', 'hfls', 'ta850', 'hfss', 'va850', 'sfcWindmax', 'evspsbl', 'mrso', 'zg500', 'uas', 'vas', 'clt', 'rsus', 'rsut', 'vas', 'clt', 'rsus', 'rsut']</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>['tasmax', 'tasmin', 'ua850', 'sfcWind', 'pr', 'rsus', 'va500', 'rlus', 'ta200', 'rlut', 'hfls', 'ua500', 'rlds', 'mrso', 'ta850', 'huss', 'mrro', 'hfss', 'rsdt', 'snw', 'vas', 'zg500', 'uas', 'rsut', 'tas', 'evspsbl', 'sfcWindmax', 'hus850', 'clt', 'va850', 'rsds', 'psl', 'ta500', 'tasmax', 'tasmin', 'ua850', 'sfcWind', 'pr', 'rsus', 'va500', 'rlus', 'ta200', 'rlut', 'hfls', 'ua500', 'rlds', 'mrso', 'ta850', 'huss', 'mrro', 'hfss', 'rsdt', 'snw', 'vas', 'zg500', 'uas', 'rsut', 'tas', 'evspsbl', 'sfcWindmax', 'hus850', 'clt', 'va850', 'rsds', 'psl', 'ta500']</t>
+          <t>['tasmax', 'tasmin', 'ua850', 'sfcWind', 'pr', 'rsus', 'va500', 'rlus', 'ta200', 'rlut', 'hfls', 'ua500', 'rlds', 'mrso', 'ta850', 'huss', 'mrro', 'hfss', 'rsdt', 'snw', 'vas', 'zg500', 'uas', 'rsut', 'tas', 'evspsbl', 'sfcWindmax', 'hus850', 'clt', 'va850', 'rsds', 'psl', 'ta500', 'va850', 'rsds', 'psl', 'ta500']</t>
         </is>
       </c>
     </row>
@@ -22441,7 +22441,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>['rlut', 'mrro', 'va500', 'hfss', 'snw', 'ts', 'rlus', 'va850', 'ua850', 'prsn', 'hfls', 'rsut', 'huss', 'vas', 'rsdt', 'ps', 'ta500', 'clt', 'prc', 'ta850', 'rsds', 'ua500', 'hus850', 'sfcWindmax', 'ta200', 'psl', 'mrso', 'evspsbl', 'rsus', 'wsgsmax', 'zg500', 'rlds', 'uas', 'rlut', 'mrro', 'va500', 'hfss', 'snw', 'ts', 'rlus', 'va850', 'ua850', 'prsn', 'hfls', 'rsut', 'huss', 'vas', 'rsdt', 'ps', 'ta500', 'clt', 'prc', 'ta850', 'rsds', 'ua500', 'hus850', 'sfcWindmax', 'ta200', 'psl', 'mrso', 'evspsbl', 'rsus', 'wsgsmax', 'zg500', 'rlds', 'uas', 'tas', 'sfcWind', 'pr', 'tasmin', 'tasmax']</t>
+          <t>['rlut', 'mrro', 'va500', 'hfss', 'snw', 'ts', 'rlus', 'va850', 'ua850', 'prsn', 'hfls', 'rsut', 'huss', 'vas', 'rsdt', 'ps', 'ta500', 'clt', 'prc', 'ta850', 'rsds', 'ua500', 'hus850', 'sfcWindmax', 'ta200', 'psl', 'mrso', 'evspsbl', 'rsus', 'wsgsmax', 'zg500', 'rlds', 'uas', 'zg500', 'rlds', 'uas', 'tas', 'sfcWind', 'pr', 'tasmin', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22473,7 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>['zg500', 'va500', 'rsut', 'mrso', 'rlut', 'va850', 'hfss', 'rsus', 'ta500', 'hus850', 'sfcWind', 'ua850', 'ta850', 'clt', 'rsds', 'psl', 'pr', 'tasmax', 'evspsbl', 'tas', 'rlus', 'sfcWindmax', 'ta200', 'hfls', 'ua500', 'mrro', 'vas', 'rlds', 'uas', 'huss', 'snw', 'tasmin', 'rsdt', 'zg500', 'va500', 'rsut', 'mrso', 'rlut', 'va850', 'hfss', 'rsus', 'ta500', 'hus850', 'sfcWind', 'ua850', 'ta850', 'clt', 'rsds', 'psl', 'pr', 'tasmax', 'evspsbl', 'tas', 'rlus', 'sfcWindmax', 'ta200', 'hfls', 'ua500', 'mrro', 'vas', 'rlds', 'uas', 'huss', 'snw', 'tasmin', 'rsdt']</t>
+          <t>['zg500', 'va500', 'rsut', 'mrso', 'rlut', 'va850', 'hfss', 'rsus', 'ta500', 'hus850', 'sfcWind', 'ua850', 'ta850', 'clt', 'rsds', 'psl', 'pr', 'tasmax', 'evspsbl', 'tas', 'rlus', 'sfcWindmax', 'ta200', 'hfls', 'ua500', 'mrro', 'vas', 'rlds', 'uas', 'huss', 'snw', 'tasmin', 'rsdt', 'huss', 'snw', 'tasmin', 'rsdt']</t>
         </is>
       </c>
     </row>
@@ -22505,7 +22505,7 @@
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>['tasmin', 'va500', 'ua850', 'sfcWindmax', 'evspsbl', 'zg500', 'ta200', 'mrro', 'hus850', 'clt', 'ta500', 'rsut', 'uas', 'rlds', 'ua500', 'tasmax', 'snw', 'va850', 'rsdt', 'hfls', 'sfcWind', 'ta850', 'rlus', 'psl', 'mrso', 'tas', 'hfss', 'rlut', 'rsus', 'huss', 'vas', 'rsds', 'pr', 'tasmin', 'va500', 'ua850', 'sfcWindmax', 'evspsbl', 'zg500', 'ta200', 'mrro', 'hus850', 'clt', 'ta500', 'rsut', 'uas', 'rlds', 'ua500', 'tasmax', 'snw', 'va850', 'rsdt', 'hfls', 'sfcWind', 'ta850', 'rlus', 'psl', 'mrso', 'tas', 'hfss', 'rlut', 'rsus', 'huss', 'vas', 'rsds', 'pr']</t>
+          <t>['tasmin', 'va500', 'ua850', 'sfcWindmax', 'evspsbl', 'zg500', 'ta200', 'mrro', 'hus850', 'clt', 'ta500', 'rsut', 'uas', 'rlds', 'ua500', 'tasmax', 'snw', 'va850', 'rsdt', 'hfls', 'sfcWind', 'ta850', 'rlus', 'psl', 'mrso', 'tas', 'hfss', 'rlut', 'rsus', 'huss', 'vas', 'rsds', 'pr', 'rsus', 'huss', 'vas', 'rsds', 'pr']</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -23297,7 +23297,7 @@
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>['pr', 'rsus', 'hurs', 'psl', 'rlds', 'tas', 'rsds', 'sfcWind', 'huss', 'ps', 'pr', 'rsus', 'hurs', 'psl', 'rlds', 'tas', 'rsds', 'sfcWind', 'huss', 'ps']</t>
+          <t>['pr', 'rsus', 'hurs', 'psl', 'rlds', 'tas', 'rsds', 'sfcWind', 'huss', 'ps']</t>
         </is>
       </c>
     </row>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23361,7 @@
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>['ua850', 'psl', 'uas', 'rsds', 'rsdt', 'huss', 'zg500', 'rlus', 'snw', 'clt', 'hus850', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'hurs', 'rlds', 'prsn', 'vas', 'ta200', 'ua500', 'hfss', 'ta500', 'wsgsmax', 'rsus', 'rlut', 'prc', 'ta850', 'mrro', 'ps', 'va500', 'ts', 'evspsbl', 'va850', 'ua850', 'psl', 'uas', 'rsds', 'rsdt', 'huss', 'zg500', 'rlus', 'snw', 'clt', 'hus850', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'hurs', 'rlds', 'prsn', 'vas', 'ta200', 'ua500', 'hfss', 'ta500', 'wsgsmax', 'rsus', 'rlut', 'prc', 'ta850', 'mrro', 'ps', 'va500', 'ts', 'evspsbl', 'va850', 'pr', 'tasmin', 'tasmax', 'sfcWind', 'tas']</t>
+          <t>['ua850', 'psl', 'uas', 'rsds', 'rsdt', 'huss', 'zg500', 'rlus', 'snw', 'clt', 'hus850', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'hurs', 'rlds', 'prsn', 'vas', 'ta200', 'ua500', 'hfss', 'ta500', 'wsgsmax', 'rsus', 'rlut', 'prc', 'ta850', 'mrro', 'ps', 'va500', 'ts', 'evspsbl', 'va850', 'pr', 'tasmin', 'tasmax', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -23393,7 +23393,7 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>['sfcWind', 'hus850', 'mrro', 'hfls', 'tas', 'ta500', 'rsus', 'tasmin', 'zg500', 'tasmax', 'psl', 'vas', 'va500', 'rsds', 'rlds', 'rsdt', 'evspsbl', 'rlut', 'rlus', 'snw', 'pr', 'uas', 'va850', 'clt', 'sfcWindmax', 'hfss', 'rsut', 'mrso', 'huss', 'ua850', 'hurs', 'ta200', 'ta850', 'ua500', 'sfcWind', 'hus850', 'mrro', 'hfls', 'tas', 'ta500', 'rsus', 'tasmin', 'zg500', 'tasmax', 'psl', 'vas', 'va500', 'rsds', 'rlds', 'rsdt', 'evspsbl', 'rlut', 'rlus', 'snw', 'pr', 'uas', 'va850', 'clt', 'sfcWindmax', 'hfss', 'rsut', 'mrso', 'huss', 'ua850', 'hurs', 'ta200', 'ta850', 'ua500']</t>
+          <t>['sfcWind', 'hus850', 'mrro', 'hfls', 'tas', 'ta500', 'rsus', 'tasmin', 'zg500', 'tasmax', 'psl', 'vas', 'va500', 'rsds', 'rlds', 'rsdt', 'evspsbl', 'rlut', 'rlus', 'snw', 'pr', 'uas', 'va850', 'clt', 'sfcWindmax', 'hfss', 'rsut', 'mrso', 'huss', 'ua850', 'hurs', 'ta200', 'ta850', 'ua500']</t>
         </is>
       </c>
     </row>
@@ -23425,7 +23425,7 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>['mrso', 'sfcWind', 'tasmax', 'hfss', 'rlut', 'zg500', 'tas', 'ua850', 'va850', 'pr', 'rlds', 'tasmin', 'vas', 'clt', 'va500', 'rsds', 'rsdt', 'ta200', 'ta500', 'sfcWindmax', 'rsus', 'rlus', 'hurs', 'uas', 'ua500', 'hfls', 'snw', 'psl', 'hus850', 'rsut', 'evspsbl', 'huss', 'ta850', 'mrro', 'mrso', 'sfcWind', 'tasmax', 'hfss', 'rlut', 'zg500', 'tas', 'ua850', 'va850', 'pr', 'rlds', 'tasmin', 'vas', 'clt', 'va500', 'rsds', 'rsdt', 'ta200', 'ta500', 'sfcWindmax', 'rsus', 'rlus', 'hurs', 'uas', 'ua500', 'hfls', 'snw', 'psl', 'hus850', 'rsut', 'evspsbl', 'huss', 'ta850', 'mrro']</t>
+          <t>['mrso', 'sfcWind', 'tasmax', 'hfss', 'rlut', 'zg500', 'tas', 'ua850', 'va850', 'pr', 'rlds', 'tasmin', 'vas', 'clt', 'va500', 'rsds', 'rsdt', 'ta200', 'ta500', 'sfcWindmax', 'rsus', 'rlus', 'hurs', 'uas', 'ua500', 'hfls', 'snw', 'psl', 'hus850', 'rsut', 'evspsbl', 'huss', 'ta850', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -24145,7 +24145,7 @@
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -24181,7 +24181,7 @@
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>['tasmax', 'mrso', 'uas', 'prsn', 'wsgsmax', 'va850', 'ta850', 'evspsbl', 'tas', 'rsds', 'rsut', 'hfss', 'ta500', 'prc', 'huss', 'ua850', 'sfcWindmax', 'rlus', 'ps', 'ta200', 'snw', 'ts', 'rsus', 'rsdt', 'zg500', 'va500', 'tasmin', 'mrro', 'vas', 'pr', 'ua500', 'psl', 'rlut', 'sfcWind', 'hus850', 'hfls', 'rlds', 'clt', 'tasmax', 'mrso', 'uas', 'prsn', 'wsgsmax', 'va850', 'ta850', 'evspsbl', 'tas', 'rsds', 'rsut', 'hfss', 'ta500', 'prc', 'huss', 'ua850', 'sfcWindmax', 'rlus', 'ps', 'ta200', 'snw', 'ts', 'rsus', 'rsdt', 'zg500', 'va500', 'tasmin', 'mrro', 'vas', 'pr', 'ua500', 'psl', 'rlut', 'sfcWind', 'hus850', 'hfls', 'rlds', 'clt']</t>
+          <t>['tasmax', 'mrso', 'uas', 'prsn', 'wsgsmax', 'va850', 'ta850', 'evspsbl', 'tas', 'rsds', 'rsut', 'hfss', 'ta500', 'prc', 'huss', 'ua850', 'sfcWindmax', 'rlus', 'ps', 'ta200', 'snw', 'ts', 'rsus', 'rsdt', 'zg500', 'va500', 'tasmin', 'mrro', 'vas', 'pr', 'ua500', 'psl', 'rlut', 'sfcWind', 'hus850', 'hfls', 'rlds', 'clt', 'hfls', 'rlds', 'clt']</t>
         </is>
       </c>
     </row>
@@ -24213,7 +24213,7 @@
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>['ta500', 'rlds', 'uas', 'mrro', 'zg500', 'rsut', 'tasmax', 'evspsbl', 'tasmin', 'huss', 'tas', 'va850', 'va500', 'ua500', 'hfss', 'vas', 'pr', 'sfcWindmax', 'mrso', 'rlut', 'rlus', 'hfls', 'snw', 'psl', 'rsds', 'sfcWind', 'hus850', 'ta850', 'rsus', 'rsdt', 'ua850', 'ta200', 'clt', 'ta500', 'rlds', 'uas', 'mrro', 'zg500', 'rsut', 'tasmax', 'evspsbl', 'tasmin', 'huss', 'tas', 'va850', 'va500', 'ua500', 'hfss', 'vas', 'pr', 'sfcWindmax', 'mrso', 'rlut', 'rlus', 'hfls', 'snw', 'psl', 'rsds', 'sfcWind', 'hus850', 'ta850', 'rsus', 'rsdt', 'ua850', 'ta200', 'clt']</t>
+          <t>['ta500', 'rlds', 'uas', 'mrro', 'zg500', 'rsut', 'tasmax', 'evspsbl', 'tasmin', 'huss', 'tas', 'va850', 'va500', 'ua500', 'hfss', 'vas', 'pr', 'sfcWindmax', 'mrso', 'rlut', 'rlus', 'hfls', 'snw', 'psl', 'rsds', 'sfcWind', 'hus850', 'ta850', 'rsus', 'rsdt', 'ua850', 'ta200', 'clt', 'ua850', 'ta200', 'clt']</t>
         </is>
       </c>
     </row>
@@ -24245,7 +24245,7 @@
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>['hfls', 'rlut', 'ua850', 'va500', 'rsus', 'sfcWind', 'snw', 'hfss', 'hus850', 'ua500', 'tasmin', 'zg500', 'rlus', 'rsut', 'va850', 'sfcWindmax', 'huss', 'ta500', 'tas', 'mrro', 'rlds', 'uas', 'mrso', 'vas', 'clt', 'ta850', 'pr', 'tasmax', 'evspsbl', 'psl', 'ta200', 'rsdt', 'rsds', 'hfls', 'rlut', 'ua850', 'va500', 'rsus', 'sfcWind', 'snw', 'hfss', 'hus850', 'ua500', 'tasmin', 'zg500', 'rlus', 'rsut', 'va850', 'sfcWindmax', 'huss', 'ta500', 'tas', 'mrro', 'rlds', 'uas', 'mrso', 'vas', 'clt', 'ta850', 'pr', 'tasmax', 'evspsbl', 'psl', 'ta200', 'rsdt', 'rsds']</t>
+          <t>['hfls', 'rlut', 'ua850', 'va500', 'rsus', 'sfcWind', 'snw', 'hfss', 'hus850', 'ua500', 'tasmin', 'zg500', 'rlus', 'rsut', 'va850', 'sfcWindmax', 'huss', 'ta500', 'tas', 'mrro', 'rlds', 'uas', 'mrso', 'vas', 'clt', 'ta850', 'pr', 'tasmax', 'evspsbl', 'psl', 'ta200', 'rsdt', 'rsds', 'ta200', 'rsdt', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -24321,7 +24321,7 @@
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>['prsn', 'hfls', 'rsds', 'mrso', 'ua500', 'rsdt', 'prc', 'uas', 'sfcWindmax', 'va500', 'ts', 'psl', 'ta850', 'rlds', 'ua850', 'rlut', 'wsgsmax', 'vas', 'rlus', 'tas', 'tasmin', 'ps', 'hus850', 'ta200', 'snw', 'clt', 'mrro', 'evspsbl', 'tasmax', 'zg500', 'ta500', 'va850', 'huss', 'pr', 'rsus', 'hfss', 'rsut', 'sfcWind', 'prsn', 'hfls', 'rsds', 'mrso', 'ua500', 'rsdt', 'prc', 'uas', 'sfcWindmax', 'va500', 'ts', 'psl', 'ta850', 'rlds', 'ua850', 'rlut', 'wsgsmax', 'vas', 'rlus', 'tas', 'tasmin', 'ps', 'hus850', 'ta200', 'snw', 'clt', 'mrro', 'evspsbl', 'tasmax', 'zg500', 'ta500', 'va850', 'huss', 'pr', 'rsus', 'hfss', 'rsut', 'sfcWind']</t>
+          <t>['prsn', 'hfls', 'rsds', 'mrso', 'ua500', 'rsdt', 'prc', 'uas', 'sfcWindmax', 'va500', 'ts', 'psl', 'ta850', 'rlds', 'ua850', 'rlut', 'wsgsmax', 'vas', 'rlus', 'tas', 'tasmin', 'ps', 'hus850', 'ta200', 'snw', 'clt', 'mrro', 'evspsbl', 'tasmax', 'zg500', 'ta500', 'va850', 'huss', 'pr', 'rsus', 'hfss', 'rsut', 'sfcWind', 'hfss', 'rsut', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>['snw', 'rlut', 'huss', 'rlus', 'mrro', 'pr', 'va850', 'ta200', 'rsdt', 'hus850', 'tasmax', 'ua850', 'hfss', 'tasmin', 'rlds', 'mrso', 'uas', 'va500', 'evspsbl', 'tas', 'ua500', 'rsus', 'sfcWind', 'psl', 'rsds', 'hfls', 'zg500', 'vas', 'ta850', 'rsut', 'sfcWindmax', 'clt', 'ta500', 'snw', 'rlut', 'huss', 'rlus', 'mrro', 'pr', 'va850', 'ta200', 'rsdt', 'hus850', 'tasmax', 'ua850', 'hfss', 'tasmin', 'rlds', 'mrso', 'uas', 'va500', 'evspsbl', 'tas', 'ua500', 'rsus', 'sfcWind', 'psl', 'rsds', 'hfls', 'zg500', 'vas', 'ta850', 'rsut', 'sfcWindmax', 'clt', 'ta500']</t>
+          <t>['snw', 'rlut', 'huss', 'rlus', 'mrro', 'pr', 'va850', 'ta200', 'rsdt', 'hus850', 'tasmax', 'ua850', 'hfss', 'tasmin', 'rlds', 'mrso', 'uas', 'va500', 'evspsbl', 'tas', 'ua500', 'rsus', 'sfcWind', 'psl', 'rsds', 'hfls', 'zg500', 'vas', 'ta850', 'rsut', 'sfcWindmax', 'clt', 'ta500', 'clt', 'ta500']</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>['tas', 'vas', 'ua850', 'evspsbl', 'rlus', 'uas', 'hus850', 'rsut', 'psl', 'va500', 'ua500', 'mrso', 'hfls', 'rsdt', 'huss', 'rsus', 'pr', 'tasmin', 'rlut', 'ta850', 'ta200', 'zg500', 'rsds', 'hfss', 'sfcWind', 'snw', 'sfcWindmax', 'ta500', 'va850', 'rlds', 'clt', 'mrro', 'tasmax', 'tas', 'vas', 'ua850', 'evspsbl', 'rlus', 'uas', 'hus850', 'rsut', 'psl', 'va500', 'ua500', 'mrso', 'hfls', 'rsdt', 'huss', 'rsus', 'pr', 'tasmin', 'rlut', 'ta850', 'ta200', 'zg500', 'rsds', 'hfss', 'sfcWind', 'snw', 'sfcWindmax', 'ta500', 'va850', 'rlds', 'clt', 'mrro', 'tasmax']</t>
+          <t>['tas', 'vas', 'ua850', 'evspsbl', 'rlus', 'uas', 'hus850', 'rsut', 'psl', 'va500', 'ua500', 'mrso', 'hfls', 'rsdt', 'huss', 'rsus', 'pr', 'tasmin', 'rlut', 'ta850', 'ta200', 'zg500', 'rsds', 'hfss', 'sfcWind', 'snw', 'sfcWindmax', 'ta500', 'va850', 'rlds', 'clt', 'mrro', 'tasmax', 'ta500', 'va850', 'rlds', 'clt', 'mrro', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25345,7 @@
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25377,7 @@
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25545,7 +25545,7 @@
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>['rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds']</t>
+          <t>['rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25745,7 +25745,7 @@
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>['ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw']</t>
+          <t>['ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw']</t>
         </is>
       </c>
     </row>
@@ -25777,7 +25777,7 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>['snw', 'snc', 'sund', 'snd', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'pr', 'ps', 'clt', 'rlds', 'psl', 'evspsbl', 'rsds']</t>
+          <t>['snw', 'snc', 'sund', 'snd', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'pr', 'ps', 'clt', 'rlds', 'psl', 'evspsbl', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'wsgsmax', 'vas', 'uas', 'sfcWindmax', 'wsgsmax', 'vas', 'uas', 'huss', 'sfcWind', 'tas', 'hurs', 'tasmin', 'tasmax']</t>
+          <t>['sfcWindmax', 'wsgsmax', 'vas', 'uas', 'huss', 'sfcWind', 'tas', 'hurs', 'tasmin', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>['ta850', 'ta200', 'ta500', 'hus850', 'ua500', 'va500', 'va500', 'ua850', 'va850', 'zg500']</t>
+          <t>['ta850', 'ta200', 'ta500', 'hus850', 'ua500', 'va500', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>['mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'snd', 'psl', 'rsds', 'clt', 'rsus', 'pr', 'evspsbl', 'rlds']</t>
+          <t>['mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'snd', 'psl', 'rsds', 'clt', 'rsus', 'pr', 'evspsbl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>['uas', 'sfcWindmax', 'vas', 'sfcWindmax', 'vas', 'huss', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'hurs']</t>
+          <t>['uas', 'sfcWindmax', 'vas', 'huss', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'ta200', 'ta500', 'ta850', 'ua850', 'zg500', 'va850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26157,7 +26157,7 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'sund', 'snc', 'snd', 'hfss', 'hfls', 'mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'sund', 'snc', 'snd', 'clt', 'rlds', 'evspsbl', 'rsus', 'psl', 'pr', 'rsds']</t>
+          <t>['hfss', 'hfls', 'mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'sund', 'snc', 'snd', 'clt', 'rlds', 'evspsbl', 'rsus', 'psl', 'pr', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -26185,7 +26185,7 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'uas', 'vas', 'sfcWindmax', 'uas', 'vas', 'sfcWind', 'tasmin', 'tas', 'tasmax', 'hurs', 'huss']</t>
+          <t>['sfcWindmax', 'uas', 'vas', 'sfcWind', 'tasmin', 'tas', 'tasmax', 'hurs', 'huss']</t>
         </is>
       </c>
     </row>
@@ -26213,7 +26213,7 @@
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'va850', 'zg500']</t>
+          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>['pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss']</t>
+          <t>['pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss']</t>
         </is>
       </c>
     </row>
@@ -26289,7 +26289,7 @@
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>['rlus', 'hfss', 'snw', 'wsgsmax', 'rsut', 'snc', 'mrso', 'snd', 'hfls', 'vas', 'uas', 'prsn', 'ua500', 'rsdt', 'ta200', 'prhmax', 'sund', 'hus850', 'mrro', 'ta850', 'ta500', 'sfcWindmax', 'rlut', 'prc', 'va500', 'ts', 'rlus', 'hfss', 'snw', 'wsgsmax', 'rsut', 'snc', 'mrso', 'snd', 'hfls', 'vas', 'uas', 'prsn', 'ua500', 'rsdt', 'ta200', 'prhmax', 'sund', 'hus850', 'mrro', 'ta850', 'ta500', 'sfcWindmax', 'rlut', 'prc', 'va500', 'ts', 'rlds', 'psl', 'sfcWind', 'evspsbl', 'ps', 'tasmax', 'pr', 'huss', 'clt', 'ua850', 'rsus', 'va850', 'tas', 'rsds', 'hurs', 'zg500', 'tasmin']</t>
+          <t>['rlus', 'hfss', 'snw', 'wsgsmax', 'rsut', 'snc', 'mrso', 'snd', 'hfls', 'vas', 'uas', 'prsn', 'ua500', 'rsdt', 'ta200', 'prhmax', 'sund', 'hus850', 'mrro', 'ta850', 'ta500', 'sfcWindmax', 'rlut', 'prc', 'va500', 'ts', 'rlds', 'psl', 'sfcWind', 'evspsbl', 'ps', 'tasmax', 'pr', 'huss', 'clt', 'ua850', 'rsus', 'va850', 'tas', 'rsds', 'hurs', 'zg500', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -26385,7 +26385,7 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'ua500', 'vas', 'ta500', 'snd', 'mrso', 'hfss', 'rsdt', 'rsut', 'rlus', 'rlut', 'hus850', 'snc', 'uas', 'snw', 'va500', 'ta200', 'sund', 'hfls', 'ta850', 'mrro', 'sfcWindmax', 'ua500', 'vas', 'ta500', 'snd', 'mrso', 'hfss', 'rsdt', 'rsut', 'rlus', 'rlut', 'hus850', 'snc', 'uas', 'snw', 'va500', 'ta200', 'sund', 'hfls', 'ta850', 'mrro', 'va850', 'psl', 'hurs', 'rsus', 'clt', 'ua850', 'zg500', 'tasmin', 'evspsbl', 'pr', 'tasmax', 'sfcWind', 'tas', 'huss', 'rlds', 'rsds']</t>
+          <t>['sfcWindmax', 'ua500', 'vas', 'ta500', 'snd', 'mrso', 'hfss', 'rsdt', 'rsut', 'rlus', 'rlut', 'hus850', 'snc', 'uas', 'snw', 'va500', 'ta200', 'sund', 'hfls', 'ta850', 'mrro', 'va850', 'psl', 'hurs', 'rsus', 'clt', 'ua850', 'zg500', 'tasmin', 'evspsbl', 'pr', 'tasmax', 'sfcWind', 'tas', 'huss', 'rlds', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>['ua500', 'rsut', 'vas', 'uas', 'mrro', 'va500', 'ta850', 'hfls', 'sund', 'ta500', 'ta200', 'sfcWindmax', 'rlus', 'hus850', 'snd', 'hfss', 'mrso', 'snc', 'rsdt', 'rlut', 'snw', 'ua500', 'rsut', 'vas', 'uas', 'mrro', 'va500', 'ta850', 'hfls', 'sund', 'ta500', 'ta200', 'sfcWindmax', 'rlus', 'hus850', 'snd', 'hfss', 'mrso', 'snc', 'rsdt', 'rlut', 'snw', 'rsds', 'sfcWind', 'pr', 'tas', 'ua850', 'rlds', 'tasmin', 'hurs', 'va850', 'rsus', 'clt', 'tasmax', 'psl', 'huss', 'zg500', 'evspsbl']</t>
+          <t>['ua500', 'rsut', 'vas', 'uas', 'mrro', 'va500', 'ta850', 'hfls', 'sund', 'ta500', 'ta200', 'sfcWindmax', 'rlus', 'hus850', 'snd', 'hfss', 'mrso', 'snc', 'rsdt', 'rlut', 'snw', 'rsds', 'sfcWind', 'pr', 'tas', 'ua850', 'rlds', 'tasmin', 'hurs', 'va850', 'rsus', 'clt', 'tasmax', 'psl', 'huss', 'zg500', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -26453,7 +26453,7 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>['huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs']</t>
+          <t>['huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26609,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'vas', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'huss', 'tasmax', 'hurs', 'clt', 'rsus', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'huss', 'tasmax', 'hurs', 'clt', 'rsus', 'psl']</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26669,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>['rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'tasmax', 'huss', 'tasmin', 'tas', 'psl', 'sfcWind', 'evspsbl', 'rlds', 'hurs', 'rsds', 'rsus', 'pr', 'clt']</t>
+          <t>['rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'tasmax', 'huss', 'tasmin', 'tas', 'psl', 'sfcWind', 'evspsbl', 'rlds', 'hurs', 'rsds', 'rsus', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -26697,7 +26697,7 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'va850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -26765,7 +26765,7 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26933,7 +26933,7 @@
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26997,7 +26997,7 @@
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>['snw', 'mrro', 'ua500', 'sund', 'ta850', 'rlut', 'ta500', 'rlus', 'hfls', 'rsdt', 'rsut', 'sfcWindmax', 'prsn', 'wsgsmax', 'snc', 'uas', 'mrso', 'prhmax', 'va500', 'snd', 'hus850', 'ts', 'prc', 'hfss', 'vas', 'ta200', 'snw', 'mrro', 'ua500', 'sund', 'ta850', 'rlut', 'ta500', 'rlus', 'hfls', 'rsdt', 'rsut', 'sfcWindmax', 'prsn', 'wsgsmax', 'snc', 'uas', 'mrso', 'prhmax', 'va500', 'snd', 'hus850', 'ts', 'prc', 'hfss', 'vas', 'ta200', 'rsus', 'zg500', 'ps', 'tasmin', 'tas', 'va850', 'rsds', 'sfcWind', 'evspsbl', 'clt', 'ua850', 'huss', 'psl', 'hurs', 'rlds', 'tasmax', 'pr']</t>
+          <t>['snw', 'mrro', 'ua500', 'sund', 'ta850', 'rlut', 'ta500', 'rlus', 'hfls', 'rsdt', 'rsut', 'sfcWindmax', 'prsn', 'wsgsmax', 'snc', 'uas', 'mrso', 'prhmax', 'va500', 'snd', 'hus850', 'ts', 'prc', 'hfss', 'vas', 'ta200', 'rsus', 'zg500', 'ps', 'tasmin', 'tas', 'va850', 'rsds', 'sfcWind', 'evspsbl', 'clt', 'ua850', 'huss', 'psl', 'hurs', 'rlds', 'tasmax', 'pr']</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -27061,7 +27061,7 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>['ta500', 'sund', 'ta850', 'hfss', 'ua500', 'vas', 'ta200', 'rsut', 'snw', 'uas', 'snc', 'va500', 'rlus', 'mrro', 'snd', 'sfcWindmax', 'rlut', 'rsdt', 'mrso', 'hfls', 'hus850', 'ta500', 'sund', 'ta850', 'hfss', 'ua500', 'vas', 'ta200', 'rsut', 'snw', 'uas', 'snc', 'va500', 'rlus', 'mrro', 'snd', 'sfcWindmax', 'rlut', 'rsdt', 'mrso', 'hfls', 'hus850', 'rsds', 'clt', 'va850', 'zg500', 'sfcWind', 'tas', 'tasmax', 'pr', 'evspsbl', 'rlds', 'psl', 'huss', 'tasmin', 'ua850', 'hurs', 'rsus']</t>
+          <t>['ta500', 'sund', 'ta850', 'hfss', 'ua500', 'vas', 'ta200', 'rsut', 'snw', 'uas', 'snc', 'va500', 'rlus', 'mrro', 'snd', 'sfcWindmax', 'rlut', 'rsdt', 'mrso', 'hfls', 'hus850', 'rsds', 'clt', 'va850', 'zg500', 'sfcWind', 'tas', 'tasmax', 'pr', 'evspsbl', 'rlds', 'psl', 'huss', 'tasmin', 'ua850', 'hurs', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>['mrso', 'ta500', 'rlus', 'uas', 'hfss', 'hfls', 'sund', 'ua500', 'rsdt', 'ta200', 'snc', 'snd', 'vas', 'rlut', 'hus850', 'snw', 'va500', 'sfcWindmax', 'ta850', 'rsut', 'mrro', 'mrso', 'ta500', 'rlus', 'uas', 'hfss', 'hfls', 'sund', 'ua500', 'rsdt', 'ta200', 'snc', 'snd', 'vas', 'rlut', 'hus850', 'snw', 'va500', 'sfcWindmax', 'ta850', 'rsut', 'mrro', 'sfcWind', 'tas', 'rsds', 'huss', 'tasmin', 'va850', 'pr', 'rsus', 'evspsbl', 'psl', 'hurs', 'ua850', 'clt', 'zg500', 'rlds', 'tasmax']</t>
+          <t>['mrso', 'ta500', 'rlus', 'uas', 'hfss', 'hfls', 'sund', 'ua500', 'rsdt', 'ta200', 'snc', 'snd', 'vas', 'rlut', 'hus850', 'snw', 'va500', 'sfcWindmax', 'ta850', 'rsut', 'mrro', 'sfcWind', 'tas', 'rsds', 'huss', 'tasmin', 'va850', 'pr', 'rsus', 'evspsbl', 'psl', 'hurs', 'ua850', 'clt', 'zg500', 'rlds', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -27133,7 +27133,7 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27165,7 +27165,7 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -27197,7 +27197,7 @@
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>['prsn', 'mrro', 'ua500', 'prhmax', 'prc', 'ta500', 'snw', 'wsgsmax', 'va500', 'vas', 'hus850', 'ta850', 'rlus', 'ts', 'uas', 'rlut', 'rsdt', 'snd', 'hfss', 'snc', 'ta200', 'hfls', 'sund', 'sfcWindmax', 'rsut', 'mrso', 'prsn', 'mrro', 'ua500', 'prhmax', 'prc', 'ta500', 'snw', 'wsgsmax', 'va500', 'vas', 'hus850', 'ta850', 'rlus', 'ts', 'uas', 'rlut', 'rsdt', 'snd', 'hfss', 'snc', 'ta200', 'hfls', 'sund', 'sfcWindmax', 'rsut', 'mrso', 'clt', 'tasmin', 'huss', 'pr', 'sfcWind', 'rsds', 'rsus', 'hurs', 'tas', 'ps', 'va850', 'tasmax', 'evspsbl', 'rlds', 'zg500', 'psl', 'ua850']</t>
+          <t>['prsn', 'mrro', 'ua500', 'prhmax', 'prc', 'ta500', 'snw', 'wsgsmax', 'va500', 'vas', 'hus850', 'ta850', 'rlus', 'ts', 'uas', 'rlut', 'rsdt', 'snd', 'hfss', 'snc', 'ta200', 'hfls', 'sund', 'sfcWindmax', 'rsut', 'mrso', 'clt', 'tasmin', 'huss', 'pr', 'sfcWind', 'rsds', 'rsus', 'hurs', 'tas', 'ps', 'va850', 'tasmax', 'evspsbl', 'rlds', 'zg500', 'psl', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -27229,7 +27229,7 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27261,7 +27261,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>['hfls', 'rsdt', 'rlut', 'vas', 'snw', 'rsut', 'sund', 'ta200', 'ta850', 'snd', 'hus850', 'hfss', 'uas', 'snc', 'va500', 'ta500', 'rlus', 'mrso', 'ua500', 'sfcWindmax', 'mrro', 'hfls', 'rsdt', 'rlut', 'vas', 'snw', 'rsut', 'sund', 'ta200', 'ta850', 'snd', 'hus850', 'hfss', 'uas', 'snc', 'va500', 'ta500', 'rlus', 'mrso', 'ua500', 'sfcWindmax', 'mrro', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'pr', 'psl', 'tas', 'sfcWind', 'rsus', 'tasmax', 'tasmin', 'ua850', 'evspsbl', 'rsds', 'hurs']</t>
+          <t>['hfls', 'rsdt', 'rlut', 'vas', 'snw', 'rsut', 'sund', 'ta200', 'ta850', 'snd', 'hus850', 'hfss', 'uas', 'snc', 'va500', 'ta500', 'rlus', 'mrso', 'ua500', 'sfcWindmax', 'mrro', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'pr', 'psl', 'tas', 'sfcWind', 'rsus', 'tasmax', 'tasmin', 'ua850', 'evspsbl', 'rsds', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -27293,7 +27293,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>['vas', 'snw', 'rsdt', 'rlut', 'rsut', 'hfls', 'ta200', 'snc', 'sund', 'ua500', 'mrro', 'rlus', 'uas', 'ta850', 'sfcWindmax', 'hfss', 'hus850', 'snd', 'va500', 'ta500', 'mrso', 'vas', 'snw', 'rsdt', 'rlut', 'rsut', 'hfls', 'ta200', 'snc', 'sund', 'ua500', 'mrro', 'rlus', 'uas', 'ta850', 'sfcWindmax', 'hfss', 'hus850', 'snd', 'va500', 'ta500', 'mrso', 'tas', 'ua850', 'rsds', 'tasmax', 'va850', 'psl', 'clt', 'tasmin', 'rsus', 'pr', 'rlds', 'zg500', 'hurs', 'evspsbl', 'sfcWind', 'huss']</t>
+          <t>['vas', 'snw', 'rsdt', 'rlut', 'rsut', 'hfls', 'ta200', 'snc', 'sund', 'ua500', 'mrro', 'rlus', 'uas', 'ta850', 'sfcWindmax', 'hfss', 'hus850', 'snd', 'va500', 'ta500', 'mrso', 'tas', 'ua850', 'rsds', 'tasmax', 'va850', 'psl', 'clt', 'tasmin', 'rsus', 'pr', 'rlds', 'zg500', 'hurs', 'evspsbl', 'sfcWind', 'huss']</t>
         </is>
       </c>
     </row>
@@ -27329,7 +27329,7 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27361,7 +27361,7 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -27393,7 +27393,7 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'vas', 'hfss', 'hfls', 'mrso', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'uas', 'ts', 'hfss', 'hfls', 'mrso', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'uas', 'ts', 'clt', 'pr', 'ps', 'rsus', 'huss', 'rlds', 'tas', 'psl', 'sfcWind', 'tasmax', 'tasmin', 'evspsbl', 'rsds', 'hurs']</t>
+          <t>['wsgsmax', 'vas', 'hfss', 'hfls', 'mrso', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'uas', 'ts', 'clt', 'pr', 'ps', 'rsus', 'huss', 'rlds', 'tas', 'psl', 'sfcWind', 'tasmax', 'tasmin', 'evspsbl', 'rsds', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>['va500', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'zg500', 'va850', 'ua850']</t>
+          <t>['va500', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'zg500', 'va850', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps']</t>
+          <t>['psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps']</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -27677,7 +27677,7 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>['rsdt', 'prhmax', 'snc', 'prsn', 'uas', 'sund', 'ta200', 'mrso', 'snw', 'rsut', 'vas', 'ta850', 'ta500', 'ua500', 'rsds', 'sfcWindmax', 'ts', 'hfss', 'hfls', 'rlut', 'va500', 'wsgsmax', 'prc', 'hus850', 'rlus', 'mrro', 'snd', 'rsdt', 'prhmax', 'snc', 'prsn', 'uas', 'sund', 'ta200', 'mrso', 'snw', 'rsut', 'vas', 'ta850', 'ta500', 'ua500', 'rsds', 'sfcWindmax', 'ts', 'hfss', 'hfls', 'rlut', 'va500', 'wsgsmax', 'prc', 'hus850', 'rlus', 'mrro', 'snd', 'pr', 'rlds', 'hurs', 'ps', 'rsus', 'ua850', 'va850', 'evspsbl', 'zg500', 'tasmax', 'sfcWind', 'tas', 'psl', 'tasmin', 'huss', 'clt']</t>
+          <t>['rsdt', 'prhmax', 'snc', 'prsn', 'uas', 'sund', 'ta200', 'mrso', 'snw', 'rsut', 'vas', 'ta850', 'ta500', 'ua500', 'rsds', 'sfcWindmax', 'ts', 'hfss', 'hfls', 'rlut', 'va500', 'wsgsmax', 'prc', 'hus850', 'rlus', 'mrro', 'snd', 'pr', 'rlds', 'hurs', 'ps', 'rsus', 'ua850', 'va850', 'evspsbl', 'zg500', 'tasmax', 'sfcWind', 'tas', 'psl', 'tasmin', 'huss', 'clt']</t>
         </is>
       </c>
     </row>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>['hfss', 'mrso', 'hus850', 'ta850', 'rlut', 'uas', 'sund', 'snd', 'hfls', 'ta500', 'snc', 'rsdt', 'ta200', 'rlus', 'mrro', 'rsut', 'sfcWindmax', 'snw', 'vas', 'ua500', 'va500', 'hfss', 'mrso', 'hus850', 'ta850', 'rlut', 'uas', 'sund', 'snd', 'hfls', 'ta500', 'snc', 'rsdt', 'ta200', 'rlus', 'mrro', 'rsut', 'sfcWindmax', 'snw', 'vas', 'ua500', 'va500', 'tas', 'va850', 'sfcWind', 'evspsbl', 'huss', 'rsds', 'tasmin', 'zg500', 'tasmax', 'hurs', 'pr', 'ua850', 'clt', 'psl', 'rsus', 'rlds']</t>
+          <t>['hfss', 'mrso', 'hus850', 'ta850', 'rlut', 'uas', 'sund', 'snd', 'hfls', 'ta500', 'snc', 'rsdt', 'ta200', 'rlus', 'mrro', 'rsut', 'sfcWindmax', 'snw', 'vas', 'ua500', 'va500', 'tas', 'va850', 'sfcWind', 'evspsbl', 'huss', 'rsds', 'tasmin', 'zg500', 'tasmax', 'hurs', 'pr', 'ua850', 'clt', 'psl', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>['ua500', 'uas', 'mrro', 'sfcWindmax', 'rsut', 'vas', 'snw', 'snd', 'ta850', 'ta500', 'hus850', 'hfls', 'va500', 'snc', 'sund', 'mrso', 'ta200', 'rlus', 'hfss', 'rsdt', 'rlut', 'ua500', 'uas', 'mrro', 'sfcWindmax', 'rsut', 'vas', 'snw', 'snd', 'ta850', 'ta500', 'hus850', 'hfls', 'va500', 'snc', 'sund', 'mrso', 'ta200', 'rlus', 'hfss', 'rsdt', 'rlut', 'pr', 'rsds', 'hurs', 'tas', 'va850', 'tasmax', 'zg500', 'sfcWind', 'huss', 'tasmin', 'clt', 'psl', 'ua850', 'rlds', 'rsus', 'evspsbl']</t>
+          <t>['ua500', 'uas', 'mrro', 'sfcWindmax', 'rsut', 'vas', 'snw', 'snd', 'ta850', 'ta500', 'hus850', 'hfls', 'va500', 'snc', 'sund', 'mrso', 'ta200', 'rlus', 'hfss', 'rsdt', 'rlut', 'pr', 'rsds', 'hurs', 'tas', 'va850', 'tasmax', 'zg500', 'sfcWind', 'huss', 'tasmin', 'clt', 'psl', 'ua850', 'rlds', 'rsus', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>['uas']</t>
+          <t>['uas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -27901,7 +27901,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>['uas', 'ts', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'huss', 'tasmax', 'psl', 'hurs', 'clt', 'pr', 'sfcWind', 'rsds', 'rsus', 'ps', 'evspsbl', 'tasmin', 'tas', 'rlds']</t>
+          <t>['uas', 'ts', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'huss', 'tasmax', 'psl', 'hurs', 'clt', 'pr', 'sfcWind', 'rsds', 'rsus', 'ps', 'evspsbl', 'tasmin', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -27929,7 +27929,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>['va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'hus850', 'ua850', 'va850', 'zg500']</t>
+          <t>['va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'clt', 'tasmin', 'rsus', 'pr', 'huss', 'tasmax', 'tas', 'psl', 'rlds', 'hurs', 'rsds', 'sfcWind', 'evspsbl']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'clt', 'tasmin', 'rsus', 'pr', 'huss', 'tasmax', 'tas', 'psl', 'rlds', 'hurs', 'rsds', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'hus850', 'va500', 'ua500', 'va850', 'ua850', 'zg500']</t>
+          <t>['ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'va850', 'ua850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -28053,7 +28053,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rsds', 'clt', 'evspsbl', 'tasmin']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rsds', 'clt', 'evspsbl', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -28081,7 +28081,7 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'va850', 'ua850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'va850', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -28117,7 +28117,7 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28149,7 +28149,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28321,7 +28321,7 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'clt', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['rlds', 'rlus', 'clt', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'rlds', 'rlus', 'clt', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28353,7 +28353,7 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -28521,7 +28521,7 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'hfls', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['psl', 'rlds', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'hfls', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'psl', 'rlds', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'hfls', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28553,7 +28553,7 @@
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28725,7 +28725,7 @@
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28757,7 +28757,7 @@
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>['mrso', 'prc', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'ts', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'clt', 'sfcWind', 'zg500', 'evspsbl', 'tas', 'pr', 'rsus', 'rlds']</t>
+          <t>['mrso', 'prc', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'ts', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'clt', 'sfcWind', 'zg500', 'evspsbl', 'tas', 'pr', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -28821,7 +28821,7 @@
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28853,7 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'va850', 'tasmin', 'hurs', 'ua850', 'rlds', 'zg500', 'psl', 'tas', 'tasmax', 'rsus', 'evspsbl', 'sfcWind', 'huss', 'rsds', 'pr', 'clt']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'va850', 'tasmin', 'hurs', 'ua850', 'rlds', 'zg500', 'psl', 'tas', 'tasmax', 'rsus', 'evspsbl', 'sfcWind', 'huss', 'rsds', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28885,7 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'tasmax', 'sfcWind', 'rsds', 'ua850', 'va850', 'hurs', 'zg500', 'psl', 'rsus']</t>
+          <t>['sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'tasmax', 'sfcWind', 'rsds', 'ua850', 'va850', 'hurs', 'zg500', 'psl', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -28925,7 +28925,7 @@
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28957,7 +28957,7 @@
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rlut', 'prsn', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'tasmax', 'pr', 'rsds', 'huss', 'tasmin', 'rsus', 'tas', 'va850', 'evspsbl', 'ua850', 'hurs', 'ps', 'rlds', 'sfcWind', 'clt', 'zg500', 'psl']</t>
+          <t>['rlus', 'rsdt', 'rlut', 'prsn', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'tasmax', 'pr', 'rsds', 'huss', 'tasmin', 'rsus', 'tas', 'va850', 'evspsbl', 'ua850', 'hurs', 'ps', 'rlds', 'sfcWind', 'clt', 'zg500', 'psl']</t>
         </is>
       </c>
     </row>
@@ -29021,7 +29021,7 @@
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -29053,7 +29053,7 @@
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'tasmin', 'tas', 'ua850', 'rsds', 'rlds', 'zg500', 'evspsbl', 'psl', 'rsus', 'clt', 'tasmax', 'hurs', 'sfcWind', 'va850', 'huss', 'pr']</t>
+          <t>['vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'tasmin', 'tas', 'ua850', 'rsds', 'rlds', 'zg500', 'evspsbl', 'psl', 'rsus', 'clt', 'tasmax', 'hurs', 'sfcWind', 'va850', 'huss', 'pr']</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29085,7 @@
       </c>
       <c r="J882" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'vas', 'uas', 'va500', 'huss', 'tasmax', 'rsds', 'pr', 'rsus', 'evspsbl', 'psl', 'clt', 'rlds', 'hurs', 'tasmin', 'ua850', 'zg500', 'va850', 'tas', 'sfcWind']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'huss', 'tasmax', 'rsds', 'pr', 'rsus', 'evspsbl', 'psl', 'clt', 'rlds', 'hurs', 'tasmin', 'ua850', 'zg500', 'va850', 'tas', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -29125,7 +29125,7 @@
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'hfls', 'hfss', 'clt', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['rlds', 'rlus', 'hfls', 'hfss', 'clt', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'rlds', 'rlus', 'hfls', 'hfss', 'clt', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29157,7 @@
       </c>
       <c r="J884" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -29189,7 +29189,7 @@
       </c>
       <c r="J885" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'tasmin', 'evspsbl', 'tas', 'huss', 'ua850', 'tasmax', 'va850', 'psl', 'ps', 'pr', 'hurs', 'zg500']</t>
+          <t>['hfss', 'hfls', 'hus850', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'tasmin', 'evspsbl', 'tas', 'huss', 'ua850', 'tasmax', 'va850', 'psl', 'ps', 'pr', 'hurs', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -29253,7 +29253,7 @@
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'sund', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'sfcWindmax', 'rsut', 'snw', 'snc', 'sund', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'rsus', 'rsds', 'sfcWind', 'ua850', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'hurs', 'huss', 'psl', 'rlds', 'pr', 'tas', 'va850', 'clt']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'sund', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'rsus', 'rsds', 'sfcWind', 'ua850', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'hurs', 'huss', 'psl', 'rlds', 'pr', 'tas', 'va850', 'clt']</t>
         </is>
       </c>
     </row>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="J888" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'zg500', 'rlds', 'huss', 'rsus', 'ua850', 'psl']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'zg500', 'rlds', 'huss', 'rsus', 'ua850', 'psl']</t>
         </is>
       </c>
     </row>
@@ -29325,7 +29325,7 @@
       </c>
       <c r="J889" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="J890" t="inlineStr">
         <is>
-          <t>['uas']</t>
+          <t>['uas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -29417,7 +29417,7 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ps', 'ua850', 'rsus', 'clt', 'pr', 'evspsbl', 'hurs', 'tasmin', 'zg500', 'tas', 'va850', 'huss', 'rlds', 'psl', 'sfcWind', 'tasmax', 'rsds']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ps', 'ua850', 'rsus', 'clt', 'pr', 'evspsbl', 'hurs', 'tasmin', 'zg500', 'tas', 'va850', 'huss', 'rlds', 'psl', 'sfcWind', 'tasmax', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'sfcWindmax', 'uas', 'ua500', 'ta500', 'ta850', 'vas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'snd', 'hfss', 'hfls', 'mrso', 'sfcWindmax', 'uas', 'ua500', 'ta500', 'ta850', 'vas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'snd', 'pr', 'tasmin', 'ua850', 'va850', 'tasmax', 'rlds', 'rsds', 'rsus', 'evspsbl', 'sfcWind', 'zg500', 'clt', 'tas', 'psl', 'huss', 'hurs']</t>
+          <t>['hfss', 'hfls', 'mrso', 'sfcWindmax', 'uas', 'ua500', 'ta500', 'ta850', 'vas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'snd', 'pr', 'tasmin', 'ua850', 'va850', 'tasmax', 'rlds', 'rsds', 'rsus', 'evspsbl', 'sfcWind', 'zg500', 'clt', 'tas', 'psl', 'huss', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>['hfls', 'sfcWindmax', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'ua500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'hfls', 'sfcWindmax', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'ua500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'tas', 'psl', 'sfcWind', 'rlds', 'clt', 'ua850', 'rsds', 'tasmin', 'tasmax', 'zg500', 'rsus', 'evspsbl', 'va850', 'huss', 'hurs', 'pr']</t>
+          <t>['hfls', 'sfcWindmax', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'ua500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'tas', 'psl', 'sfcWind', 'rlds', 'clt', 'ua850', 'rsds', 'tasmin', 'tasmax', 'zg500', 'rsus', 'evspsbl', 'va850', 'huss', 'hurs', 'pr']</t>
         </is>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
       </c>
       <c r="J896" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'rlus', 'rsds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['psl', 'rlds', 'rlus', 'rsds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'tas', 'psl', 'rlds', 'rlus', 'rsds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="J897" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -29757,7 +29757,7 @@
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>['clt', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'rlds', 'hfls', 'huss', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['clt', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'rlds', 'hfls', 'huss', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'clt', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'rlds', 'hfls', 'huss', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29789,7 +29789,7 @@
       </c>
       <c r="J903" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -29957,7 +29957,7 @@
       </c>
       <c r="J908" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29989,7 +29989,7 @@
       </c>
       <c r="J909" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -30161,7 +30161,7 @@
       </c>
       <c r="J914" t="inlineStr">
         <is>
-          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -30193,7 +30193,7 @@
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="J920" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'hfls', 'huss', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'rlds']</t>
+          <t>['hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'hfls', 'huss', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'rlds', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'hfls', 'huss', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -30393,7 +30393,7 @@
       </c>
       <c r="J921" t="inlineStr">
         <is>
-          <t>['vas', 'uas']</t>
+          <t>['vas', 'uas', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'clt', 'pr', 'prw', 'hfls', 'huss', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'psl', 'rlds', 'rlus']</t>
+          <t>['hfss', 'hurs', 'clt', 'pr', 'prw', 'hfls', 'huss', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'psl', 'rlds', 'rlus', 'hfss', 'hurs', 'clt', 'pr', 'prw', 'hfls', 'huss', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'psl', 'rlds', 'rlus']</t>
         </is>
       </c>
     </row>
@@ -30593,7 +30593,7 @@
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>['uas', 'vas']</t>
+          <t>['uas', 'vas', 'uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -34697,7 +34697,7 @@
       </c>
       <c r="J1054" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rlut', 'prsn', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rlut', 'prsn', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'psl', 'ps', 'tasmax', 'huss', 'tasmin', 'pr', 'rsds', 'zg500', 'sfcWind', 'tas', 'evspsbl', 'va850', 'ua850', 'rlds', 'clt', 'rsus']</t>
+          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rlut', 'prsn', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'psl', 'ps', 'tasmax', 'huss', 'tasmin', 'pr', 'rsds', 'zg500', 'sfcWind', 'tas', 'evspsbl', 'va850', 'ua850', 'rlds', 'clt', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -34729,7 +34729,7 @@
       </c>
       <c r="J1055" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWind', 'pr', 'rsds', 'clt', 'tas', 'va850', 'zg500', 'tasmax', 'rlds', 'evspsbl', 'rsus', 'huss', 'ua850', 'tasmin', 'psl']</t>
+          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWind', 'pr', 'rsds', 'clt', 'tas', 'va850', 'zg500', 'tasmax', 'rlds', 'evspsbl', 'rsus', 'huss', 'ua850', 'tasmin', 'psl']</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="J1056" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'snw', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'snw', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'va850', 'ua850', 'psl', 'rsds', 'huss', 'tasmax', 'zg500', 'pr', 'clt', 'tasmin', 'tas', 'rlds', 'sfcWind', 'evspsbl', 'rsus']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'snw', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'va850', 'ua850', 'psl', 'rsds', 'huss', 'tasmax', 'zg500', 'pr', 'clt', 'tasmin', 'tas', 'rlds', 'sfcWind', 'evspsbl', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -34841,7 +34841,7 @@
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'prc', 'prsn', 'vas', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rlut', 'mrso', 'prc', 'prsn', 'vas', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'huss', 'ps', 'rlds', 'zg500', 'rsus', 'clt', 'ua850', 'va850', 'psl', 'rsds', 'evspsbl', 'tas', 'tasmax', 'tasmin']</t>
+          <t>['rlus', 'rlut', 'mrso', 'prc', 'prsn', 'vas', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'huss', 'ps', 'rlds', 'zg500', 'rsus', 'clt', 'ua850', 'va850', 'psl', 'rsds', 'evspsbl', 'tas', 'tasmax', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -34873,7 +34873,7 @@
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'huss', 'rsds', 'sfcWind', 'evspsbl', 'tasmin', 'tasmax', 'rsus', 'zg500', 'tas', 'psl', 'pr', 'clt', 'va850', 'ua850', 'rlds']</t>
+          <t>['ta200', 'ta500', 'ta850', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'huss', 'rsds', 'sfcWind', 'evspsbl', 'tasmin', 'tasmax', 'rsus', 'zg500', 'tas', 'psl', 'pr', 'clt', 'va850', 'ua850', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -34905,7 +34905,7 @@
       </c>
       <c r="J1060" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'psl', 'ua850', 'huss', 'rsus', 'rsds', 'rlds', 'sfcWind', 'tas', 'clt', 'evspsbl', 'tasmax', 'pr', 'tasmin', 'zg500', 'va850']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'psl', 'ua850', 'huss', 'rsus', 'rsds', 'rlds', 'sfcWind', 'tas', 'clt', 'evspsbl', 'tasmax', 'pr', 'tasmin', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -34941,7 +34941,7 @@
       </c>
       <c r="J1061" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'mrso', 'prc', 'prsn', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'mrso', 'prc', 'prsn', 'uas', 'va500', 'ua500', 'ts', 'ua850', 'rlds', 'rsds', 'ps', 'huss', 'rsus', 'tasmax', 'tasmin', 'evspsbl', 'clt', 'pr', 'psl', 'va850', 'sfcWind', 'zg500', 'tas']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'mrso', 'prc', 'prsn', 'uas', 'va500', 'ua500', 'ts', 'ua850', 'rlds', 'rsds', 'ps', 'huss', 'rsus', 'tasmax', 'tasmin', 'evspsbl', 'clt', 'pr', 'psl', 'va850', 'sfcWind', 'zg500', 'tas']</t>
         </is>
       </c>
     </row>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="J1062" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'ua850', 'rsds', 'clt', 'tasmin', 'va850', 'sfcWind', 'tasmax', 'zg500', 'huss', 'tas', 'rsus', 'rlds', 'psl', 'evspsbl', 'pr']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'ua850', 'rsds', 'clt', 'tasmin', 'va850', 'sfcWind', 'tasmax', 'zg500', 'huss', 'tas', 'rsus', 'rlds', 'psl', 'evspsbl', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35005,7 +35005,7 @@
       </c>
       <c r="J1063" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'va500', 'ua500', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'va500', 'ua500', 'vas', 'evspsbl', 'rsds', 'rsus', 'tasmax', 'psl', 'tasmin', 'clt', 'va850', 'huss', 'pr', 'ua850', 'tas', 'sfcWind', 'rlds', 'zg500']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'va500', 'ua500', 'vas', 'evspsbl', 'rsds', 'rsus', 'tasmax', 'psl', 'tasmin', 'clt', 'va850', 'huss', 'pr', 'ua850', 'tas', 'sfcWind', 'rlds', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'tas', 'va850', 'tasmax', 'rlds', 'pr', 'tasmin', 'zg500', 'ua850', 'psl', 'sfcWind', 'huss', 'rsus', 'rsds', 'clt', 'evspsbl', 'ps']</t>
+          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'tas', 'va850', 'tasmax', 'rlds', 'pr', 'tasmin', 'zg500', 'ua850', 'psl', 'sfcWind', 'huss', 'rsus', 'rsds', 'clt', 'evspsbl', 'ps']</t>
         </is>
       </c>
     </row>
@@ -35113,7 +35113,7 @@
       </c>
       <c r="J1066" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'tas', 'va850', 'rsus', 'huss', 'zg500', 'clt', 'ua850', 'tasmax', 'tasmin', 'rsds', 'pr', 'sfcWind', 'evspsbl', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'tas', 'va850', 'rsus', 'huss', 'zg500', 'clt', 'ua850', 'tasmax', 'tasmin', 'rsds', 'pr', 'sfcWind', 'evspsbl', 'psl']</t>
         </is>
       </c>
     </row>
@@ -35145,7 +35145,7 @@
       </c>
       <c r="J1067" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'pr', 'rsds', 'tas', 'psl', 'clt', 'ua850', 'tasmax', 'rsus', 'huss', 'tasmin', 'rlds', 'va850', 'zg500', 'sfcWind', 'evspsbl']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'pr', 'rsds', 'tas', 'psl', 'clt', 'ua850', 'tasmax', 'rsus', 'huss', 'tasmin', 'rlds', 'va850', 'zg500', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -35181,7 +35181,7 @@
       </c>
       <c r="J1068" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'wsgsmax', 'vas', 'uas', 'va500', 'hfls', 'hfss', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua500', 'ts', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'wsgsmax', 'vas', 'uas', 'va500', 'hfls', 'hfss', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua500', 'ts', 'tasmax', 'pr', 'psl', 'tas', 'huss', 'ps', 'rlds', 'clt', 'va850', 'ua850', 'evspsbl', 'tasmin', 'sfcWind', 'rsus', 'zg500', 'rsds']</t>
+          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'wsgsmax', 'vas', 'uas', 'va500', 'hfls', 'hfss', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua500', 'ts', 'tasmax', 'pr', 'psl', 'tas', 'huss', 'ps', 'rlds', 'clt', 'va850', 'ua850', 'evspsbl', 'tasmin', 'sfcWind', 'rsus', 'zg500', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'va850', 'zg500', 'huss', 'evspsbl', 'tas', 'clt', 'psl', 'rsus', 'ua850', 'rlds', 'sfcWind', 'tasmax', 'rsds', 'tasmin', 'pr']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'va850', 'zg500', 'huss', 'evspsbl', 'tas', 'clt', 'psl', 'rsus', 'ua850', 'rlds', 'sfcWind', 'tasmax', 'rsds', 'tasmin', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snw', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'rsus', 'ua850', 'tasmax', 'tasmin', 'psl', 'tas', 'sfcWind', 'pr', 'rsds', 'zg500', 'huss', 'evspsbl', 'rlds', 'va850', 'clt']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snw', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'rsus', 'ua850', 'tasmax', 'tasmin', 'psl', 'tas', 'sfcWind', 'pr', 'rsds', 'zg500', 'huss', 'evspsbl', 'rlds', 'va850', 'clt']</t>
         </is>
       </c>
     </row>
@@ -35321,7 +35321,7 @@
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'prc', 'prsn', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'prc', 'prsn', 'rsds', 'rlds', 'ua850', 'clt', 'tasmin', 'evspsbl', 'zg500', 'rsus', 'va850', 'sfcWind', 'ps', 'tas', 'pr', 'tasmax', 'huss', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'prc', 'prsn', 'rsds', 'rlds', 'ua850', 'clt', 'tasmin', 'evspsbl', 'zg500', 'rsus', 'va850', 'sfcWind', 'ps', 'tas', 'pr', 'tasmax', 'huss', 'psl']</t>
         </is>
       </c>
     </row>
@@ -35353,7 +35353,7 @@
       </c>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'rsds', 'pr', 'tasmax', 'ua850', 'evspsbl', 'clt', 'rsus', 'va850', 'huss', 'rlds', 'zg500', 'psl', 'tas', 'tasmin', 'sfcWind']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'rsds', 'pr', 'tasmax', 'ua850', 'evspsbl', 'clt', 'rsus', 'va850', 'huss', 'rlds', 'zg500', 'psl', 'tas', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -35385,7 +35385,7 @@
       </c>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'snw', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'snw', 'ta200', 'ta500', 'ta850', 'rsds', 'zg500', 'pr', 'rsus', 'tasmax', 'ua850', 'rlds', 'tas', 'sfcWind', 'clt', 'psl', 'huss', 'tasmin', 'evspsbl', 'va850']</t>
+          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'snw', 'ta200', 'ta500', 'ta850', 'rsds', 'zg500', 'pr', 'rsus', 'tasmax', 'ua850', 'rlds', 'tas', 'sfcWind', 'clt', 'psl', 'huss', 'tasmin', 'evspsbl', 'va850']</t>
         </is>
       </c>
     </row>
@@ -35421,7 +35421,7 @@
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rlut', 'mrso', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rlut', 'mrso', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'ps', 'zg500', 'rlds', 'tasmax', 'ua850', 'clt', 'va850', 'tas', 'rsus', 'pr', 'evspsbl', 'tasmin', 'psl', 'sfcWind', 'rsds', 'huss']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rlut', 'mrso', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'ps', 'zg500', 'rlds', 'tasmax', 'ua850', 'clt', 'va850', 'tas', 'rsus', 'pr', 'evspsbl', 'tasmin', 'psl', 'sfcWind', 'rsds', 'huss']</t>
         </is>
       </c>
     </row>
@@ -35453,7 +35453,7 @@
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'rsds', 'huss', 'rsus', 'tasmax', 'clt', 'tasmin', 'ua850', 'psl', 'zg500', 'evspsbl', 'va850', 'sfcWind', 'rlds', 'pr', 'tas']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'rsds', 'huss', 'rsus', 'tasmax', 'clt', 'tasmin', 'ua850', 'psl', 'zg500', 'evspsbl', 'va850', 'sfcWind', 'rlds', 'pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -35485,7 +35485,7 @@
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'huss', 'tas', 'va850', 'clt', 'sfcWind', 'pr', 'rsus', 'rlds', 'rsds', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'psl', 'ua850']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'huss', 'tas', 'va850', 'clt', 'sfcWind', 'pr', 'rsus', 'rlds', 'rsds', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'psl', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -35561,7 +35561,7 @@
       </c>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrso', 'prc', 'prsn', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrso', 'prc', 'prsn', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'zg500', 'ua850', 'sfcWind', 'psl', 'va850', 'pr', 'rlds', 'rsus', 'huss', 'tasmin', 'rsds', 'tas', 'tasmax', 'ps', 'clt', 'evspsbl']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrso', 'prc', 'prsn', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'zg500', 'ua850', 'sfcWind', 'psl', 'va850', 'pr', 'rlds', 'rsus', 'huss', 'tasmin', 'rsds', 'tas', 'tasmax', 'ps', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>['snw', 'ta200', 'ta500', 'ta850', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'snw', 'ta200', 'ta500', 'ta850', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'tas', 'clt', 'ua850', 'zg500', 'sfcWind', 'pr', 'rlds', 'evspsbl', 'rsus', 'va850', 'psl', 'huss', 'rsds', 'tasmax', 'tasmin']</t>
+          <t>['snw', 'ta200', 'ta500', 'ta850', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'tas', 'clt', 'ua850', 'zg500', 'sfcWind', 'pr', 'rlds', 'evspsbl', 'rsus', 'va850', 'psl', 'huss', 'rsds', 'tasmax', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ta850', 'ua500', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ta850', 'ua500', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'sfcWind', 'evspsbl', 'rsus', 'rlds', 'tasmin', 'huss', 'psl', 'pr', 'zg500', 'rsds', 'clt', 'va850', 'tasmax', 'tas', 'ua850']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ta850', 'ua500', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'sfcWind', 'evspsbl', 'rsus', 'rlds', 'tasmin', 'huss', 'psl', 'pr', 'zg500', 'rsds', 'clt', 'va850', 'tasmax', 'tas', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -35661,7 +35661,7 @@
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'uas', 'ua500', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'uas', 'ua500', 'ts', 'tas', 'rlds', 'pr', 'sfcWind', 'rsus', 'huss', 'clt', 'psl', 'tasmin', 'rsds', 'zg500', 'ua850', 'tasmax', 'ps', 'va850', 'evspsbl']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'uas', 'ua500', 'ts', 'tas', 'rlds', 'pr', 'sfcWind', 'rsus', 'huss', 'clt', 'psl', 'tasmin', 'rsds', 'zg500', 'ua850', 'tasmax', 'ps', 'va850', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -35693,7 +35693,7 @@
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ua850', 'pr', 'sfcWind', 'va850', 'psl', 'rlds', 'tas', 'tasmax', 'rsus', 'evspsbl', 'clt', 'huss', 'rsds', 'zg500', 'tasmin']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ua850', 'pr', 'sfcWind', 'va850', 'psl', 'rlds', 'tas', 'tasmax', 'rsus', 'evspsbl', 'clt', 'huss', 'rsds', 'zg500', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -35725,7 +35725,7 @@
       </c>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'huss', 'tasmin', 'sfcWind', 'ua850', 'va850', 'rsds', 'rsus', 'tas', 'pr', 'evspsbl', 'zg500', 'psl', 'tasmax', 'clt', 'rlds']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'huss', 'tasmin', 'sfcWind', 'ua850', 'va850', 'rsds', 'rsus', 'tas', 'pr', 'evspsbl', 'zg500', 'psl', 'tasmax', 'clt', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="J1085" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35809,7 +35809,7 @@
       </c>
       <c r="J1086" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35841,7 @@
       </c>
       <c r="J1087" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35881,7 +35881,7 @@
       </c>
       <c r="J1088" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35913,7 +35913,7 @@
       </c>
       <c r="J1089" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35945,7 +35945,7 @@
       </c>
       <c r="J1090" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35985,7 +35985,7 @@
       </c>
       <c r="J1091" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36017,7 @@
       </c>
       <c r="J1092" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="J1093" t="inlineStr">
         <is>
-          <t>['pr', 'tas', 'pr', 'tas']</t>
+          <t>['pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36089,7 @@
       </c>
       <c r="J1094" t="inlineStr">
         <is>
-          <t>['pr', 'tas', 'pr', 'tas']</t>
+          <t>['pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -36121,7 +36121,7 @@
       </c>
       <c r="J1095" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -36153,7 +36153,7 @@
       </c>
       <c r="J1096" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -36197,7 +36197,7 @@
       </c>
       <c r="J1097" t="inlineStr">
         <is>
-          <t>['pr', 'tas', 'pr', 'tas']</t>
+          <t>['pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -36229,7 +36229,7 @@
       </c>
       <c r="J1098" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -36261,7 +36261,7 @@
       </c>
       <c r="J1099" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -36293,7 +36293,7 @@
       </c>
       <c r="J1100" t="inlineStr">
         <is>
-          <t>['tas', 'pr', 'tas', 'pr']</t>
+          <t>['tas', 'pr']</t>
         </is>
       </c>
     </row>

--- a/euro-cordex-esgf.xlsx
+++ b/euro-cordex-esgf.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>['orog', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>['clwvi', 'clivi', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'zmla', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'va850', 'tasmin', 'psl', 'huss', 'ps', 'va850', 'tasmin', 'psl', 'huss', 'ps', 'sfcWind', 'tas', 'pr', 'clt', 'rlds', 'rsus', 'rsds', 'zg500', 'ua850', 'tasmax']</t>
+          <t>['clwvi', 'clivi', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'zmla', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'va850', 'tasmin', 'psl', 'huss', 'ps', 'sfcWind', 'tas', 'pr', 'clt', 'rlds', 'rsus', 'rsds', 'zg500', 'ua850', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'sund', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'sfcWind', 'rsus', 'rsds', 'zg500', 'tasmax', 'rlds', 'tasmin', 'va850', 'ua850', 'sfcWind', 'rsus', 'rsds', 'zg500', 'tasmax', 'rlds', 'tasmin', 'va850', 'pr', 'psl', 'huss', 'clt', 'tas']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'sund', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'sfcWind', 'rsus', 'rsds', 'zg500', 'tasmax', 'rlds', 'tasmin', 'va850', 'pr', 'psl', 'huss', 'clt', 'tas']</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>['uas', 'va200', 'ua200', 'ua500', 'ta850', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua850', 'psl', 'clt', 'ua850', 'psl', 'clt', 'sfcWind', 'huss', 'rsus', 'rsds', 'tasmax', 'zg500', 'tas', 'va850', 'tasmin', 'rlds', 'pr']</t>
+          <t>['uas', 'va200', 'ua200', 'ua500', 'ta850', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'vas', 'zg200', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua850', 'psl', 'clt', 'sfcWind', 'huss', 'rsus', 'rsds', 'tasmax', 'zg500', 'tas', 'va850', 'tasmin', 'rlds', 'pr']</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'zg500', 'psl', 'tas', 'tasmin', 'rsds', 'rsus', 'tasmax', 'rlds', 'huss']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'zmla', 'zg200', 'prhmax', 'rlus', 'mrso', 'prc', 'prw', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'clt', 'ua850', 'va850', 'ps', 'sfcWind', 'pr', 'zg500', 'psl', 'tas', 'tasmin', 'rsds', 'rsus', 'tasmax', 'rlds', 'huss']</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'rlds', 'tas', 'clt', 'huss', 'tasmax', 'psl', 'va850']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'ua850', 'rsus', 'zg500', 'tasmin', 'rsds', 'rlds', 'tas', 'clt', 'huss', 'tasmax', 'psl', 'va850']</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'pr', 'rsds', 'tasmin', 'rlds', 'rsus', 'va850', 'tasmax']</t>
+          <t>['rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'vas', 'zg200', 'uas', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rsut', 'snm', 'snw', 'sund', 'snc', 'snd', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'huss', 'psl', 'tas', 'clt', 'pr', 'rsds', 'tasmin', 'rlds', 'rsus', 'va850', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'uas', 'va200', 'va500', 'ua500', 'ts', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'pr', 'pr', 'tasmin', 'ua850', 'ps', 'clt', 'zg500', 'rsus', 'tasmax', 'rlds', 'tas', 'huss', 'va850', 'psl', 'rsds', 'sfcWind']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'uas', 'va200', 'va500', 'ua500', 'ts', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'zmla', 'vas', 'zg200', 'ua200', 'pr', 'tasmin', 'ua850', 'ps', 'clt', 'zg500', 'rsus', 'tasmax', 'rlds', 'tas', 'huss', 'va850', 'psl', 'rsds', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>['hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'psl', 'sfcWind', 'zg500', 'clt', 'tas', 'huss', 'rsds', 'rsus', 'rlds']</t>
+          <t>['hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'hfls', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'tasmin', 'ua850', 'pr', 'tasmax', 'va850', 'psl', 'sfcWind', 'zg500', 'clt', 'tas', 'huss', 'rsds', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>['rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'snw', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'huss', 'tas', 'sfcWind', 'rsus', 'tasmin', 'rsds', 'huss', 'tas', 'sfcWind', 'rsus', 'tasmin', 'rsds', 'ua850', 'zg500', 'va850', 'clt', 'pr', 'tasmax', 'psl', 'rlds']</t>
+          <t>['rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'snw', 'sund', 'ua200', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'huss', 'tas', 'sfcWind', 'rsus', 'tasmin', 'rsds', 'ua850', 'zg500', 'va850', 'clt', 'pr', 'tasmax', 'psl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'ua200', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'ps', 'ua850', 'clt', 'huss', 'rlds', 'pr', 'zg500', 'rsus', 'sfcWind']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'ua200', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'tas', 'rsds', 'tasmin', 'psl', 'tasmax', 'va850', 'ps', 'ua850', 'clt', 'huss', 'rlds', 'pr', 'zg500', 'rsus', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'va850', 'psl', 'rsus', 'tasmin', 'va850', 'psl', 'rsus', 'tasmin', 'sfcWind', 'rsds', 'huss', 'tasmax', 'ua850', 'clt', 'pr', 'zg500', 'tas', 'rlds']</t>
+          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'va850', 'psl', 'rsus', 'tasmin', 'sfcWind', 'rsds', 'huss', 'tasmax', 'ua850', 'clt', 'pr', 'zg500', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'zg500', 'tasmax', 'ua850', 'va850', 'zg500', 'tasmax', 'ua850', 'va850', 'clt', 'huss', 'rlds', 'rsds', 'rsus', 'tasmin', 'pr', 'sfcWind', 'psl', 'tas']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'zg500', 'tasmax', 'ua850', 'va850', 'clt', 'huss', 'rlds', 'rsds', 'rsus', 'tasmin', 'pr', 'sfcWind', 'psl', 'tas']</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>['hfss', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'prhmax', 'rlus', 'rsdt', 'rlut', 'prw', 'ua500', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'clt', 'zg500', 'tas', 'va850', 'psl', 'clt', 'zg500', 'tas', 'va850', 'psl', 'tasmax', 'tasmin', 'ua850', 'huss', 'rsds', 'ps', 'sfcWind', 'rlds', 'pr', 'rsus']</t>
+          <t>['hfss', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'prhmax', 'rlus', 'rsdt', 'rlut', 'prw', 'ua500', 'ua200', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'zmla', 'clwvi', 'hfls', 'clivi', 'clt', 'zg500', 'tas', 'va850', 'psl', 'tasmax', 'tasmin', 'ua850', 'huss', 'rsds', 'ps', 'sfcWind', 'rlds', 'pr', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'ua850', 'va850', 'rsds', 'tas', 'sfcWind', 'psl', 'zg500', 'huss', 'pr', 'rlds', 'rsus', 'tasmin', 'tasmax', 'clt']</t>
+          <t>['sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'va850', 'rsds', 'tas', 'sfcWind', 'psl', 'zg500', 'huss', 'pr', 'rlds', 'rsus', 'tasmin', 'tasmax', 'clt']</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'psl', 'zg500', 'sfcWind', 'rsus', 'rsds', 'tasmin']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'zg200', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'tasmax', 'va850', 'huss', 'pr', 'rlds', 'clt', 'tas', 'psl', 'zg500', 'sfcWind', 'rsus', 'rsds', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>['orog', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>['rsdt', 'mrso', 'sfcWindmax', 'uas', 'va500', 'ta500', 'ta200', 'clwvi', 'prw', 'mrro', 'rlus', 'snm', 'snw', 'zg200', 'wsgsmax', 'vas', 'clivi', 'prc', 'hus850', 'ta850', 'prhmax', 'zmla', 'sund', 'rsut', 'rlut', 'mrros', 'snc', 'prsn', 'va200', 'ua200', 'ts', 'hfss', 'hfls', 'mrfso', 'ua500', 'snd', 'tas', 'huss', 'rsus', 'evspsbl', 'sfcWind', 'tas', 'huss', 'rsus', 'evspsbl', 'sfcWind', 'pr', 'rsds', 'ua850', 'clt', 'tasmax', 'psl', 'tasmin', 'ps', 'rlds', 'hurs', 'va850', 'zg500']</t>
+          <t>['rsdt', 'mrso', 'sfcWindmax', 'uas', 'va500', 'ta500', 'ta200', 'clwvi', 'prw', 'mrro', 'rlus', 'snm', 'snw', 'zg200', 'wsgsmax', 'vas', 'clivi', 'prc', 'hus850', 'ta850', 'prhmax', 'zmla', 'sund', 'rsut', 'rlut', 'mrros', 'snc', 'prsn', 'va200', 'ua200', 'ts', 'hfss', 'hfls', 'mrfso', 'ua500', 'snd', 'tas', 'huss', 'rsus', 'evspsbl', 'sfcWind', 'pr', 'rsds', 'ua850', 'clt', 'tasmax', 'psl', 'tasmin', 'ps', 'rlds', 'hurs', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>['zg200', 'ta850', 'rsdt', 'sund', 'mrso', 'va200', 'ta500', 'hfss', 'rlut', 'snw', 'hus850', 'snc', 'ua200', 'rlus', 'snm', 'mrro', 'ua500', 'hfls', 'rsut', 'vas', 'va500', 'ta200', 'uas', 'snd', 'mrros', 'sfcWindmax', 'mrfso', 'hurs', 'huss', 'zg500', 'evspsbl', 'tasmin', 'rlds', 'rsus', 'ua850', 'hurs', 'huss', 'zg500', 'evspsbl', 'tasmin', 'rlds', 'rsus', 'ua850', 'clt', 'psl', 'rsds', 'pr', 'tasmax', 'tas', 'sfcWind', 'va850']</t>
+          <t>['zg200', 'ta850', 'rsdt', 'sund', 'mrso', 'va200', 'ta500', 'hfss', 'rlut', 'snw', 'hus850', 'snc', 'ua200', 'rlus', 'snm', 'mrro', 'ua500', 'hfls', 'rsut', 'vas', 'va500', 'ta200', 'uas', 'snd', 'mrros', 'sfcWindmax', 'mrfso', 'hurs', 'huss', 'zg500', 'evspsbl', 'tasmin', 'rlds', 'rsus', 'ua850', 'clt', 'psl', 'rsds', 'pr', 'tasmax', 'tas', 'sfcWind', 'va850']</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>['rlut', 'va200', 'ta200', 'ta500', 'sund', 'snc', 'va500', 'rlus', 'rsdt', 'mrro', 'hfss', 'uas', 'ta850', 'hus850', 'snd', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'zg200', 'vas', 'mrros', 'mrfso', 'ua200', 'snm', 'snw', 'ua500', 'va850', 'pr', 'sfcWind', 'hurs', 'clt', 'zg500', 'evspsbl', 'va850', 'pr', 'sfcWind', 'hurs', 'clt', 'zg500', 'evspsbl', 'huss', 'rsds', 'psl', 'rlds', 'tasmin', 'tasmax', 'tas', 'rsus', 'ua850']</t>
+          <t>['rlut', 'va200', 'ta200', 'ta500', 'sund', 'snc', 'va500', 'rlus', 'rsdt', 'mrro', 'hfss', 'uas', 'ta850', 'hus850', 'snd', 'sfcWindmax', 'rsut', 'mrso', 'hfls', 'zg200', 'vas', 'mrros', 'mrfso', 'ua200', 'snm', 'snw', 'ua500', 'va850', 'pr', 'sfcWind', 'hurs', 'clt', 'zg500', 'evspsbl', 'huss', 'rsds', 'psl', 'rlds', 'tasmin', 'tasmax', 'tas', 'rsus', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>['orog', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>['clwvi', 'clivi', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'rsus', 'rlds', 'va850', 'rsus', 'rlds', 'va850', 'ps', 'tasmax', 'sfcWind', 'clt', 'pr', 'psl', 'ua850', 'zg500', 'tas', 'huss', 'tasmin', 'rsds']</t>
+          <t>['clwvi', 'clivi', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'zmla', 'zg200', 'rsus', 'rlds', 'va850', 'ps', 'tasmax', 'sfcWind', 'clt', 'pr', 'psl', 'ua850', 'zg500', 'tas', 'huss', 'tasmin', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'zg500', 'rsds', 'rsus', 'ua850', 'tasmin', 'rlds', 'va850']</t>
+          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'tasmax', 'pr', 'tas', 'huss', 'psl', 'clt', 'sfcWind', 'zg500', 'rsds', 'rsus', 'ua850', 'tasmin', 'rlds', 'va850']</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>['vas', 'zg200', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ta500', 'ta850', 'ua200', 'ua500', 'va850', 'psl', 'rlds', 'va850', 'psl', 'rlds', 'rsds', 'rsus', 'pr', 'ua850', 'tasmin', 'tasmax', 'huss', 'clt', 'tas', 'sfcWind', 'zg500']</t>
+          <t>['vas', 'zg200', 'va200', 'va500', 'hfss', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ta500', 'ta850', 'ua200', 'ua500', 'va850', 'psl', 'rlds', 'rsds', 'rsus', 'pr', 'ua850', 'tasmin', 'tasmax', 'huss', 'clt', 'tas', 'sfcWind', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>['clivi', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'ua850', 'tas', 'psl', 'va850', 'tasmax', 'pr', 'zg500', 'ps', 'tasmin']</t>
+          <t>['clivi', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'hus850', 'mrro', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'clt', 'huss', 'sfcWind', 'rsus', 'rsds', 'ua850', 'tas', 'psl', 'va850', 'tasmax', 'pr', 'zg500', 'ps', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'tasmax', 'sfcWind']</t>
+          <t>['snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'hfss', 'hfls', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'zg200', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'psl', 'pr', 'tas', 'ua850', 'rsus', 'tasmin', 'rsds', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'tasmax', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'rsus', 'psl', 'tasmax', 'huss']</t>
+          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'hfss', 'hfls', 'mrfso', 'hus850', 'rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'pr', 'clt', 'sfcWind', 'tas', 'tasmin', 'rlds', 'va850', 'zg500', 'ua850', 'rsds', 'rsus', 'psl', 'tasmax', 'huss']</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'va200', 'ua500', 'ua200', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'tasmax', 'rlds', 'ps', 'zg500', 'rsds', 'evspsbl', 'huss', 'pr', 'va850', 'tasmin', 'sfcWind']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'uas', 'va200', 'ua500', 'ua200', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'va500', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'clt', 'psl', 'rsus', 'ua850', 'tas', 'tasmax', 'rlds', 'ps', 'zg500', 'rsds', 'evspsbl', 'huss', 'pr', 'va850', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'tasmax', 'rlds', 'tasmin', 'pr', 'tasmax', 'rlds', 'tasmin', 'pr', 'ua850', 'huss', 'sfcWind', 'zg500', 'psl', 'rsus', 'va850', 'rsds', 'evspsbl', 'tas', 'clt']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'tasmax', 'rlds', 'tasmin', 'pr', 'ua850', 'huss', 'sfcWind', 'zg500', 'psl', 'rsus', 'va850', 'rsds', 'evspsbl', 'tas', 'clt']</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'va850', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'va850', 'clt', 'zg500', 'rlds', 'rsds', 'pr', 'ua850', 'huss', 'rsus', 'evspsbl', 'psl']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'va850', 'clt', 'zg500', 'rlds', 'rsds', 'pr', 'ua850', 'huss', 'rsus', 'evspsbl', 'psl']</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>['hfss', 'clwvi', 'hfls', 'clivi', 'prhmax', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'prw', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ta500', 'ta850', 'ua200', 'ua500', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'rsus', 'tas', 'va850', 'tasmin', 'huss', 'evspsbl', 'rsds', 'rsus', 'tas', 'va850', 'tasmin', 'huss', 'evspsbl', 'clt', 'psl', 'rlds', 'ua850', 'zg500', 'pr', 'tasmax', 'sfcWind', 'ps']</t>
+          <t>['hfss', 'clwvi', 'hfls', 'clivi', 'prhmax', 'mrfso', 'mrso', 'prc', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'prw', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ta500', 'ta850', 'ua200', 'ua500', 'ts', 'wsgsmax', 'zmla', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'rsus', 'tas', 'va850', 'tasmin', 'huss', 'evspsbl', 'clt', 'psl', 'rlds', 'ua850', 'zg500', 'pr', 'tasmax', 'sfcWind', 'ps']</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua200', 'ua500', 'ta500', 'ta850', 'vas', 'zg200', 'va200', 'va500', 'zg500', 'huss', 'ua850', 'pr', 'zg500', 'huss', 'ua850', 'pr', 'rlds', 'sfcWind', 'rsus', 'evspsbl', 'va850', 'rsds', 'clt', 'tasmin', 'psl', 'tasmax', 'tas']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua200', 'ua500', 'ta500', 'ta850', 'vas', 'zg200', 'va200', 'va500', 'zg500', 'huss', 'ua850', 'pr', 'rlds', 'sfcWind', 'rsus', 'evspsbl', 'va850', 'rsds', 'clt', 'tasmin', 'psl', 'tasmax', 'tas']</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'va850', 'clt', 'evspsbl', 'rlds', 'rsus', 'tasmin', 'ua850', 'pr']</t>
+          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg500', 'psl', 'sfcWind', 'huss', 'tas', 'rsds', 'tasmax', 'va850', 'clt', 'evspsbl', 'rlds', 'rsus', 'tasmin', 'ua850', 'pr']</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ts', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rsus', 'rsds', 'evspsbl', 'ps', 'huss', 'ua850', 'pr', 'tas', 'tasmin', 'zg500']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ts', 'clwvi', 'clivi', 'wsgsmax', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'zmla', 'rlds', 'psl', 'va850', 'clt', 'tasmax', 'sfcWind', 'rsus', 'rsds', 'evspsbl', 'ps', 'huss', 'ua850', 'pr', 'tas', 'tasmin', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'sfcWind', 'ua850', 'rsds', 'sfcWind', 'ua850', 'zg500', 'pr', 'tasmin', 'va850', 'clt', 'rlds', 'psl', 'evspsbl', 'huss', 'tasmax', 'rsus', 'tas']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrros', 'mrro', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hfss', 'hfls', 'mrfso', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'rsds', 'sfcWind', 'ua850', 'zg500', 'pr', 'tasmin', 'va850', 'clt', 'rlds', 'psl', 'evspsbl', 'huss', 'tasmax', 'rsus', 'tas']</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'zg500', 'psl', 'tasmin', 'huss', 'ua850', 'va850', 'clt', 'zg500', 'psl', 'tasmin', 'huss', 'ua850', 'va850', 'clt', 'tas', 'pr', 'evspsbl', 'rsus', 'tasmax', 'sfcWind', 'rsds', 'rlds']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'va200', 'ua200', 'ua500', 'ta850', 'vas', 'zg200', 'va500', 'zg500', 'psl', 'tasmin', 'huss', 'ua850', 'va850', 'clt', 'tas', 'pr', 'evspsbl', 'rsus', 'tasmax', 'sfcWind', 'rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>['prhmax', 'rlus', 'mrso', 'prc', 'prw', 'wsgsmax', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'tas', 'pr', 'clt', 'ps', 'huss', 'rsds', 'rsus', 'zg500']</t>
+          <t>['prhmax', 'rlus', 'mrso', 'prc', 'prw', 'wsgsmax', 'zmla', 'zg200', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clivi', 'hfss', 'clwvi', 'hfls', 'mrfso', 'mrros', 'hus850', 'mrro', 'vas', 'uas', 'va200', 'va500', 'ua500', 'ua200', 'ts', 'sfcWind', 'psl', 'tasmax', 'rlds', 'ua850', 'va850', 'tasmin', 'tas', 'pr', 'clt', 'ps', 'huss', 'rsds', 'rsus', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'clt', 'tasmax', 'rlds', 'huss', 'tasmin', 'zg500', 'ua850', 'rsus']</t>
+          <t>['hfss', 'hfls', 'hus850', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'rlus', 'mrfso', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'pr', 'rsds', 'va850', 'sfcWind', 'tas', 'psl', 'clt', 'tasmax', 'rlds', 'huss', 'tasmin', 'zg500', 'ua850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'ua850', 'tasmin', 'rsus', 'sfcWind', 'rlds', 'pr', 'tas']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'mrros', 'sfcWindmax', 'rsut', 'snm', 'snw', 'snc', 'sund', 'snd', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'vas', 'zg200', 'uas', 'va200', 'va500', 'zg500', 'huss', 'tasmax', 'rsds', 'clt', 'psl', 'va850', 'ua850', 'tasmin', 'rsus', 'sfcWind', 'rlds', 'pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'tasmax', 'rsds', 'psl', 'sfcWind', 'huss', 'tasmax', 'rsds', 'psl', 'sfcWind', 'huss', 'zg500', 'ua850', 'pr', 'tasmin', 'tas', 'rlds', 'clt', 'ps', 'va850', 'rsus']</t>
+          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'hfss', 'clwvi', 'hfls', 'mrfso', 'clivi', 'hus850', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ts', 'tasmax', 'rsds', 'psl', 'sfcWind', 'huss', 'zg500', 'ua850', 'pr', 'tasmin', 'tas', 'rlds', 'clt', 'ps', 'va850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'zg500', 'sfcWind', 'rlds', 'pr', 'zg500', 'sfcWind', 'rlds', 'pr', 'tasmax', 'va850', 'psl', 'tas', 'rsds', 'clt', 'ua850', 'tasmin', 'rsus', 'huss']</t>
+          <t>['hfls', 'hfss', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'vas', 'zg200', 'zg500', 'sfcWind', 'rlds', 'pr', 'tasmax', 'va850', 'psl', 'tas', 'rsds', 'clt', 'ua850', 'tasmin', 'rsus', 'huss']</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'psl', 'rsds', 'tasmax', 'sfcWind', 'zg500', 'rlds', 'pr', 'psl', 'rsds', 'tasmax', 'sfcWind', 'zg500', 'rlds', 'pr', 'huss', 'tas', 'tasmin', 'clt', 'ua850', 'va850', 'rsus']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'vas', 'zg200', 'uas', 'va200', 'va500', 'ua500', 'psl', 'rsds', 'tasmax', 'sfcWind', 'zg500', 'rlds', 'pr', 'huss', 'tas', 'tasmin', 'clt', 'ua850', 'va850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'tas', 'rlds', 'tasmin', 'tas', 'rlds', 'tasmin', 'tasmax', 'clt', 'va850', 'rsds', 'rsus', 'psl', 'ps', 'ua850', 'huss', 'sfcWind', 'pr', 'zg500']</t>
+          <t>['wsgsmax', 'zmla', 'vas', 'zg200', 'va200', 'va500', 'hfss', 'clwvi', 'hfls', 'clivi', 'hus850', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'ua200', 'ua500', 'ts', 'prhmax', 'mrfso', 'mrso', 'prc', 'prw', 'mrros', 'mrro', 'tas', 'rlds', 'tasmin', 'tasmax', 'clt', 'va850', 'rsds', 'rsus', 'psl', 'ps', 'ua850', 'huss', 'sfcWind', 'pr', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'va200', 'ua200', 'ua500', 'vas', 'zg200', 'va500', 'rsus', 'pr', 'ua850', 'tas', 'rsus', 'pr', 'ua850', 'tas', 'zg500', 'rlds', 'clt', 'tasmin', 'rsds', 'sfcWind', 'tasmax', 'va850', 'psl', 'huss']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'snd', 'uas', 'ta850', 'va200', 'ua200', 'ua500', 'vas', 'zg200', 'va500', 'rsus', 'pr', 'ua850', 'tas', 'zg500', 'rlds', 'clt', 'tasmin', 'rsds', 'sfcWind', 'tasmax', 'va850', 'psl', 'huss']</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg200', 'tas', 'tasmin', 'rlds', 'pr', 'rsus', 'tas', 'tasmin', 'rlds', 'pr', 'rsus', 'zg500', 'rsds', 'va850', 'tasmax', 'ua850', 'psl', 'clt', 'huss']</t>
+          <t>['hfss', 'hfls', 'mrfso', 'mrso', 'mrros', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snc', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'zg200', 'tas', 'tasmin', 'rlds', 'pr', 'rsus', 'zg500', 'rsds', 'va850', 'tasmax', 'ua850', 'psl', 'clt', 'huss']</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>['evspsbl', 'evspsbl']</t>
+          <t>['evspsbl']</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'sfcWind', 'sfcWind']</t>
+          <t>['sfcWindmax', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m', 'tas', 'tds', 'pr', 'prc', 'ua100m', 'va100m', 'tas', 'tds', 'pr', 'prc']</t>
+          <t>['ua100m', 'va100m', 'tas', 'tds', 'pr', 'prc']</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'psl', 'rlds', 'rlus', 'rsds', 'ts', 'sund', 'tas', 'cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'psl', 'rlds', 'rlus', 'rsds', 'ts', 'sund', 'tas']</t>
+          <t>['cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'psl', 'rlds', 'rlus', 'rsds', 'ts', 'sund', 'tas']</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>['prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus400', 'hus500', 'hus600', 'hus700', 'va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va100', 'va200', 'va700', 'va850', 'va300', 'va400', 'va500', 'va600', 'ta925', 'ts', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua100', 'ua200', 'ta100', 'ta200', 'ta300', 'ta400', 'ta700', 'ta850', 'ta500', 'ta600', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'zg925', 'zmla', 'zg700', 'zg850', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus400', 'hus500', 'hus600', 'hus700', 'va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va100', 'va200', 'va700', 'va850', 'va300', 'va400', 'va500', 'va600', 'ta925', 'ts', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua100', 'ua200', 'ta100', 'ta200', 'ta300', 'ta400', 'ta700', 'ta850', 'ta500', 'ta600', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'zg925', 'zmla', 'zg700', 'zg850']</t>
+          <t>['prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus400', 'hus500', 'hus600', 'hus700', 'va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va100', 'va200', 'va700', 'va850', 'va300', 'va400', 'va500', 'va600', 'ta925', 'ts', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua100', 'ua200', 'ta100', 'ta200', 'ta300', 'ta400', 'ta700', 'ta850', 'ta500', 'ta600', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'zg925', 'zmla', 'zg700', 'zg850']</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>['zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'tas', 'tasmax', 'tasmin', 'ts', 'ua925', 'uas', 'va100', 'va200', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'ua500', 'ua600', 'ua700', 'ua850', 'ua100', 'ua200', 'ua300', 'ua400', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'rlds', 'rlus', 'rlut', 'psl', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'clh', 'clivi', 'cll', 'clm', 'clt', 'prhmax', 'prsn', 'prw', 'ps', 'mrros', 'mrso', 'pr', 'prc', 'hus925', 'huss', 'mrfso', 'mrro', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'tas', 'tasmax', 'tasmin', 'ts', 'ua925', 'uas', 'va100', 'va200', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'ua500', 'ua600', 'ua700', 'ua850', 'ua100', 'ua200', 'ua300', 'ua400', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'rlds', 'rlus', 'rlut', 'psl', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'clh', 'clivi', 'cll', 'clm', 'clt', 'prhmax', 'prsn', 'prw', 'ps', 'mrros', 'mrso', 'pr', 'prc', 'hus925', 'huss', 'mrfso', 'mrro', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850']</t>
+          <t>['zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'tas', 'tasmax', 'tasmin', 'ts', 'ua925', 'uas', 'va100', 'va200', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'ua500', 'ua600', 'ua700', 'ua850', 'ua100', 'ua200', 'ua300', 'ua400', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'rlds', 'rlus', 'rlut', 'psl', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'clh', 'clivi', 'cll', 'clm', 'clt', 'prhmax', 'prsn', 'prw', 'ps', 'mrros', 'mrso', 'pr', 'prc', 'hus925', 'huss', 'mrfso', 'mrro', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850']</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>['clt', 'evspsbl', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'zg700', 'zg850', 'zg925', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'clt', 'evspsbl', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'zg700', 'zg850', 'zg925', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600']</t>
+          <t>['clt', 'evspsbl', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'zg700', 'zg850', 'zg925', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600']</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>['zg600', 'zg700', 'zg850', 'zg925', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'zg300', 'zg400', 'zg500']</t>
+          <t>['zg600', 'zg700', 'zg850', 'zg925', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'zg300', 'zg400', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>['tds', 'tas', 'prc', 'pr', 'prc', 'pr']</t>
+          <t>['tds', 'tas', 'prc', 'pr']</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'pr', 'tas', 'ts', 'rsds', 'rlds', 'rsus', 'rlus', 'prc', 'sfcWind', 'psl', 'sund', 'ps', 'tas', 'ts', 'rsds', 'rlds', 'rsus', 'rlus', 'prc', 'sfcWind', 'psl', 'sund', 'ps']</t>
+          <t>['hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'pr', 'tas', 'ts', 'rsds', 'rlds', 'rsus', 'rlus', 'prc', 'sfcWind', 'psl', 'sund', 'ps']</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>['hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'vas', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'clwvi', 'clh', 'evspsbl', 'clivi', 'cll', 'clm', 'mrfso', 'mrso', 'prw', 'mrros', 'hus850', 'hus925', 'mrro', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ts', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'snd', 'uas', 'va100', 'va200', 'va300', 'ua700', 'ua850', 'ua925', 'zmla', 'zg850', 'zg925', 'clwvi', 'clh', 'evspsbl', 'clivi', 'cll', 'clm', 'mrfso', 'mrso', 'prw', 'mrros', 'hus850', 'hus925', 'mrro', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ts', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'snd', 'uas', 'va100', 'va200', 'va300', 'ua700', 'ua850', 'ua925', 'zmla', 'zg850', 'zg925']</t>
+          <t>['hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'vas', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'clwvi', 'clh', 'evspsbl', 'clivi', 'cll', 'clm', 'mrfso', 'mrso', 'prw', 'mrros', 'hus850', 'hus925', 'mrro', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ts', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'snd', 'uas', 'va100', 'va200', 'va300', 'ua700', 'ua850', 'ua925', 'zmla', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>['hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'mrfso', 'huss', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta100', 'ta200', 'snd', 'wsgsmax', 'vas', 'zg100', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'clh', 'clivi', 'cll', 'clm', 'clt', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'ps', 'pr', 'tas', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'ua600', 'ua700', 'ua850', 'ua925', 'rlut', 'sfcWind', 'psl', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'mrfso', 'huss', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta100', 'ta200', 'snd', 'wsgsmax', 'vas', 'zg100', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'clh', 'clivi', 'cll', 'clm', 'clt', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'ps', 'pr', 'tas', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'ua600', 'ua700', 'ua850', 'ua925']</t>
+          <t>['hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'mrfso', 'huss', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'sfcWindmax', 'snm', 'snw', 'snc', 'sund', 'ta100', 'ta200', 'snd', 'wsgsmax', 'vas', 'zg100', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'clh', 'clivi', 'cll', 'clm', 'clt', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'ps', 'pr', 'tas', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'ua600', 'ua700', 'ua850', 'ua925']</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ta700', 'ta850', 'ta925', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'rsds', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'uas', 'va100', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'vas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va850', 'va925', 'va700', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ta700', 'ta850', 'ta925', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'rsds', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'uas', 'va100', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'vas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va850', 'va925', 'va700']</t>
+          <t>['rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ta700', 'ta850', 'ta925', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'rsds', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'uas', 'va100', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'vas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va850', 'va925', 'va700']</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'clt', 'mrfso', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'vas', 'va925', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'clt', 'mrfso', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'vas', 'va925', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'clt', 'mrfso', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'vas', 'va925', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr', 'prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
+          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rlus', 'prc', 'psl', 'ps', 'pr', 'cape', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'rsus', 'sfcWind', 'tas', 'sund', 'ts', 'rsds', 'rlds', 'rlus', 'prc', 'psl', 'ps', 'pr', 'cape', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'rsus', 'sfcWind', 'tas', 'sund', 'ts']</t>
+          <t>['rsds', 'rlds', 'rlus', 'prc', 'psl', 'ps', 'pr', 'cape', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'rsus', 'sfcWind', 'tas', 'sund', 'ts']</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>['hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ua200', 'ua100', 'ta850', 'ta700', 'ta925', 'ts', 'vas', 'zg100', 'va925', 'va600', 'va700', 'va850', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clwvi', 'evspsbl', 'clivi', 'cll', 'clm', 'hus100', 'hus200', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua925', 'clh', 'rlut', 'mrfso', 'mrso', 'prw', 'mrros', 'hus925', 'mrro', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'zmla', 'zg925', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ua200', 'ua100', 'ta850', 'ta700', 'ta925', 'ts', 'vas', 'zg100', 'va925', 'va600', 'va700', 'va850', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clwvi', 'evspsbl', 'clivi', 'cll', 'clm', 'hus100', 'hus200', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua925', 'clh', 'rlut', 'mrfso', 'mrso', 'prw', 'mrros', 'hus925', 'mrro', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'zmla', 'zg925']</t>
+          <t>['hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ua200', 'ua100', 'ta850', 'ta700', 'ta925', 'ts', 'vas', 'zg100', 'va925', 'va600', 'va700', 'va850', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clwvi', 'evspsbl', 'clivi', 'cll', 'clm', 'hus100', 'hus200', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'ua850', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua925', 'clh', 'rlut', 'mrfso', 'mrso', 'prw', 'mrros', 'hus925', 'mrro', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'zmla', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'uas', 'va100', 'va200', 'va300', 'ua600', 'ua700', 'ua850', 'ua925', 'zmla', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'mrfso', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'sfcWindmax', 'sfcWind', 'snm', 'snw', 'sund', 'snc', 'ta100', 'snd', 'zg200', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zg100', 'zg300', 'clh', 'clm', 'cll', 'clivi', 'clt', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'mrro', 'ps', 'pr', 'ta400', 'ta200', 'ta300', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'wsgsmax', 'vas', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'uas', 'va100', 'va200', 'va300', 'ua600', 'ua700', 'ua850', 'ua925', 'zmla', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'mrfso', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'sfcWindmax', 'sfcWind', 'snm', 'snw', 'sund', 'snc', 'ta100', 'snd', 'zg200', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zg100', 'zg300', 'clh', 'clm', 'cll', 'clivi', 'clt', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'mrro', 'ps', 'pr', 'ta400', 'ta200', 'ta300', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'wsgsmax', 'vas', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
+          <t>['rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'uas', 'va100', 'va200', 'va300', 'ua600', 'ua700', 'ua850', 'ua925', 'zmla', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'mrfso', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'sfcWindmax', 'sfcWind', 'snm', 'snw', 'sund', 'snc', 'ta100', 'snd', 'zg200', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zg100', 'zg300', 'clh', 'clm', 'cll', 'clivi', 'clt', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'mrro', 'ps', 'pr', 'ta400', 'ta200', 'ta300', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'wsgsmax', 'vas', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'sund', 'ta300', 'ta100', 'ta200', 'ta400', 'ta600', 'ta700', 'ta850', 'ta500', 'uas', 'va100', 'va200', 'va300', 'va400', 'ua600', 'ua700', 'ua850', 'ua925', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg300', 'zg100', 'zg200', 'va925', 'va500', 'va600', 'va700', 'va850', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'sund', 'ta300', 'ta100', 'ta200', 'ta400', 'ta600', 'ta700', 'ta850', 'ta500', 'uas', 'va100', 'va200', 'va300', 'va400', 'ua600', 'ua700', 'ua850', 'ua925', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg300', 'zg100', 'zg200', 'va925', 'va500', 'va600', 'va700', 'va850', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'sund', 'ta300', 'ta100', 'ta200', 'ta400', 'ta600', 'ta700', 'ta850', 'ta500', 'uas', 'va100', 'va200', 'va300', 'va400', 'ua600', 'ua700', 'ua850', 'ua925', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'vas', 'zg300', 'zg100', 'zg200', 'va925', 'va500', 'va600', 'va700', 'va850', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'mrfso', 'mrso', 'mrros', 'huss', 'hus850', 'hus925', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snm', 'snw', 'snc', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'snd', 'tasmax', 'tasmin', 'tas', 'ua100', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'vas', 'zg700', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'hfls', 'evspsbl', 'clt', 'va850', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va925', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'mrfso', 'mrso', 'mrros', 'huss', 'hus850', 'hus925', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snm', 'snw', 'snc', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'snd', 'tasmax', 'tasmin', 'tas', 'ua100', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'vas', 'zg700', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'hfls', 'evspsbl', 'clt', 'va850', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va925']</t>
+          <t>['hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'mrfso', 'mrso', 'mrros', 'huss', 'hus850', 'hus925', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snm', 'snw', 'snc', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'snd', 'tasmax', 'tasmin', 'tas', 'ua100', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'vas', 'zg700', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'hfls', 'evspsbl', 'clt', 'va850', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va925']</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>['cape', 'hfls', 'hfss', 'clt', 'evspsbl', 'hurs', 'huss', 'rsds', 'rsus', 'rlds', 'rlus', 'sfcWind', 'sund', 'pr', 'prc', 'ps', 'psl', 'tas', 'ts', 'rsds', 'rsus', 'rlds', 'rlus', 'sfcWind', 'sund', 'pr', 'prc', 'ps', 'psl', 'tas', 'ts']</t>
+          <t>['cape', 'hfls', 'hfss', 'clt', 'evspsbl', 'hurs', 'huss', 'rsds', 'rsus', 'rlds', 'rlus', 'sfcWind', 'sund', 'pr', 'prc', 'ps', 'psl', 'tas', 'ts']</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>['snd', 'snm', 'snw', 'ta100', 'ts', 'ua100', 'ua400', 'ua500', 'ua200', 'ua300', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsut', 'snc', 'rlut', 'rsdt', 'hus925', 'mrfso', 'mrso', 'prw', 'mrro', 'mrros', 'hus100', 'hus200', 'hus700', 'hus850', 'hus300', 'hus400', 'hus500', 'hus600', 'vas', 'zg100', 'uas', 'va100', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua850', 'ua925', 'ua600', 'ua700', 'zmla', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'clwvi', 'evspsbl', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'evspsbl', 'clh', 'clivi', 'cll', 'clm']</t>
+          <t>['snd', 'snm', 'snw', 'ta100', 'ts', 'ua100', 'ua400', 'ua500', 'ua200', 'ua300', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsut', 'snc', 'rlut', 'rsdt', 'hus925', 'mrfso', 'mrso', 'prw', 'mrro', 'mrros', 'hus100', 'hus200', 'hus700', 'hus850', 'hus300', 'hus400', 'hus500', 'hus600', 'vas', 'zg100', 'uas', 'va100', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua850', 'ua925', 'ua600', 'ua700', 'zmla', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'clwvi', 'evspsbl', 'clh', 'clivi', 'cll', 'clm']</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>['evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'clt', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'clt', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m', 'tas', 'tds', 'pr', 'prc', 'ua100m', 'va100m', 'tas', 'tds', 'pr', 'prc']</t>
+          <t>['ua100m', 'va100m', 'tas', 'tds', 'pr', 'prc']</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'rsus', 'sfcWind', 'psl', 'rlds', 'rlus', 'rsds', 'prc', 'ps', 'ts', 'sund', 'tas', 'huss', 'pr', 'cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'rsus', 'sfcWind', 'psl', 'rlds', 'rlus', 'rsds', 'prc', 'ps', 'ts', 'sund', 'tas', 'huss', 'pr']</t>
+          <t>['cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'rsus', 'sfcWind', 'psl', 'rlds', 'rlus', 'rsds', 'prc', 'ps', 'ts', 'sund', 'tas', 'huss', 'pr']</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>['va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'va700', 'va850', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua700', 'ua850', 'ua500', 'ua600', 'zg925', 'zmla', 'zg700', 'zg850', 'zg300', 'zg400', 'zg500', 'zg600', 'snm', 'snw', 'snc', 'snd', 'ta925', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ta100', 'ta200', 'ta700', 'ta850', 'ta300', 'ta400', 'ta500', 'ta600', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'evspsbl', 'hus100', 'rsdt', 'rsut', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clm', 'clwvi', 'clivi', 'cll', 'clh', 'va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'va700', 'va850', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua700', 'ua850', 'ua500', 'ua600', 'zg925', 'zmla', 'zg700', 'zg850', 'zg300', 'zg400', 'zg500', 'zg600', 'snm', 'snw', 'snc', 'snd', 'ta925', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ta100', 'ta200', 'ta700', 'ta850', 'ta300', 'ta400', 'ta500', 'ta600', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'evspsbl', 'hus100', 'rsdt', 'rsut', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clm', 'clwvi', 'clivi', 'cll', 'clh']</t>
+          <t>['va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'va700', 'va850', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua700', 'ua850', 'ua500', 'ua600', 'zg925', 'zmla', 'zg700', 'zg850', 'zg300', 'zg400', 'zg500', 'zg600', 'snm', 'snw', 'snc', 'snd', 'ta925', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ta100', 'ta200', 'ta700', 'ta850', 'ta300', 'ta400', 'ta500', 'ta600', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'evspsbl', 'hus100', 'rsdt', 'rsut', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clm', 'clwvi', 'clivi', 'cll', 'clh']</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clh', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg700', 'zg850', 'zg925', 'zmla', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clh', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg700', 'zg850', 'zg925', 'zmla', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clh', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg700', 'zg850', 'zg925', 'zmla', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600']</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>['zg700', 'zg850', 'zg925', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'clt', 'zg700', 'zg850', 'zg925', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'clt']</t>
+          <t>['zg700', 'zg850', 'zg925', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'clt']</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>['pr', 'prc', 'tas', 'tds', 'va100m', 'ua100m', 'pr', 'prc', 'tas', 'tds', 'va100m', 'ua100m']</t>
+          <t>['pr', 'prc', 'tas', 'tds', 'va100m', 'ua100m']</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prc', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'sund', 'tas', 'ts', 'cape', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prc', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'sund', 'tas', 'ts']</t>
+          <t>['cape', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prc', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'sund', 'tas', 'ts']</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'ua700', 'ua850', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snc', 'mrro', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ta850', 'ta925', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'mrfso', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'snm', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'ua700', 'ua850', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snc', 'mrro', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ta850', 'ta925', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'mrfso', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925']</t>
+          <t>['snm', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'ua700', 'ua850', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snc', 'mrro', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ta850', 'ta925', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'mrfso', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925']</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>['zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'ta700', 'ta850', 'ta925', 'tas', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'hus600', 'hus700', 'hus850', 'hus925', 'ta300', 'ta400', 'ta500', 'ta600', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'ta700', 'ta850', 'ta925', 'tas', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'hus600', 'hus700', 'hus850', 'hus925', 'ta300', 'ta400', 'ta500', 'ta600']</t>
+          <t>['zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'ta700', 'ta850', 'ta925', 'tas', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'hus600', 'hus700', 'hus850', 'hus925', 'ta300', 'ta400', 'ta500', 'ta600']</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>['ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg700', 'zg850', 'zg925', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va200', 'va300', 'va400', 'va500', 'va600', 'va850', 'va925', 'vas', 'zg100', 'va700', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'clt', 'evspsbl', 'hfls', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg700', 'zg850', 'zg925', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va200', 'va300', 'va400', 'va500', 'va600', 'va850', 'va925', 'vas', 'zg100', 'va700', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'clt', 'evspsbl', 'hfls', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700']</t>
+          <t>['ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg700', 'zg850', 'zg925', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va200', 'va300', 'va400', 'va500', 'va600', 'va850', 'va925', 'vas', 'zg100', 'va700', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'clt', 'evspsbl', 'hfls', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700']</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>['hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'clt', 'evspsbl', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'clt', 'evspsbl', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'clt', 'evspsbl', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m', 'pr', 'prc', 'tas', 'tds', 'ua100m', 'va100m', 'pr', 'prc', 'tas', 'tds']</t>
+          <t>['ua100m', 'va100m', 'pr', 'prc', 'tas', 'tds']</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'psl', 'rlds', 'ts', 'sund', 'tas', 'cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'psl', 'rlds', 'ts', 'sund', 'tas']</t>
+          <t>['cape', 'clt', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'psl', 'rlds', 'ts', 'sund', 'tas']</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>['va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va100', 'va200', 'va700', 'va850', 'va300', 'va400', 'va500', 'va600', 'ta925', 'ts', 'ua700', 'ua850', 'ua100', 'ua200', 'ua500', 'ua600', 'ua300', 'ua400', 'ta100', 'ta200', 'ta700', 'ta850', 'ta300', 'ta400', 'ta500', 'ta600', 'zg925', 'zmla', 'zg700', 'zg850', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus400', 'hus500', 'hus600', 'hus700', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va100', 'va200', 'va700', 'va850', 'va300', 'va400', 'va500', 'va600', 'ta925', 'ts', 'ua700', 'ua850', 'ua100', 'ua200', 'ua500', 'ua600', 'ua300', 'ua400', 'ta100', 'ta200', 'ta700', 'ta850', 'ta300', 'ta400', 'ta500', 'ta600', 'zg925', 'zmla', 'zg700', 'zg850', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus400', 'hus500', 'hus600', 'hus700', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300']</t>
+          <t>['va925', 'vas', 'ua925', 'uas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va100', 'va200', 'va700', 'va850', 'va300', 'va400', 'va500', 'va600', 'ta925', 'ts', 'ua700', 'ua850', 'ua100', 'ua200', 'ua500', 'ua600', 'ua300', 'ua400', 'ta100', 'ta200', 'ta700', 'ta850', 'ta300', 'ta400', 'ta500', 'ta600', 'zg925', 'zmla', 'zg700', 'zg850', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus400', 'hus500', 'hus600', 'hus700', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300']</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va300', 'va400', 'va500', 'va600', 'ua400', 'ua500', 'ua600', 'ua700', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clh', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va300', 'va400', 'va500', 'va600', 'ua400', 'ua500', 'ua600', 'ua700', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clh', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500']</t>
+          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va300', 'va400', 'va500', 'va600', 'ua400', 'ua500', 'ua600', 'ua700', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clh', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600']</t>
+          <t>['psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600']</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>['snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'clt', 'evspsbl', 'hfls', 'hfss', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'clt', 'evspsbl', 'hfls', 'hfss', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut']</t>
+          <t>['snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'clt', 'evspsbl', 'hfls', 'hfss', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut']</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr', 'prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
+          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>['rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'cape', 'evspsbl', 'clt', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts', 'rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'cape', 'evspsbl', 'clt', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts']</t>
+          <t>['rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'cape', 'evspsbl', 'clt', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts']</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>['clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'uas', 'ua200', 'ua925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clh', 'clivi', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'ua100', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg925', 'clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'uas', 'ua200', 'ua925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clh', 'clivi', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'ua100', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg925']</t>
+          <t>['clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'uas', 'ua200', 'ua925', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'clh', 'clivi', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'ua100', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'zmla', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'psl', 'rlds', 'rlus', 'rlut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'tas', 'tasmax', 'tasmin', 'ts', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'prhmax', 'prsn', 'prw', 'ps', 'hfls', 'hfss', 'hurs', 'hus100', 'mrros', 'mrso', 'pr', 'prc', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'huss', 'mrfso', 'mrro', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'uas', 'va100', 'va200', 'ua700', 'ua850', 'ua925', 'rsds', 'rsdt', 'rsus', 'rsut', 'psl', 'rlds', 'rlus', 'rlut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'tas', 'tasmax', 'tasmin', 'ts', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'prhmax', 'prsn', 'prw', 'ps', 'hfls', 'hfss', 'hurs', 'hus100', 'mrros', 'mrso', 'pr', 'prc', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'huss', 'mrfso', 'mrro', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'uas', 'va100', 'va200', 'ua700', 'ua850', 'ua925']</t>
+          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'psl', 'rlds', 'rlus', 'rlut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'tas', 'tasmax', 'tasmin', 'ts', 'ta600', 'ta700', 'ta850', 'ta925', 'ta200', 'ta300', 'ta400', 'ta500', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'prhmax', 'prsn', 'prw', 'ps', 'hfls', 'hfss', 'hurs', 'hus100', 'mrros', 'mrso', 'pr', 'prc', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'huss', 'mrfso', 'mrro', 'zg850', 'zg925', 'zmla', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'vas', 'zg400', 'zg500', 'zg600', 'zg700', 'va300', 'va400', 'va500', 'va600', 'uas', 'va100', 'va200', 'ua700', 'ua850', 'ua925']</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clt', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'uas', 'va100', 'va200', 'va300', 'va400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'va500', 'va600', 'va700', 'va850', 'va925', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clt', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'uas', 'va100', 'va200', 'va300', 'va400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'clt', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'uas', 'va100', 'va200', 'va300', 'va400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>['rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ua925', 'uas', 'va100', 'va200', 'va300', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ua925', 'uas', 'va100', 'va200', 'va300', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ua925', 'uas', 'va100', 'va200', 'va300', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>['pr', 'prc', 'tds', 'tas', 'pr', 'prc', 'tds', 'tas']</t>
+          <t>['pr', 'prc', 'tds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>['hfss', 'huss', 'hurs', 'tas', 'ts', 'rsds', 'rsus', 'rlus', 'clt', 'hfls', 'evspsbl', 'sfcWind', 'sund', 'rlds', 'psl', 'prc', 'ps', 'pr', 'hfss', 'huss', 'hurs', 'tas', 'ts', 'rsds', 'rsus', 'rlus', 'clt', 'hfls', 'evspsbl', 'sfcWind', 'sund', 'rlds', 'psl', 'prc', 'ps', 'pr']</t>
+          <t>['hfss', 'huss', 'hurs', 'tas', 'ts', 'rsds', 'rsus', 'rlus', 'clt', 'hfls', 'evspsbl', 'sfcWind', 'sund', 'rlds', 'psl', 'prc', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>['rlut', 'mrso', 'prw', 'ua100', 'ts', 'uas', 'va100', 'va200', 'va300', 'clwvi', 'evspsbl', 'hus100', 'mrfso', 'mrros', 'mrro', 'ta100', 'ta200', 'clh', 'ta300', 'ta400', 'ta500', 'ta600', 'zg200', 'zg300', 'zg400', 'rsdt', 'rsut', 'snc', 'zmla', 'zg850', 'zg925', 'cll', 'clm', 'clivi', 'hus400', 'hus500', 'hus600', 'ua200', 'ua300', 'ua400', 'ua500', 'va400', 'va500', 'va600', 'snm', 'snw', 'snd', 'ua600', 'ua700', 'ua850', 'ua925', 'hus700', 'hus850', 'hus925', 'ta700', 'ta850', 'ta925', 'hus200', 'hus300', 'vas', 'zg100', 'va700', 'va850', 'va925', 'zg500', 'zg600', 'zg700', 'rlut', 'mrso', 'prw', 'ua100', 'ts', 'uas', 'va100', 'va200', 'va300', 'clwvi', 'evspsbl', 'hus100', 'mrfso', 'mrros', 'mrro', 'ta100', 'ta200', 'clh', 'ta300', 'ta400', 'ta500', 'ta600', 'zg200', 'zg300', 'zg400', 'rsdt', 'rsut', 'snc', 'zmla', 'zg850', 'zg925', 'cll', 'clm', 'clivi', 'hus400', 'hus500', 'hus600', 'ua200', 'ua300', 'ua400', 'ua500', 'va400', 'va500', 'va600', 'snm', 'snw', 'snd', 'ua600', 'ua700', 'ua850', 'ua925', 'hus700', 'hus850', 'hus925', 'ta700', 'ta850', 'ta925', 'hus200', 'hus300', 'vas', 'zg100', 'va700', 'va850', 'va925', 'zg500', 'zg600', 'zg700']</t>
+          <t>['rlut', 'mrso', 'prw', 'ua100', 'ts', 'uas', 'va100', 'va200', 'va300', 'clwvi', 'evspsbl', 'hus100', 'mrfso', 'mrros', 'mrro', 'ta100', 'ta200', 'clh', 'ta300', 'ta400', 'ta500', 'ta600', 'zg200', 'zg300', 'zg400', 'rsdt', 'rsut', 'snc', 'zmla', 'zg850', 'zg925', 'cll', 'clm', 'clivi', 'hus400', 'hus500', 'hus600', 'ua200', 'ua300', 'ua400', 'ua500', 'va400', 'va500', 'va600', 'snm', 'snw', 'snd', 'ua600', 'ua700', 'ua850', 'ua925', 'hus700', 'hus850', 'hus925', 'ta700', 'ta850', 'ta925', 'hus200', 'hus300', 'vas', 'zg100', 'va700', 'va850', 'va925', 'zg500', 'zg600', 'zg700']</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>['tasmax', 'tas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'mrfso', 'huss', 'mrros', 'hus700', 'hus850', 'hus925', 'mrro', 'wsgsmax', 'vas', 'zg200', 'zg300', 'zg400', 'zg100', 'va925', 'clh', 'clivi', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'psl', 'ps', 'zmla', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'hfss', 'clwvi', 'hfls', 'clm', 'cll', 'evspsbl', 'clt', 'uas', 'va100', 'ua600', 'ua700', 'ua850', 'ua925', 'prhmax', 'mrso', 'prc', 'prw', 'prsn', 'pr', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'mrfso', 'huss', 'mrros', 'hus700', 'hus850', 'hus925', 'mrro', 'wsgsmax', 'vas', 'zg200', 'zg300', 'zg400', 'zg100', 'va925', 'clh', 'clivi', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'psl', 'ps', 'zmla', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'hfss', 'clwvi', 'hfls', 'clm', 'cll', 'evspsbl', 'clt', 'uas', 'va100', 'ua600', 'ua700', 'ua850', 'ua925', 'prhmax', 'mrso', 'prc', 'prw', 'prsn', 'pr', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850']</t>
+          <t>['tasmax', 'tas', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ts', 'mrfso', 'huss', 'mrros', 'hus700', 'hus850', 'hus925', 'mrro', 'wsgsmax', 'vas', 'zg200', 'zg300', 'zg400', 'zg100', 'va925', 'clh', 'clivi', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'psl', 'ps', 'zmla', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'hfss', 'clwvi', 'hfls', 'clm', 'cll', 'evspsbl', 'clt', 'uas', 'va100', 'ua600', 'ua700', 'ua850', 'ua925', 'prhmax', 'mrso', 'prc', 'prw', 'prsn', 'pr', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850']</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'mrfso', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'uas', 'va100', 'va200', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'clt', 'zg850', 'zg925', 'zg700', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'snd', 'rlds', 'rlus', 'mrfso', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'uas', 'va100', 'va200', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'clt', 'zg850', 'zg925', 'zg700', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'snd']</t>
+          <t>['rlds', 'rlus', 'mrfso', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'uas', 'va100', 'va200', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'clt', 'zg850', 'zg925', 'zg700', 'huss', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'snd']</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>['uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua925', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'vas', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'psl', 'pr', 'hfss', 'hfls', 'evspsbl', 'clt', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'tasmax', 'tasmin', 'tas', 'ta700', 'ta850', 'ta925', 'ua100', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'mrfso', 'mrso', 'huss', 'mrros', 'hus850', 'hus925', 'mrro', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua925', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'vas', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'psl', 'pr', 'hfss', 'hfls', 'evspsbl', 'clt', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'tasmax', 'tasmin', 'tas', 'ta700', 'ta850', 'ta925', 'ua100', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'mrfso', 'mrso', 'huss', 'mrros', 'hus850', 'hus925', 'mrro', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd']</t>
+          <t>['uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua925', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'vas', 'zg100', 'zg200', 'zg300', 'va700', 'va850', 'va925', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'psl', 'pr', 'hfss', 'hfls', 'evspsbl', 'clt', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'tasmax', 'tasmin', 'tas', 'ta700', 'ta850', 'ta925', 'ua100', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'mrfso', 'mrso', 'huss', 'mrros', 'hus850', 'hus925', 'mrro', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd']</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>['tas', 'tds', 'pr', 'prc', 'tas', 'tds', 'pr', 'prc']</t>
+          <t>['tas', 'tds', 'pr', 'prc']</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m', 'ua100m', 'va100m']</t>
+          <t>['ua100m', 'va100m']</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'psl', 'rlds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'ts', 'sund', 'tas', 'cape', 'clt', 'psl', 'rlds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'ts', 'sund', 'tas']</t>
+          <t>['cape', 'clt', 'psl', 'rlds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'rlus', 'rsds', 'ts', 'sund', 'tas']</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>['prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus600', 'hus700', 'ta100', 'ta200', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'va700', 'va850', 'va100', 'va200', 'va500', 'va600', 'va300', 'va400', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'hus400', 'hus500', 'ta925', 'ts', 'ua925', 'uas', 'ta700', 'ta850', 'ta300', 'ta400', 'ua700', 'ua850', 'ta500', 'ta600', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg925', 'zmla', 'prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus600', 'hus700', 'ta100', 'ta200', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'va700', 'va850', 'va100', 'va200', 'va500', 'va600', 'va300', 'va400', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'hus400', 'hus500', 'ta925', 'ts', 'ua925', 'uas', 'ta700', 'ta850', 'ta300', 'ta400', 'ua700', 'ua850', 'ta500', 'ta600', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg925', 'zmla']</t>
+          <t>['prw', 'rlut', 'mrros', 'mrso', 'mrfso', 'mrro', 'rsdt', 'rsut', 'snm', 'snw', 'snc', 'snd', 'hus850', 'hus925', 'hus600', 'hus700', 'ta100', 'ta200', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'va700', 'va850', 'va100', 'va200', 'va500', 'va600', 'va300', 'va400', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus200', 'hus300', 'hus400', 'hus500', 'ta925', 'ts', 'ua925', 'uas', 'ta700', 'ta850', 'ta300', 'ta400', 'ua700', 'ua850', 'ta500', 'ta600', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'zg925', 'zmla']</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clh', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clh']</t>
+          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'va700', 'va850', 'va925', 'vas', 'wsgsmax', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clh']</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>['clt', 'zg600', 'zg700', 'zg850', 'zg925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'clt', 'zg600', 'zg700', 'zg850', 'zg925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
+          <t>['clt', 'zg600', 'zg700', 'zg850', 'zg925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg600', 'zg700', 'zg850', 'zg925', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg600', 'zg700', 'zg850', 'zg925']</t>
+          <t>['rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'zg600', 'zg700', 'zg850', 'zg925']</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>['tas', 'tds', 'pr', 'prc', 'tas', 'tds', 'pr', 'prc']</t>
+          <t>['tas', 'tds', 'pr', 'prc']</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>['va100m', 'ua100m', 'va100m', 'ua100m']</t>
+          <t>['va100m', 'ua100m']</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'cape', 'clt', 'rlus', 'rsds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'ts', 'sund', 'tas', 'psl', 'rlds', 'cape', 'clt', 'rlus', 'rsds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'ts', 'sund', 'tas']</t>
+          <t>['psl', 'rlds', 'cape', 'clt', 'rlus', 'rsds', 'hfss', 'hurs', 'evspsbl', 'hfls', 'prc', 'ps', 'huss', 'pr', 'rsus', 'sfcWind', 'ts', 'sund', 'tas']</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>['zmla', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus600', 'hus700', 'hus200', 'hus300', 'hus400', 'hus500', 'vas', 'zg100', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'rsdt', 'rsut', 'prw', 'rlut', 'snd', 'snm', 'snc', 'mrros', 'mrso', 'mrfso', 'mrro', 'snw', 'ta100', 'hus850', 'hus925', 'ta200', 'ta300', 'uas', 'va100', 'ts', 'ua100', 'ta850', 'ta925', 'ua850', 'ua925', 'ta400', 'ta500', 'ta600', 'ta700', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'zmla', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus600', 'hus700', 'hus200', 'hus300', 'hus400', 'hus500', 'vas', 'zg100', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'rsdt', 'rsut', 'prw', 'rlut', 'snd', 'snm', 'snc', 'mrros', 'mrso', 'mrfso', 'mrro', 'snw', 'ta100', 'hus850', 'hus925', 'ta200', 'ta300', 'uas', 'va100', 'ts', 'ua100', 'ta850', 'ta925', 'ua850', 'ua925', 'ta400', 'ta500', 'ta600', 'ta700', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
+          <t>['zmla', 'clm', 'clwvi', 'clivi', 'cll', 'evspsbl', 'hus100', 'clh', 'hus600', 'hus700', 'hus200', 'hus300', 'hus400', 'hus500', 'vas', 'zg100', 'zg850', 'zg925', 'zg400', 'zg500', 'zg600', 'zg700', 'zg200', 'zg300', 'va850', 'va925', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'rsdt', 'rsut', 'prw', 'rlut', 'snd', 'snm', 'snc', 'mrros', 'mrso', 'mrfso', 'mrro', 'snw', 'ta100', 'hus850', 'hus925', 'ta200', 'ta300', 'uas', 'va100', 'ts', 'ua100', 'ta850', 'ta925', 'ua850', 'ua925', 'ta400', 'ta500', 'ta600', 'ta700', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>['hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'clh', 'clivi', 'cll', 'clm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snc', 'snd', 'snm', 'snw', 'sund', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'zg850', 'zg925', 'zmla', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'clh', 'clivi', 'cll', 'clm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snc', 'snd', 'snm', 'snw', 'sund', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'zg850', 'zg925', 'zmla', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100']</t>
+          <t>['hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'clh', 'clivi', 'cll', 'clm', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'snc', 'snd', 'snm', 'snw', 'sund', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'zg850', 'zg925', 'zmla', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100']</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>['pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clt', 'evspsbl', 'hfls', 'hfss', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clt', 'evspsbl', 'hfls', 'hfss']</t>
+          <t>['pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'clt', 'evspsbl', 'hfls', 'hfss']</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>['rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl']</t>
+          <t>['rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>['prc', 'tds', 'tas', 'pr', 'prc', 'tds', 'tas', 'pr']</t>
+          <t>['prc', 'tds', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ts', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ts']</t>
+          <t>['hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ts']</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>['ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va850', 'va925', 'mrfso', 'mrros', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'zg700', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'hus300', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va850', 'va925', 'mrfso', 'mrros', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'zg700', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'hus300']</t>
+          <t>['ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'snm', 'snw', 'snc', 'snd', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'va850', 'va925', 'mrfso', 'mrros', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'zg700', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'hus300']</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'clh', 'cll', 'clm', 'clivi', 'clt', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'clh', 'cll', 'clm', 'clivi', 'clt', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
+          <t>['snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'mrfso', 'huss', 'mrros', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'zmla', 'zg850', 'zg925', 'rlds', 'prhmax', 'mrso', 'prc', 'prw', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'clh', 'cll', 'clm', 'clivi', 'clt', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'clwvi', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>['tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'huss', 'hus200', 'hus300', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hus400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'huss', 'hus200', 'hus300', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hus400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd']</t>
+          <t>['tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'ua100', 'ua200', 'ua300', 'ua400', 'vas', 'zg100', 'zg200', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'clt', 'uas', 'va100', 'va200', 'va300', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'rlds', 'rlus', 'mrfso', 'rlut', 'mrso', 'mrros', 'psl', 'mrro', 'pr', 'zg300', 'zg400', 'zg500', 'zg600', 'zg850', 'zg925', 'zg700', 'huss', 'hus200', 'hus300', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hus400', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snc', 'snd']</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>['mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg850', 'zg925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg850', 'zg925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl']</t>
+          <t>['mrfso', 'mrso', 'mrros', 'huss', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta925', 'ta850', 'evspsbl', 'clt', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg850', 'zg925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl']</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>['pr', 'prc', 'tas', 'tds', 'pr', 'prc', 'tas', 'tds']</t>
+          <t>['pr', 'prc', 'tas', 'tds']</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>['ua100m', 'va100m', 'ua100m', 'va100m']</t>
+          <t>['ua100m', 'va100m']</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>['cape', 'clt', 'evspsbl', 'hfls', 'tas', 'ts', 'cape', 'clt', 'evspsbl', 'hfls', 'tas', 'ts']</t>
+          <t>['cape', 'clt', 'evspsbl', 'hfls', 'tas', 'ts']</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'clh', 'clivi', 'hus925', 'mrfso', 'mrro', 'mrros', 'mrso', 'prw', 'rlut', 'rsdt', 'rsut', 'snc', 'snd', 'snm', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'ua100', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'clh', 'clivi', 'hus925', 'mrfso', 'mrro', 'mrros', 'mrso', 'prw', 'rlut', 'rsdt', 'rsut', 'snc', 'snd', 'snm', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'ua100', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300']</t>
+          <t>['zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'clh', 'clivi', 'hus925', 'mrfso', 'mrro', 'mrros', 'mrso', 'prw', 'rlut', 'rsdt', 'rsut', 'snc', 'snd', 'snm', 'cll', 'clm', 'clwvi', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ts', 'ua100', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300']</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>['hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700']</t>
+          <t>['hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'va850', 'va925', 'vas', 'wsgsmax', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'zmla', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ts', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700']</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>['zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clt', 'evspsbl', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clt', 'evspsbl']</t>
+          <t>['zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>['snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700']</t>
+          <t>['snc', 'snd', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700']</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr', 'prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
+          <t>['prc', 'va100m', 'ua100m', 'tds', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>['cape', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ps', 'ts', 'cape', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ps', 'ts']</t>
+          <t>['cape', 'hfss', 'hfls', 'evspsbl', 'prc', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'sfcWind', 'psl', 'tas', 'sund', 'ps', 'ts']</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>['clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'mrfso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'snw', 'ta300', 'ta100', 'ta200', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'zmla', 'zg600', 'zg850', 'zg700', 'zg925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snm', 'snc', 'snd', 'ta925', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua200', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'mrfso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'snw', 'ta300', 'ta100', 'ta200', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'zmla', 'zg600', 'zg850', 'zg700', 'zg925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snm', 'snc', 'snd', 'ta925', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua200', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925']</t>
+          <t>['clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'hus200', 'mrfso', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'snw', 'ta300', 'ta100', 'ta200', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'zmla', 'zg600', 'zg850', 'zg700', 'zg925', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snm', 'snc', 'snd', 'ta925', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua200', 'ts', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>['clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'ta700', 'ta850', 'ta925', 'tas', 'ta300', 'ta400', 'ta500', 'ta600', 'clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'ta700', 'ta850', 'ta925', 'tas', 'ta300', 'ta400', 'ta500', 'ta600']</t>
+          <t>['clh', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus600', 'hus700', 'hus850', 'hus925', 'hus200', 'hus300', 'hus400', 'hus500', 'zg925', 'zmla', 'tasmax', 'tasmin', 'ts', 'ua100', 'va850', 'va925', 'vas', 'wsgsmax', 'uas', 'va100', 'va200', 'va300', 'zg500', 'zg600', 'zg700', 'zg850', 'zg100', 'zg200', 'zg300', 'zg400', 'ua600', 'ua700', 'ua850', 'ua925', 'va400', 'va500', 'va600', 'va700', 'ua200', 'ua300', 'ua400', 'ua500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'mrso', 'pr', 'prc', 'prhmax', 'huss', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'ps', 'psl', 'snw', 'sund', 'ta100', 'ta200', 'ta700', 'ta850', 'ta925', 'tas', 'ta300', 'ta400', 'ta500', 'ta600']</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>['clt', 'evspsbl', 'hfls', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'clt', 'evspsbl', 'hfls', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
+          <t>['clt', 'evspsbl', 'hfls', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'hus925', 'huss', 'mrfso', 'mrro', 'mrros', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>['mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
+          <t>['mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'hus700', 'hus850', 'hus925', 'huss', 'mrfso', 'mrro', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'sfcWind', 'sfcWindmax', 'snc', 'snd', 'snm', 'snw', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'tas', 'tasmax', 'tasmin', 'ua100', 'ua200', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'ua850', 'ua925', 'uas', 'va100', 'va200', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>['prc', 'tds', 'tas', 'pr', 'prc', 'tds', 'tas', 'pr']</t>
+          <t>['prc', 'tds', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>['rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts', 'evspsbl', 'clt', 'rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr', 'rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts', 'evspsbl', 'clt', 'rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr']</t>
+          <t>['rsds', 'rsus', 'rlus', 'sfcWind', 'tas', 'sund', 'ts', 'evspsbl', 'clt', 'rlds', 'hfss', 'hfls', 'prc', 'huss', 'hurs', 'psl', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>['clh', 'clivi', 'zmla', 'zg925', 'zg700', 'zg850', 'clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'clh', 'clivi', 'zmla', 'zg925', 'zg700', 'zg850', 'clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600']</t>
+          <t>['clh', 'clivi', 'zmla', 'zg925', 'zg700', 'zg850', 'clwvi', 'cll', 'clm', 'evspsbl', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'mrfso', 'mrso', 'prw', 'mrros', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'rsdt', 'rsut', 'rlut', 'snm', 'snw', 'snc', 'ta100', 'ta200', 'snd', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ts', 'uas', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600']</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>['sund', 'ta100', 'ta200', 'ta300', 'tasmin', 'ua100', 'ua200', 'ua300', 'ts', 'wsgsmax', 'vas', 'va850', 'va925', 'zmla', 'zg925', 'mrfso', 'mrso', 'huss', 'mrros', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'rlds', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'psl', 'prsn', 'ps', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'ta400', 'ta500', 'ta600', 'ta700', 'ua400', 'ua500', 'ua600', 'ua700', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg500', 'zg600', 'zg700', 'zg850', 'clwvi', 'clh', 'clm', 'cll', 'evspsbl', 'clivi', 'clt', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'tasmax', 'tas', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'ua850', 'ua925', 'zg300', 'zg200', 'zg400', 'zg100', 'sund', 'ta100', 'ta200', 'ta300', 'tasmin', 'ua100', 'ua200', 'ua300', 'ts', 'wsgsmax', 'vas', 'va850', 'va925', 'zmla', 'zg925', 'mrfso', 'mrso', 'huss', 'mrros', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'rlds', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'psl', 'prsn', 'ps', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'ta400', 'ta500', 'ta600', 'ta700', 'ua400', 'ua500', 'ua600', 'ua700', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg500', 'zg600', 'zg700', 'zg850', 'clwvi', 'clh', 'clm', 'cll', 'evspsbl', 'clivi', 'clt', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'tasmax', 'tas', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'ua850', 'ua925', 'zg300', 'zg200', 'zg400', 'zg100']</t>
+          <t>['sund', 'ta100', 'ta200', 'ta300', 'tasmin', 'ua100', 'ua200', 'ua300', 'ts', 'wsgsmax', 'vas', 'va850', 'va925', 'zmla', 'zg925', 'mrfso', 'mrso', 'huss', 'mrros', 'hus700', 'hus850', 'hus925', 'mrro', 'pr', 'rlds', 'prhmax', 'rlus', 'rlut', 'prc', 'prw', 'psl', 'prsn', 'ps', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snm', 'snw', 'snc', 'snd', 'ta400', 'ta500', 'ta600', 'ta700', 'ua400', 'ua500', 'ua600', 'ua700', 'va300', 'va400', 'va500', 'va600', 'va700', 'zg500', 'zg600', 'zg700', 'zg850', 'clwvi', 'clh', 'clm', 'cll', 'evspsbl', 'clivi', 'clt', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'tasmax', 'tas', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'ua850', 'ua925', 'zg300', 'zg200', 'zg400', 'zg100']</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>['hfls', 'evspsbl', 'clt', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'rsds', 'rsus', 'rlus', 'rsdt', 'rlut', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'uas', 'ua600', 'ua700', 'ua850', 'ua925', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'mrfso', 'mrros', 'huss', 'hus925', 'mrro', 'sfcWindmax', 'rsut', 'sfcWind', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'zg700', 'zg850', 'zg925', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'rlds', 'mrso', 'psl', 'pr', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'vas', 'zg100', 'va700', 'va850', 'va925', 'hfls', 'evspsbl', 'clt', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'rsds', 'rsus', 'rlus', 'rsdt', 'rlut', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'uas', 'ua600', 'ua700', 'ua850', 'ua925', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'mrfso', 'mrros', 'huss', 'hus925', 'mrro', 'sfcWindmax', 'rsut', 'sfcWind', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'zg700', 'zg850', 'zg925', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'rlds', 'mrso', 'psl', 'pr', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'vas', 'zg100', 'va700', 'va850', 'va925']</t>
+          <t>['hfls', 'evspsbl', 'clt', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'rsds', 'rsus', 'rlus', 'rsdt', 'rlut', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'uas', 'ua600', 'ua700', 'ua850', 'ua925', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'mrfso', 'mrros', 'huss', 'hus925', 'mrro', 'sfcWindmax', 'rsut', 'sfcWind', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ta850', 'ta925', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'zg700', 'zg850', 'zg925', 'hfss', 'hurs', 'hus100', 'hus200', 'hus300', 'rlds', 'mrso', 'psl', 'pr', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'vas', 'zg100', 'va700', 'va850', 'va925']</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>['hus400', 'hus500', 'hus600', 'hus700', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'ua925', 'va400', 'va500', 'va600', 'va700', 'va850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va925', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'evspsbl', 'clt', 'mrfso', 'huss', 'mrros', 'hus850', 'hus925', 'mrro', 'sfcWindmax', 'sfcWind', 'snm', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'rlds', 'rlus', 'mrso', 'psl', 'pr', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'hus400', 'hus500', 'hus600', 'hus700', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'ua925', 'va400', 'va500', 'va600', 'va700', 'va850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va925', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'evspsbl', 'clt', 'mrfso', 'huss', 'mrros', 'hus850', 'hus925', 'mrro', 'sfcWindmax', 'sfcWind', 'snm', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'rlds', 'rlus', 'mrso', 'psl', 'pr', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850']</t>
+          <t>['hus400', 'hus500', 'hus600', 'hus700', 'rsds', 'rsus', 'rsdt', 'rsut', 'rlut', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'uas', 'va100', 'va200', 'va300', 'ua925', 'va400', 'va500', 'va600', 'va700', 'va850', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va925', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'evspsbl', 'clt', 'mrfso', 'huss', 'mrros', 'hus850', 'hus925', 'mrro', 'sfcWindmax', 'sfcWind', 'snm', 'snc', 'snd', 'tasmax', 'tasmin', 'tas', 'ua100', 'ua200', 'hfss', 'hfls', 'hurs', 'hus100', 'hus200', 'hus300', 'rlds', 'rlus', 'mrso', 'psl', 'pr', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>['tds', 'prc', 'tas', 'pr', 'tds', 'prc', 'tas', 'pr']</t>
+          <t>['tds', 'prc', 'tas', 'pr']</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>['tas', 'ts', 'rsds', 'rlds', 'rsus', 'rlus', 'prc', 'sfcWind', 'psl', 'sund', 'ps', 'cape', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'pr', 'tas', 'ts', 'rsds', 'rlds', 'rsus', 'rlus', 'prc', 'sfcWind', 'psl', 'sund', 'ps', 'cape', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'pr']</t>
+          <t>['tas', 'ts', 'rsds', 'rlds', 'rsus', 'rlus', 'prc', 'sfcWind', 'psl', 'sund', 'ps', 'cape', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'clt', 'pr']</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snc', 'mrro', 'snd', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'zmla', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va600', 'va700', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'ua700', 'ua850', 'ua925', 'ta850', 'ta925', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ts', 'snm', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snc', 'mrro', 'snd', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'zmla', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va600', 'va700', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'ua700', 'ua850', 'ua925', 'ta850', 'ta925', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ts']</t>
+          <t>['snm', 'snw', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'rsdt', 'rsut', 'rlut', 'mrso', 'prw', 'mrros', 'snc', 'mrro', 'snd', 'mrfso', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'clwvi', 'clh', 'cll', 'clm', 'evspsbl', 'clivi', 'hus100', 'zmla', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'va600', 'va700', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'ua700', 'ua850', 'ua925', 'ta850', 'ta925', 'ua200', 'ua100', 'ua300', 'ua400', 'ua500', 'ua600', 'ts']</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'mrro', 'ps', 'pr', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hfss', 'clwvi', 'hfls', 'clm', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'zmla', 'zg925', 'zg600', 'zg700', 'zg850', 'clh', 'cll', 'clivi', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'mrro', 'ps', 'pr', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hfss', 'clwvi', 'hfls', 'clm', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'zmla', 'zg925', 'zg600', 'zg700', 'zg850', 'clh', 'cll', 'clivi', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
+          <t>['sfcWindmax', 'snm', 'snw', 'sund', 'snc', 'ta100', 'ta200', 'ta300', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'psl', 'prhmax', 'mrso', 'prc', 'prw', 'mrros', 'prsn', 'mrro', 'ps', 'pr', 'mrfso', 'huss', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'hfss', 'clwvi', 'hfls', 'clm', 'evspsbl', 'hurs', 'hus100', 'hus200', 'clt', 'zmla', 'zg925', 'zg600', 'zg700', 'zg850', 'clh', 'cll', 'clivi', 'wsgsmax', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'ua925', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ts', 'tasmax', 'tasmin', 'tas', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925']</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>['snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'rlds', 'mrfso', 'mrso', 'mrros', 'huss', 'hus925', 'psl', 'mrro', 'pr', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hfss', 'hfls', 'evspsbl', 'clt', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'uas', 'va100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ua200', 'snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'rlds', 'mrfso', 'mrso', 'mrros', 'huss', 'hus925', 'psl', 'mrro', 'pr', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hfss', 'hfls', 'evspsbl', 'clt', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'uas', 'va100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ua200']</t>
+          <t>['snm', 'snw', 'sund', 'ta100', 'ta200', 'ta300', 'ta400', 'ta500', 'snd', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snc', 'rlds', 'mrfso', 'mrso', 'mrros', 'huss', 'hus925', 'psl', 'mrro', 'pr', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'hus500', 'hus600', 'hus700', 'hus850', 'hfss', 'hfls', 'evspsbl', 'clt', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'va200', 'va300', 'va400', 'va500', 'va600', 'va700', 'va850', 'va925', 'uas', 'va100', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'ua850', 'ua925', 'tasmax', 'tasmin', 'tas', 'ta600', 'ta700', 'ta850', 'ta925', 'ua100', 'ua200']</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>['tas', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'sfcWindmax', 'rsut', 'sfcWind', 'snm', 'snw', 'sund', 'snc', 'ta100', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'pr', 'mrfso', 'mrros', 'huss', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'clt', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700', 'tas', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'sfcWindmax', 'rsut', 'sfcWind', 'snm', 'snw', 'sund', 'snc', 'ta100', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'pr', 'mrfso', 'mrros', 'huss', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'clt', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
+          <t>['tas', 'ta200', 'ta300', 'ta400', 'ta500', 'ta600', 'ta700', 'ta850', 'ta925', 'sfcWindmax', 'rsut', 'sfcWind', 'snm', 'snw', 'sund', 'snc', 'ta100', 'snd', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'pr', 'mrfso', 'mrros', 'huss', 'hus500', 'hus600', 'hus700', 'hus850', 'hus925', 'mrro', 'hfss', 'hfls', 'evspsbl', 'hurs', 'hus100', 'hus200', 'hus300', 'hus400', 'clt', 'zg600', 'zg700', 'zg850', 'zg925', 'vas', 'zg100', 'zg200', 'zg300', 'zg400', 'zg500', 'va700', 'va850', 'va925', 'uas', 'va100', 'va200', 'va300', 'va400', 'va500', 'va600', 'ua850', 'ua925', 'tasmax', 'tasmin', 'ua100', 'ua200', 'ua300', 'ua400', 'ua500', 'ua600', 'ua700']</t>
         </is>
       </c>
     </row>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>['clwvi', 'rlds', 'clivi', 'tasmin', 'va850', 'prc', 'sic', 'hurs', 'hus850', 'va500', 'rsus', 'mrros', 'ta850', 'hfls', 'cll', 'ua200', 'rlut', 'sfcWind', 'uas', 'tauv', 'snc', 'evspsbl', 'rlus', 'clm', 'huss', 'ts', 'hfss', 'psl', 'prhmax', 'clt', 'clh', 'vas', 'ua850', 'va200', 'tasmax', 'snm', 'rsut', 'ua500', 'ta500', 'rsdt', 'mrro', 'pr', 'tauu', 'mrso', 'prw', 'sfcWindmax', 'rsds', 'ps', 'ta200', 'tas', 'prsn', 'clwvi', 'rlds', 'clivi', 'tasmin', 'va850', 'prc', 'sic', 'hurs', 'hus850', 'va500', 'rsus', 'mrros', 'ta850', 'hfls', 'cll', 'ua200', 'rlut', 'sfcWind', 'uas', 'tauv', 'snc', 'evspsbl', 'rlus', 'clm', 'huss', 'ts', 'hfss', 'psl', 'prhmax', 'clt', 'clh', 'vas', 'ua850', 'va200', 'tasmax', 'snm', 'rsut', 'ua500', 'ta500', 'rsdt', 'mrro', 'pr', 'tauu', 'mrso', 'prw', 'sfcWindmax', 'rsds', 'ps', 'ta200', 'tas', 'prsn']</t>
+          <t>['clwvi', 'rlds', 'clivi', 'tasmin', 'va850', 'prc', 'sic', 'hurs', 'hus850', 'va500', 'rsus', 'mrros', 'ta850', 'hfls', 'cll', 'ua200', 'rlut', 'sfcWind', 'uas', 'tauv', 'snc', 'evspsbl', 'rlus', 'clm', 'huss', 'ts', 'hfss', 'psl', 'prhmax', 'clt', 'clh', 'vas', 'ua850', 'va200', 'tasmax', 'snm', 'rsut', 'ua500', 'ta500', 'rsdt', 'mrro', 'pr', 'tauu', 'mrso', 'prw', 'sfcWindmax', 'rsds', 'ps', 'ta200', 'tas', 'prsn']</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>['ta850', 'va200', 'rlds', 'sfcWind', 'ua500', 'snc', 'hurs', 'hus850', 'tas', 'ta200', 'hfls', 'rsdt', 'pr', 'vas', 'rlus', 'huss', 'va500', 'clt', 'ua200', 'hfss', 'psl', 'va850', 'snm', 'rsut', 'tasmin', 'rlut', 'uas', 'sic', 'ua850', 'rsus', 'mrro', 'tasmax', 'mrso', 'sfcWindmax', 'rsds', 'ta500', 'evspsbl', 'mrros', 'ta850', 'va200', 'rlds', 'sfcWind', 'ua500', 'snc', 'hurs', 'hus850', 'tas', 'ta200', 'hfls', 'rsdt', 'pr', 'vas', 'rlus', 'huss', 'va500', 'clt', 'ua200', 'hfss', 'psl', 'va850', 'snm', 'rsut', 'tasmin', 'rlut', 'uas', 'sic', 'ua850', 'rsus', 'mrro', 'tasmax', 'mrso', 'sfcWindmax', 'rsds', 'ta500', 'evspsbl', 'mrros']</t>
+          <t>['ta850', 'va200', 'rlds', 'sfcWind', 'ua500', 'snc', 'hurs', 'hus850', 'tas', 'ta200', 'hfls', 'rsdt', 'pr', 'vas', 'rlus', 'huss', 'va500', 'clt', 'ua200', 'hfss', 'psl', 'va850', 'snm', 'rsut', 'tasmin', 'rlut', 'uas', 'sic', 'ua850', 'rsus', 'mrro', 'tasmax', 'mrso', 'sfcWindmax', 'rsds', 'ta500', 'evspsbl', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg500', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>['hurs', 'vas', 'clt', 'evspsbl', 'psl', 'ua850', 'hfls', 'rsdt', 'hus850', 'pr', 'rlds', 'va200', 'snm', 'ua500', 'ta200', 'hfss', 'rlut', 'va850', 'tasmax', 'rsut', 'snc', 'rlus', 'huss', 'va500', 'sic', 'ua200', 'sfcWindmax', 'rsus', 'tasmin', 'mrros', 'tas', 'sfcWind', 'ta850', 'mrso', 'rsds', 'uas', 'ta500', 'mrro', 'hurs', 'vas', 'clt', 'evspsbl', 'psl', 'ua850', 'hfls', 'rsdt', 'hus850', 'pr', 'rlds', 'va200', 'snm', 'ua500', 'ta200', 'hfss', 'rlut', 'va850', 'tasmax', 'rsut', 'snc', 'rlus', 'huss', 'va500', 'sic', 'ua200', 'sfcWindmax', 'rsus', 'tasmin', 'mrros', 'tas', 'sfcWind', 'ta850', 'mrso', 'rsds', 'uas', 'ta500', 'mrro']</t>
+          <t>['hurs', 'vas', 'clt', 'evspsbl', 'psl', 'ua850', 'hfls', 'rsdt', 'hus850', 'pr', 'rlds', 'va200', 'snm', 'ua500', 'ta200', 'hfss', 'rlut', 'va850', 'tasmax', 'rsut', 'snc', 'rlus', 'huss', 'va500', 'sic', 'ua200', 'sfcWindmax', 'rsus', 'tasmin', 'mrros', 'tas', 'sfcWind', 'ta850', 'mrso', 'rsds', 'uas', 'ta500', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>['clt', 'sfcWindmax', 'rlds', 'tasmax', 'clh', 'sfcWind', 'ua200', 'vas', 'clm', 'va500', 'snm', 'psl', 'ps', 'hurs', 'prhmax', 'clivi', 'rsus', 'ta500', 'ts', 'hfls', 'rsdt', 'mrros', 'tauv', 'prc', 'huss', 'rlus', 'ua500', 'pr', 'hfss', 'hus850', 'va200', 'cll', 'snc', 'ua850', 'tasmin', 'rsut', 'sic', 'rlut', 'va850', 'mrro', 'ta850', 'mrso', 'ta200', 'clwvi', 'tauu', 'rsds', 'tas', 'evspsbl', 'uas', 'prw', 'prsn', 'clt', 'sfcWindmax', 'rlds', 'tasmax', 'clh', 'sfcWind', 'ua200', 'vas', 'clm', 'va500', 'snm', 'psl', 'ps', 'hurs', 'prhmax', 'clivi', 'rsus', 'ta500', 'ts', 'hfls', 'rsdt', 'mrros', 'tauv', 'prc', 'huss', 'rlus', 'ua500', 'pr', 'hfss', 'hus850', 'va200', 'cll', 'snc', 'ua850', 'tasmin', 'rsut', 'sic', 'rlut', 'va850', 'mrro', 'ta850', 'mrso', 'ta200', 'clwvi', 'tauu', 'rsds', 'tas', 'evspsbl', 'uas', 'prw', 'prsn']</t>
+          <t>['clt', 'sfcWindmax', 'rlds', 'tasmax', 'clh', 'sfcWind', 'ua200', 'vas', 'clm', 'va500', 'snm', 'psl', 'ps', 'hurs', 'prhmax', 'clivi', 'rsus', 'ta500', 'ts', 'hfls', 'rsdt', 'mrros', 'tauv', 'prc', 'huss', 'rlus', 'ua500', 'pr', 'hfss', 'hus850', 'va200', 'cll', 'snc', 'ua850', 'tasmin', 'rsut', 'sic', 'rlut', 'va850', 'mrro', 'ta850', 'mrso', 'ta200', 'clwvi', 'tauu', 'rsds', 'tas', 'evspsbl', 'uas', 'prw', 'prsn']</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg500', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'psl', 'ua850', 'rlds', 'vas', 'clt', 'ua500', 'hurs', 'va200', 'rsus', 'tasmax', 'rsut', 'hfls', 'snm', 'rlut', 'sfcWind', 'ta200', 'evspsbl', 'rlus', 'huss', 'hfss', 'va850', 'ua200', 'pr', 'sic', 'snc', 'va500', 'rsdt', 'mrro', 'mrros', 'tasmin', 'mrso', 'ta850', 'tas', 'rsds', 'hus850', 'uas', 'ta500', 'sfcWindmax', 'psl', 'ua850', 'rlds', 'vas', 'clt', 'ua500', 'hurs', 'va200', 'rsus', 'tasmax', 'rsut', 'hfls', 'snm', 'rlut', 'sfcWind', 'ta200', 'evspsbl', 'rlus', 'huss', 'hfss', 'va850', 'ua200', 'pr', 'sic', 'snc', 'va500', 'rsdt', 'mrro', 'mrros', 'tasmin', 'mrso', 'ta850', 'tas', 'rsds', 'hus850', 'uas', 'ta500']</t>
+          <t>['sfcWindmax', 'psl', 'ua850', 'rlds', 'vas', 'clt', 'ua500', 'hurs', 'va200', 'rsus', 'tasmax', 'rsut', 'hfls', 'snm', 'rlut', 'sfcWind', 'ta200', 'evspsbl', 'rlus', 'huss', 'hfss', 'va850', 'ua200', 'pr', 'sic', 'snc', 'va500', 'rsdt', 'mrro', 'mrros', 'tasmin', 'mrso', 'ta850', 'tas', 'rsds', 'hus850', 'uas', 'ta500']</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>['hurs', 'ua500', 'rsdt', 'va200', 'hfls', 'rlds', 'sic', 'ua850', 'rlut', 'snm', 'evspsbl', 'psl', 'ua200', 'sfcWind', 'tasmin', 'vas', 'va500', 'rsut', 'clt', 'rlus', 'huss', 'sfcWindmax', 'hus850', 'va850', 'hfss', 'rsus', 'tasmax', 'snc', 'uas', 'ta500', 'mrros', 'mrso', 'ta850', 'rsds', 'pr', 'tas', 'mrro', 'ta200', 'hurs', 'ua500', 'rsdt', 'va200', 'hfls', 'rlds', 'sic', 'ua850', 'rlut', 'snm', 'evspsbl', 'psl', 'ua200', 'sfcWind', 'tasmin', 'vas', 'va500', 'rsut', 'clt', 'rlus', 'huss', 'sfcWindmax', 'hus850', 'va850', 'hfss', 'rsus', 'tasmax', 'snc', 'uas', 'ta500', 'mrros', 'mrso', 'ta850', 'rsds', 'pr', 'tas', 'mrro', 'ta200']</t>
+          <t>['hurs', 'ua500', 'rsdt', 'va200', 'hfls', 'rlds', 'sic', 'ua850', 'rlut', 'snm', 'evspsbl', 'psl', 'ua200', 'sfcWind', 'tasmin', 'vas', 'va500', 'rsut', 'clt', 'rlus', 'huss', 'sfcWindmax', 'hus850', 'va850', 'hfss', 'rsus', 'tasmax', 'snc', 'uas', 'ta500', 'mrros', 'mrso', 'ta850', 'rsds', 'pr', 'tas', 'mrro', 'ta200']</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>['mrso', 'mrso']</t>
+          <t>['mrso']</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>['mrso', 'mrso']</t>
+          <t>['mrso']</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>['mrso', 'mrso']</t>
+          <t>['mrso']</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>['pr', 'hfss', 'hfls', 'rsus', 'rlds', 'rlus', 'rsds', 'rsds']</t>
+          <t>['pr', 'hfss', 'hfls', 'rsus', 'rlds', 'rlus', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>['hurs', 'huss', 'ps', 'psl', 'sfcWind', 'tas', 'hurs', 'huss', 'ps', 'psl', 'sfcWind', 'tas']</t>
+          <t>['hurs', 'huss', 'ps', 'psl', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>['prhmax', 'prhmax']</t>
+          <t>['prhmax']</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>['prhmax', 'ta200', 'tauv', 'rsut', 'prc', 'ts', 'rlut', 'prw', 'pr', 'cll', 'ua850', 'rsus', 'ta850', 'snm', 'va850', 'sic', 'rsds', 'tauu', 'mrso', 'uas', 'hfls', 'rsdt', 'ua200', 'clt', 'rlus', 'huss', 'tasmin', 'mrro', 'ps', 'sfcWind', 'tas', 'hfss', 'hurs', 'snc', 'va200', 'ta500', 'clwvi', 'clh', 'evspsbl', 'vas', 'clm', 'ua500', 'hus850', 'tasmax', 'sfcWindmax', 'rlds', 'clivi', 'psl', 'va500', 'mrros', 'prsn', 'prhmax', 'ta200', 'tauv', 'rsut', 'prc', 'ts', 'rlut', 'prw', 'pr', 'cll', 'ua850', 'rsus', 'ta850', 'snm', 'va850', 'sic', 'rsds', 'tauu', 'mrso', 'uas', 'hfls', 'rsdt', 'ua200', 'clt', 'rlus', 'huss', 'tasmin', 'mrro', 'ps', 'sfcWind', 'tas', 'hfss', 'hurs', 'snc', 'va200', 'ta500', 'clwvi', 'clh', 'evspsbl', 'vas', 'clm', 'ua500', 'hus850', 'tasmax', 'sfcWindmax', 'rlds', 'clivi', 'psl', 'va500', 'mrros', 'prsn']</t>
+          <t>['prhmax', 'ta200', 'tauv', 'rsut', 'prc', 'ts', 'rlut', 'prw', 'pr', 'cll', 'ua850', 'rsus', 'ta850', 'snm', 'va850', 'sic', 'rsds', 'tauu', 'mrso', 'uas', 'hfls', 'rsdt', 'ua200', 'clt', 'rlus', 'huss', 'tasmin', 'mrro', 'ps', 'sfcWind', 'tas', 'hfss', 'hurs', 'snc', 'va200', 'ta500', 'clwvi', 'clh', 'evspsbl', 'vas', 'clm', 'ua500', 'hus850', 'tasmax', 'sfcWindmax', 'rlds', 'clivi', 'psl', 'va500', 'mrros', 'prsn']</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>['tas', 'hfls', 'rsdt', 'hus850', 'psl', 'ua850', 'sfcWind', 'sic', 'ua200', 'evspsbl', 'hfss', 'pr', 'tasmin', 'ua500', 'snm', 'rlus', 'rsus', 'mrso', 'huss', 'snc', 'va500', 'tasmax', 'va850', 'mrro', 'rsds', 'uas', 'mrros', 'vas', 'ta850', 'rlds', 'hurs', 'clt', 'rsut', 'ta500', 'sfcWindmax', 'va200', 'ta200', 'rlut', 'tas', 'hfls', 'rsdt', 'hus850', 'psl', 'ua850', 'sfcWind', 'sic', 'ua200', 'evspsbl', 'hfss', 'pr', 'tasmin', 'ua500', 'snm', 'rlus', 'rsus', 'mrso', 'huss', 'snc', 'va500', 'tasmax', 'va850', 'mrro', 'rsds', 'uas', 'mrros', 'vas', 'ta850', 'rlds', 'hurs', 'clt', 'rsut', 'ta500', 'sfcWindmax', 'va200', 'ta200', 'rlut']</t>
+          <t>['tas', 'hfls', 'rsdt', 'hus850', 'psl', 'ua850', 'sfcWind', 'sic', 'ua200', 'evspsbl', 'hfss', 'pr', 'tasmin', 'ua500', 'snm', 'rlus', 'rsus', 'mrso', 'huss', 'snc', 'va500', 'tasmax', 'va850', 'mrro', 'rsds', 'uas', 'mrros', 'vas', 'ta850', 'rlds', 'hurs', 'clt', 'rsut', 'ta500', 'sfcWindmax', 'va200', 'ta200', 'rlut']</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>['rsds', 'ua500', 'snm', 'hfss', 'psl', 'ua200', 'sfcWind', 'tasmax', 'hfls', 'mrso', 'pr', 'uas', 'rsdt', 'sic', 'ua850', 'hurs', 'evspsbl', 'va850', 'rlut', 'sfcWindmax', 'va500', 'clt', 'mrros', 'rsut', 'rlus', 'huss', 'rsus', 'tas', 'ta500', 'snc', 'rlds', 'va200', 'hus850', 'mrro', 'ta200', 'ta850', 'tasmin', 'vas', 'rsds', 'ua500', 'snm', 'hfss', 'psl', 'ua200', 'sfcWind', 'tasmax', 'hfls', 'mrso', 'pr', 'uas', 'rsdt', 'sic', 'ua850', 'hurs', 'evspsbl', 'va850', 'rlut', 'sfcWindmax', 'va500', 'clt', 'mrros', 'rsut', 'rlus', 'huss', 'rsus', 'tas', 'ta500', 'snc', 'rlds', 'va200', 'hus850', 'mrro', 'ta200', 'ta850', 'tasmin', 'vas']</t>
+          <t>['rsds', 'ua500', 'snm', 'hfss', 'psl', 'ua200', 'sfcWind', 'tasmax', 'hfls', 'mrso', 'pr', 'uas', 'rsdt', 'sic', 'ua850', 'hurs', 'evspsbl', 'va850', 'rlut', 'sfcWindmax', 'va500', 'clt', 'mrros', 'rsut', 'rlus', 'huss', 'rsus', 'tas', 'ta500', 'snc', 'rlds', 'va200', 'hus850', 'mrro', 'ta200', 'ta850', 'tasmin', 'vas']</t>
         </is>
       </c>
     </row>
@@ -13605,7 +13605,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -14797,7 +14797,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg500', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>['hurs', 'huss', 'ps', 'psl', 'sfcWind', 'tas', 'hurs', 'huss', 'ps', 'psl', 'sfcWind', 'tas']</t>
+          <t>['hurs', 'huss', 'ps', 'psl', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>['cll', 'pr', 'snc', 'va500', 'prsn', 'rsus', 'prc', 'clivi', 'va850', 'ta200', 'sfcWindmax', 'tasmax', 'clwvi', 'ts', 'tauv', 'rsut', 'prw', 'rlus', 'huss', 'hfss', 'ta500', 'hurs', 'hfls', 'rsdt', 'hus850', 'rlds', 'ta850', 'sfcWind', 'mrros', 'tas', 'tasmin', 'evspsbl', 'ua500', 'snm', 'va200', 'mrso', 'psl', 'ua850', 'clt', 'ua200', 'uas', 'tauu', 'clm', 'clh', 'vas', 'ps', 'rsds', 'rlut', 'sic', 'mrro', 'rlut', 'sic', 'mrro']</t>
+          <t>['cll', 'pr', 'snc', 'va500', 'prsn', 'rsus', 'prc', 'clivi', 'va850', 'ta200', 'sfcWindmax', 'tasmax', 'clwvi', 'ts', 'tauv', 'rsut', 'prw', 'rlus', 'huss', 'hfss', 'ta500', 'hurs', 'hfls', 'rsdt', 'hus850', 'rlds', 'ta850', 'sfcWind', 'mrros', 'tas', 'tasmin', 'evspsbl', 'ua500', 'snm', 'va200', 'mrso', 'psl', 'ua850', 'clt', 'ua200', 'uas', 'tauu', 'clm', 'clh', 'vas', 'ps', 'rsds', 'rlut', 'sic', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>['prhmax', 'prhmax']</t>
+          <t>['prhmax']</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>['sfcWind', 'sic', 'ua500', 'hus850', 'va200', 'pr', 'rsus', 'sfcWindmax', 'mrros', 'ta850', 'rsut', 'rlus', 'evspsbl', 'huss', 'ta500', 'hfss', 'hurs', 'hfls', 'rsdt', 'uas', 'rlds', 'ta200', 'tas', 'snm', 'vas', 'rsds', 'psl', 'tasmin', 'rlut', 'snc', 'va850', 'mrso', 'ua200', 'clt', 'tasmax', 'va500', 'ua850', 'mrro', 'ua850', 'mrro']</t>
+          <t>['sfcWind', 'sic', 'ua500', 'hus850', 'va200', 'pr', 'rsus', 'sfcWindmax', 'mrros', 'ta850', 'rsut', 'rlus', 'evspsbl', 'huss', 'ta500', 'hfss', 'hurs', 'hfls', 'rsdt', 'uas', 'rlds', 'ta200', 'tas', 'snm', 'vas', 'rsds', 'psl', 'tasmin', 'rlut', 'snc', 'va850', 'mrso', 'ua200', 'clt', 'tasmax', 'va500', 'ua850', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>['rsus', 'va200', 'rlut', 'ua850', 'clt', 'vas', 'mrro', 'psl', 'rlus', 'huss', 'ta500', 'hfss', 'uas', 'sfcWind', 'mrros', 'ta850', 'rsut', 'tas', 'tasmax', 'rlds', 'tasmin', 'ta200', 'hurs', 'sfcWindmax', 'hus850', 'hfls', 'rsdt', 'ua200', 'pr', 'mrso', 'snc', 'sic', 'evspsbl', 'rsds', 'va500', 'va850', 'snm', 'ua500', 'snm', 'ua500']</t>
+          <t>['rsus', 'va200', 'rlut', 'ua850', 'clt', 'vas', 'mrro', 'psl', 'rlus', 'huss', 'ta500', 'hfss', 'uas', 'sfcWind', 'mrros', 'ta850', 'rsut', 'tas', 'tasmax', 'rlds', 'tasmin', 'ta200', 'hurs', 'sfcWindmax', 'hus850', 'hfls', 'rsdt', 'ua200', 'pr', 'mrso', 'snc', 'sic', 'evspsbl', 'rsds', 'va500', 'va850', 'snm', 'ua500']</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -15549,7 +15549,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>['sic', 'mrso', 'ua850', 'tas', 'ua200', 'rsus', 'mrros', 'huss', 'mrro', 'rlds', 'sfcWindmax', 'clwvi', 'rsut', 'clm', 'psl', 'tasmin', 'prw', 'ua500', 'prhmax', 'va500', 'clh', 'vas', 'ts', 'hfls', 'rsds', 'sfcWind', 'hus850', 'rlut', 'va850', 'rlus', 'tauv', 'rsdt', 'evspsbl', 'cll', 'snc', 'pr', 'tasmax', 'clivi', 'hfss', 'prc', 'hurs', 'ta850', 'uas', 'prsn', 'clt', 'ta500', 'va200', 'tauu', 'ps', 'ta200', 'snm', 'sic', 'mrso', 'ua850', 'tas', 'ua200', 'rsus', 'mrros', 'huss', 'mrro', 'rlds', 'sfcWindmax', 'clwvi', 'rsut', 'clm', 'psl', 'tasmin', 'prw', 'ua500', 'prhmax', 'va500', 'clh', 'vas', 'ts', 'hfls', 'rsds', 'sfcWind', 'hus850', 'rlut', 'va850', 'rlus', 'tauv', 'rsdt', 'evspsbl', 'cll', 'snc', 'pr', 'tasmax', 'clivi', 'hfss', 'prc', 'hurs', 'ta850', 'uas', 'prsn', 'clt', 'ta500', 'va200', 'tauu', 'ps', 'ta200', 'snm']</t>
+          <t>['sic', 'mrso', 'ua850', 'tas', 'ua200', 'rsus', 'mrros', 'huss', 'mrro', 'rlds', 'sfcWindmax', 'clwvi', 'rsut', 'clm', 'psl', 'tasmin', 'prw', 'ua500', 'prhmax', 'va500', 'clh', 'vas', 'ts', 'hfls', 'rsds', 'sfcWind', 'hus850', 'rlut', 'va850', 'rlus', 'tauv', 'rsdt', 'evspsbl', 'cll', 'snc', 'pr', 'tasmax', 'clivi', 'hfss', 'prc', 'hurs', 'ta850', 'uas', 'prsn', 'clt', 'ta500', 'va200', 'tauu', 'ps', 'ta200', 'snm']</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>['ta200', 'rsds', 'tasmin', 'mrros', 'mrro', 'rlds', 'sfcWindmax', 'ua850', 'clt', 'rsut', 'ta850', 'va850', 'tas', 'vas', 'ua200', 'rlut', 'uas', 'pr', 'ta500', 'hfls', 'rsdt', 'snc', 'sic', 'va200', 'snm', 'hurs', 'rsus', 'evspsbl', 'ua500', 'hfss', 'hus850', 'psl', 'tasmax', 'mrso', 'va500', 'sfcWind', 'rlus', 'huss', 'ta200', 'rsds', 'tasmin', 'mrros', 'mrro', 'rlds', 'sfcWindmax', 'ua850', 'clt', 'rsut', 'ta850', 'va850', 'tas', 'vas', 'ua200', 'rlut', 'uas', 'pr', 'ta500', 'hfls', 'rsdt', 'snc', 'sic', 'va200', 'snm', 'hurs', 'rsus', 'evspsbl', 'ua500', 'hfss', 'hus850', 'psl', 'tasmax', 'mrso', 'va500', 'sfcWind', 'rlus', 'huss']</t>
+          <t>['ta200', 'rsds', 'tasmin', 'mrros', 'mrro', 'rlds', 'sfcWindmax', 'ua850', 'clt', 'rsut', 'ta850', 'va850', 'tas', 'vas', 'ua200', 'rlut', 'uas', 'pr', 'ta500', 'hfls', 'rsdt', 'snc', 'sic', 'va200', 'snm', 'hurs', 'rsus', 'evspsbl', 'ua500', 'hfss', 'hus850', 'psl', 'tasmax', 'mrso', 'va500', 'sfcWind', 'rlus', 'huss']</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>['hfls', 'rsdt', 'va200', 'sfcWind', 'sic', 'mrros', 'huss', 'mrro', 'rsds', 'pr', 'tasmax', 'ua500', 'evspsbl', 'hfss', 'ta500', 'ua200', 'hus850', 'va500', 'rlds', 'vas', 'sfcWindmax', 'snc', 'ta850', 'ta200', 'hurs', 'rsus', 'rlut', 'rsut', 'snm', 'psl', 'mrso', 'uas', 'ua850', 'rlus', 'clt', 'tas', 'tasmin', 'va850', 'hfls', 'rsdt', 'va200', 'sfcWind', 'sic', 'mrros', 'huss', 'mrro', 'rsds', 'pr', 'tasmax', 'ua500', 'evspsbl', 'hfss', 'ta500', 'ua200', 'hus850', 'va500', 'rlds', 'vas', 'sfcWindmax', 'snc', 'ta850', 'ta200', 'hurs', 'rsus', 'rlut', 'rsut', 'snm', 'psl', 'mrso', 'uas', 'ua850', 'rlus', 'clt', 'tas', 'tasmin', 'va850']</t>
+          <t>['hfls', 'rsdt', 'va200', 'sfcWind', 'sic', 'mrros', 'huss', 'mrro', 'rsds', 'pr', 'tasmax', 'ua500', 'evspsbl', 'hfss', 'ta500', 'ua200', 'hus850', 'va500', 'rlds', 'vas', 'sfcWindmax', 'snc', 'ta850', 'ta200', 'hurs', 'rsus', 'rlut', 'rsut', 'snm', 'psl', 'mrso', 'uas', 'ua850', 'rlus', 'clt', 'tas', 'tasmin', 'va850']</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg200', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -16257,7 +16257,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg200', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps']</t>
+          <t>['hfls', 'hfss', 'hurs', 'huss', 'pr', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps']</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>['clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'clh', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'clh', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin']</t>
+          <t>['clivi', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'clh', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt', 'zg200', 'zg500', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt', 'zg200', 'zg500', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas']</t>
+          <t>['psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt', 'zg200', 'zg500', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas']</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>['mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500']</t>
+          <t>['mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl']</t>
+          <t>['rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl']</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>['clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'clh', 'clivi', 'cll', 'clm', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'zg200', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'clh', 'clivi', 'cll', 'clm', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'zg200', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas']</t>
+          <t>['clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'prc', 'prhmax', 'prsn', 'clh', 'clivi', 'cll', 'clm', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'zg200', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas']</t>
         </is>
       </c>
     </row>
@@ -16741,7 +16741,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>['hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'clt', 'evspsbl', 'hfls', 'hfss', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'clt', 'evspsbl', 'hfls', 'hfss', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850']</t>
+          <t>['hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'clt', 'evspsbl', 'hfls', 'hfss', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'clt', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'clt', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas']</t>
+          <t>['zg200', 'zg500', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'clt', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas']</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>['sfcWind', 'tas', 'hfls', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus']</t>
+          <t>['sfcWind', 'tas', 'hfls', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>['sic', 'ua500', 'ua200', 'sfcWindmax', 'uas', 'rsds', 'evspsbl', 'ta500', 'hurs', 'clivi', 'clt', 'prw', 'sfcWind', 'ua850', 'tasmax', 'clh', 'vas', 'va850', 'hfss', 'pr', 'clwvi', 'prsn', 'tasmin', 'rsus', 'ta200', 'tauu', 'cll', 'snc', 'prhmax', 'rlus', 'huss', 'snm', 'va500', 'ts', 'mrso', 'ta850', 'hfls', 'rsdt', 'hus850', 'rsut', 'rlut', 'rlds', 'va200', 'tauv', 'tas', 'prc', 'ps', 'clm', 'psl', 'mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['sic', 'ua500', 'ua200', 'sfcWindmax', 'uas', 'rsds', 'evspsbl', 'ta500', 'hurs', 'clivi', 'clt', 'prw', 'sfcWind', 'ua850', 'tasmax', 'clh', 'vas', 'va850', 'hfss', 'pr', 'clwvi', 'prsn', 'tasmin', 'rsus', 'ta200', 'tauu', 'cll', 'snc', 'prhmax', 'rlus', 'huss', 'snm', 'va500', 'ts', 'mrso', 'ta850', 'hfls', 'rsdt', 'hus850', 'rsut', 'rlut', 'rlds', 'va200', 'tauv', 'tas', 'prc', 'ps', 'clm', 'psl', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'clh', 'clivi', 'va850', 'vas', 'zg200', 'zg500', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'clh', 'clivi', 'va850', 'vas', 'zg200', 'zg500', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
+          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'prhmax', 'prsn', 'prw', 'ps', 'psl', 'cll', 'clm', 'clt', 'clwvi', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'clh', 'clivi', 'va850', 'vas', 'zg200', 'zg500', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>['vas', 'zg200', 'zg500', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt', 'vas', 'zg200', 'zg500', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt']</t>
+          <t>['vas', 'zg200', 'zg500', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snc', 'snd', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'clt']</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['hfls', 'hfss', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>['tasmax', 'tauu', 'mrso', 'snm', 'ua200', 'va500', 'rsds', 'ua850', 'snd', 'clwvi', 'rsut', 'sund', 'hfss', 'tas', 'tasmin', 'rlut', 'prsn', 'vas', 'clh', 'cll', 'ua500', 'prhmax', 'mrros', 'ta850', 'ps', 'uas', 'pr', 'sfcWind', 'hus850', 'ts', 'snc', 'sic', 'prc', 'hurs', 'snw', 'ta200', 'evspsbl', 'rsus', 'clt', 'clm', 'va850', 'zg200', 'va200', 'hfls', 'rsdt', 'ta500', 'sfcWindmax', 'rlds', 'prw', 'rlus', 'tauv', 'huss', 'zg500', 'mrro', 'psl', 'clivi', 'tasmax', 'tauu', 'mrso', 'snm', 'ua200', 'va500', 'rsds', 'ua850', 'snd', 'clwvi', 'rsut', 'sund', 'hfss', 'tas', 'tasmin', 'rlut', 'prsn', 'vas', 'clh', 'cll', 'ua500', 'prhmax', 'mrros', 'ta850', 'ps', 'uas', 'pr', 'sfcWind', 'hus850', 'ts', 'snc', 'sic', 'prc', 'hurs', 'snw', 'ta200', 'evspsbl', 'rsus', 'clt', 'clm', 'va850', 'zg200', 'va200', 'hfls', 'rsdt', 'ta500', 'sfcWindmax', 'rlds', 'prw', 'rlus', 'tauv', 'huss', 'zg500', 'mrro', 'psl', 'clivi']</t>
+          <t>['tasmax', 'tauu', 'mrso', 'snm', 'ua200', 'va500', 'rsds', 'ua850', 'snd', 'clwvi', 'rsut', 'sund', 'hfss', 'tas', 'tasmin', 'rlut', 'prsn', 'vas', 'clh', 'cll', 'ua500', 'prhmax', 'mrros', 'ta850', 'ps', 'uas', 'pr', 'sfcWind', 'hus850', 'ts', 'snc', 'sic', 'prc', 'hurs', 'snw', 'ta200', 'evspsbl', 'rsus', 'clt', 'clm', 'va850', 'zg200', 'va200', 'hfls', 'rsdt', 'ta500', 'sfcWindmax', 'rlds', 'prw', 'rlus', 'tauv', 'huss', 'zg500', 'mrro', 'psl', 'clivi']</t>
         </is>
       </c>
     </row>
@@ -17681,7 +17681,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>['snc', 'mrso', 'zg500', 'hurs', 'hfss', 'ua850', 'mrro', 'snm', 'rlut', 'sfcWind', 'ua200', 'rsut', 'sund', 'tas', 'ta500', 'pr', 'rlus', 'huss', 'ua500', 'va850', 'va500', 'sfcWindmax', 'evspsbl', 'hus850', 'ta200', 'rsus', 'psl', 'sic', 'rsds', 'tasmin', 'mrros', 'uas', 'tasmax', 'clt', 'hfls', 'rsdt', 'snw', 'rlds', 'ta850', 'snd', 'vas', 'zg200', 'va200', 'snc', 'mrso', 'zg500', 'hurs', 'hfss', 'ua850', 'mrro', 'snm', 'rlut', 'sfcWind', 'ua200', 'rsut', 'sund', 'tas', 'ta500', 'pr', 'rlus', 'huss', 'ua500', 'va850', 'va500', 'sfcWindmax', 'evspsbl', 'hus850', 'ta200', 'rsus', 'psl', 'sic', 'rsds', 'tasmin', 'mrros', 'uas', 'tasmax', 'clt', 'hfls', 'rsdt', 'snw', 'rlds', 'ta850', 'snd', 'vas', 'zg200', 'va200']</t>
+          <t>['snc', 'mrso', 'zg500', 'hurs', 'hfss', 'ua850', 'mrro', 'snm', 'rlut', 'sfcWind', 'ua200', 'rsut', 'sund', 'tas', 'ta500', 'pr', 'rlus', 'huss', 'ua500', 'va850', 'va500', 'sfcWindmax', 'evspsbl', 'hus850', 'ta200', 'rsus', 'psl', 'sic', 'rsds', 'tasmin', 'mrros', 'uas', 'tasmax', 'clt', 'hfls', 'rsdt', 'snw', 'rlds', 'ta850', 'snd', 'vas', 'zg200', 'va200']</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>['clt', 'sfcWindmax', 'rlus', 'snc', 'tasmin', 'zg200', 'va200', 'rsds', 'psl', 'hfls', 'rsdt', 'tas', 'hfss', 'snw', 'snd', 'evspsbl', 'tasmax', 'mrso', 'zg500', 'va500', 'vas', 'va850', 'ta200', 'sfcWind', 'huss', 'rsut', 'ta850', 'rsus', 'ua850', 'ua200', 'pr', 'mrros', 'sund', 'sic', 'ua500', 'rlut', 'snm', 'rlds', 'uas', 'hurs', 'ta500', 'hus850', 'mrro', 'clt', 'sfcWindmax', 'rlus', 'snc', 'tasmin', 'zg200', 'va200', 'rsds', 'psl', 'hfls', 'rsdt', 'tas', 'hfss', 'snw', 'snd', 'evspsbl', 'tasmax', 'mrso', 'zg500', 'va500', 'vas', 'va850', 'ta200', 'sfcWind', 'huss', 'rsut', 'ta850', 'rsus', 'ua850', 'ua200', 'pr', 'mrros', 'sund', 'sic', 'ua500', 'rlut', 'snm', 'rlds', 'uas', 'hurs', 'ta500', 'hus850', 'mrro']</t>
+          <t>['clt', 'sfcWindmax', 'rlus', 'snc', 'tasmin', 'zg200', 'va200', 'rsds', 'psl', 'hfls', 'rsdt', 'tas', 'hfss', 'snw', 'snd', 'evspsbl', 'tasmax', 'mrso', 'zg500', 'va500', 'vas', 'va850', 'ta200', 'sfcWind', 'huss', 'rsut', 'ta850', 'rsus', 'ua850', 'ua200', 'pr', 'mrros', 'sund', 'sic', 'ua500', 'rlut', 'snm', 'rlds', 'uas', 'hurs', 'ta500', 'hus850', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>['hfls', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'hfls', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['hfls', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>['rlut', 'ua200', 'hus850', 'sfcWind', 'psl', 'ta200', 'tasmin', 'rlus', 'tauv', 'huss', 'prhmax', 'clivi', 'uas', 'rsds', 'evspsbl', 'tasmax', 'tas', 'ua500', 'hurs', 'hfss', 'snm', 'rsus', 'prw', 'ta500', 'rsut', 'vas', 'clt', 'va200', 'hfls', 'rsdt', 'prc', 'ta850', 'clh', 'tauu', 'rlds', 'sic', 'clwvi', 'clm', 'ps', 'va500', 'mrso', 'sfcWindmax', 'va850', 'prsn', 'ua850', 'ts', 'cll', 'snc', 'pr', 'mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['rlut', 'ua200', 'hus850', 'sfcWind', 'psl', 'ta200', 'tasmin', 'rlus', 'tauv', 'huss', 'prhmax', 'clivi', 'uas', 'rsds', 'evspsbl', 'tasmax', 'tas', 'ua500', 'hurs', 'hfss', 'snm', 'rsus', 'prw', 'ta500', 'rsut', 'vas', 'clt', 'va200', 'hfls', 'rsdt', 'prc', 'ta850', 'clh', 'tauu', 'rlds', 'sic', 'clwvi', 'clm', 'ps', 'va500', 'mrso', 'sfcWindmax', 'va850', 'prsn', 'ua850', 'ts', 'cll', 'snc', 'pr', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -18253,7 +18253,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>['hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus', 'hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus']</t>
+          <t>['hfss', 'sfcWind', 'rlds', 'ps', 'rsds', 'hurs', 'pr', 'tas', 'rlus', 'huss', 'psl', 'hfls', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>['clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200', 'clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200']</t>
+          <t>['clt', 'ps', 'sfcWind', 'ta500', 'ts', 'clwvi', 'clh', 'vas', 'hfss', 'va850', 'rlds', 'zg200', 'snw', 'va200', 'hus850', 'mrro', 'ta200', 'rsut', 'zg500', 'sund', 'va500', 'prw', 'hurs', 'ua500', 'tauu', 'sic', 'ta850', 'pr', 'rsus', 'tasmin', 'evspsbl', 'ua850', 'sfcWindmax', 'rlut', 'clm', 'psl', 'rlus', 'tauv', 'clivi', 'huss', 'uas', 'tasmax', 'prc', 'snm', 'tas', 'prsn', 'hfls', 'rsdt', 'snd', 'rsds', 'prhmax', 'cll', 'mrso', 'mrros', 'snc', 'ua200']</t>
         </is>
       </c>
     </row>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>['snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund', 'snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund']</t>
+          <t>['snm', 'psl', 'hus850', 'vas', 'ta850', 'hfss', 'uas', 'va200', 'rlds', 'tasmin', 'hfls', 'ua200', 'evspsbl', 'mrros', 'mrro', 'clt', 'rlus', 'huss', 'ua500', 'hurs', 'snd', 'mrso', 'snc', 'rsus', 'ta500', 'zg500', 'snw', 'va500', 'sfcWindmax', 'rlut', 'sic', 'tasmax', 'sfcWind', 'zg200', 'pr', 'ua850', 'rsdt', 'va850', 'rsds', 'ta200', 'rsut', 'tas', 'sund']</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>['rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr', 'rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr']</t>
+          <t>['rsus', 'mrros', 'mrro', 'hfls', 'rsdt', 'mrso', 'clt', 'sfcWindmax', 'tasmin', 'ta500', 'rsut', 'snw', 'sund', 'sfcWind', 'evspsbl', 'ua850', 'rlds', 'ua200', 'tasmax', 'rlut', 'hus850', 'snc', 'ta850', 'hurs', 'uas', 'va850', 'rsds', 'snm', 'vas', 'psl', 'ta200', 'rlus', 'huss', 'sic', 'ua500', 'snd', 'zg500', 'tas', 'va500', 'hfss', 'zg200', 'va200', 'pr']</t>
         </is>
       </c>
     </row>
@@ -18525,7 +18525,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>['rsus', 'psl', 'pr', 'rlus', 'huss', 'rsds', 'hfss', 'sfcWind', 'hurs', 'tas', 'rlds', 'ps', 'hfls', 'rsus', 'psl', 'pr', 'rlus', 'huss', 'rsds', 'hfss', 'sfcWind', 'hurs', 'tas', 'rlds', 'ps', 'hfls']</t>
+          <t>['rsus', 'psl', 'pr', 'rlus', 'huss', 'rsds', 'hfss', 'sfcWind', 'hurs', 'tas', 'rlds', 'ps', 'hfls']</t>
         </is>
       </c>
     </row>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>['evspsbl', 'sfcWindmax', 'clt', 'rlus', 'hfss', 'ta850', 'rlds', 'snw', 'ts', 'hfls', 'zg500', 'snm', 'psl', 'ua850', 'huss', 'uas', 'ta200', 'mrso', 'sic', 'rsds', 'prsn', 'clh', 'vas', 'tas', 'clwvi', 'snd', 'rsus', 'rlut', 'va200', 'tauv', 'ua500', 'rsut', 'prw', 'hurs', 'tauu', 'clivi', 'cll', 'tasmin', 'prc', 'ua200', 'clm', 'mrro', 'zg200', 'mrros', 'va850', 'hus850', 'tasmax', 'prhmax', 'ps', 'ta500', 'sund', 'rsdt', 'snc', 'pr', 'sfcWind', 'va500', 'evspsbl', 'sfcWindmax', 'clt', 'rlus', 'hfss', 'ta850', 'rlds', 'snw', 'ts', 'hfls', 'zg500', 'snm', 'psl', 'ua850', 'huss', 'uas', 'ta200', 'mrso', 'sic', 'rsds', 'prsn', 'clh', 'vas', 'tas', 'clwvi', 'snd', 'rsus', 'rlut', 'va200', 'tauv', 'ua500', 'rsut', 'prw', 'hurs', 'tauu', 'clivi', 'cll', 'tasmin', 'prc', 'ua200', 'clm', 'mrro', 'zg200', 'mrros', 'va850', 'hus850', 'tasmax', 'prhmax', 'ps', 'ta500', 'sund', 'rsdt', 'snc', 'pr', 'sfcWind', 'va500']</t>
+          <t>['evspsbl', 'sfcWindmax', 'clt', 'rlus', 'hfss', 'ta850', 'rlds', 'snw', 'ts', 'hfls', 'zg500', 'snm', 'psl', 'ua850', 'huss', 'uas', 'ta200', 'mrso', 'sic', 'rsds', 'prsn', 'clh', 'vas', 'tas', 'clwvi', 'snd', 'rsus', 'rlut', 'va200', 'tauv', 'ua500', 'rsut', 'prw', 'hurs', 'tauu', 'clivi', 'cll', 'tasmin', 'prc', 'ua200', 'clm', 'mrro', 'zg200', 'mrros', 'va850', 'hus850', 'tasmax', 'prhmax', 'ps', 'ta500', 'sund', 'rsdt', 'snc', 'pr', 'sfcWind', 'va500']</t>
         </is>
       </c>
     </row>
@@ -18621,7 +18621,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -18653,7 +18653,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>['rlds', 'mrso', 'zg200', 'va200', 'va850', 'mrro', 'psl', 'hfss', 'sund', 'ua500', 'rlut', 'rlus', 'tasmin', 'sfcWind', 'huss', 'rsut', 'tasmax', 'mrros', 'ua200', 'hus850', 'hfls', 'rsdt', 'pr', 'clt', 'tas', 'hurs', 'snd', 'ua850', 'sfcWindmax', 'vas', 'uas', 'ta200', 'snw', 'ta500', 'snc', 'rsds', 'sic', 'snm', 'zg500', 'va500', 'ta850', 'rsus', 'evspsbl', 'rlds', 'mrso', 'zg200', 'va200', 'va850', 'mrro', 'psl', 'hfss', 'sund', 'ua500', 'rlut', 'rlus', 'tasmin', 'sfcWind', 'huss', 'rsut', 'tasmax', 'mrros', 'ua200', 'hus850', 'hfls', 'rsdt', 'pr', 'clt', 'tas', 'hurs', 'snd', 'ua850', 'sfcWindmax', 'vas', 'uas', 'ta200', 'snw', 'ta500', 'snc', 'rsds', 'sic', 'snm', 'zg500', 'va500', 'ta850', 'rsus', 'evspsbl']</t>
+          <t>['rlds', 'mrso', 'zg200', 'va200', 'va850', 'mrro', 'psl', 'hfss', 'sund', 'ua500', 'rlut', 'rlus', 'tasmin', 'sfcWind', 'huss', 'rsut', 'tasmax', 'mrros', 'ua200', 'hus850', 'hfls', 'rsdt', 'pr', 'clt', 'tas', 'hurs', 'snd', 'ua850', 'sfcWindmax', 'vas', 'uas', 'ta200', 'snw', 'ta500', 'snc', 'rsds', 'sic', 'snm', 'zg500', 'va500', 'ta850', 'rsus', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -18685,7 +18685,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>['hfls', 'rsdt', 'mrros', 'snm', 'snc', 'mrro', 'va500', 'rsut', 'sund', 'hurs', 'ta500', 'rsds', 'vas', 'tas', 'sfcWindmax', 'va200', 'rsus', 'rlus', 'pr', 'snd', 'hfss', 'hus850', 'zg200', 'clt', 'tasmin', 'ua850', 'ua500', 'zg500', 'huss', 'snw', 'ta200', 'rlds', 'uas', 'ta850', 'rlut', 'psl', 'va850', 'tasmax', 'ua200', 'mrso', 'sic', 'sfcWind', 'evspsbl', 'hfls', 'rsdt', 'mrros', 'snm', 'snc', 'mrro', 'va500', 'rsut', 'sund', 'hurs', 'ta500', 'rsds', 'vas', 'tas', 'sfcWindmax', 'va200', 'rsus', 'rlus', 'pr', 'snd', 'hfss', 'hus850', 'zg200', 'clt', 'tasmin', 'ua850', 'ua500', 'zg500', 'huss', 'snw', 'ta200', 'rlds', 'uas', 'ta850', 'rlut', 'psl', 'va850', 'tasmax', 'ua200', 'mrso', 'sic', 'sfcWind', 'evspsbl']</t>
+          <t>['hfls', 'rsdt', 'mrros', 'snm', 'snc', 'mrro', 'va500', 'rsut', 'sund', 'hurs', 'ta500', 'rsds', 'vas', 'tas', 'sfcWindmax', 'va200', 'rsus', 'rlus', 'pr', 'snd', 'hfss', 'hus850', 'zg200', 'clt', 'tasmin', 'ua850', 'ua500', 'zg500', 'huss', 'snw', 'ta200', 'rlds', 'uas', 'ta850', 'rlut', 'psl', 'va850', 'tasmax', 'ua200', 'mrso', 'sic', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -18793,7 +18793,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>['ts', 'va200', 'ta500', 'tas', 'ua500', 'hfss', 'sfcWind', 'hus850', 'rsus', 'clivi', 'va850', 'rsds', 'hfls', 'rsdt', 'cll', 'psl', 'clwvi', 'rlut', 'tasmin', 'snm', 'ta200', 'ps', 'va500', 'tauu', 'prw', 'rlds', 'tasmax', 'ta850', 'sfcWindmax', 'vas', 'clt', 'rlus', 'clm', 'evspsbl', 'mrso', 'ua850', 'prc', 'clh', 'rsut', 'snc', 'pr', 'tauv', 'huss', 'prhmax', 'hurs', 'sic', 'prsn', 'uas', 'ua200', 'mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['ts', 'va200', 'ta500', 'tas', 'ua500', 'hfss', 'sfcWind', 'hus850', 'rsus', 'clivi', 'va850', 'rsds', 'hfls', 'rsdt', 'cll', 'psl', 'clwvi', 'rlut', 'tasmin', 'snm', 'ta200', 'ps', 'va500', 'tauu', 'prw', 'rlds', 'tasmax', 'ta850', 'sfcWindmax', 'vas', 'clt', 'rlus', 'clm', 'evspsbl', 'mrso', 'ua850', 'prc', 'clh', 'rsut', 'snc', 'pr', 'tauv', 'huss', 'prhmax', 'hurs', 'sic', 'prsn', 'uas', 'ua200', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -19025,7 +19025,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -19053,7 +19053,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19197,7 +19197,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>['va850', 'rsds', 'tauu', 'uas', 'clh', 'ua850', 'ua200', 'tas', 'rsut', 'vas', 'snc', 'clm', 'psl', 'hfss', 'sfcWind', 'va500', 'hus850', 'rsus', 'ta500', 'ts', 'clivi', 'hurs', 'rlds', 'prhmax', 'mrso', 'tasmin', 'tauv', 'va200', 'prc', 'rlut', 'evspsbl', 'ta850', 'huss', 'sic', 'clwvi', 'pr', 'hfls', 'rsdt', 'ps', 'tasmax', 'prw', 'rlus', 'clt', 'cll', 'ta200', 'prsn', 'sfcWindmax', 'snm', 'ua500', 'mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['va850', 'rsds', 'tauu', 'uas', 'clh', 'ua850', 'ua200', 'tas', 'rsut', 'vas', 'snc', 'clm', 'psl', 'hfss', 'sfcWind', 'va500', 'hus850', 'rsus', 'ta500', 'ts', 'clivi', 'hurs', 'rlds', 'prhmax', 'mrso', 'tasmin', 'tauv', 'va200', 'prc', 'rlut', 'evspsbl', 'ta850', 'huss', 'sic', 'clwvi', 'pr', 'hfls', 'rsdt', 'ps', 'tasmax', 'prw', 'rlus', 'clt', 'cll', 'ta200', 'prsn', 'sfcWindmax', 'snm', 'ua500', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -19705,7 +19705,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrro', 'mrros']</t>
+          <t>['mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>['prsn', 'rsds', 'tasmin', 'evspsbl', 'sic', 'tauv', 'ps', 'tasmax', 'ta850', 'hurs', 'pr', 'ua500', 'prhmax', 'psl', 'ta500', 'va850', 'hfls', 'rsdt', 'hfss', 'rsus', 'clt', 'cll', 'clwvi', 'rsut', 'clh', 'vas', 'mrso', 'ta200', 'rlut', 'sfcWindmax', 'snc', 'uas', 'va200', 'clm', 'hus850', 'prc', 'ua850', 'snm', 'ts', 'va500', 'rlus', 'huss', 'tas', 'tauu', 'sfcWind', 'clivi', 'rlds', 'prw', 'ua200', 'mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['prsn', 'rsds', 'tasmin', 'evspsbl', 'sic', 'tauv', 'ps', 'tasmax', 'ta850', 'hurs', 'pr', 'ua500', 'prhmax', 'psl', 'ta500', 'va850', 'hfls', 'rsdt', 'hfss', 'rsus', 'clt', 'cll', 'clwvi', 'rsut', 'clh', 'vas', 'mrso', 'ta200', 'rlut', 'sfcWindmax', 'snc', 'uas', 'va200', 'clm', 'hus850', 'prc', 'ua850', 'snm', 'ts', 'va500', 'rlus', 'huss', 'tas', 'tauu', 'sfcWind', 'clivi', 'rlds', 'prw', 'ua200', 'mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>['zg500', 'zg200', 'zg200']</t>
+          <t>['zg500', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20185,7 +20185,7 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>['zg200', 'zg500', 'zg500']</t>
+          <t>['zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>['mrros', 'mrro', 'mrros', 'mrro']</t>
+          <t>['mrros', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20265,7 +20265,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -20301,7 +20301,7 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>['clt', 'hurs', 'huss', 'pr', 'ps', 'rlds', 'rsds', 'sfcWind', 'tas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hurs', 'huss', 'pr', 'ps', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -20333,7 +20333,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>['vas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'rsus', 'sfcWind', 'tas', 'uas', 'vas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'rsus', 'sfcWind', 'tas', 'uas']</t>
+          <t>['vas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'rsus', 'sfcWind', 'tas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>['mrso', 'pr', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros']</t>
+          <t>['mrso', 'pr', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>['va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso']</t>
+          <t>['va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso']</t>
         </is>
       </c>
     </row>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>['ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut']</t>
+          <t>['ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut']</t>
         </is>
       </c>
     </row>
@@ -20501,7 +20501,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt']</t>
+          <t>['rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt']</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas', 'hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
+          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20633,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>['prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'hus850', 'huss', 'mrro', 'rsds', 'rsdt', 'rsus', 'rsut', 'tasmin', 'tauu', 'tauv', 'ts', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'zg200', 'zg500', 'va850', 'vas', 'wsgsmax', 'ta850', 'tas', 'tasmax', 'snw', 'ta200', 'ta500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'hus850', 'huss', 'mrro', 'rsds', 'rsdt', 'rsus', 'rsut', 'tasmin', 'tauu', 'tauv', 'ts', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'zg200', 'zg500', 'va850', 'vas', 'wsgsmax', 'ta850', 'tas', 'tasmax', 'snw', 'ta200', 'ta500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850']</t>
+          <t>['prc', 'prsn', 'ps', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'hus850', 'huss', 'mrro', 'rsds', 'rsdt', 'rsus', 'rsut', 'tasmin', 'tauu', 'tauv', 'ts', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'zg200', 'zg500', 'va850', 'vas', 'wsgsmax', 'ta850', 'tas', 'tasmax', 'snw', 'ta200', 'ta500', 'uas', 'va200', 'va500', 'ua200', 'ua500', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -20665,7 +20665,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>['clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'vas', 'zg200', 'zg500', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'vas', 'zg200', 'zg500', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850']</t>
+          <t>['clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'vas', 'zg200', 'zg500', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'clt', 'evspsbl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'clt', 'evspsbl']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>['hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr']</t>
+          <t>['hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'huss', 'tas', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas', 'hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
+          <t>['hurs', 'clt', 'rsds', 'rlds', 'rsus', 'sfcWind', 'huss', 'psl', 'tas', 'ps', 'pr', 'vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20837,7 +20837,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>['rsut', 'sfcWind', 'sfcWindmax', 'sic', 'tasmin', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zg500', 'snm', 'snw', 'ta200', 'ta500', 'va200', 'va500', 'va850', 'vas', 'ua200', 'ua500', 'ua850', 'uas', 'rsds', 'rsdt', 'rsus', 'ta850', 'tas', 'tasmax', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'hus850', 'huss', 'mrro', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'tasmin', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zg500', 'snm', 'snw', 'ta200', 'ta500', 'va200', 'va500', 'va850', 'vas', 'ua200', 'ua500', 'ua850', 'uas', 'rsds', 'rsdt', 'rsus', 'ta850', 'tas', 'tasmax', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'hus850', 'huss', 'mrro']</t>
+          <t>['rsut', 'sfcWind', 'sfcWindmax', 'sic', 'tasmin', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zg500', 'snm', 'snw', 'ta200', 'ta500', 'va200', 'va500', 'va850', 'vas', 'ua200', 'ua500', 'ua850', 'uas', 'rsds', 'rsdt', 'rsus', 'ta850', 'tas', 'tasmax', 'psl', 'rlds', 'rlus', 'rlut', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'hus850', 'huss', 'mrro']</t>
         </is>
       </c>
     </row>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>['evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'va850', 'vas', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'va850', 'vas', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
+          <t>['evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'va850', 'vas', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500']</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>['va850', 'vas', 'zg200', 'zg500', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt', 'va850', 'vas', 'zg200', 'zg500', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt']</t>
+          <t>['va850', 'vas', 'zg200', 'zg500', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -20977,7 +20977,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>['sftlf', 'orog', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>['ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'pr', 'tasmax', 'pr', 'tasmax', 'tas', 'tasmin', 'sfcWind']</t>
+          <t>['ts', 'va500', 'vas', 'prc', 'huss', 'snw', 'hus850', 'mrso', 'rlus', 'hfls', 'rlut', 'uas', 'ua850', 'ta850', 'ta200', 'rsdt', 'prsn', 'clt', 'wsgsmax', 'rsds', 'mrro', 'hfss', 'ua500', 'rsus', 'zg500', 'ta500', 'sfcWindmax', 'evspsbl', 'psl', 'ps', 'va850', 'rsut', 'rlds', 'pr', 'tasmax', 'tas', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -21785,7 +21785,7 @@
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -21821,7 +21821,7 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'sfcWind', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'sfcWind', 'tas']</t>
+          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'vas', 'uas', 'psl', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'vas', 'uas', 'psl', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr']</t>
+          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'vas', 'uas', 'psl', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -21885,7 +21885,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -21917,7 +21917,7 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>['va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'rlds', 'rlus', 'rlut', 'evspsbl', 'hfls', 'hfss', 'huss', 'mrro', 'mrros', 'rsds', 'rsdt', 'clt', 'mrso', 'pr', 'prc', 'prsn', 'hurs', 'hus850', 'ps', 'psl', 'rsus', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'ua500', 'ua850', 'uas', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'sic', 'tauu', 'tauv', 'snm', 'snw', 'ts', 'ua200', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'rlds', 'rlus', 'rlut', 'evspsbl', 'hfls', 'hfss', 'huss', 'mrro', 'mrros', 'rsds', 'rsdt', 'clt', 'mrso', 'pr', 'prc', 'prsn', 'hurs', 'hus850', 'ps', 'psl', 'rsus', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'ua500', 'ua850', 'uas', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'sic', 'tauu', 'tauv', 'snm', 'snw', 'ts', 'ua200', 'va200', 'va500']</t>
+          <t>['va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'rlds', 'rlus', 'rlut', 'evspsbl', 'hfls', 'hfss', 'huss', 'mrro', 'mrros', 'rsds', 'rsdt', 'clt', 'mrso', 'pr', 'prc', 'prsn', 'hurs', 'hus850', 'ps', 'psl', 'rsus', 'rsut', 'sfcWind', 'tas', 'tasmax', 'tasmin', 'ua500', 'ua850', 'uas', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'sic', 'tauu', 'tauv', 'snm', 'snw', 'ts', 'ua200', 'va200', 'va500']</t>
         </is>
       </c>
     </row>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'evspsbl', 'hfls', 'hfss', 'hurs', 'sfcWindmax', 'sic', 'snm', 'snw', 'mrros', 'mrso', 'pr', 'psl', 'ta200', 'ta500', 'ta850', 'tas', 'hus850', 'huss', 'mrro', 'clt', 'tasmax', 'tasmin', 'ua200', 'ua500', 'va850', 'vas', 'zg200', 'zg500', 'ua850', 'uas', 'va200', 'va500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'evspsbl', 'hfls', 'hfss', 'hurs', 'sfcWindmax', 'sic', 'snm', 'snw', 'mrros', 'mrso', 'pr', 'psl', 'ta200', 'ta500', 'ta850', 'tas', 'hus850', 'huss', 'mrro', 'clt', 'tasmax', 'tasmin', 'ua200', 'ua500', 'va850', 'vas', 'zg200', 'zg500', 'ua850', 'uas', 'va200', 'va500']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'evspsbl', 'hfls', 'hfss', 'hurs', 'sfcWindmax', 'sic', 'snm', 'snw', 'mrros', 'mrso', 'pr', 'psl', 'ta200', 'ta500', 'ta850', 'tas', 'hus850', 'huss', 'mrro', 'clt', 'tasmax', 'tasmin', 'ua200', 'ua500', 'va850', 'vas', 'zg200', 'zg500', 'ua850', 'uas', 'va200', 'va500']</t>
         </is>
       </c>
     </row>
@@ -21981,7 +21981,7 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'va500', 'va850', 'vas', 'zg200', 'ua500', 'ua850', 'uas', 'va200', 'zg500', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'va500', 'va850', 'vas', 'zg200', 'ua500', 'ua850', 'uas', 'va200', 'zg500']</t>
+          <t>['rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'va500', 'va850', 'vas', 'zg200', 'ua500', 'ua850', 'uas', 'va200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -22021,7 +22021,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22057,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'tas', 'ps', 'pr', 'huss', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'tas', 'ps', 'pr']</t>
+          <t>['huss', 'hurs', 'clt', 'rsds', 'rlds', 'sfcWind', 'tas', 'ps', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'uas', 'tas', 'psl', 'ps', 'pr', 'huss', 'hurs', 'clt', 'vas', 'rsds', 'rlds', 'rsus', 'sfcWind', 'uas', 'tas', 'psl', 'ps', 'pr', 'huss', 'hurs', 'clt', 'vas']</t>
+          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'uas', 'tas', 'psl', 'ps', 'pr', 'huss', 'hurs', 'clt', 'vas']</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -22153,7 +22153,7 @@
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>['zg500', 'tasmax', 'tasmin', 'tauu', 'vas', 'wsgsmax', 'zg200', 'sfcWind', 'sfcWindmax', 'sic', 'tauv', 'ts', 'ua200', 'snm', 'snw', 'ta200', 'ua500', 'ua850', 'uas', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'hfls', 'hfss', 'hurs', 'hus850', 'mrso', 'pr', 'prc', 'prsn', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'clt', 'evspsbl', 'ps', 'psl', 'rlds', 'huss', 'mrro', 'mrros', 'zg500', 'tasmax', 'tasmin', 'tauu', 'vas', 'wsgsmax', 'zg200', 'sfcWind', 'sfcWindmax', 'sic', 'tauv', 'ts', 'ua200', 'snm', 'snw', 'ta200', 'ua500', 'ua850', 'uas', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'hfls', 'hfss', 'hurs', 'hus850', 'mrso', 'pr', 'prc', 'prsn', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'clt', 'evspsbl', 'ps', 'psl', 'rlds', 'huss', 'mrro', 'mrros']</t>
+          <t>['zg500', 'tasmax', 'tasmin', 'tauu', 'vas', 'wsgsmax', 'zg200', 'sfcWind', 'sfcWindmax', 'sic', 'tauv', 'ts', 'ua200', 'snm', 'snw', 'ta200', 'ua500', 'ua850', 'uas', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'hfls', 'hfss', 'hurs', 'hus850', 'mrso', 'pr', 'prc', 'prsn', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'clt', 'evspsbl', 'ps', 'psl', 'rlds', 'huss', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200']</t>
+          <t>['ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'clt', 'evspsbl', 'hfls', 'hfss', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'zg500', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200']</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22217,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>['mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros']</t>
+          <t>['mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'zg500', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros']</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>['mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'tasmin', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
+          <t>['mrro', 'rsdt', 'rlus', 'evspsbl', 'rsus', 'mrso', 'rlds', 'ta200', 'sfcWindmax', 'hfss', 'va850', 'huss', 'clt', 'va500', 'ta850', 'ua850', 'snw', 'wsgsmax', 'prc', 'prsn', 'ts', 'hfls', 'zg500', 'ta500', 'ua500', 'rlut', 'psl', 'uas', 'rsds', 'vas', 'ps', 'rsut', 'hus850', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'sfcWind', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'sfcWind', 'tas']</t>
+          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -22613,7 +22613,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'vas', 'uas', 'psl', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'vas', 'uas', 'psl', 'tas']</t>
+          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'vas', 'uas', 'psl', 'tas']</t>
         </is>
       </c>
     </row>
@@ -22645,7 +22645,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'hus850', 'pr', 'prc', 'prsn', 'rlut', 'rsds', 'rlds', 'rlus', 'evspsbl', 'hfls', 'clt', 'mrros', 'mrso', 'huss', 'mrro', 'ps', 'psl', 'zg500', 'wsgsmax', 'zg200', 'uas', 'va200', 'va850', 'vas', 'ua500', 'ua850', 'va500', 'snw', 'ta200', 'ta500', 'rsus', 'rsut', 'tauu', 'tauv', 'sfcWind', 'sfcWindmax', 'tasmax', 'tasmin', 'sic', 'snm', 'ts', 'ua200', 'ta850', 'tas', 'rsdt', 'hfss', 'hurs', 'hus850', 'pr', 'prc', 'prsn', 'rlut', 'rsds', 'rlds', 'rlus', 'evspsbl', 'hfls', 'clt', 'mrros', 'mrso', 'huss', 'mrro', 'ps', 'psl', 'zg500', 'wsgsmax', 'zg200', 'uas', 'va200', 'va850', 'vas', 'ua500', 'ua850', 'va500', 'snw', 'ta200', 'ta500', 'rsus', 'rsut', 'tauu', 'tauv', 'sfcWind', 'sfcWindmax', 'tasmax', 'tasmin', 'sic', 'snm', 'ts', 'ua200', 'ta850', 'tas', 'rsdt']</t>
+          <t>['hfss', 'hurs', 'hus850', 'pr', 'prc', 'prsn', 'rlut', 'rsds', 'rlds', 'rlus', 'evspsbl', 'hfls', 'clt', 'mrros', 'mrso', 'huss', 'mrro', 'ps', 'psl', 'zg500', 'wsgsmax', 'zg200', 'uas', 'va200', 'va850', 'vas', 'ua500', 'ua850', 'va500', 'snw', 'ta200', 'ta500', 'rsus', 'rsut', 'tauu', 'tauv', 'sfcWind', 'sfcWindmax', 'tasmax', 'tasmin', 'sic', 'snm', 'ts', 'ua200', 'ta850', 'tas', 'rsdt']</t>
         </is>
       </c>
     </row>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>['zg500', 'va500', 'va850', 'vas', 'zg200', 'ua500', 'ua850', 'uas', 'va200', 'ta200', 'ta500', 'ta850', 'tas', 'rsut', 'sfcWind', 'sfcWindmax', 'rlut', 'rsds', 'rsdt', 'psl', 'rlds', 'rlus', 'tasmax', 'tasmin', 'ua200', 'sic', 'snm', 'snw', 'rsus', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'evspsbl', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'zg500', 'va500', 'va850', 'vas', 'zg200', 'ua500', 'ua850', 'uas', 'va200', 'ta200', 'ta500', 'ta850', 'tas', 'rsut', 'sfcWind', 'sfcWindmax', 'rlut', 'rsds', 'rsdt', 'psl', 'rlds', 'rlus', 'tasmax', 'tasmin', 'ua200', 'sic', 'snm', 'snw', 'rsus', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'evspsbl', 'huss', 'mrro', 'mrros', 'mrso', 'pr']</t>
+          <t>['zg500', 'va500', 'va850', 'vas', 'zg200', 'ua500', 'ua850', 'uas', 'va200', 'ta200', 'ta500', 'ta850', 'tas', 'rsut', 'sfcWind', 'sfcWindmax', 'rlut', 'rsds', 'rsdt', 'psl', 'rlds', 'rlus', 'tasmax', 'tasmin', 'ua200', 'sic', 'snm', 'snw', 'rsus', 'hfls', 'hfss', 'hurs', 'hus850', 'clt', 'evspsbl', 'huss', 'mrro', 'mrros', 'mrso', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'huss', 'mrro', 'mrros', 'mrso', 'sic', 'snm', 'snw', 'ta200', 'pr', 'psl', 'rlds', 'hfss', 'hurs', 'hus850', 'tasmax', 'tasmin', 'ua200', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'vas', 'ua500', 'ua850', 'uas', 'zg200', 'zg500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'huss', 'mrro', 'mrros', 'mrso', 'sic', 'snm', 'snw', 'ta200', 'pr', 'psl', 'rlds', 'hfss', 'hurs', 'hus850', 'tasmax', 'tasmin', 'ua200', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'vas', 'ua500', 'ua850', 'uas', 'zg200', 'zg500']</t>
+          <t>['rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'huss', 'mrro', 'mrros', 'mrso', 'sic', 'snm', 'snw', 'ta200', 'pr', 'psl', 'rlds', 'hfss', 'hurs', 'hus850', 'tasmax', 'tasmin', 'ua200', 'ta500', 'ta850', 'tas', 'va200', 'va500', 'va850', 'vas', 'ua500', 'ua850', 'uas', 'zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -22785,7 +22785,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>['huss', 'tas', 'clt', 'ps', 'pr', 'sfcWind', 'hurs', 'rsds', 'huss', 'tas', 'clt', 'ps', 'pr', 'sfcWind', 'hurs', 'rsds']</t>
+          <t>['huss', 'tas', 'clt', 'ps', 'pr', 'sfcWind', 'hurs', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>['rsds', 'clt', 'ps', 'pr', 'rsus', 'sfcWind', 'huss', 'hurs', 'psl', 'tas', 'rlds', 'rsds', 'clt', 'ps', 'pr', 'rsus', 'sfcWind', 'huss', 'hurs', 'psl', 'tas', 'rlds']</t>
+          <t>['rsds', 'clt', 'ps', 'pr', 'rsus', 'sfcWind', 'huss', 'hurs', 'psl', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -22885,7 +22885,7 @@
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -22917,7 +22917,7 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>['ta850', 'wsgsmax', 'vas', 'zg500', 'va500', 'va850', 'uas', 'ua500', 'ua850', 'ts', 'rlds', 'rlus', 'rlut', 'prc', 'psl', 'prsn', 'ps', 'clt', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'ta850', 'wsgsmax', 'vas', 'zg500', 'va500', 'va850', 'uas', 'ua500', 'ua850', 'ts', 'rlds', 'rlus', 'rlut', 'prc', 'psl', 'prsn', 'ps', 'clt', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
+          <t>['ta850', 'wsgsmax', 'vas', 'zg500', 'va500', 'va850', 'uas', 'ua500', 'ua850', 'ts', 'rlds', 'rlus', 'rlut', 'prc', 'psl', 'prsn', 'ps', 'clt', 'rsds', 'rsus', 'rsdt', 'rsut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22949,7 +22949,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>['clt', 'tasmax', 'tasmin', 'tas', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'vas', 'zg500', 'va850', 'uas', 'va500', 'ua500', 'ua850', 'sfcWindmax', 'rsut', 'sfcWind', 'snw', 'ta200', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rlut', 'psl', 'pr', 'clt', 'tasmax', 'tasmin', 'tas', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'vas', 'zg500', 'va850', 'uas', 'va500', 'ua500', 'ua850', 'sfcWindmax', 'rsut', 'sfcWind', 'snw', 'ta200', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rlut', 'psl', 'pr']</t>
+          <t>['clt', 'tasmax', 'tasmin', 'tas', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'vas', 'zg500', 'va850', 'uas', 'va500', 'ua500', 'ua850', 'sfcWindmax', 'rsut', 'sfcWind', 'snw', 'ta200', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rlut', 'psl', 'pr']</t>
         </is>
       </c>
     </row>
@@ -22981,7 +22981,7 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'sfcWindmax', 'sfcWind', 'snw', 'ta200', 'ta500', 'ta850', 'tasmax', 'tasmin', 'tas', 'uas', 'ua500', 'ua850', 'evspsbl', 'clt', 'vas', 'zg500', 'va500', 'va850', 'hfss', 'hfls', 'mrso', 'huss', 'hurs', 'hus850', 'mrro', 'pr', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'sfcWindmax', 'sfcWind', 'snw', 'ta200', 'ta500', 'ta850', 'tasmax', 'tasmin', 'tas', 'uas', 'ua500', 'ua850', 'evspsbl', 'clt', 'vas', 'zg500', 'va500', 'va850', 'hfss', 'hfls', 'mrso', 'huss', 'hurs', 'hus850', 'mrro', 'pr']</t>
+          <t>['rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'sfcWindmax', 'sfcWind', 'snw', 'ta200', 'ta500', 'ta850', 'tasmax', 'tasmin', 'tas', 'uas', 'ua500', 'ua850', 'evspsbl', 'clt', 'vas', 'zg500', 'va500', 'va850', 'hfss', 'hfls', 'mrso', 'huss', 'hurs', 'hus850', 'mrro', 'pr']</t>
         </is>
       </c>
     </row>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'pr', 'rsds', 'sfcWind', 'tas', 'ps', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'sfcWind', 'tas', 'ps']</t>
+          <t>['huss', 'hurs', 'clt', 'pr', 'rsds', 'sfcWind', 'tas', 'ps']</t>
         </is>
       </c>
     </row>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'psl', 'tas', 'ps', 'huss', 'hurs', 'clt', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'psl', 'tas', 'ps', 'huss', 'hurs', 'clt', 'pr']</t>
+          <t>['rsds', 'rlds', 'rsus', 'sfcWind', 'psl', 'tas', 'ps', 'huss', 'hurs', 'clt', 'pr']</t>
         </is>
       </c>
     </row>
@@ -23121,7 +23121,7 @@
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -23153,7 +23153,7 @@
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'clt', 'rlds', 'rlus', 'rlut', 'mrso', 'prc', 'psl', 'prsn', 'ps', 'wsgsmax', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'zg500', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'snw', 'sfcWind', 'tas', 'ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'clt', 'rlds', 'rlus', 'rlut', 'mrso', 'prc', 'psl', 'prsn', 'ps', 'wsgsmax', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'zg500', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'snw', 'sfcWind', 'tas', 'tasmin', 'pr', 'tasmax']</t>
+          <t>['ta200', 'ta500', 'ta850', 'ts', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'clt', 'rlds', 'rlus', 'rlut', 'mrso', 'prc', 'psl', 'prsn', 'ps', 'wsgsmax', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'zg500', 'sfcWindmax', 'rsds', 'rsus', 'rsdt', 'rsut', 'snw', 'sfcWind', 'tas', 'tasmin', 'pr', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snw', 'ta200', 'tasmax', 'tasmin', 'tas', 'uas', 'ta500', 'ta850', 'ua500', 'ua850', 'vas', 'zg500', 'va500', 'va850', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'clt', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'psl', 'mrro', 'pr', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snw', 'ta200', 'tasmax', 'tasmin', 'tas', 'uas', 'ta500', 'ta850', 'ua500', 'ua850', 'vas', 'zg500', 'va500', 'va850', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'clt', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'psl', 'mrro', 'pr']</t>
+          <t>['sfcWindmax', 'rsus', 'rsdt', 'rsut', 'sfcWind', 'snw', 'ta200', 'tasmax', 'tasmin', 'tas', 'uas', 'ta500', 'ta850', 'ua500', 'ua850', 'vas', 'zg500', 'va500', 'va850', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'clt', 'rsds', 'rlds', 'rlus', 'rlut', 'mrso', 'psl', 'mrro', 'pr']</t>
         </is>
       </c>
     </row>
@@ -23217,7 +23217,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>['zg500', 'hfls', 'evspsbl', 'clt', 'sfcWindmax', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'hfss', 'mrso', 'huss', 'hurs', 'hus850', 'psl', 'mrro', 'pr', 'tasmax', 'tasmin', 'snw', 'tas', 'ta200', 'ta500', 'ta850', 'zg500', 'hfls', 'evspsbl', 'clt', 'sfcWindmax', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'hfss', 'mrso', 'huss', 'hurs', 'hus850', 'psl', 'mrro', 'pr', 'tasmax', 'tasmin', 'snw', 'tas', 'ta200', 'ta500', 'ta850']</t>
+          <t>['zg500', 'hfls', 'evspsbl', 'clt', 'sfcWindmax', 'rsds', 'rlds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'hfss', 'mrso', 'huss', 'hurs', 'hus850', 'psl', 'mrro', 'pr', 'tasmax', 'tasmin', 'snw', 'tas', 'ta200', 'ta500', 'ta850']</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -23501,7 +23501,7 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'sfcWind', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'sfcWind', 'tas']</t>
+          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -23533,7 +23533,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'psl', 'tas', 'huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'psl', 'tas']</t>
+          <t>['huss', 'hurs', 'clt', 'ps', 'pr', 'rsds', 'rlds', 'rsus', 'sfcWind', 'psl', 'tas']</t>
         </is>
       </c>
     </row>
@@ -23565,7 +23565,7 @@
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -23597,7 +23597,7 @@
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'zg500', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'clt', 'rsds', 'rlds', 'rlus', 'rlut', 'prc', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'wsgsmax', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'zg500', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'clt', 'rsds', 'rlds', 'rlus', 'rlut', 'prc', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'sfcWind', 'tas']</t>
+          <t>['wsgsmax', 'vas', 'uas', 'va500', 'va850', 'ua500', 'ua850', 'zg500', 'hfss', 'hfls', 'mrso', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'sfcWindmax', 'rsus', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'clt', 'rsds', 'rlds', 'rlus', 'rlut', 'prc', 'psl', 'prsn', 'ps', 'pr', 'tasmax', 'tasmin', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -23629,7 +23629,7 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'clt', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snw', 'ta200', 'ta500', 'tasmax', 'tasmin', 'tas', 'uas', 'ta850', 'ua500', 'ua850', 'vas', 'zg500', 'va500', 'va850', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'pr', 'hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'clt', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snw', 'ta200', 'ta500', 'tasmax', 'tasmin', 'tas', 'uas', 'ta850', 'ua500', 'ua850', 'vas', 'zg500', 'va500', 'va850', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'pr']</t>
+          <t>['hfss', 'hfls', 'evspsbl', 'huss', 'hurs', 'hus850', 'mrro', 'clt', 'sfcWindmax', 'rsus', 'rsut', 'sfcWind', 'snw', 'ta200', 'ta500', 'tasmax', 'tasmin', 'tas', 'uas', 'ta850', 'ua500', 'ua850', 'vas', 'zg500', 'va500', 'va850', 'rsds', 'rlds', 'rlus', 'rsdt', 'rlut', 'mrso', 'psl', 'pr']</t>
         </is>
       </c>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'zg500', 'va500', 'va850', 'ua500', 'ua850', 'tasmax', 'tasmin', 'snw', 'tas', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'evspsbl', 'clt', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'rlds', 'mrso', 'huss', 'hurs', 'hus850', 'psl', 'mrro', 'pr', 'vas', 'uas', 'zg500', 'va500', 'va850', 'ua500', 'ua850', 'tasmax', 'tasmin', 'snw', 'tas', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'evspsbl', 'clt', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'rlds', 'mrso', 'huss', 'hurs', 'hus850', 'psl', 'mrro', 'pr']</t>
+          <t>['vas', 'uas', 'zg500', 'va500', 'va850', 'ua500', 'ua850', 'tasmax', 'tasmin', 'snw', 'tas', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'evspsbl', 'clt', 'sfcWindmax', 'rsds', 'rsus', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'rlds', 'mrso', 'huss', 'hurs', 'hus850', 'psl', 'mrro', 'pr']</t>
         </is>
       </c>
     </row>
@@ -23701,7 +23701,7 @@
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -23737,7 +23737,7 @@
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>['clt', 'hurs', 'huss', 'pr', 'ps', 'rlds', 'rsds', 'sfcWind', 'tas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hurs', 'huss', 'pr', 'ps', 'rlds', 'rsds', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>['sfcWind', 'tas', 'uas', 'vas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'rsus', 'sfcWind', 'tas', 'uas', 'vas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'rsus']</t>
+          <t>['sfcWind', 'tas', 'uas', 'vas', 'clt', 'hurs', 'huss', 'pr', 'ps', 'psl', 'rlds', 'rsds', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'clt', 'evspsbl', 'hfls', 'hfss', 'ta500', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'clt', 'evspsbl', 'hfls', 'hfss', 'ta500', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas']</t>
+          <t>['rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'prc', 'prsn', 'ps', 'psl', 'rlds', 'clt', 'evspsbl', 'hfls', 'hfss', 'ta500', 'va200', 'va500', 'va850', 'vas', 'wsgsmax', 'zg200', 'zg500', 'ta850', 'tas', 'tasmax', 'tasmin', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'ua850', 'uas']</t>
         </is>
       </c>
     </row>
@@ -23865,7 +23865,7 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>['tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs']</t>
+          <t>['tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rsus', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -23897,7 +23897,7 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>['rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500', 'rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500']</t>
+          <t>['rsut', 'sfcWind', 'sfcWindmax', 'sic', 'snm', 'snw', 'ta200', 'ta500', 'ta850', 'tas', 'tasmax', 'tasmin', 'ua200', 'ua500', 'ua850', 'uas', 'clt', 'evspsbl', 'hfls', 'hfss', 'hurs', 'hus850', 'huss', 'mrro', 'mrros', 'mrso', 'pr', 'psl', 'rlds', 'rlus', 'rlut', 'rsds', 'rsdt', 'rsus', 'va200', 'va500', 'va850', 'vas', 'zg200', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -24037,7 +24037,7 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>['psl', 'clt', 'rlds', 'ta850', 'vas', 'ta500', 'rsds', 'hurs', 'snw', 'mrro', 'va500', 'rsus', 'rlut', 'huss', 'prc', 'ps', 'ua500', 'ua850', 'ts', 'va850', 'wsgsmax', 'uas', 'prsn', 'rlus', 'hfss', 'rsdt', 'evspsbl', 'zg500', 'sfcWindmax', 'hfls', 'mrso', 'rsut', 'hus850', 'ta200', 'tasmin', 'tasmin', 'tas', 'sfcWind', 'tasmax', 'pr']</t>
+          <t>['psl', 'clt', 'rlds', 'ta850', 'vas', 'ta500', 'rsds', 'hurs', 'snw', 'mrro', 'va500', 'rsus', 'rlut', 'huss', 'prc', 'ps', 'ua500', 'ua850', 'ts', 'va850', 'wsgsmax', 'uas', 'prsn', 'rlus', 'hfss', 'rsdt', 'evspsbl', 'zg500', 'sfcWindmax', 'hfls', 'mrso', 'rsut', 'hus850', 'ta200', 'tasmin', 'tas', 'sfcWind', 'tasmax', 'pr']</t>
         </is>
       </c>
     </row>
@@ -25145,7 +25145,7 @@
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>['va500', 'hus850', 'rsdt', 'snc', 'rlut', 'prhmax', 'vas', 'wsgsmax', 'mrro', 'snw', 'hfss', 'hfls', 'mrso', 'ts', 'sfcWindmax', 'ta500', 'rlus', 'ta850', 'ua500', 'prc', 'uas', 'ta200', 'rsut', 'sund', 'prsn', 'snd', 'ua850', 'tasmin', 'tas', 'rsds', 'rlus', 'ta850', 'ua500', 'prc', 'uas', 'ta200', 'rsut', 'sund', 'prsn', 'snd', 'ua850', 'tasmin', 'tas', 'rsds', 'huss', 'sfcWind', 'pr', 'ps', 'tasmax', 'clt', 'zg500', 'rsus', 'hurs', 'evspsbl', 'va850', 'rlds', 'psl']</t>
+          <t>['va500', 'hus850', 'rsdt', 'snc', 'rlut', 'prhmax', 'vas', 'wsgsmax', 'mrro', 'snw', 'hfss', 'hfls', 'mrso', 'ts', 'sfcWindmax', 'ta500', 'rlus', 'ta850', 'ua500', 'prc', 'uas', 'ta200', 'rsut', 'sund', 'prsn', 'snd', 'ua850', 'tasmin', 'tas', 'rsds', 'huss', 'sfcWind', 'pr', 'ps', 'tasmax', 'clt', 'zg500', 'rsus', 'hurs', 'evspsbl', 'va850', 'rlds', 'psl']</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'orog', 'sftlf', 'sftgif']</t>
+          <t>['areacella', 'orog', 'sftlf', 'sftgif']</t>
         </is>
       </c>
     </row>
@@ -25273,7 +25273,7 @@
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>['ta850', 'hfls', 'rsdt', 'snw', 'sund', 'sfcWindmax', 'mrso', 'snd', 'va500', 'mrro', 'hfss', 'hus850', 'rlut', 'uas', 'ta500', 'rsut', 'snc', 'ta200', 'vas', 'rlus', 'ua500', 'ua850', 'rsds', 'snc', 'ta200', 'vas', 'rlus', 'ua500', 'ua850', 'rsds', 'hurs', 'pr', 'clt', 'tasmax', 'va850', 'huss', 'rlds', 'psl', 'zg500', 'sfcWind', 'tasmin', 'tas', 'rsus', 'evspsbl']</t>
+          <t>['ta850', 'hfls', 'rsdt', 'snw', 'sund', 'sfcWindmax', 'mrso', 'snd', 'va500', 'mrro', 'hfss', 'hus850', 'rlut', 'uas', 'ta500', 'rsut', 'snc', 'ta200', 'vas', 'rlus', 'ua500', 'ua850', 'rsds', 'hurs', 'pr', 'clt', 'tasmax', 'va850', 'huss', 'rlds', 'psl', 'zg500', 'sfcWind', 'tasmin', 'tas', 'rsus', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>['vas', 'rlus', 'ta500', 'snw', 'uas', 'rsut', 'snd', 'ua500', 'ta850', 'hfss', 'sfcWindmax', 'snc', 'hfls', 'hus850', 'mrso', 'rsdt', 'mrro', 'ta200', 'va500', 'rlut', 'sund', 'tas', 'clt', 'tasmax', 'tasmin', 'ua850', 'va500', 'rlut', 'sund', 'tas', 'clt', 'tasmax', 'tasmin', 'ua850', 'zg500', 'rsus', 'evspsbl', 'hurs', 'pr', 'rsds', 'sfcWind', 'huss', 'psl', 'va850', 'rlds']</t>
+          <t>['vas', 'rlus', 'ta500', 'snw', 'uas', 'rsut', 'snd', 'ua500', 'ta850', 'hfss', 'sfcWindmax', 'snc', 'hfls', 'hus850', 'mrso', 'rsdt', 'mrro', 'ta200', 'va500', 'rlut', 'sund', 'tas', 'clt', 'tasmax', 'tasmin', 'ua850', 'zg500', 'rsus', 'evspsbl', 'hurs', 'pr', 'rsds', 'sfcWind', 'huss', 'psl', 'va850', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -25345,7 +25345,7 @@
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25377,7 @@
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25409,7 +25409,7 @@
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'rlds', 'ua850', 'tasmax', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'rlds', 'ua850', 'tasmax', 'evspsbl', 'psl', 'rsds', 'pr', 'tas', 'hurs', 'zg500', 'va850', 'rsus', 'clt', 'sfcWind', 'huss', 'tasmin', 'ps']</t>
+          <t>['ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'rlds', 'ua850', 'tasmax', 'evspsbl', 'psl', 'rsds', 'pr', 'tas', 'hurs', 'zg500', 'va850', 'rsus', 'clt', 'sfcWind', 'huss', 'tasmin', 'ps']</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'areacella', 'sftlf', 'orog', 'sftgif']</t>
+          <t>['areacella', 'sftlf', 'orog', 'sftgif']</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="J771" t="inlineStr">
         <is>
-          <t>['ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'tas', 'huss', 'rsus', 'clt', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'tas', 'huss', 'rsus', 'clt', 'zg500', 'tasmax', 'rsds', 'rlds', 'va850', 'ua850', 'hurs', 'pr', 'psl', 'evspsbl', 'tasmin', 'sfcWind']</t>
+          <t>['ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'tas', 'huss', 'rsus', 'clt', 'zg500', 'tasmax', 'rsds', 'rlds', 'va850', 'ua850', 'hurs', 'pr', 'psl', 'evspsbl', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>['uas', 'ua500', 'ta500', 'ta850', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'vas', 'va500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'tasmin', 'hurs', 'evspsbl', 'sfcWind', 'pr', 'uas', 'ua500', 'ta500', 'ta850', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'vas', 'va500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'tasmin', 'hurs', 'evspsbl', 'sfcWind', 'pr', 'rsds', 'clt', 'ua850', 'huss', 'tas', 'rsus', 'zg500', 'va850', 'rlds', 'tasmax']</t>
+          <t>['uas', 'ua500', 'ta500', 'ta850', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'vas', 'va500', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'psl', 'tasmin', 'hurs', 'evspsbl', 'sfcWind', 'pr', 'rsds', 'clt', 'ua850', 'huss', 'tas', 'rsus', 'zg500', 'va850', 'rlds', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -25545,7 +25545,7 @@
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>['rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds']</t>
+          <t>['rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25609,7 +25609,7 @@
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'ts', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'va850', 'clt', 'tasmax', 'tas', 'rsds', 'psl', 'rlds', 'evspsbl', 'va850', 'clt', 'tasmax', 'tas', 'rsds', 'psl', 'rlds', 'evspsbl', 'tasmin', 'huss', 'hurs', 'ps', 'sfcWind', 'pr', 'ua850', 'zg500', 'rsus']</t>
+          <t>['wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'ts', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'prhmax', 'rlus', 'rlut', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'va850', 'clt', 'tasmax', 'tas', 'rsds', 'psl', 'rlds', 'evspsbl', 'tasmin', 'huss', 'hurs', 'ps', 'sfcWind', 'pr', 'ua850', 'zg500', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -25641,7 +25641,7 @@
       </c>
       <c r="J776" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog', 'sftgif']</t>
+          <t>['areacella', 'sftlf', 'orog', 'sftgif']</t>
         </is>
       </c>
     </row>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta850', 'ta500', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'vas', 'uas', 'va500', 'ua500', 'ua850', 'pr', 'sfcWind', 'rsds', 'huss', 'ua850', 'pr', 'sfcWind', 'rsds', 'huss', 'tasmax', 'rlds', 'tasmin', 'psl', 'tas', 'hurs', 'va850', 'evspsbl', 'clt', 'rsus', 'zg500']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta850', 'ta500', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'vas', 'uas', 'va500', 'ua500', 'ua850', 'pr', 'sfcWind', 'rsds', 'huss', 'tasmax', 'rlds', 'tasmin', 'psl', 'tas', 'hurs', 'va850', 'evspsbl', 'clt', 'rsus', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -25705,7 +25705,7 @@
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'huss', 'tasmin', 'zg500', 'tasmax', 'rsds', 'pr', 'rlds', 'huss', 'tasmin', 'zg500', 'tasmax', 'rsds', 'pr', 'rlds', 'rsus', 'psl', 'evspsbl', 'clt', 'hurs', 'tas', 'sfcWind', 'va850', 'ua850']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'huss', 'tasmin', 'zg500', 'tasmax', 'rsds', 'pr', 'rlds', 'rsus', 'psl', 'evspsbl', 'clt', 'hurs', 'tas', 'sfcWind', 'va850', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -25745,7 +25745,7 @@
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>['ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw']</t>
+          <t>['ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw']</t>
         </is>
       </c>
     </row>
@@ -25777,7 +25777,7 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="J781" t="inlineStr">
         <is>
-          <t>['prc', 'snw', 'ua500', 'uas', 'snd', 'vas', 'rsut', 'mrro', 'ta200', 'snc', 'hus850', 'ta850', 'wsgsmax', 'va500', 'sfcWindmax', 'rlut', 'ta500', 'prhmax', 'ts', 'rlus', 'rsdt', 'sund', 'hfss', 'hfls', 'prsn', 'mrso', 'pr', 'ua850', 'tasmin', 'rlds', 'va850', 'rsus', 'rsdt', 'sund', 'hfss', 'hfls', 'prsn', 'mrso', 'pr', 'ua850', 'tasmin', 'rlds', 'va850', 'rsus', 'evspsbl', 'rsds', 'clt', 'psl', 'huss', 'sfcWind', 'ps', 'tas', 'zg500', 'hurs', 'tasmax']</t>
+          <t>['prc', 'snw', 'ua500', 'uas', 'snd', 'vas', 'rsut', 'mrro', 'ta200', 'snc', 'hus850', 'ta850', 'wsgsmax', 'va500', 'sfcWindmax', 'rlut', 'ta500', 'prhmax', 'ts', 'rlus', 'rsdt', 'sund', 'hfss', 'hfls', 'prsn', 'mrso', 'pr', 'ua850', 'tasmin', 'rlds', 'va850', 'rsus', 'evspsbl', 'rsds', 'clt', 'psl', 'huss', 'sfcWind', 'ps', 'tas', 'zg500', 'hurs', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog', 'sftgif']</t>
+          <t>['areacella', 'sftlf', 'orog', 'sftgif']</t>
         </is>
       </c>
     </row>
@@ -25873,7 +25873,7 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>['hfss', 'sfcWindmax', 'snc', 'rlut', 'ta200', 'hfls', 'vas', 'mrro', 'mrso', 'uas', 'ta500', 'ua500', 'hus850', 'rsdt', 'va500', 'ta850', 'rsut', 'snw', 'snd', 'rlus', 'sund', 'clt', 'rlds', 'psl', 'rsut', 'snw', 'snd', 'rlus', 'sund', 'clt', 'rlds', 'psl', 'huss', 'rsus', 'rsds', 'evspsbl', 'tasmax', 'va850', 'tas', 'tasmin', 'ua850', 'zg500', 'hurs', 'sfcWind', 'pr']</t>
+          <t>['hfss', 'sfcWindmax', 'snc', 'rlut', 'ta200', 'hfls', 'vas', 'mrro', 'mrso', 'uas', 'ta500', 'ua500', 'hus850', 'rsdt', 'va500', 'ta850', 'rsut', 'snw', 'snd', 'rlus', 'sund', 'clt', 'rlds', 'psl', 'huss', 'rsus', 'rsds', 'evspsbl', 'tasmax', 'va850', 'tas', 'tasmin', 'ua850', 'zg500', 'hurs', 'sfcWind', 'pr']</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>['snd', 'ua500', 'ta500', 'rsut', 'snw', 'uas', 'mrso', 'sfcWindmax', 'vas', 'rsdt', 'va500', 'mrro', 'hfss', 'snc', 'ta850', 'rlus', 'hus850', 'hfls', 'rlut', 'ta200', 'sund', 'tasmin', 'pr', 'hfls', 'rlut', 'ta200', 'sund', 'tasmin', 'pr', 'rsds', 'tasmax', 'rsus', 'zg500', 'clt', 'ua850', 'tas', 'hurs', 'psl', 'va850', 'huss', 'evspsbl', 'sfcWind', 'rlds']</t>
+          <t>['snd', 'ua500', 'ta500', 'rsut', 'snw', 'uas', 'mrso', 'sfcWindmax', 'vas', 'rsdt', 'va500', 'mrro', 'hfss', 'snc', 'ta850', 'rlus', 'hus850', 'hfls', 'rlut', 'ta200', 'sund', 'tasmin', 'pr', 'rsds', 'tasmax', 'rsus', 'zg500', 'clt', 'ua850', 'tas', 'hurs', 'psl', 'va850', 'huss', 'evspsbl', 'sfcWind', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>['snw', 'snc', 'sund', 'snd', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'pr', 'ps', 'rsus', 'pr', 'ps', 'clt', 'rlds', 'psl', 'evspsbl', 'rsds']</t>
+          <t>['snw', 'snc', 'sund', 'snd', 'hfss', 'hfls', 'mrro', 'ts', 'rlus', 'rsdt', 'rsut', 'rlut', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'pr', 'ps', 'clt', 'rlds', 'psl', 'evspsbl', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'wsgsmax', 'vas', 'uas', 'huss', 'huss', 'sfcWind', 'tas', 'hurs', 'tasmin', 'tasmax']</t>
+          <t>['sfcWindmax', 'wsgsmax', 'vas', 'uas', 'huss', 'sfcWind', 'tas', 'hurs', 'tasmin', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -26005,7 +26005,7 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>['ta850', 'ta200', 'ta500', 'hus850', 'ua500', 'va500', 'ua850', 'va850', 'ua850', 'va850', 'zg500']</t>
+          <t>['ta850', 'ta200', 'ta500', 'hus850', 'ua500', 'va500', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>['mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'snd', 'psl', 'psl', 'rsds', 'clt', 'rsus', 'pr', 'evspsbl', 'rlds']</t>
+          <t>['mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'snd', 'psl', 'rsds', 'clt', 'rsus', 'pr', 'evspsbl', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>['uas', 'sfcWindmax', 'vas', 'huss', 'huss', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'hurs']</t>
+          <t>['uas', 'sfcWindmax', 'vas', 'huss', 'tasmin', 'tas', 'tasmax', 'sfcWind', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'zg500', 'ua850', 'zg500', 'va850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'ua850', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26157,7 +26157,7 @@
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'sund', 'snc', 'snd', 'clt', 'rlds', 'evspsbl', 'rsus', 'clt', 'rlds', 'evspsbl', 'rsus', 'psl', 'pr', 'rsds']</t>
+          <t>['hfss', 'hfls', 'mrso', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'sund', 'snc', 'snd', 'clt', 'rlds', 'evspsbl', 'rsus', 'psl', 'pr', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -26185,7 +26185,7 @@
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'uas', 'vas', 'sfcWind', 'sfcWind', 'tasmin', 'tas', 'tasmax', 'hurs', 'huss']</t>
+          <t>['sfcWindmax', 'uas', 'vas', 'sfcWind', 'tasmin', 'tas', 'tasmax', 'hurs', 'huss']</t>
         </is>
       </c>
     </row>
@@ -26213,7 +26213,7 @@
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'va850', 'ua850', 'va850', 'zg500']</t>
+          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>['pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss']</t>
+          <t>['pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss']</t>
         </is>
       </c>
     </row>
@@ -26289,7 +26289,7 @@
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>['rlus', 'hfss', 'snw', 'wsgsmax', 'rsut', 'snc', 'mrso', 'snd', 'hfls', 'vas', 'uas', 'prsn', 'ua500', 'rsdt', 'ta200', 'prhmax', 'sund', 'hus850', 'mrro', 'ta850', 'ta500', 'sfcWindmax', 'rlut', 'prc', 'va500', 'ts', 'rlds', 'psl', 'sfcWind', 'evspsbl', 'ps', 'tasmax', 'pr', 'rlds', 'psl', 'sfcWind', 'evspsbl', 'ps', 'tasmax', 'pr', 'huss', 'clt', 'ua850', 'rsus', 'va850', 'tas', 'rsds', 'hurs', 'zg500', 'tasmin']</t>
+          <t>['rlus', 'hfss', 'snw', 'wsgsmax', 'rsut', 'snc', 'mrso', 'snd', 'hfls', 'vas', 'uas', 'prsn', 'ua500', 'rsdt', 'ta200', 'prhmax', 'sund', 'hus850', 'mrro', 'ta850', 'ta500', 'sfcWindmax', 'rlut', 'prc', 'va500', 'ts', 'rlds', 'psl', 'sfcWind', 'evspsbl', 'ps', 'tasmax', 'pr', 'huss', 'clt', 'ua850', 'rsus', 'va850', 'tas', 'rsds', 'hurs', 'zg500', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -26385,7 +26385,7 @@
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'ua500', 'vas', 'ta500', 'snd', 'mrso', 'hfss', 'rsdt', 'rsut', 'rlus', 'rlut', 'hus850', 'snc', 'uas', 'snw', 'va500', 'ta200', 'sund', 'hfls', 'ta850', 'mrro', 'va850', 'psl', 'hurs', 'va850', 'psl', 'hurs', 'rsus', 'clt', 'ua850', 'zg500', 'tasmin', 'evspsbl', 'pr', 'tasmax', 'sfcWind', 'tas', 'huss', 'rlds', 'rsds']</t>
+          <t>['sfcWindmax', 'ua500', 'vas', 'ta500', 'snd', 'mrso', 'hfss', 'rsdt', 'rsut', 'rlus', 'rlut', 'hus850', 'snc', 'uas', 'snw', 'va500', 'ta200', 'sund', 'hfls', 'ta850', 'mrro', 'va850', 'psl', 'hurs', 'rsus', 'clt', 'ua850', 'zg500', 'tasmin', 'evspsbl', 'pr', 'tasmax', 'sfcWind', 'tas', 'huss', 'rlds', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>['ua500', 'rsut', 'vas', 'uas', 'mrro', 'va500', 'ta850', 'hfls', 'sund', 'ta500', 'ta200', 'sfcWindmax', 'rlus', 'hus850', 'snd', 'hfss', 'mrso', 'snc', 'rsdt', 'rlut', 'snw', 'rsds', 'sfcWind', 'pr', 'tas', 'ua850', 'rsds', 'sfcWind', 'pr', 'tas', 'ua850', 'rlds', 'tasmin', 'hurs', 'va850', 'rsus', 'clt', 'tasmax', 'psl', 'huss', 'zg500', 'evspsbl']</t>
+          <t>['ua500', 'rsut', 'vas', 'uas', 'mrro', 'va500', 'ta850', 'hfls', 'sund', 'ta500', 'ta200', 'sfcWindmax', 'rlus', 'hus850', 'snd', 'hfss', 'mrso', 'snc', 'rsdt', 'rlut', 'snw', 'rsds', 'sfcWind', 'pr', 'tas', 'ua850', 'rlds', 'tasmin', 'hurs', 'va850', 'rsus', 'clt', 'tasmax', 'psl', 'huss', 'zg500', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -26453,7 +26453,7 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>['huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs']</t>
+          <t>['huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26609,7 @@
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'huss', 'tasmax', 'hurs', 'clt', 'rsus', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'mrro', 'pr', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWind', 'snw', 'tas', 'snc', 'sund', 'snd', 'uas', 'vas', 'rlds', 'evspsbl', 'tasmin', 'rsds', 'huss', 'tasmax', 'hurs', 'clt', 'rsus', 'psl']</t>
         </is>
       </c>
     </row>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'zg500', 'ua850', 'zg500', 'va850']</t>
+          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'ua850', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26669,7 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>['rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'tasmax', 'huss', 'tasmin', 'tas', 'tasmax', 'huss', 'tasmin', 'tas', 'psl', 'sfcWind', 'evspsbl', 'rlds', 'hurs', 'rsds', 'rsus', 'pr', 'clt']</t>
+          <t>['rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'snd', 'tasmax', 'huss', 'tasmin', 'tas', 'psl', 'sfcWind', 'evspsbl', 'rlds', 'hurs', 'rsds', 'rsus', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -26697,7 +26697,7 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'zg500', 'ua850', 'va850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'ua850', 'va850']</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -26765,7 +26765,7 @@
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26797,7 +26797,7 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>['ua500', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prsn', 'psl', 'va850', 'tasmin', 'ua500', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prsn', 'psl', 'va850', 'tasmin', 'rlds', 'clt', 'tasmax', 'rsus', 'huss', 'pr', 'ua850', 'evspsbl', 'ps', 'sfcWind', 'tas', 'hurs', 'rsds', 'zg500']</t>
+          <t>['ua500', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'prhmax', 'mrso', 'prc', 'prsn', 'psl', 'va850', 'tasmin', 'rlds', 'clt', 'tasmax', 'rsus', 'huss', 'pr', 'ua850', 'evspsbl', 'ps', 'sfcWind', 'tas', 'hurs', 'rsds', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -26829,7 +26829,7 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -26861,7 +26861,7 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>['uas', 'va500', 'ua500', 'mrso', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rsds', 'va850', 'rsus', 'hurs', 'uas', 'va500', 'ua500', 'mrso', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rsds', 'va850', 'rsus', 'hurs', 'evspsbl', 'pr', 'tasmax', 'huss', 'psl', 'clt', 'tasmin', 'rlds', 'zg500', 'ua850', 'tas', 'sfcWind']</t>
+          <t>['uas', 'va500', 'ua500', 'mrso', 'hus850', 'mrro', 'hfss', 'hfls', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rsds', 'va850', 'rsus', 'hurs', 'evspsbl', 'pr', 'tasmax', 'huss', 'psl', 'clt', 'tasmin', 'rlds', 'zg500', 'ua850', 'tas', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'vas', 'clt', 'evspsbl', 'rsus', 'sfcWind', 'tasmin', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'vas', 'clt', 'evspsbl', 'rsus', 'sfcWind', 'tasmin', 'tasmax', 'psl', 'zg500', 'rsds', 'tas', 'rlds', 'ua850', 'pr', 'va850', 'hurs', 'huss']</t>
+          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'vas', 'clt', 'evspsbl', 'rsus', 'sfcWind', 'tasmin', 'tasmax', 'psl', 'zg500', 'rsds', 'tas', 'rlds', 'ua850', 'pr', 'va850', 'hurs', 'huss']</t>
         </is>
       </c>
     </row>
@@ -26933,7 +26933,7 @@
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -26965,7 +26965,7 @@
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -26997,7 +26997,7 @@
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>['snw', 'mrro', 'ua500', 'sund', 'ta850', 'rlut', 'ta500', 'rlus', 'hfls', 'rsdt', 'rsut', 'sfcWindmax', 'prsn', 'wsgsmax', 'snc', 'uas', 'mrso', 'prhmax', 'va500', 'snd', 'hus850', 'ts', 'prc', 'hfss', 'vas', 'ta200', 'rsus', 'zg500', 'ps', 'tasmin', 'tas', 'rsus', 'zg500', 'ps', 'tasmin', 'tas', 'va850', 'rsds', 'sfcWind', 'evspsbl', 'clt', 'ua850', 'huss', 'psl', 'hurs', 'rlds', 'tasmax', 'pr']</t>
+          <t>['snw', 'mrro', 'ua500', 'sund', 'ta850', 'rlut', 'ta500', 'rlus', 'hfls', 'rsdt', 'rsut', 'sfcWindmax', 'prsn', 'wsgsmax', 'snc', 'uas', 'mrso', 'prhmax', 'va500', 'snd', 'hus850', 'ts', 'prc', 'hfss', 'vas', 'ta200', 'rsus', 'zg500', 'ps', 'tasmin', 'tas', 'va850', 'rsds', 'sfcWind', 'evspsbl', 'clt', 'ua850', 'huss', 'psl', 'hurs', 'rlds', 'tasmax', 'pr']</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -27061,7 +27061,7 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>['ta500', 'sund', 'ta850', 'hfss', 'ua500', 'vas', 'ta200', 'rsut', 'snw', 'uas', 'snc', 'va500', 'rlus', 'mrro', 'snd', 'sfcWindmax', 'rlut', 'rsdt', 'mrso', 'hfls', 'hus850', 'rsds', 'clt', 'va850', 'zg500', 'sfcWind', 'rsds', 'clt', 'va850', 'zg500', 'sfcWind', 'tas', 'tasmax', 'pr', 'evspsbl', 'rlds', 'psl', 'huss', 'tasmin', 'ua850', 'hurs', 'rsus']</t>
+          <t>['ta500', 'sund', 'ta850', 'hfss', 'ua500', 'vas', 'ta200', 'rsut', 'snw', 'uas', 'snc', 'va500', 'rlus', 'mrro', 'snd', 'sfcWindmax', 'rlut', 'rsdt', 'mrso', 'hfls', 'hus850', 'rsds', 'clt', 'va850', 'zg500', 'sfcWind', 'tas', 'tasmax', 'pr', 'evspsbl', 'rlds', 'psl', 'huss', 'tasmin', 'ua850', 'hurs', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>['mrso', 'ta500', 'rlus', 'uas', 'hfss', 'hfls', 'sund', 'ua500', 'rsdt', 'ta200', 'snc', 'snd', 'vas', 'rlut', 'hus850', 'snw', 'va500', 'sfcWindmax', 'ta850', 'rsut', 'mrro', 'sfcWind', 'tas', 'rsds', 'huss', 'tasmin', 'sfcWind', 'tas', 'rsds', 'huss', 'tasmin', 'va850', 'pr', 'rsus', 'evspsbl', 'psl', 'hurs', 'ua850', 'clt', 'zg500', 'rlds', 'tasmax']</t>
+          <t>['mrso', 'ta500', 'rlus', 'uas', 'hfss', 'hfls', 'sund', 'ua500', 'rsdt', 'ta200', 'snc', 'snd', 'vas', 'rlut', 'hus850', 'snw', 'va500', 'sfcWindmax', 'ta850', 'rsut', 'mrro', 'sfcWind', 'tas', 'rsds', 'huss', 'tasmin', 'va850', 'pr', 'rsus', 'evspsbl', 'psl', 'hurs', 'ua850', 'clt', 'zg500', 'rlds', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -27133,7 +27133,7 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27165,7 +27165,7 @@
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -27197,7 +27197,7 @@
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>['prsn', 'mrro', 'ua500', 'prhmax', 'prc', 'ta500', 'snw', 'wsgsmax', 'va500', 'vas', 'hus850', 'ta850', 'rlus', 'ts', 'uas', 'rlut', 'rsdt', 'snd', 'hfss', 'snc', 'ta200', 'hfls', 'sund', 'sfcWindmax', 'rsut', 'mrso', 'clt', 'tasmin', 'huss', 'pr', 'sfcWind', 'clt', 'tasmin', 'huss', 'pr', 'sfcWind', 'rsds', 'rsus', 'hurs', 'tas', 'ps', 'va850', 'tasmax', 'evspsbl', 'rlds', 'zg500', 'psl', 'ua850']</t>
+          <t>['prsn', 'mrro', 'ua500', 'prhmax', 'prc', 'ta500', 'snw', 'wsgsmax', 'va500', 'vas', 'hus850', 'ta850', 'rlus', 'ts', 'uas', 'rlut', 'rsdt', 'snd', 'hfss', 'snc', 'ta200', 'hfls', 'sund', 'sfcWindmax', 'rsut', 'mrso', 'clt', 'tasmin', 'huss', 'pr', 'sfcWind', 'rsds', 'rsus', 'hurs', 'tas', 'ps', 'va850', 'tasmax', 'evspsbl', 'rlds', 'zg500', 'psl', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -27229,7 +27229,7 @@
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27261,7 +27261,7 @@
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>['hfls', 'rsdt', 'rlut', 'vas', 'snw', 'rsut', 'sund', 'ta200', 'ta850', 'snd', 'hus850', 'hfss', 'uas', 'snc', 'va500', 'ta500', 'rlus', 'mrso', 'ua500', 'sfcWindmax', 'mrro', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'pr', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'pr', 'psl', 'tas', 'sfcWind', 'rsus', 'tasmax', 'tasmin', 'ua850', 'evspsbl', 'rsds', 'hurs']</t>
+          <t>['hfls', 'rsdt', 'rlut', 'vas', 'snw', 'rsut', 'sund', 'ta200', 'ta850', 'snd', 'hus850', 'hfss', 'uas', 'snc', 'va500', 'ta500', 'rlus', 'mrso', 'ua500', 'sfcWindmax', 'mrro', 'rlds', 'huss', 'clt', 'va850', 'zg500', 'pr', 'psl', 'tas', 'sfcWind', 'rsus', 'tasmax', 'tasmin', 'ua850', 'evspsbl', 'rsds', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -27293,7 +27293,7 @@
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>['vas', 'snw', 'rsdt', 'rlut', 'rsut', 'hfls', 'ta200', 'snc', 'sund', 'ua500', 'mrro', 'rlus', 'uas', 'ta850', 'sfcWindmax', 'hfss', 'hus850', 'snd', 'va500', 'ta500', 'mrso', 'tas', 'ua850', 'rsds', 'tasmax', 'va850', 'psl', 'clt', 'tas', 'ua850', 'rsds', 'tasmax', 'va850', 'psl', 'clt', 'tasmin', 'rsus', 'pr', 'rlds', 'zg500', 'hurs', 'evspsbl', 'sfcWind', 'huss']</t>
+          <t>['vas', 'snw', 'rsdt', 'rlut', 'rsut', 'hfls', 'ta200', 'snc', 'sund', 'ua500', 'mrro', 'rlus', 'uas', 'ta850', 'sfcWindmax', 'hfss', 'hus850', 'snd', 'va500', 'ta500', 'mrso', 'tas', 'ua850', 'rsds', 'tasmax', 'va850', 'psl', 'clt', 'tasmin', 'rsus', 'pr', 'rlds', 'zg500', 'hurs', 'evspsbl', 'sfcWind', 'huss']</t>
         </is>
       </c>
     </row>
@@ -27329,7 +27329,7 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27361,7 +27361,7 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -27393,7 +27393,7 @@
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>['wsgsmax', 'vas', 'hfss', 'hfls', 'mrso', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'uas', 'ts', 'clt', 'pr', 'ps', 'rsus', 'huss', 'clt', 'pr', 'ps', 'rsus', 'huss', 'rlds', 'tas', 'psl', 'sfcWind', 'tasmax', 'tasmin', 'evspsbl', 'rsds', 'hurs']</t>
+          <t>['wsgsmax', 'vas', 'hfss', 'hfls', 'mrso', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'uas', 'ts', 'clt', 'pr', 'ps', 'rsus', 'huss', 'rlds', 'tas', 'psl', 'sfcWind', 'tasmax', 'tasmin', 'evspsbl', 'rsds', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>['va500', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'zg500', 'va850', 'zg500', 'va850', 'ua850']</t>
+          <t>['va500', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'zg500', 'va850', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -27453,7 +27453,7 @@
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27485,7 +27485,7 @@
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'vas', 'uas', 'huss', 'clt', 'rsds', 'psl', 'huss', 'clt', 'rsds', 'psl', 'hurs', 'rsus', 'evspsbl', 'sfcWind', 'pr', 'tasmax', 'tasmin', 'rlds', 'tas']</t>
+          <t>['hfss', 'hfls', 'rlus', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'snd', 'vas', 'uas', 'huss', 'clt', 'rsds', 'psl', 'hurs', 'rsus', 'evspsbl', 'sfcWind', 'pr', 'tasmax', 'tasmin', 'rlds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'snw', 'sund', 'vas', 'uas', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'psl', 'clt', 'sfcWind', 'tas', 'psl', 'clt', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rlds', 'huss', 'hurs', 'evspsbl', 'rsds', 'tasmin']</t>
+          <t>['hfss', 'hfls', 'snw', 'sund', 'vas', 'uas', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'psl', 'clt', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rlds', 'huss', 'hurs', 'evspsbl', 'rsds', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -27573,7 +27573,7 @@
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'va850', 'va850', 'ua850', 'zg500']</t>
+          <t>['hus850', 'ta200', 'ta500', 'ta850', 'va500', 'ua500', 'va850', 'ua850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -27613,7 +27613,7 @@
       </c>
       <c r="J837" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps']</t>
+          <t>['psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps']</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27645,7 @@
       </c>
       <c r="J838" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -27677,7 +27677,7 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t>['rsdt', 'prhmax', 'snc', 'prsn', 'uas', 'sund', 'ta200', 'mrso', 'snw', 'rsut', 'vas', 'ta850', 'ta500', 'ua500', 'rsds', 'sfcWindmax', 'ts', 'hfss', 'hfls', 'rlut', 'va500', 'wsgsmax', 'prc', 'hus850', 'rlus', 'mrro', 'snd', 'pr', 'rlds', 'hurs', 'ps', 'rsus', 'ua850', 'va850', 'evspsbl', 'zg500', 'pr', 'rlds', 'hurs', 'ps', 'rsus', 'ua850', 'va850', 'evspsbl', 'zg500', 'tasmax', 'sfcWind', 'tas', 'psl', 'tasmin', 'huss', 'clt']</t>
+          <t>['rsdt', 'prhmax', 'snc', 'prsn', 'uas', 'sund', 'ta200', 'mrso', 'snw', 'rsut', 'vas', 'ta850', 'ta500', 'ua500', 'rsds', 'sfcWindmax', 'ts', 'hfss', 'hfls', 'rlut', 'va500', 'wsgsmax', 'prc', 'hus850', 'rlus', 'mrro', 'snd', 'pr', 'rlds', 'hurs', 'ps', 'rsus', 'ua850', 'va850', 'evspsbl', 'zg500', 'tasmax', 'sfcWind', 'tas', 'psl', 'tasmin', 'huss', 'clt']</t>
         </is>
       </c>
     </row>
@@ -27709,7 +27709,7 @@
       </c>
       <c r="J840" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="J841" t="inlineStr">
         <is>
-          <t>['hfss', 'mrso', 'hus850', 'ta850', 'rlut', 'uas', 'sund', 'snd', 'hfls', 'ta500', 'snc', 'rsdt', 'ta200', 'rlus', 'mrro', 'rsut', 'sfcWindmax', 'snw', 'vas', 'ua500', 'va500', 'tas', 'va850', 'tas', 'va850', 'sfcWind', 'evspsbl', 'huss', 'rsds', 'tasmin', 'zg500', 'tasmax', 'hurs', 'pr', 'ua850', 'clt', 'psl', 'rsus', 'rlds']</t>
+          <t>['hfss', 'mrso', 'hus850', 'ta850', 'rlut', 'uas', 'sund', 'snd', 'hfls', 'ta500', 'snc', 'rsdt', 'ta200', 'rlus', 'mrro', 'rsut', 'sfcWindmax', 'snw', 'vas', 'ua500', 'va500', 'tas', 'va850', 'sfcWind', 'evspsbl', 'huss', 'rsds', 'tasmin', 'zg500', 'tasmax', 'hurs', 'pr', 'ua850', 'clt', 'psl', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>['ua500', 'uas', 'mrro', 'sfcWindmax', 'rsut', 'vas', 'snw', 'snd', 'ta850', 'ta500', 'hus850', 'hfls', 'va500', 'snc', 'sund', 'mrso', 'ta200', 'rlus', 'hfss', 'rsdt', 'rlut', 'pr', 'rsds', 'hurs', 'tas', 'va850', 'pr', 'rsds', 'hurs', 'tas', 'va850', 'tasmax', 'zg500', 'sfcWind', 'huss', 'tasmin', 'clt', 'psl', 'ua850', 'rlds', 'rsus', 'evspsbl']</t>
+          <t>['ua500', 'uas', 'mrro', 'sfcWindmax', 'rsut', 'vas', 'snw', 'snd', 'ta850', 'ta500', 'hus850', 'hfls', 'va500', 'snc', 'sund', 'mrso', 'ta200', 'rlus', 'hfss', 'rsdt', 'rlut', 'pr', 'rsds', 'hurs', 'tas', 'va850', 'tasmax', 'zg500', 'sfcWind', 'huss', 'tasmin', 'clt', 'psl', 'ua850', 'rlds', 'rsus', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'hfls', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'psl', 'rlds', 'rlus', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>['uas', 'uas']</t>
+          <t>['uas']</t>
         </is>
       </c>
     </row>
@@ -27869,7 +27869,7 @@
       </c>
       <c r="J845" t="inlineStr">
         <is>
-          <t>['vas', 'vas']</t>
+          <t>['vas']</t>
         </is>
       </c>
     </row>
@@ -27901,7 +27901,7 @@
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>['uas', 'ts', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'huss', 'tasmax', 'psl', 'hurs', 'huss', 'tasmax', 'psl', 'hurs', 'clt', 'pr', 'sfcWind', 'rsds', 'rsus', 'ps', 'evspsbl', 'tasmin', 'tas', 'rlds']</t>
+          <t>['uas', 'ts', 'snw', 'sund', 'hfls', 'hfss', 'mrso', 'mrro', 'wsgsmax', 'vas', 'prhmax', 'rlus', 'rlut', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'huss', 'tasmax', 'psl', 'hurs', 'clt', 'pr', 'sfcWind', 'rsds', 'rsus', 'ps', 'evspsbl', 'tasmin', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -27929,7 +27929,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>['va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'ua850', 'va850', 'ua850', 'va850', 'zg500']</t>
+          <t>['va500', 'ua500', 'ta200', 'ta500', 'ta850', 'hus850', 'ua850', 'va850', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'clt', 'tasmin', 'rsus', 'pr', 'clt', 'tasmin', 'rsus', 'pr', 'huss', 'tasmax', 'tas', 'psl', 'rlds', 'hurs', 'rsds', 'sfcWind', 'evspsbl']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'clt', 'tasmin', 'rsus', 'pr', 'huss', 'tasmax', 'tas', 'psl', 'rlds', 'hurs', 'rsds', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -28053,7 +28053,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rsds', 'clt', 'evspsbl', 'tasmin']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'vas', 'uas', 'snw', 'sund', 'psl', 'huss', 'rlds', 'hurs', 'sfcWind', 'tas', 'rsus', 'pr', 'tasmax', 'rsds', 'clt', 'evspsbl', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -28081,7 +28081,7 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'zg500', 'va850', 'ua850']</t>
+          <t>['hus850', 'va500', 'ua500', 'ta200', 'ta500', 'ta850', 'zg500', 'va850', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -28117,7 +28117,7 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28149,7 +28149,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28181,7 +28181,7 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'wsgsmax', 'vas', 'va500', 'uas', 'ua500', 'ts', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'zg500', 'va850', 'huss', 'tas', 'ua850', 'ps', 'tasmax', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'wsgsmax', 'vas', 'va500', 'uas', 'ua500', 'ts', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'zg500', 'va850', 'huss', 'tas', 'ua850', 'ps', 'tasmax', 'evspsbl', 'psl', 'pr', 'rlds', 'tasmin', 'sfcWind', 'clt', 'hurs', 'rsus', 'rsds']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'wsgsmax', 'vas', 'va500', 'uas', 'ua500', 'ts', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'prhmax', 'rlus', 'prc', 'prsn', 'zg500', 'va850', 'huss', 'tas', 'ua850', 'ps', 'tasmax', 'evspsbl', 'psl', 'pr', 'rlds', 'tasmin', 'sfcWind', 'clt', 'hurs', 'rsus', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -28213,7 +28213,7 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -28245,7 +28245,7 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'tas', 'tasmax', 'pr', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'tas', 'tasmax', 'pr', 'psl', 'zg500', 'rlds', 'evspsbl', 'clt', 'huss', 'tasmin', 'rsus', 'hurs', 'sfcWind', 'va850', 'ua850', 'rsds']</t>
+          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'tas', 'tasmax', 'pr', 'psl', 'zg500', 'rlds', 'evspsbl', 'clt', 'huss', 'tasmin', 'rsus', 'hurs', 'sfcWind', 'va850', 'ua850', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'clt', 'sfcWind', 'tasmax', 'hurs', 'pr', 'va850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'clt', 'sfcWind', 'tasmax', 'hurs', 'pr', 'va850', 'ua850', 'rsds', 'tas', 'zg500', 'tasmin', 'psl', 'rsus', 'huss', 'evspsbl']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'clt', 'sfcWind', 'tasmax', 'hurs', 'pr', 'va850', 'ua850', 'rsds', 'tas', 'zg500', 'tasmin', 'psl', 'rsus', 'huss', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -28321,7 +28321,7 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'clt', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'rlds', 'rlus', 'clt', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['rlds', 'rlus', 'clt', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28353,7 +28353,7 @@
       </c>
       <c r="J860" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -28385,7 +28385,7 @@
       </c>
       <c r="J861" t="inlineStr">
         <is>
-          <t>['snw', 'snc', 'snd', 'sfcWindmax', 'rlus', 'prsn', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'ts', 'prhmax', 'mrso', 'prc', 'mrro', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'sund', 'ta200', 'ta500', 'ta850', 'tasmin', 'psl', 'clt', 'va850', 'huss', 'zg500', 'evspsbl', 'snw', 'snc', 'snd', 'sfcWindmax', 'rlus', 'prsn', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'ts', 'prhmax', 'mrso', 'prc', 'mrro', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'sund', 'ta200', 'ta500', 'ta850', 'tasmin', 'psl', 'clt', 'va850', 'huss', 'zg500', 'evspsbl', 'pr', 'tasmax', 'rlds', 'rsds', 'ps', 'sfcWind', 'hurs', 'ua850', 'rsus', 'tas']</t>
+          <t>['snw', 'snc', 'snd', 'sfcWindmax', 'rlus', 'prsn', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'ts', 'prhmax', 'mrso', 'prc', 'mrro', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'sund', 'ta200', 'ta500', 'ta850', 'tasmin', 'psl', 'clt', 'va850', 'huss', 'zg500', 'evspsbl', 'pr', 'tasmax', 'rlds', 'rsds', 'ps', 'sfcWind', 'hurs', 'ua850', 'rsus', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28417,7 +28417,7 @@
       </c>
       <c r="J862" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'rsds', 'va850', 'sund', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'rsds', 'va850', 'tas', 'hurs', 'zg500', 'tasmin', 'rsus', 'pr', 'ua850', 'clt', 'sfcWind', 'rlds', 'evspsbl', 'psl', 'huss', 'tasmax']</t>
+          <t>['sund', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'rsds', 'va850', 'tas', 'hurs', 'zg500', 'tasmin', 'rsus', 'pr', 'ua850', 'clt', 'sfcWind', 'rlds', 'evspsbl', 'psl', 'huss', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -28481,7 +28481,7 @@
       </c>
       <c r="J864" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ua500', 'huss', 'tas', 'evspsbl', 'hurs', 'rsus', 'tasmax', 'tasmin', 'sfcWindmax', 'rsut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ua500', 'huss', 'tas', 'evspsbl', 'hurs', 'rsus', 'tasmax', 'tasmin', 'clt', 'psl', 'va850', 'rsds', 'ua850', 'zg500', 'rlds', 'pr', 'sfcWind']</t>
+          <t>['sfcWindmax', 'rsut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ua500', 'huss', 'tas', 'evspsbl', 'hurs', 'rsus', 'tasmax', 'tasmin', 'clt', 'psl', 'va850', 'rsds', 'ua850', 'zg500', 'rlds', 'pr', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -28521,7 +28521,7 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'hfls', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'psl', 'rlds', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'hfls', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['psl', 'rlds', 'hfss', 'hurs', 'huss', 'pr', 'prw', 'ps', 'hfls', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28553,7 +28553,7 @@
       </c>
       <c r="J866" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28585,7 +28585,7 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'hfss', 'hfls', 'ta500', 'ta850', 'hus850', 'snw', 'sund', 'ta200', 'uas', 'va500', 'ua500', 'mrso', 'mrro', 'wsgsmax', 'vas', 'rlus', 'prhmax', 'prc', 'prsn', 'ts', 'psl', 'tasmin', 'va850', 'ps', 'tasmax', 'sfcWind', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'hfss', 'hfls', 'ta500', 'ta850', 'hus850', 'snw', 'sund', 'ta200', 'uas', 'va500', 'ua500', 'mrso', 'mrro', 'wsgsmax', 'vas', 'rlus', 'prhmax', 'prc', 'prsn', 'ts', 'psl', 'tasmin', 'va850', 'ps', 'tasmax', 'sfcWind', 'rlds', 'pr', 'ua850', 'clt', 'evspsbl', 'rsds', 'zg500', 'rsus', 'hurs', 'tas', 'huss']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snd', 'hfss', 'hfls', 'ta500', 'ta850', 'hus850', 'snw', 'sund', 'ta200', 'uas', 'va500', 'ua500', 'mrso', 'mrro', 'wsgsmax', 'vas', 'rlus', 'prhmax', 'prc', 'prsn', 'ts', 'psl', 'tasmin', 'va850', 'ps', 'tasmax', 'sfcWind', 'rlds', 'pr', 'ua850', 'clt', 'evspsbl', 'rsds', 'zg500', 'rsus', 'hurs', 'tas', 'huss']</t>
         </is>
       </c>
     </row>
@@ -28617,7 +28617,7 @@
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'orog', 'areacella', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -28649,7 +28649,7 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>['hus850', 'mrro', 'vas', 'va500', 'mrso', 'rlus', 'rsdt', 'rlut', 'snw', 'snd', 'sund', 'ta200', 'ta500', 'hfss', 'hfls', 'uas', 'ta850', 'ua500', 'sfcWindmax', 'rsut', 'snc', 'clt', 'hurs', 'pr', 'rlds', 'huss', 'hus850', 'mrro', 'vas', 'va500', 'mrso', 'rlus', 'rsdt', 'rlut', 'snw', 'snd', 'sund', 'ta200', 'ta500', 'hfss', 'hfls', 'uas', 'ta850', 'ua500', 'sfcWindmax', 'rsut', 'snc', 'clt', 'hurs', 'pr', 'rlds', 'huss', 'zg500', 'tasmax', 'rsds', 'sfcWind', 'va850', 'tas', 'psl', 'evspsbl', 'tasmin', 'ua850', 'rsus']</t>
+          <t>['hus850', 'mrro', 'vas', 'va500', 'mrso', 'rlus', 'rsdt', 'rlut', 'snw', 'snd', 'sund', 'ta200', 'ta500', 'hfss', 'hfls', 'uas', 'ta850', 'ua500', 'sfcWindmax', 'rsut', 'snc', 'clt', 'hurs', 'pr', 'rlds', 'huss', 'zg500', 'tasmax', 'rsds', 'sfcWind', 'va850', 'tas', 'psl', 'evspsbl', 'tasmin', 'ua850', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -28681,7 +28681,7 @@
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snc', 'snd', 'ua500', 'mrso', 'mrro', 'tasmax', 'rsds', 'huss', 'sfcWind', 'rlds', 'evspsbl', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snc', 'snd', 'ua500', 'mrso', 'mrro', 'tasmax', 'rsds', 'huss', 'sfcWind', 'rlds', 'evspsbl', 'ua850', 'va850', 'rsus', 'clt', 'tas', 'tasmin', 'zg500', 'pr', 'psl', 'hurs']</t>
+          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snc', 'snd', 'ua500', 'mrso', 'mrro', 'tasmax', 'rsds', 'huss', 'sfcWind', 'rlds', 'evspsbl', 'ua850', 'va850', 'rsus', 'clt', 'tas', 'tasmin', 'zg500', 'pr', 'psl', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -28725,7 +28725,7 @@
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28757,7 +28757,7 @@
       </c>
       <c r="J872" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="J873" t="inlineStr">
         <is>
-          <t>['mrso', 'prc', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'ts', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'clt', 'sfcWind', 'zg500', 'evspsbl', 'tas', 'pr', 'rsus', 'rlds']</t>
+          <t>['mrso', 'prc', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'ts', 'hfss', 'hfls', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'prhmax', 'rlus', 'rlut', 'prsn', 'wsgsmax', 'vas', 'tasmin', 'va850', 'ua850', 'tasmax', 'huss', 'rsds', 'hurs', 'psl', 'ps', 'clt', 'sfcWind', 'zg500', 'evspsbl', 'tas', 'pr', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -28821,7 +28821,7 @@
       </c>
       <c r="J874" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28853,7 @@
       </c>
       <c r="J875" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'va850', 'tasmin', 'hurs', 'ua850', 'rlds', 'va850', 'tasmin', 'hurs', 'ua850', 'rlds', 'zg500', 'psl', 'tas', 'tasmax', 'rsus', 'evspsbl', 'sfcWind', 'huss', 'rsds', 'pr', 'clt']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'va850', 'tasmin', 'hurs', 'ua850', 'rlds', 'zg500', 'psl', 'tas', 'tasmax', 'rsus', 'evspsbl', 'sfcWind', 'huss', 'rsds', 'pr', 'clt']</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28885,7 @@
       </c>
       <c r="J876" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'tasmax', 'sfcWind', 'rsds', 'ua850', 'va850', 'hurs', 'zg500', 'psl', 'rsus']</t>
+          <t>['sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'clt', 'evspsbl', 'tas', 'rlds', 'tasmin', 'pr', 'huss', 'tasmax', 'sfcWind', 'rsds', 'ua850', 'va850', 'hurs', 'zg500', 'psl', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -28925,7 +28925,7 @@
       </c>
       <c r="J877" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -28957,7 +28957,7 @@
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -28989,7 +28989,7 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rlut', 'prsn', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'tasmax', 'pr', 'rsds', 'huss', 'tasmax', 'pr', 'rsds', 'huss', 'tasmin', 'rsus', 'tas', 'va850', 'evspsbl', 'ua850', 'hurs', 'ps', 'rlds', 'sfcWind', 'clt', 'zg500', 'psl']</t>
+          <t>['rlus', 'rsdt', 'rlut', 'prsn', 'hfss', 'hfls', 'prhmax', 'mrso', 'prc', 'hus850', 'mrro', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'tasmax', 'pr', 'rsds', 'huss', 'tasmin', 'rsus', 'tas', 'va850', 'evspsbl', 'ua850', 'hurs', 'ps', 'rlds', 'sfcWind', 'clt', 'zg500', 'psl']</t>
         </is>
       </c>
     </row>
@@ -29021,7 +29021,7 @@
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -29053,7 +29053,7 @@
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'tasmin', 'tas', 'ua850', 'tasmin', 'tas', 'ua850', 'rsds', 'rlds', 'zg500', 'evspsbl', 'psl', 'rsus', 'clt', 'tasmax', 'hurs', 'sfcWind', 'va850', 'huss', 'pr']</t>
+          <t>['vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'snd', 'sund', 'ua500', 'ta200', 'ta500', 'ta850', 'tasmin', 'tas', 'ua850', 'rsds', 'rlds', 'zg500', 'evspsbl', 'psl', 'rsus', 'clt', 'tasmax', 'hurs', 'sfcWind', 'va850', 'huss', 'pr']</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29085,7 @@
       </c>
       <c r="J882" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'huss', 'tasmax', 'huss', 'tasmax', 'rsds', 'pr', 'rsus', 'evspsbl', 'psl', 'clt', 'rlds', 'hurs', 'tasmin', 'ua850', 'zg500', 'va850', 'tas', 'sfcWind']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'huss', 'tasmax', 'rsds', 'pr', 'rsus', 'evspsbl', 'psl', 'clt', 'rlds', 'hurs', 'tasmin', 'ua850', 'zg500', 'va850', 'tas', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -29125,7 +29125,7 @@
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>['rlds', 'rlus', 'hfls', 'hfss', 'clt', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'rlds', 'rlus', 'hfls', 'hfss', 'clt', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['rlds', 'rlus', 'hfls', 'hfss', 'clt', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29157,7 @@
       </c>
       <c r="J884" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -29189,7 +29189,7 @@
       </c>
       <c r="J885" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'tasmin', 'evspsbl', 'tas', 'huss', 'ua850', 'tasmax', 'va850', 'psl', 'ps', 'pr', 'hurs', 'zg500']</t>
+          <t>['hfss', 'hfls', 'hus850', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'ta200', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'sund', 'snc', 'snd', 'rlus', 'rsdt', 'rlut', 'sfcWind', 'rsds', 'clt', 'rlds', 'rsus', 'tasmin', 'evspsbl', 'tas', 'huss', 'ua850', 'tasmax', 'va850', 'psl', 'ps', 'pr', 'hurs', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -29221,7 +29221,7 @@
       </c>
       <c r="J886" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -29253,7 +29253,7 @@
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'sund', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'rsus', 'rsds', 'sfcWind', 'ua850', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'rsus', 'rsds', 'sfcWind', 'ua850', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'hurs', 'huss', 'psl', 'rlds', 'pr', 'tas', 'va850', 'clt']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'snc', 'sund', 'snd', 'ua500', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'rsus', 'rsds', 'sfcWind', 'ua850', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'hurs', 'huss', 'psl', 'rlds', 'pr', 'tas', 'va850', 'clt']</t>
         </is>
       </c>
     </row>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="J888" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'zg500', 'rlds', 'huss', 'rsus', 'ua850', 'psl']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'uas', 'ua500', 'ta500', 'ta850', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'va850', 'tas', 'hurs', 'evspsbl', 'tasmax', 'rsds', 'clt', 'pr', 'sfcWind', 'tasmin', 'zg500', 'rlds', 'huss', 'rsus', 'ua850', 'psl']</t>
         </is>
       </c>
     </row>
@@ -29325,7 +29325,7 @@
       </c>
       <c r="J889" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rlds', 'psl', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="J890" t="inlineStr">
         <is>
-          <t>['uas', 'uas']</t>
+          <t>['uas']</t>
         </is>
       </c>
     </row>
@@ -29385,7 +29385,7 @@
       </c>
       <c r="J891" t="inlineStr">
         <is>
-          <t>['vas', 'vas']</t>
+          <t>['vas']</t>
         </is>
       </c>
     </row>
@@ -29417,7 +29417,7 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ps', 'ua850', 'rsus', 'ps', 'ua850', 'rsus', 'clt', 'pr', 'evspsbl', 'hurs', 'tasmin', 'zg500', 'tas', 'va850', 'huss', 'rlds', 'psl', 'sfcWind', 'tasmax', 'rsds']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prsn', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfss', 'hfls', 'hus850', 'ta500', 'ta850', 'ts', 'sfcWindmax', 'snw', 'sund', 'snc', 'ta200', 'snd', 'ps', 'ua850', 'rsus', 'clt', 'pr', 'evspsbl', 'hurs', 'tasmin', 'zg500', 'tas', 'va850', 'huss', 'rlds', 'psl', 'sfcWind', 'tasmax', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -29481,7 +29481,7 @@
       </c>
       <c r="J894" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'sfcWindmax', 'uas', 'ua500', 'ta500', 'ta850', 'vas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'snd', 'pr', 'tasmin', 'ua850', 'va850', 'tasmax', 'pr', 'tasmin', 'ua850', 'va850', 'tasmax', 'rlds', 'rsds', 'rsus', 'evspsbl', 'sfcWind', 'zg500', 'clt', 'tas', 'psl', 'huss', 'hurs']</t>
+          <t>['hfss', 'hfls', 'mrso', 'sfcWindmax', 'uas', 'ua500', 'ta500', 'ta850', 'vas', 'va500', 'rlus', 'rsdt', 'rsut', 'rlut', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'snd', 'pr', 'tasmin', 'ua850', 'va850', 'tasmax', 'rlds', 'rsds', 'rsus', 'evspsbl', 'sfcWind', 'zg500', 'clt', 'tas', 'psl', 'huss', 'hurs']</t>
         </is>
       </c>
     </row>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="J895" t="inlineStr">
         <is>
-          <t>['hfls', 'sfcWindmax', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'ua500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'tas', 'psl', 'sfcWind', 'rlds', 'clt', 'ua850', 'rsds', 'tas', 'psl', 'sfcWind', 'rlds', 'clt', 'ua850', 'rsds', 'tasmin', 'tasmax', 'zg500', 'rsus', 'evspsbl', 'va850', 'huss', 'hurs', 'pr']</t>
+          <t>['hfls', 'sfcWindmax', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'snd', 'rlus', 'rsdt', 'rsut', 'rlut', 'uas', 'ua500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'va500', 'tas', 'psl', 'sfcWind', 'rlds', 'clt', 'ua850', 'rsds', 'tasmin', 'tasmax', 'zg500', 'rsus', 'evspsbl', 'va850', 'huss', 'hurs', 'pr']</t>
         </is>
       </c>
     </row>
@@ -29557,7 +29557,7 @@
       </c>
       <c r="J896" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'rlus', 'rsds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'tas', 'psl', 'rlds', 'rlus', 'rsds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['psl', 'rlds', 'rlus', 'rsds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="J897" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -29621,7 +29621,7 @@
       </c>
       <c r="J898" t="inlineStr">
         <is>
-          <t>['prhmax', 'mrso', 'prc', 'prsn', 'uas', 'ua500', 'ts', 'hfss', 'hfls', 'hus850', 'mrro', 'wsgsmax', 'vas', 'va500', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'huss', 'clt', 'sfcWind', 'pr', 'tasmax', 'hurs', 'rlds', 'ps', 'evspsbl', 'tas', 'huss', 'clt', 'sfcWind', 'pr', 'tasmax', 'hurs', 'rlds', 'ps', 'evspsbl', 'tas', 'rsus', 'tasmin', 'psl', 'va850', 'zg500', 'rsds', 'ua850']</t>
+          <t>['prhmax', 'mrso', 'prc', 'prsn', 'uas', 'ua500', 'ts', 'hfss', 'hfls', 'hus850', 'mrro', 'wsgsmax', 'vas', 'va500', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'huss', 'clt', 'sfcWind', 'pr', 'tasmax', 'hurs', 'rlds', 'ps', 'evspsbl', 'tas', 'rsus', 'tasmin', 'psl', 'va850', 'zg500', 'rsds', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -29653,7 +29653,7 @@
       </c>
       <c r="J899" t="inlineStr">
         <is>
-          <t>['areacella', 'sftlf', 'sftlf', 'orog']</t>
+          <t>['areacella', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -29685,7 +29685,7 @@
       </c>
       <c r="J900" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'mrso', 'hus850', 'mrro', 'vas', 'hfss', 'hfls', 'uas', 'va500', 'ua500', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rsus', 'va850', 'sfcWind', 'pr', 'rsds', 'rlds', 'rsus', 'va850', 'sfcWind', 'pr', 'rsds', 'rlds', 'ua850', 'psl', 'tas', 'zg500', 'tasmax', 'huss', 'hurs', 'evspsbl', 'tasmin', 'clt']</t>
+          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'mrso', 'hus850', 'mrro', 'vas', 'hfss', 'hfls', 'uas', 'va500', 'ua500', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rsus', 'va850', 'sfcWind', 'pr', 'rsds', 'rlds', 'ua850', 'psl', 'tas', 'zg500', 'tasmax', 'huss', 'hurs', 'evspsbl', 'tasmin', 'clt']</t>
         </is>
       </c>
     </row>
@@ -29717,7 +29717,7 @@
       </c>
       <c r="J901" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'hurs', 'pr', 'huss', 'rsds', 'tasmax', 'zg500', 'hurs', 'pr', 'huss', 'rsds', 'tasmax', 'zg500', 'tasmin', 'sfcWind', 'rsus', 'clt', 'tas', 'psl', 'evspsbl', 'rlds', 'va850', 'ua850']</t>
+          <t>['vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'hurs', 'pr', 'huss', 'rsds', 'tasmax', 'zg500', 'tasmin', 'sfcWind', 'rsus', 'clt', 'tas', 'psl', 'evspsbl', 'rlds', 'va850', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -29757,7 +29757,7 @@
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>['clt', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'rlds', 'hfls', 'huss', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'clt', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'rlds', 'hfls', 'huss', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['clt', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'rlds', 'hfls', 'huss', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29789,7 +29789,7 @@
       </c>
       <c r="J903" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="J904" t="inlineStr">
         <is>
-          <t>['prc', 'prhmax', 'prsn', 'prw', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'hfls', 'hfss', 'hus850', 'mrfso', 'mrro', 'mrros', 'mrso', 'uas', 'va200', 'va500', 'vas', 'wsgsmax', 'zg200', 'zmla', 'rlds', 'rsus', 'evspsbl', 'tas', 'va850', 'prc', 'prhmax', 'prsn', 'prw', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'hfls', 'hfss', 'hus850', 'mrfso', 'mrro', 'mrros', 'mrso', 'uas', 'va200', 'va500', 'vas', 'wsgsmax', 'zg200', 'zmla', 'rlds', 'rsus', 'evspsbl', 'tas', 'va850', 'sfcWind', 'tasmin', 'psl', 'clt', 'ps', 'zg500', 'ua850', 'pr', 'rsds', 'hurs', 'tasmax', 'huss']</t>
+          <t>['prc', 'prhmax', 'prsn', 'prw', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'tauu', 'tauv', 'ts', 'ua200', 'ua500', 'clh', 'clivi', 'cll', 'clm', 'clwvi', 'hfls', 'hfss', 'hus850', 'mrfso', 'mrro', 'mrros', 'mrso', 'uas', 'va200', 'va500', 'vas', 'wsgsmax', 'zg200', 'zmla', 'rlds', 'rsus', 'evspsbl', 'tas', 'va850', 'sfcWind', 'tasmin', 'psl', 'clt', 'ps', 'zg500', 'ua850', 'pr', 'rsds', 'hurs', 'tasmax', 'huss']</t>
         </is>
       </c>
     </row>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="J905" t="inlineStr">
         <is>
-          <t>['areacella', 'mrsofc', 'sftgif', 'areacella', 'mrsofc', 'sftgif', 'sftlf', 'orog']</t>
+          <t>['areacella', 'mrsofc', 'sftgif', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -29885,7 +29885,7 @@
       </c>
       <c r="J906" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'hus850', 'mrfso', 'mrro', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rsds', 'tasmin', 'rsus', 'ua850', 'clt', 'hfls', 'hfss', 'hus850', 'mrfso', 'mrro', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rsds', 'tasmin', 'rsus', 'ua850', 'clt', 'psl', 'tasmax', 'tas', 'huss', 'zg500', 'evspsbl', 'rlds', 'va850', 'hurs', 'pr', 'sfcWind']</t>
+          <t>['hfls', 'hfss', 'hus850', 'mrfso', 'mrro', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'rsds', 'tasmin', 'rsus', 'ua850', 'clt', 'psl', 'tasmax', 'tas', 'huss', 'zg500', 'evspsbl', 'rlds', 'va850', 'hurs', 'pr', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="J907" t="inlineStr">
         <is>
-          <t>['mrro', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'hfls', 'hfss', 'hus850', 'mrfso', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'huss', 'psl', 'clt', 'tas', 'pr', 'hurs', 'rsds', 'ua850', 'mrro', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'hfls', 'hfss', 'hus850', 'mrfso', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'huss', 'psl', 'clt', 'tas', 'pr', 'hurs', 'rsds', 'ua850', 'va850', 'evspsbl', 'tasmax', 'sfcWind', 'zg500', 'rsus', 'tasmin', 'rlds']</t>
+          <t>['mrro', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'hfls', 'hfss', 'hus850', 'mrfso', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'huss', 'psl', 'clt', 'tas', 'pr', 'hurs', 'rsds', 'ua850', 'va850', 'evspsbl', 'tasmax', 'sfcWind', 'zg500', 'rsus', 'tasmin', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -29957,7 +29957,7 @@
       </c>
       <c r="J908" t="inlineStr">
         <is>
-          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
+          <t>['psl', 'rlds', 'hfss', 'hurs', 'clt', 'hfls', 'huss', 'pr', 'prw', 'ps', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas']</t>
         </is>
       </c>
     </row>
@@ -29989,7 +29989,7 @@
       </c>
       <c r="J909" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -30021,7 +30021,7 @@
       </c>
       <c r="J910" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'rlds', 'rsds', 'va850', 'ps', 'sfcWind', 'rsus', 'rlds', 'rsds', 'va850', 'ps', 'sfcWind', 'evspsbl', 'psl', 'ua850', 'huss', 'clt', 'zg500', 'hurs', 'tasmax', 'tas', 'tasmin', 'pr']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'snw', 'snc', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'uas', 'ua500', 'ts', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'prhmax', 'mrso', 'prc', 'prsn', 'rsus', 'rlds', 'rsds', 'va850', 'ps', 'sfcWind', 'evspsbl', 'psl', 'ua850', 'huss', 'clt', 'zg500', 'hurs', 'tasmax', 'tas', 'tasmin', 'pr']</t>
         </is>
       </c>
     </row>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="J911" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -30085,7 +30085,7 @@
       </c>
       <c r="J912" t="inlineStr">
         <is>
-          <t>['mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'rsds', 'tasmin', 'clt', 'huss', 'psl', 'rsds', 'tasmin', 'clt', 'huss', 'psl', 'evspsbl', 'va850', 'hurs', 'tasmax', 'pr', 'ua850', 'sfcWind', 'tas', 'zg500', 'rsus', 'rlds']</t>
+          <t>['mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'snw', 'sund', 'snc', 'ta200', 'ta500', 'ta850', 'snd', 'vas', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'rsds', 'tasmin', 'clt', 'huss', 'psl', 'evspsbl', 'va850', 'hurs', 'tasmax', 'pr', 'ua850', 'sfcWind', 'tas', 'zg500', 'rsus', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -30117,7 +30117,7 @@
       </c>
       <c r="J913" t="inlineStr">
         <is>
-          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'rlus', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'zg500', 'hurs', 'tasmin', 'zg500', 'hurs', 'tasmin', 'rsds', 'tasmax', 'ua850', 'evspsbl', 'pr', 'clt', 'tas', 'psl', 'va850', 'huss', 'rlds', 'rsus', 'sfcWind']</t>
+          <t>['snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'rlus', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'hfss', 'hfls', 'hus850', 'zg500', 'hurs', 'tasmin', 'rsds', 'tasmax', 'ua850', 'evspsbl', 'pr', 'clt', 'tas', 'psl', 'va850', 'huss', 'rlds', 'rsus', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -30161,7 +30161,7 @@
       </c>
       <c r="J914" t="inlineStr">
         <is>
-          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas', 'clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
+          <t>['clt', 'rlds', 'rlus', 'hfls', 'hfss', 'pr', 'prw', 'hurs', 'huss', 'ps', 'psl', 'rsds', 'rsus', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -30193,7 +30193,7 @@
       </c>
       <c r="J915" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="J916" t="inlineStr">
         <is>
-          <t>['hfls', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'prhmax', 'rlut', 'prc', 'prsn', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'wsgsmax', 'vas', 'huss', 'zg500', 'evspsbl', 'pr', 'rsds', 'va850', 'rlds', 'ps', 'hfls', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'prhmax', 'rlut', 'prc', 'prsn', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'wsgsmax', 'vas', 'huss', 'zg500', 'evspsbl', 'pr', 'rsds', 'va850', 'rlds', 'ps', 'clt', 'tasmax', 'rsus', 'ua850', 'psl', 'tasmin', 'hurs', 'sfcWind', 'tas']</t>
+          <t>['hfls', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'prhmax', 'rlut', 'prc', 'prsn', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'hfss', 'mrso', 'hus850', 'mrro', 'wsgsmax', 'vas', 'huss', 'zg500', 'evspsbl', 'pr', 'rsds', 'va850', 'rlds', 'ps', 'clt', 'tasmax', 'rsus', 'ua850', 'psl', 'tasmin', 'hurs', 'sfcWind', 'tas']</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="J917" t="inlineStr">
         <is>
-          <t>['areacella', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="J918" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rsds', 'sfcWind', 'clt', 'pr', 'zg500', 'rlds', 'tasmin', 'rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rsds', 'sfcWind', 'clt', 'pr', 'zg500', 'rlds', 'tasmin', 'tasmax', 'psl', 'va850', 'huss', 'tas', 'evspsbl', 'rsus', 'hurs', 'ua850']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrro', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'rsds', 'sfcWind', 'clt', 'pr', 'zg500', 'rlds', 'tasmin', 'tasmax', 'psl', 'va850', 'huss', 'tas', 'evspsbl', 'rsus', 'hurs', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -30321,7 +30321,7 @@
       </c>
       <c r="J919" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'ua500', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'rlds', 'tas', 'ua850', 'tasmax', 'rsus', 'rsds', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'ua500', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'rlds', 'tas', 'ua850', 'tasmax', 'rsus', 'rsds', 'tasmin', 'huss', 'hurs', 'evspsbl', 'clt', 'pr', 'psl', 'va850', 'zg500', 'sfcWind']</t>
+          <t>['hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'ua500', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'rlus', 'rlut', 'mrso', 'mrro', 'rlds', 'tas', 'ua850', 'tasmax', 'rsus', 'rsds', 'tasmin', 'huss', 'hurs', 'evspsbl', 'clt', 'pr', 'psl', 'va850', 'zg500', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="J920" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'hfls', 'huss', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'rlds', 'hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'hfls', 'huss', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'rlds']</t>
+          <t>['hfss', 'hurs', 'pr', 'prw', 'ps', 'psl', 'hfls', 'huss', 'clt', 'rsus', 'sfcWind', 'rlus', 'rsds', 'tas', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -30393,7 +30393,7 @@
       </c>
       <c r="J921" t="inlineStr">
         <is>
-          <t>['vas', 'uas', 'vas', 'uas']</t>
+          <t>['vas', 'uas']</t>
         </is>
       </c>
     </row>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="J922" t="inlineStr">
         <is>
-          <t>['clwvi', 'hfls', 'mrso', 'prc', 'prhmax', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'clh', 'clivi', 'cll', 'clm', 'hfss', 'hus850', 'rlus', 'rlut', 'rsdt', 'rsut', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zmla', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'va200', 'va500', 'vas', 'ua200', 'ua500', 'uas', 'ps', 'psl', 'zg500', 'hurs', 'tasmax', 'rlds', 'rsus', 'clwvi', 'hfls', 'mrso', 'prc', 'prhmax', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'clh', 'clivi', 'cll', 'clm', 'hfss', 'hus850', 'rlus', 'rlut', 'rsdt', 'rsut', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zmla', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'va200', 'va500', 'vas', 'ua200', 'ua500', 'uas', 'ps', 'psl', 'zg500', 'hurs', 'tasmax', 'rlds', 'rsus', 'evspsbl', 'va850', 'huss', 'rsds', 'ua850', 'pr', 'tas', 'sfcWind', 'tasmin', 'clt']</t>
+          <t>['clwvi', 'hfls', 'mrso', 'prc', 'prhmax', 'mrfso', 'mrro', 'mrros', 'prsn', 'prw', 'clh', 'clivi', 'cll', 'clm', 'hfss', 'hus850', 'rlus', 'rlut', 'rsdt', 'rsut', 'tauu', 'tauv', 'ts', 'wsgsmax', 'zg200', 'zmla', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'va200', 'va500', 'vas', 'ua200', 'ua500', 'uas', 'ps', 'psl', 'zg500', 'hurs', 'tasmax', 'rlds', 'rsus', 'evspsbl', 'va850', 'huss', 'rsds', 'ua850', 'pr', 'tas', 'sfcWind', 'tasmin', 'clt']</t>
         </is>
       </c>
     </row>
@@ -30457,7 +30457,7 @@
       </c>
       <c r="J923" t="inlineStr">
         <is>
-          <t>['areacella', 'mrsofc', 'sftgif', 'areacella', 'mrsofc', 'sftgif', 'sftlf', 'orog']</t>
+          <t>['areacella', 'mrsofc', 'sftgif', 'sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="J924" t="inlineStr">
         <is>
-          <t>['mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'rsut', 'hfss', 'hus850', 'mrfso', 'mrro', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'va500', 'vas', 'zg200', 'ua200', 'ua500', 'uas', 'va200', 'sund', 'ta200', 'ta500', 'ta850', 'hfls', 'rsds', 'rsus', 'tasmax', 'mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'rsut', 'hfss', 'hus850', 'mrfso', 'mrro', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'va500', 'vas', 'zg200', 'ua200', 'ua500', 'uas', 'va200', 'sund', 'ta200', 'ta500', 'ta850', 'hfls', 'rsds', 'rsus', 'tasmax', 'rlds', 'va850', 'hurs', 'tas', 'ua850', 'tasmin', 'evspsbl', 'zg500', 'huss', 'clt', 'sfcWind', 'psl', 'pr']</t>
+          <t>['mrros', 'mrso', 'rlus', 'rlut', 'rsdt', 'rsut', 'hfss', 'hus850', 'mrfso', 'mrro', 'sfcWindmax', 'sic', 'snc', 'snd', 'snm', 'snw', 'va500', 'vas', 'zg200', 'ua200', 'ua500', 'uas', 'va200', 'sund', 'ta200', 'ta500', 'ta850', 'hfls', 'rsds', 'rsus', 'tasmax', 'rlds', 'va850', 'hurs', 'tas', 'ua850', 'tasmin', 'evspsbl', 'zg500', 'huss', 'clt', 'sfcWind', 'psl', 'pr']</t>
         </is>
       </c>
     </row>
@@ -30521,7 +30521,7 @@
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>['hfls', 'hfss', 'hus850', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'mrfso', 'mrro', 'mrros', 'mrso', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'evspsbl', 'huss', 'pr', 'rlds', 'rsus', 'psl', 'hfls', 'hfss', 'hus850', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'mrfso', 'mrro', 'mrros', 'mrso', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'evspsbl', 'huss', 'pr', 'rlds', 'rsus', 'psl', 'tas', 'clt', 'tasmin', 'ua850', 'sfcWind', 'zg500', 'tasmax', 'rsds', 'hurs', 'va850']</t>
+          <t>['hfls', 'hfss', 'hus850', 'rlus', 'rlut', 'rsdt', 'rsut', 'sfcWindmax', 'sic', 'snc', 'snd', 'mrfso', 'mrro', 'mrros', 'mrso', 'snm', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'ua200', 'ua500', 'uas', 'va200', 'va500', 'vas', 'zg200', 'evspsbl', 'huss', 'pr', 'rlds', 'rsus', 'psl', 'tas', 'clt', 'tasmin', 'ua850', 'sfcWind', 'zg500', 'tasmax', 'rsds', 'hurs', 'va850']</t>
         </is>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>['hfss', 'hurs', 'clt', 'pr', 'prw', 'hfls', 'huss', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'psl', 'rlds', 'rlus', 'hfss', 'hurs', 'clt', 'pr', 'prw', 'hfls', 'huss', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'psl', 'rlds', 'rlus']</t>
+          <t>['hfss', 'hurs', 'clt', 'pr', 'prw', 'hfls', 'huss', 'rsds', 'rsus', 'sfcWind', 'tas', 'ps', 'psl', 'rlds', 'rlus']</t>
         </is>
       </c>
     </row>
@@ -30593,7 +30593,7 @@
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>['uas', 'vas', 'uas', 'vas']</t>
+          <t>['uas', 'vas']</t>
         </is>
       </c>
     </row>
@@ -30625,7 +30625,7 @@
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'prhmax', 'rlus', 'prc', 'prsn', 'wsgsmax', 'vas', 'va500', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'tasmin', 'sfcWind', 'tas', 'rsus', 'ps', 'tasmax', 'huss', 'hurs', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'prhmax', 'rlus', 'prc', 'prsn', 'wsgsmax', 'vas', 'va500', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'tasmin', 'sfcWind', 'tas', 'rsus', 'ps', 'tasmax', 'huss', 'hurs', 'evspsbl', 'pr', 'rsds', 'zg500', 'rlds', 'psl', 'va850', 'ua850', 'clt']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'prhmax', 'rlus', 'prc', 'prsn', 'wsgsmax', 'vas', 'va500', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'tasmin', 'sfcWind', 'tas', 'rsus', 'ps', 'tasmax', 'huss', 'hurs', 'evspsbl', 'pr', 'rsds', 'zg500', 'rlds', 'psl', 'va850', 'ua850', 'clt']</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>['areacella', 'orog', 'areacella', 'orog', 'sftlf']</t>
+          <t>['areacella', 'orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30689,7 @@
       </c>
       <c r="J930" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'tasmax', 'clt', 'ua850', 'tasmin', 'tas', 'huss', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'tasmax', 'clt', 'ua850', 'tasmin', 'tas', 'huss', 'pr', 'va850', 'evspsbl', 'rsus', 'sfcWind', 'rsds', 'psl', 'hurs', 'zg500']</t>
+          <t>['hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'snd', 'rlus', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rsdt', 'rsut', 'rlut', 'snc', 'rlds', 'tasmax', 'clt', 'ua850', 'tasmin', 'tas', 'huss', 'pr', 'va850', 'evspsbl', 'rsus', 'sfcWind', 'rsds', 'psl', 'hurs', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -30721,7 +30721,7 @@
       </c>
       <c r="J931" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'mrso', 'mrro', 'rsds', 'va850', 'tasmin', 'pr', 'clt', 'hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'mrso', 'mrro', 'rsds', 'va850', 'tasmin', 'pr', 'clt', 'zg500', 'rlds', 'tasmax', 'sfcWind', 'psl', 'tas', 'hurs', 'ua850', 'evspsbl', 'huss', 'rsus']</t>
+          <t>['hfss', 'hfls', 'hus850', 'snw', 'sund', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'snc', 'snd', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'mrso', 'mrro', 'rsds', 'va850', 'tasmin', 'pr', 'clt', 'zg500', 'rlds', 'tasmax', 'sfcWind', 'psl', 'tas', 'hurs', 'ua850', 'evspsbl', 'huss', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -34697,7 +34697,7 @@
       </c>
       <c r="J1054" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rlut', 'prsn', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'psl', 'ps', 'tasmax', 'huss', 'tasmin', 'pr', 'rsds', 'zg500', 'psl', 'ps', 'tasmax', 'huss', 'tasmin', 'pr', 'rsds', 'zg500', 'sfcWind', 'tas', 'evspsbl', 'va850', 'ua850', 'rlds', 'clt', 'rsus']</t>
+          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'mrro', 'wsgsmax', 'vas', 'uas', 'va500', 'rlus', 'rsdt', 'rlut', 'prsn', 'ua500', 'ta850', 'ts', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'psl', 'ps', 'tasmax', 'huss', 'tasmin', 'pr', 'rsds', 'zg500', 'sfcWind', 'tas', 'evspsbl', 'va850', 'ua850', 'rlds', 'clt', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -34729,7 +34729,7 @@
       </c>
       <c r="J1055" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWind', 'pr', 'rsds', 'clt', 'tas', 'sfcWind', 'pr', 'rsds', 'clt', 'tas', 'va850', 'zg500', 'tasmax', 'rlds', 'evspsbl', 'rsus', 'huss', 'ua850', 'tasmin', 'psl']</t>
+          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWind', 'pr', 'rsds', 'clt', 'tas', 'va850', 'zg500', 'tasmax', 'rlds', 'evspsbl', 'rsus', 'huss', 'ua850', 'tasmin', 'psl']</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="J1056" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'snw', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'va850', 'ua850', 'psl', 'rsds', 'huss', 'tasmax', 'zg500', 'va850', 'ua850', 'psl', 'rsds', 'huss', 'tasmax', 'zg500', 'pr', 'clt', 'tasmin', 'tas', 'rlds', 'sfcWind', 'evspsbl', 'rsus']</t>
+          <t>['rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'snw', 'ua500', 'ta200', 'ta500', 'ta850', 'sfcWindmax', 'rsdt', 'rsut', 'va850', 'ua850', 'psl', 'rsds', 'huss', 'tasmax', 'zg500', 'pr', 'clt', 'tasmin', 'tas', 'rlds', 'sfcWind', 'evspsbl', 'rsus']</t>
         </is>
       </c>
     </row>
@@ -34805,7 +34805,7 @@
       </c>
       <c r="J1057" t="inlineStr">
         <is>
-          <t>['orog', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -34841,7 +34841,7 @@
       </c>
       <c r="J1058" t="inlineStr">
         <is>
-          <t>['rlus', 'rlut', 'mrso', 'prc', 'prsn', 'vas', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'huss', 'ps', 'rlds', 'zg500', 'sfcWind', 'pr', 'huss', 'ps', 'rlds', 'zg500', 'rsus', 'clt', 'ua850', 'va850', 'psl', 'rsds', 'evspsbl', 'tas', 'tasmax', 'tasmin']</t>
+          <t>['rlus', 'rlut', 'mrso', 'prc', 'prsn', 'vas', 'uas', 'va500', 'ua500', 'ts', 'sfcWindmax', 'rsdt', 'rsut', 'wsgsmax', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'sfcWind', 'pr', 'huss', 'ps', 'rlds', 'zg500', 'rsus', 'clt', 'ua850', 'va850', 'psl', 'rsds', 'evspsbl', 'tas', 'tasmax', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -34873,7 +34873,7 @@
       </c>
       <c r="J1059" t="inlineStr">
         <is>
-          <t>['ta200', 'ta500', 'ta850', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'huss', 'rsds', 'sfcWind', 'evspsbl', 'tasmin', 'tasmax', 'huss', 'rsds', 'sfcWind', 'evspsbl', 'tasmin', 'tasmax', 'rsus', 'zg500', 'tas', 'psl', 'pr', 'clt', 'va850', 'ua850', 'rlds']</t>
+          <t>['ta200', 'ta500', 'ta850', 'ua500', 'hfss', 'hfls', 'hus850', 'vas', 'uas', 'va500', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'huss', 'rsds', 'sfcWind', 'evspsbl', 'tasmin', 'tasmax', 'rsus', 'zg500', 'tas', 'psl', 'pr', 'clt', 'va850', 'ua850', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -34905,7 +34905,7 @@
       </c>
       <c r="J1060" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'psl', 'ua850', 'huss', 'rsus', 'rsds', 'rlds', 'sfcWind', 'tas', 'psl', 'ua850', 'huss', 'rsus', 'rsds', 'rlds', 'sfcWind', 'tas', 'clt', 'evspsbl', 'tasmax', 'pr', 'tasmin', 'zg500', 'va850']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'psl', 'ua850', 'huss', 'rsus', 'rsds', 'rlds', 'sfcWind', 'tas', 'clt', 'evspsbl', 'tasmax', 'pr', 'tasmin', 'zg500', 'va850']</t>
         </is>
       </c>
     </row>
@@ -34941,7 +34941,7 @@
       </c>
       <c r="J1061" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'mrso', 'prc', 'prsn', 'uas', 'va500', 'ua500', 'ts', 'ua850', 'rlds', 'rsds', 'ps', 'huss', 'rsus', 'tasmax', 'ua850', 'rlds', 'rsds', 'ps', 'huss', 'rsus', 'tasmax', 'tasmin', 'evspsbl', 'clt', 'pr', 'psl', 'va850', 'sfcWind', 'zg500', 'tas']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'hfss', 'hfls', 'hus850', 'mrro', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'mrso', 'prc', 'prsn', 'uas', 'va500', 'ua500', 'ts', 'ua850', 'rlds', 'rsds', 'ps', 'huss', 'rsus', 'tasmax', 'tasmin', 'evspsbl', 'clt', 'pr', 'psl', 'va850', 'sfcWind', 'zg500', 'tas']</t>
         </is>
       </c>
     </row>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="J1062" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'ua850', 'rsds', 'clt', 'tasmin', 'va850', 'sfcWind', 'tasmax', 'zg500', 'ua850', 'rsds', 'clt', 'tasmin', 'va850', 'sfcWind', 'tasmax', 'zg500', 'huss', 'tas', 'rsus', 'rlds', 'psl', 'evspsbl', 'pr']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'ua850', 'rsds', 'clt', 'tasmin', 'va850', 'sfcWind', 'tasmax', 'zg500', 'huss', 'tas', 'rsus', 'rlds', 'psl', 'evspsbl', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35005,7 +35005,7 @@
       </c>
       <c r="J1063" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'va500', 'ua500', 'vas', 'evspsbl', 'rsds', 'rsus', 'tasmax', 'psl', 'tasmin', 'evspsbl', 'rsds', 'rsus', 'tasmax', 'psl', 'tasmin', 'clt', 'va850', 'huss', 'pr', 'ua850', 'tas', 'sfcWind', 'rlds', 'zg500']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'va500', 'ua500', 'vas', 'evspsbl', 'rsds', 'rsus', 'tasmax', 'psl', 'tasmin', 'clt', 'va850', 'huss', 'pr', 'ua850', 'tas', 'sfcWind', 'rlds', 'zg500']</t>
         </is>
       </c>
     </row>
@@ -35045,7 +35045,7 @@
       </c>
       <c r="J1064" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -35081,7 +35081,7 @@
       </c>
       <c r="J1065" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'tas', 'va850', 'tasmax', 'rlds', 'pr', 'tas', 'va850', 'tasmax', 'rlds', 'pr', 'tasmin', 'zg500', 'ua850', 'psl', 'sfcWind', 'huss', 'rsus', 'rsds', 'clt', 'evspsbl', 'ps']</t>
+          <t>['hfss', 'hfls', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'tas', 'va850', 'tasmax', 'rlds', 'pr', 'tasmin', 'zg500', 'ua850', 'psl', 'sfcWind', 'huss', 'rsus', 'rsds', 'clt', 'evspsbl', 'ps']</t>
         </is>
       </c>
     </row>
@@ -35113,7 +35113,7 @@
       </c>
       <c r="J1066" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'tas', 'va850', 'rlds', 'tas', 'va850', 'rsus', 'huss', 'zg500', 'clt', 'ua850', 'tasmax', 'tasmin', 'rsds', 'pr', 'sfcWind', 'evspsbl', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'rlds', 'tas', 'va850', 'rsus', 'huss', 'zg500', 'clt', 'ua850', 'tasmax', 'tasmin', 'rsds', 'pr', 'sfcWind', 'evspsbl', 'psl']</t>
         </is>
       </c>
     </row>
@@ -35145,7 +35145,7 @@
       </c>
       <c r="J1067" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'pr', 'rsds', 'tas', 'psl', 'pr', 'rsds', 'tas', 'psl', 'clt', 'ua850', 'tasmax', 'rsus', 'huss', 'tasmin', 'rlds', 'va850', 'zg500', 'sfcWind', 'evspsbl']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'pr', 'rsds', 'tas', 'psl', 'clt', 'ua850', 'tasmax', 'rsus', 'huss', 'tasmin', 'rlds', 'va850', 'zg500', 'sfcWind', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -35181,7 +35181,7 @@
       </c>
       <c r="J1068" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'wsgsmax', 'vas', 'uas', 'va500', 'hfls', 'hfss', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua500', 'ts', 'tasmax', 'pr', 'psl', 'tas', 'huss', 'ps', 'rlds', 'tasmax', 'pr', 'psl', 'tas', 'huss', 'ps', 'rlds', 'clt', 'va850', 'ua850', 'evspsbl', 'tasmin', 'sfcWind', 'rsus', 'zg500', 'rsds']</t>
+          <t>['sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'wsgsmax', 'vas', 'uas', 'va500', 'hfls', 'hfss', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'rlus', 'rsdt', 'rsut', 'rlut', 'ua500', 'ts', 'tasmax', 'pr', 'psl', 'tas', 'huss', 'ps', 'rlds', 'clt', 'va850', 'ua850', 'evspsbl', 'tasmin', 'sfcWind', 'rsus', 'zg500', 'rsds']</t>
         </is>
       </c>
     </row>
@@ -35213,7 +35213,7 @@
       </c>
       <c r="J1069" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'va850', 'zg500', 'huss', 'evspsbl', 'tas', 'clt', 'psl', 'rsus', 'va850', 'zg500', 'huss', 'evspsbl', 'tas', 'clt', 'psl', 'rsus', 'ua850', 'rlds', 'sfcWind', 'tasmax', 'rsds', 'tasmin', 'pr']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'uas', 'va500', 'ua500', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'va850', 'zg500', 'huss', 'evspsbl', 'tas', 'clt', 'psl', 'rsus', 'ua850', 'rlds', 'sfcWind', 'tasmax', 'rsds', 'tasmin', 'pr']</t>
         </is>
       </c>
     </row>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rsdt', 'rsut', 'snw', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'rsus', 'ua850', 'tasmax', 'tasmin', 'psl', 'tas', 'sfcWind', 'rsus', 'ua850', 'tasmax', 'tasmin', 'psl', 'tas', 'sfcWind', 'pr', 'rsds', 'zg500', 'huss', 'evspsbl', 'rlds', 'va850', 'clt']</t>
+          <t>['sfcWindmax', 'rsdt', 'rsut', 'snw', 'rlus', 'rlut', 'mrso', 'mrro', 'vas', 'uas', 'va500', 'hfss', 'hfls', 'hus850', 'ta200', 'ta500', 'ta850', 'ua500', 'rsus', 'ua850', 'tasmax', 'tasmin', 'psl', 'tas', 'sfcWind', 'pr', 'rsds', 'zg500', 'huss', 'evspsbl', 'rlds', 'va850', 'clt']</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
       </c>
       <c r="J1071" t="inlineStr">
         <is>
-          <t>['orog', 'sftlf', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -35321,7 +35321,7 @@
       </c>
       <c r="J1072" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'prc', 'prsn', 'rsds', 'rlds', 'rsds', 'rlds', 'ua850', 'clt', 'tasmin', 'evspsbl', 'zg500', 'rsus', 'va850', 'sfcWind', 'ps', 'tas', 'pr', 'tasmax', 'huss', 'psl']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ts', 'wsgsmax', 'vas', 'uas', 'va500', 'ua500', 'rlus', 'rlut', 'prc', 'prsn', 'rsds', 'rlds', 'ua850', 'clt', 'tasmin', 'evspsbl', 'zg500', 'rsus', 'va850', 'sfcWind', 'ps', 'tas', 'pr', 'tasmax', 'huss', 'psl']</t>
         </is>
       </c>
     </row>
@@ -35353,7 +35353,7 @@
       </c>
       <c r="J1073" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'rsds', 'pr', 'tasmax', 'ua850', 'rsds', 'pr', 'tasmax', 'ua850', 'evspsbl', 'clt', 'rsus', 'va850', 'huss', 'rlds', 'zg500', 'psl', 'tas', 'tasmin', 'sfcWind']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'rsds', 'pr', 'tasmax', 'ua850', 'evspsbl', 'clt', 'rsus', 'va850', 'huss', 'rlds', 'zg500', 'psl', 'tas', 'tasmin', 'sfcWind']</t>
         </is>
       </c>
     </row>
@@ -35385,7 +35385,7 @@
       </c>
       <c r="J1074" t="inlineStr">
         <is>
-          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'snw', 'ta200', 'ta500', 'ta850', 'rsds', 'zg500', 'pr', 'rsus', 'tasmax', 'ua850', 'rlds', 'tas', 'rsds', 'zg500', 'pr', 'rsus', 'tasmax', 'ua850', 'rlds', 'tas', 'sfcWind', 'clt', 'psl', 'huss', 'tasmin', 'evspsbl', 'va850']</t>
+          <t>['sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'vas', 'uas', 'va500', 'ua500', 'snw', 'ta200', 'ta500', 'ta850', 'rsds', 'zg500', 'pr', 'rsus', 'tasmax', 'ua850', 'rlds', 'tas', 'sfcWind', 'clt', 'psl', 'huss', 'tasmin', 'evspsbl', 'va850']</t>
         </is>
       </c>
     </row>
@@ -35421,7 +35421,7 @@
       </c>
       <c r="J1075" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rlut', 'mrso', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'ps', 'zg500', 'rlds', 'tasmax', 'ps', 'zg500', 'rlds', 'tasmax', 'ua850', 'clt', 'va850', 'tas', 'rsus', 'pr', 'evspsbl', 'tasmin', 'psl', 'sfcWind', 'rsds', 'huss']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rlut', 'mrso', 'prc', 'prsn', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ts', 'wsgsmax', 'ps', 'zg500', 'rlds', 'tasmax', 'ua850', 'clt', 'va850', 'tas', 'rsus', 'pr', 'evspsbl', 'tasmin', 'psl', 'sfcWind', 'rsds', 'huss']</t>
         </is>
       </c>
     </row>
@@ -35453,7 +35453,7 @@
       </c>
       <c r="J1076" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'rsds', 'huss', 'rsus', 'tasmax', 'clt', 'tasmin', 'ua850', 'psl', 'rsds', 'huss', 'rsus', 'tasmax', 'clt', 'tasmin', 'ua850', 'psl', 'zg500', 'evspsbl', 'va850', 'sfcWind', 'rlds', 'pr', 'tas']</t>
+          <t>['hfss', 'hfls', 'hus850', 'rlus', 'rlut', 'mrso', 'mrro', 'sfcWindmax', 'rsdt', 'rsut', 'snw', 'ta200', 'ta500', 'ta850', 'ua500', 'vas', 'uas', 'va500', 'rsds', 'huss', 'rsus', 'tasmax', 'clt', 'tasmin', 'ua850', 'psl', 'zg500', 'evspsbl', 'va850', 'sfcWind', 'rlds', 'pr', 'tas']</t>
         </is>
       </c>
     </row>
@@ -35485,7 +35485,7 @@
       </c>
       <c r="J1077" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'huss', 'tas', 'va850', 'clt', 'huss', 'tas', 'va850', 'clt', 'sfcWind', 'pr', 'rsus', 'rlds', 'rsds', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'psl', 'ua850']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'huss', 'tas', 'va850', 'clt', 'sfcWind', 'pr', 'rsus', 'rlds', 'rsds', 'tasmax', 'evspsbl', 'zg500', 'tasmin', 'psl', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -35525,7 +35525,7 @@
       </c>
       <c r="J1078" t="inlineStr">
         <is>
-          <t>['orog', 'orog', 'sftlf']</t>
+          <t>['orog', 'sftlf']</t>
         </is>
       </c>
     </row>
@@ -35561,7 +35561,7 @@
       </c>
       <c r="J1079" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrso', 'prc', 'prsn', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'zg500', 'ua850', 'sfcWind', 'zg500', 'ua850', 'sfcWind', 'psl', 'va850', 'pr', 'rlds', 'rsus', 'huss', 'tasmin', 'rsds', 'tas', 'tasmax', 'ps', 'clt', 'evspsbl']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrso', 'prc', 'prsn', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'uas', 'ua500', 'ts', 'wsgsmax', 'vas', 'va500', 'zg500', 'ua850', 'sfcWind', 'psl', 'va850', 'pr', 'rlds', 'rsus', 'huss', 'tasmin', 'rsds', 'tas', 'tasmax', 'ps', 'clt', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -35593,7 +35593,7 @@
       </c>
       <c r="J1080" t="inlineStr">
         <is>
-          <t>['snw', 'ta200', 'ta500', 'ta850', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'tas', 'clt', 'ua850', 'zg500', 'sfcWind', 'pr', 'tas', 'clt', 'ua850', 'zg500', 'sfcWind', 'pr', 'rlds', 'evspsbl', 'rsus', 'va850', 'psl', 'huss', 'rsds', 'tasmax', 'tasmin']</t>
+          <t>['snw', 'ta200', 'ta500', 'ta850', 'hfls', 'hfss', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'vas', 'uas', 'va500', 'ua500', 'tas', 'clt', 'ua850', 'zg500', 'sfcWind', 'pr', 'rlds', 'evspsbl', 'rsus', 'va850', 'psl', 'huss', 'rsds', 'tasmax', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="J1081" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ta850', 'ua500', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'sfcWind', 'evspsbl', 'rsus', 'rlds', 'sfcWind', 'evspsbl', 'rsus', 'rlds', 'tasmin', 'huss', 'psl', 'pr', 'zg500', 'rsds', 'clt', 'va850', 'tasmax', 'tas', 'ua850']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'uas', 'ta850', 'ua500', 'rlus', 'rsdt', 'rlut', 'mrso', 'vas', 'va500', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'ta500', 'sfcWind', 'evspsbl', 'rsus', 'rlds', 'tasmin', 'huss', 'psl', 'pr', 'zg500', 'rsds', 'clt', 'va850', 'tasmax', 'tas', 'ua850']</t>
         </is>
       </c>
     </row>
@@ -35661,7 +35661,7 @@
       </c>
       <c r="J1082" t="inlineStr">
         <is>
-          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'uas', 'ua500', 'ts', 'tas', 'rlds', 'pr', 'sfcWind', 'rsus', 'huss', 'tas', 'rlds', 'pr', 'sfcWind', 'rsus', 'huss', 'clt', 'psl', 'tasmin', 'rsds', 'zg500', 'ua850', 'tasmax', 'ps', 'va850', 'evspsbl']</t>
+          <t>['rlus', 'rsdt', 'rsut', 'rlut', 'wsgsmax', 'vas', 'va500', 'hfss', 'hfls', 'sfcWindmax', 'snw', 'ta200', 'ta500', 'ta850', 'mrso', 'prc', 'hus850', 'prsn', 'mrro', 'uas', 'ua500', 'ts', 'tas', 'rlds', 'pr', 'sfcWind', 'rsus', 'huss', 'clt', 'psl', 'tasmin', 'rsds', 'zg500', 'ua850', 'tasmax', 'ps', 'va850', 'evspsbl']</t>
         </is>
       </c>
     </row>
@@ -35693,7 +35693,7 @@
       </c>
       <c r="J1083" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ua850', 'pr', 'sfcWind', 'va850', 'psl', 'rlds', 'ua850', 'pr', 'sfcWind', 'va850', 'psl', 'rlds', 'tas', 'tasmax', 'rsus', 'evspsbl', 'clt', 'huss', 'rsds', 'zg500', 'tasmin']</t>
+          <t>['hfss', 'hfls', 'mrso', 'hus850', 'mrro', 'sfcWindmax', 'rlus', 'rsdt', 'rsut', 'rlut', 'snw', 'ta200', 'ta500', 'ta850', 'vas', 'uas', 'va500', 'ua500', 'ua850', 'pr', 'sfcWind', 'va850', 'psl', 'rlds', 'tas', 'tasmax', 'rsus', 'evspsbl', 'clt', 'huss', 'rsds', 'zg500', 'tasmin']</t>
         </is>
       </c>
     </row>
@@ -35725,7 +35725,7 @@
       </c>
       <c r="J1084" t="inlineStr">
         <is>
-          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'huss', 'tasmin', 'sfcWind', 'ua850', 'va850', 'huss', 'tasmin', 'sfcWind', 'ua850', 'va850', 'rsds', 'rsus', 'tas', 'pr', 'evspsbl', 'zg500', 'psl', 'tasmax', 'clt', 'rlds']</t>
+          <t>['hfss', 'hfls', 'hus850', 'mrro', 'rlus', 'rsdt', 'rlut', 'mrso', 'sfcWindmax', 'rsut', 'snw', 'ta200', 'uas', 'ta500', 'ta850', 'ua500', 'vas', 'va500', 'huss', 'tasmin', 'sfcWind', 'ua850', 'va850', 'rsds', 'rsus', 'tas', 'pr', 'evspsbl', 'zg500', 'psl', 'tasmax', 'clt', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36345,7 +36345,7 @@
       </c>
       <c r="J1101" t="inlineStr">
         <is>
-          <t>['sftlf', 'sftlf', 'orog']</t>
+          <t>['sftlf', 'orog']</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="J1102" t="inlineStr">
         <is>
-          <t>['sfcWind', 'tasmax', 'pr', 'tasmin', 'sfcWind', 'tasmax', 'pr', 'tasmin', 'tas']</t>
+          <t>['sfcWind', 'tasmax', 'pr', 'tasmin', 'tas']</t>
         </is>
       </c>
     </row>
@@ -36465,7 +36465,7 @@
       </c>
       <c r="J1105" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsds', 'rlds']</t>
+          <t>['rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36581,7 +36581,7 @@
       </c>
       <c r="J1109" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsds', 'rlds']</t>
+          <t>['rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36609,7 +36609,7 @@
       </c>
       <c r="J1110" t="inlineStr">
         <is>
-          <t>['clivi', 'zmla', 'ts', 'clwvi', 'prc', 'prw', 'prsn', 'ps', 'clivi', 'zmla', 'ts', 'clwvi', 'prc', 'prw', 'prsn', 'ps']</t>
+          <t>['clivi', 'zmla', 'ts', 'clwvi', 'prc', 'prw', 'prsn', 'ps']</t>
         </is>
       </c>
     </row>
@@ -36641,7 +36641,7 @@
       </c>
       <c r="J1111" t="inlineStr">
         <is>
-          <t>['pr', 'tasmin', 'sfcWind', 'tas', 'tasmax', 'tasmax']</t>
+          <t>['pr', 'tasmin', 'sfcWind', 'tas', 'tasmax']</t>
         </is>
       </c>
     </row>
@@ -36725,7 +36725,7 @@
       </c>
       <c r="J1114" t="inlineStr">
         <is>
-          <t>['rsds', 'rlds', 'rsds', 'rlds']</t>
+          <t>['rsds', 'rlds']</t>
         </is>
       </c>
     </row>
@@ -36753,7 +36753,7 @@
       </c>
       <c r="J1115" t="inlineStr">
         <is>
-          <t>['prw', 'prsn', 'ps', 'clwvi', 'prc', 'clivi', 'zmla', 'ts', 'prw', 'prsn', 'ps', 'clwvi', 'prc', 'clivi', 'zmla', 'ts']</t>
+          <t>['prw', 'prsn', 'ps', 'clwvi', 'prc', 'clivi', 'zmla', 'ts']</t>
         </is>
       </c>
     </row>
